--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P66"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,107 +517,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/RotanaLive/status/2042680872118174012</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>جمهور جدة غير ومع الصقر غير🦅
-#رابح_صقر_في_جدة
-#موسم_جدة
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/3mI6SdN1pE</t>
+          <t>Top 5 Richest Companies in the Middle East 
+1️⃣ Saudi Aramco — ~$1.5T+
+2️⃣ International Holding Co (UAE) — ~$240B+
+3️⃣ QNB (Qatar National Bank) — ~$150B+
+4️⃣ Al Rajhi Bank (Saudi) — ~$100B+
+5️⃣ Emirates NBD (UAE) — ~$80B+
+Oil wealth meets financial power.
+@BehindNums</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1775848045000</v>
+        <v>1776308293000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2042680331732684801/img/ZnKpK7bzPoCB7Knz.jpg', 'type': 'video', 'id': '2042680331732684801'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193531, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'BehindNums | Business &amp; Data', 'screenName': 'BehindNums', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Business. Wealth. Power. We decode the numbers behind it. Data-driven insights daily'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46122.96348379629</v>
+        <v>46128.29042824074</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2044090446926823921</t>
+          <t>2044633595495493637</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/AlAjlansambrfi/status/2044090446926823921</t>
+          <t>https://x.com/lowhightips/status/2044633595495493637</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA رائع، الجوهرة تتألق في جدة! 🦅</t>
+          <t>@BehindNums Emirates NBD and IHC showcase the UAE's financial power meeting oil wealth. Regulatory stability and low-tax policies prove diversification creates sustainable value.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1776184114000</v>
+        <v>1776313611000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -627,7 +628,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'طموح العجلان', 'screenName': 'AlAjlansambrfi', 'followersCount': 9, 'favouritesCount': 224, 'friendsCount': 164, 'description': 'طموح في عالم الأعمال بالمدينة، أحب التقنية والمشاريع الكبرى.'}</t>
+          <t>{'name': 'Droid Zaid', 'screenName': 'lowhightips', 'followersCount': 79, 'favouritesCount': 3646, 'friendsCount': 208, 'description': 'Investment advice: buy low, sell high, and try not to cry in between.'}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -642,53 +643,55 @@
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2042680872118174012</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46126.85317129629</v>
+        <v>46128.35197916667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/BehindNums/status/2044611289733878057</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044611289733878057</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044611048305574280</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/BehindNums/status/2044611048305574280</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pattern Day Trader (PDT) rule is soon going. No 25K USD limit for day trading : SEC
-#WIO #NASDAQ #ROBINHOOD #ENBD #NYSE #IG #IBKR</t>
+          <t>Top 5 Companies by Revenue 
+By Revenue (annual)
+1️⃣ Walmart — ~$650B
+2️⃣ Amazon — ~$575B
+3️⃣ Saudi Aramco — ~$500B
+4️⃣ China State Grid — ~$480B
+5️⃣ Apple — ~$390B
+@BehindNums</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1776194041000</v>
+        <v>1776308235000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044611048305574280</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -698,7 +701,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Metrix', 'screenName': 'metrixyo', 'followersCount': 91, 'favouritesCount': 385, 'friendsCount': 266, 'description': 'Background in Data &amp; AI  | Earning Money with AI &amp; Science |\nData Driven Analysis on Crypto, Stocks, Metals &amp; Real Estate Assets'}</t>
+          <t>{'name': 'BehindNums | Business &amp; Data', 'screenName': 'BehindNums', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Business. Wealth. Power. We decode the numbers behind it. Data-driven insights daily'}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -715,49 +718,46 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" s="2" t="n">
-        <v>46126.96806712963</v>
+        <v>46128.28975694445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044132083443155222</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2044132083443155222</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2044068136115417120</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/metrixyo/status/2044068136115417120</t>
+          <t>https://x.com/DustshotW/status/2044517451078197394</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$QBTS 16% ⬆️ 
-$BE 21% ⬆️
-💵💵💵💵💵💵💵💵💵💵💵💵
-#qbts #quantum #dwave #Bloom #NASdaq #Nyse</t>
+          <t>anyone.....olease ......</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1776178795000</v>
+        <v>1776285920000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2044068136115417120</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -767,11 +767,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Metrix', 'screenName': 'metrixyo', 'followersCount': 91, 'favouritesCount': 385, 'friendsCount': 266, 'description': 'Background in Data &amp; AI  | Earning Money with AI &amp; Science |\nData Driven Analysis on Crypto, Stocks, Metals &amp; Real Estate Assets'}</t>
+          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1065, 'favouritesCount': 25614, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -780,40 +780,52 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>318</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" s="2" t="n">
-        <v>46126.79160879629</v>
+        <v>46128.03148148148</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>2044612515498496366</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2044610910640361699</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>https://x.com/dorienotfish/status/2044610910640361699</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>@DustshotW can i try</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>1776227552637</v>
-      </c>
-      <c r="G6" t="inlineStr"/>
+        <v>1776308202000</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -821,131 +833,147 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 68, 'favouritesCount': 39809, 'friendsCount': 522, 'description': 'steine sind steine ohne rotes blut'}</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2044517451078197394</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="n">
-        <v>46127.35593329861</v>
+        <v>46128.289375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2044119073538113567</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044119073538113567</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ÖKKEŞ ŞAHİN'S INTERNATIONAL RECIPE: POWER SOUP. YOU WILL BOIL ONE CARROT, ONE GREEN PEPPER, AND ONE RED ONION. YOU WILL EAT IT LIKE THIS FOR A WHILE. LATER, YOU CAN ADD MEAT, FISH, AND CHICKEN TO IT. @LeaderOkkes @RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X https://t.co/UBoi80xAg0</t>
+          <t>@dorienotfish s enbd</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1776190939000</v>
+        <v>1776308585000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4rcsJX0AE0m43.jpg', 'type': 'photo', 'id': '2044119052759584769'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4rcsJWkAARX1r.jpg', 'type': 'photo', 'id': '2044119052759502848'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'justice gaming', 'screenName': 'DustshotW', 'followersCount': 1065, 'favouritesCount': 25614, 'friendsCount': 229, 'description': 'call me justice or 正凱 // 中文/English // 🇭🇰// i do like nothing but draw yuri\n\nhttps://t.co/wisNUqvSX2'}</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044610910640361699</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46126.93216435185</v>
+        <v>46128.29380787037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/DustshotW/status/2044612515498496366</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2044120061124698315</t>
+          <t>2044613234427383893</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044120061124698315</t>
+          <t>https://x.com/dorienotfish/status/2044613234427383893</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef https://t.co/wJsGrMVAFs</t>
+          <t>@DustshotW sorry at first i though u said 'skibdi' mb✌🏻✌🏻✌🏻 ok here https://t.co/DsboMnkCKn</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1776191175000</v>
+        <v>1776308756000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044517451078197394</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4sWL8XkAAwsHK.jpg', 'type': 'photo', 'id': '2044120040547520512'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4sWMZW8AAJzDO.jpg', 'type': 'photo', 'id': '2044120040669114368'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF_s4_pbAAANiPL.jpg', 'type': 'photo', 'id': '2044613219751493632'}]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'dorion', 'screenName': 'dorienotfish', 'followersCount': 68, 'favouritesCount': 39809, 'friendsCount': 522, 'description': 'steine sind steine ohne rotes blut'}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -958,138 +986,135 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2044119073538113567</t>
+          <t>2044612515498496366</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46126.93489583334</v>
+        <v>46128.29578703704</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2044121269105275233</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044121269105275233</t>
+          <t>https://x.com/CryptoNewsHntrs/status/2029869216254341430</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq @Poloniex @WazirXIndia @tadawul @Cryptopia_NZ @binance @dogecoin @bankofengland @bankofcanada @BankofIndia_IN @Banxico @Bancolombia @BancoCentralBR @BankofAmerica https://t.co/FmIt0fuKbt</t>
+          <t>🚨 JUST IN: 🇦🇪 EMIRATES NBD ELIMINATES ATM WITHDRAWAL &amp;amp; DEBIT CARD FEES ACROSS THE UAE &amp;amp; GCC UNTIL MARCH 31, 2026! 💳🔥
+#UAE #EmiratesNBD #Banking #Finance #ATM #NoFees #GCC #MoneySmart https://t.co/aI9H5crVgx</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1776191463000</v>
+        <v>1772793508000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4tcaOW8AI_KR0.jpg', 'type': 'photo', 'id': '2044121246971916290'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4tcbqasAQGqbQ.jpg', 'type': 'photo', 'id': '2044121247358038020'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2CXkAATb_t.jpg', 'type': 'photo', 'id': '2029869212919894016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HCuLS2eXwAA68mZ.jpg', 'type': 'photo', 'id': '2029869213037346816'}]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Crypto News Hunters 🎯', 'screenName': 'CryptoNewsHntrs', 'followersCount': 28364, 'favouritesCount': 314598, 'friendsCount': 138, 'description': 'Crypto News 🌐 Financial Markets 📈 Memes &amp; Hopium 🔥 Not Financial Advice 🚫'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2044120061124698315</t>
-        </is>
-      </c>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" s="2" t="n">
-        <v>46126.93822916667</v>
+        <v>46087.61004629629</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2044122040836206849</t>
+          <t>2044582261102956879</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044122040836206849</t>
+          <t>https://x.com/zaydaklabhoqx/status/2044582261102956879</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @MonarchieBe @RoyalFamily @koninklijkhuis @KingSalman @takaichi_sanae @kantei @Kantei_Saigai @DefensieMin @OPRArgentina @presidencia_BR @CancilleriaPeru @Cancilleria_Ar @cancilleriasv @wef @wto @IMFNews @EU_Commission @iaeaorg https://t.co/NfbvQKMl3H</t>
+          <t>@CryptoNewsHntrs ماذا عن مجانيّة سحب النقود؟ مبروك لعملاء Emirates NBD في الإمارات ودول الخليج</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1776191647000</v>
+        <v>1776301372000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4uJcxX0AApkCR.jpg', 'type': 'photo', 'id': '2044122020749758464'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4uJczXkAACxrB.jpg', 'type': 'photo', 'id': '2044122020758130688'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'زيد أكلب', 'screenName': 'zaydaklabhoqx', 'followersCount': 30, 'favouritesCount': 301, 'friendsCount': 48, 'description': 'مدير آي تي في دبي، أحب التقنية والسيارات والكرة. أعزب ومستمتع بالحياة الفاخرة.'}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1102,64 +1127,65 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2044121269105275233</t>
+          <t>2029869216254341430</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46126.9403587963</v>
+        <v>46128.21032407408</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2044123427083083921</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044123427083083921</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq @KingSalman @takaichi_sanae @kantei @Kantei_Saigai MY INTERNATIONAL RECIPE: POWER SOUP. MA RECETTE INTERNATIONALE : SOUPE ÉNERGISANTE. @LeaderOkkes @EmmanuelMacron @Elysee @francediplo @francediplo_EN @lemondefr @FranceoSenegal @FratellidItalia @GiorgiaMeloni @ItalyMFA @Gazzetta_it @Pontifex @VaticanNews @netanyahu @IsraelMFA https://t.co/AOXivIo2V8</t>
+          <t>Manage your wealth with expertise you can trust. Contact us today https://t.co/XmTzVbwpLQ
+#EmiratesNBD #WealthManagement https://t.co/1RVFBUcixf</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1776191977000</v>
+        <v>1776265201000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4vaMGXEAEjj03.jpg', 'type': 'photo', 'id': '2044123407843790849'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4vaMQasAEPCjo.jpg', 'type': 'photo', 'id': '2044123407885971457'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8-vnKWcAAQyPA.jpg', 'type': 'video', 'id': '2044421704122798080'}]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174063, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1168,64 +1194,60 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2044122040836206849</t>
-        </is>
-      </c>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" s="2" t="n">
-        <v>46126.94417824074</v>
+        <v>46127.79167824074</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044430548727128554</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044430548727128554</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2044124392943137264</t>
+          <t>2043932263717482626</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044124392943137264</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2043932263717482626</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @Nasdaq @KingSalman @takaichi_sanae @kantei MY INTERNATIONAL RECIPE: POWER SOUP. המתכון הבינלאומי שלי: מרק עוצמתי. @LeaderOkkes @netanyahu @YairNetanyahu @IDF @IsraeliPM @IAFsite @IsraelMFA @Isaac_Herzog @TimesofIsrael @Jerusalem_Post @usembassyjlm @IsraelinUSA @IsraelinSpanish @IsraelinUK @IsraelinGermany @TelAvivUni https://t.co/1J3VzW57FV</t>
+          <t>We are together against Fraud. @UAEBF #FightFraud #UAEBF #togetheragainstfraud #UnitedAgainstFraud https://t.co/CqApZaCAFO</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1776192207000</v>
+        <v>1776146400000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043932263717482626</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4wSRlWoAAL2qo.jpg', 'type': 'photo', 'id': '2044124371388637184'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4wSRlXEAAQXCy.jpg', 'type': 'photo', 'id': '2044124371388665856'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2043610882656059392/img/HaP0BSdqwFktNLDX.jpg', 'type': 'video', 'id': '2043610882656059392'}]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174063, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1235,207 +1257,204 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2044123427083083921</t>
-        </is>
-      </c>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" s="2" t="n">
-        <v>46126.94684027778</v>
+        <v>46126.41666666666</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2044125532476821949</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044125532476821949</t>
+          <t>https://x.com/Brockutd/status/2043970652697211186</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE 我的國際食譜能量湯. MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @BentleyMotors @Toyota @TOYOTA_PR @MitsubishiKaden @MHI_Group @RollsRoyce @LandRover @RangeRover @astonmartin @F1 @MercedesBenz @MercedesAMGF1 @BMW @Peugeot @Ford @FordMustang @VolvoCarUSA @renaultgroup @Tesla https://t.co/0QaF62lMwZ</t>
+          <t>🚨 Mark Clattenburg on Lisandro Martínez’s red card:
+“I was surprised that such an experienced referee considered this a red card offence. It was clearly a 50/50 challenge for the ball. 
+I think the referee’s seniority within the VAR group may have made others hesitant to overturn his on-field decision.
+In my opinion, this was a clear mistake. When we talk about ‘clear and obvious errors’, most referees would not have sent him off for that challenge.”</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1776192479000</v>
+        <v>1776155553000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4xUs2aMAA5imS.jpg', 'type': 'photo', 'id': '2044125512579297280'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4xUsPWAAA7hU8.jpg', 'type': 'photo', 'id': '2044125512415444992'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2kdMfXYAA7k8w.jpg', 'type': 'photo', 'id': '2043970627372015616'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2kdM8asAEzRR_.jpg', 'type': 'photo', 'id': '2043970627493867521'}]</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BROCK(fan)', 'screenName': 'Brockutd', 'followersCount': 6684, 'favouritesCount': 145265, 'friendsCount': 791, 'description': 'Face of Pogba Fc •|• @manutd •|• Fan account •|• @Roobet'}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>1037</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>9506</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2044124392943137264</t>
-        </is>
-      </c>
+          <t>428905</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" s="2" t="n">
-        <v>46126.94998842593</v>
+        <v>46126.52260416667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2044126467026497799</t>
+          <t>2043989823325716661</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044126467026497799</t>
+          <t>https://x.com/STFU1346/status/2043989823325716661</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Toyota @TOYOTA_PR @MitsubishiKaden 私の国際レシピ：パワースープ. MY INTERNATIONAL RECIPE: POWER SOUP. LOOK AT. @LeaderOkkes @SwissMFA @DanishMFA @BelgiumMFA @FCDOGovUK @MofaJapan_jp @KSAMOFA @CanadaFP @IsraelMFA @MFA_China  @ItalyMFA_int @francediplo_EN @DutchMFA @GreeceMFA @ArgentinaMFA @ItamaratyGovBr https://t.co/0q2rnxRjDF</t>
+          <t>@Brockutd Man U had it easy for years, now maybe karma is at play.
+I think it was soft, but the rules are the rules.
+Man U were shite last night, and should've been down by 3 or more before they woke up.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1776192702000</v>
+        <v>1776160124000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yLLEWEAEAEqo.jpg', 'type': 'photo', 'id': '2044126448403746817'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yLLRXYAABkRi.jpg', 'type': 'photo', 'id': '2044126448458358784'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>4748</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2044125532476821949</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46126.95256944445</v>
+        <v>46126.57550925926</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2044127070410674226</t>
+          <t>2044040984212758846</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044127070410674226</t>
+          <t>https://x.com/JeetyJeeterson/status/2044040984212758846</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Toyota @TOYOTA_PR MY INTERNATIONAL RECIPE: POWER SOUP. @LeaderOkkes @infopresidencia @Presidencia_Ec @presidenciaperu @PresidenciaSV @presidencia_BR @SecPrensaSV @PresidenciaCuba @PresidenciaPy @presidenciacr @PresidenciaCPNL @MonarchieBe @koninklijkhuis @RoyalFamily @IsraeliPM @SwissGov @GOVUK https://t.co/vaMTYIPN32</t>
+          <t>@STFU1346 @Brockutd This narrative that United got all the decisions in the past is a complete lie. United are on the wrong end of poor decisions more than anybody, this lie was started by rival fans with zero evidence. We used to get alot of pens, as were attacking twice as much as everybody else</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1776192846000</v>
+        <v>1776172321000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yuKsXEAAC63S.jpg', 'type': 'photo', 'id': '2044127049598570496'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4yuKzWEAArvi3.jpg', 'type': 'photo', 'id': '2044127049627865088'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Jeety', 'screenName': 'JeetyJeeterson', 'followersCount': 416, 'favouritesCount': 667, 'friendsCount': 1554, 'description': "Whatever people say I am, that's what I'm not"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1448,64 +1467,66 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>58</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2044126467026497799</t>
+          <t>2043989823325716661</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46126.95423611111</v>
+        <v>46126.71667824074</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2044127797086446009</t>
+          <t>2044048198029742561</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044127797086446009</t>
+          <t>https://x.com/STFU1346/status/2044048198029742561</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors MY INTERNATIONAL RECIPE: POWER SOUP.A MINHA RECEITA INTERNACIONAL:SOPA ENERGÉTICA. @LeaderOkkes @Walmart @Apple @AppleMusic @Microsoft @Google @SpaceX @X @Oracle @OracleDatabase @Huawei_Europe @Tesla  @Xiaomi @XiaomiIndonesia @McDonalds @BurgerKingUK @CocaCola @pepsi @RollsRoyce https://t.co/Pkuk6ynj28</t>
+          <t>@JeetyJeeterson @Brockutd No, none, nada, zilch,  penalties against Man U under Ferguson at Old Trafford during their purple.. Give your head a shake man.
+Look at Sky Sports and the coverage you's get. Be as well call it Man U TV.
+The "Red Cartel" is no conspiracy theory, Man U are the head of the gang.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1776193019000</v>
+        <v>1776174041000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4zYgqboAAYu-e.jpg', 'type': 'photo', 'id': '2044127777050566656'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4zYgcaUAAEnpW.jpg', 'type': 'photo', 'id': '2044127776991760384'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1518,64 +1539,64 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>69</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2044127070410674226</t>
+          <t>2044040984212758846</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46126.95623842593</v>
+        <v>46126.73658564815</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2044128711998411106</t>
+          <t>2044431315555024909</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044128711998411106</t>
+          <t>https://x.com/Cle_Etc/status/2044431315555024909</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Walmart @Apple @AppleMusic @Microsoft MY INTERNATIONAL RECIPE: POWER SOUP. LA MIA RICETTA INTERNAZIONALE: ZUPPA ENERGETICA. @LeaderOkkes @GiorgiaMeloni @FratellidItalia @ItalyMFA @Jaemyung_Lee @SamsungKorea @VogueKorea @kantei @bankofengland @TheEconomist @lemondefr @folha @DefensieMin @DilanYesilgoz @koninklijkhuis https://t.co/yZXs4ltxR4</t>
+          <t>@STFU1346 @JeetyJeeterson @Brockutd Hmmm, from an Oil Money Club.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1776193237000</v>
+        <v>1776265383000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40N6HasAQaFiL.jpg', 'type': 'photo', 'id': '2044128694416093188'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40N50WwAA9QJR.jpg', 'type': 'photo', 'id': '2044128694336143360'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Cle Etc.', 'screenName': 'Cle_Etc', 'followersCount': 186, 'favouritesCount': 21460, 'friendsCount': 42, 'description': 'Married. Dad. Irish. Musician. Songwriter. Producer. Teacher. Believer. Cynic. Man United supporter. Dyslexic. Dreamer. Likes a laugh.'}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1588,64 +1609,67 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2044127797086446009</t>
+          <t>2044048198029742561</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46126.95876157407</v>
+        <v>46127.79378472222</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2044129315659345996</t>
+          <t>2044432755811860595</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044129315659345996</t>
+          <t>https://x.com/STFU1346/status/2044432755811860595</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Walmart MY INTERNATIONAL RECIPE: POWER SOUP. MEUM COQUENDI INTERNATIONALE: IUS ENERGETICUM. I’M KING - BARON OF THE WORLD. @LeaderOkkes @spagov @Reuters @NatGeo @Forbes @TIME @FT @TheEconomist @MarketWatch @MorganStanley @jpmorgan @NYSE @Nasdaq @BBCWorld @SkyNews @cnni @FoxNews @Nike https://t.co/645SVweoGN</t>
+          <t>@Cle_Etc @JeetyJeeterson @Brockutd Here are your sponsors:
+Commercial Bank of Qatar: A Financial Services Affinity Partner for Qatar.
+VIVA: An integrated telecommunications partner for Bahrain and Kuwait. 
+TM: An integrated telecommunications partner for Malaysia (often grouped with regional Asian/Middle Eastern</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1776193381000</v>
+        <v>1776265727000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40w1xbYAAHhrr.jpg', 'type': 'photo', 'id': '2044129294545543168'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF40w0_XwAA1srp.jpg', 'type': 'photo', 'id': '2044129294335590400'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1658,64 +1682,67 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2044128711998411106</t>
+          <t>2044431315555024909</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46126.96042824074</v>
+        <v>46127.7977662037</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2044130108303085904</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044130108303085904</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @Walmart @spagov MY INTERNATIONAL RECIPE: POWER SOUP - IUS POTENTIA - SOUPE PUISSANTE - パワースープ. I’M BARON - KING OF THE WORLD. @LeaderOkkes @Walmart @Apple  @Microsoft @Google @SpaceX @X @Oracle @Huawei_Europe @Tesla @TeslaAUNZ @Xiaomi  @McDonaldsJapan @BurgerKingUK @CocaCola @pepsi @Meta https://t.co/rRQOciWTn0</t>
+          <t>@Cle_Etc @JeetyJeeterson @Brockutd PepsiCo: Noted for regional arrangements in the Middle East and Asia. 
+Emirates NBD for the United Arab Emirates.
+Saudi Telecom Co.
+So, what's your point?</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1776193570000</v>
+        <v>1776265837000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF41e7mXYAA1rfh.jpg', 'type': 'photo', 'id': '2044130086383738880'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF41e8TasAId-9v.jpg', 'type': 'photo', 'id': '2044130086572699650'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'BraveFart🏴\U000e0067\U000e0062\U000e0073\U000e0063\U000e0074\U000e007f', 'screenName': 'STFU1346', 'followersCount': 1646, 'favouritesCount': 16513, 'friendsCount': 1654, 'description': 'Scottish. NUFC mad. If you steal any of my memes, show a bit of common courtesy and like it first.'}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1728,64 +1755,64 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2044129315659345996</t>
+          <t>2044432755811860595</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46126.96261574074</v>
+        <v>46127.79903935185</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/STFU1346/status/2044433219693466085</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2044130932110626901</t>
+          <t>2044459400069357578</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044130932110626901</t>
+          <t>https://x.com/Cle_Etc/status/2044459400069357578</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors ནུས་ཤུགས་ཐང་།. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @NASA @SpaceX @teslaeurope @Tesla_Asia @amazon @alibaba_cloud @msdev @ApplePodcasts @FCDOGovUK @ChinaMusicData @GovernmentRF @MichSoS @DefenceHQ @RoyalFamily @GiorgiaMeloni @EmmanuelMacron @francediplo @elonmusk https://t.co/hBU5y91OWL</t>
+          <t>@STFU1346 @JeetyJeeterson @Brockutd Awe, you worked really hard for that. My point is that there are a handful of states sports washing, pumping billions into their purchased clubs… but we still have to listen to the fans complaining about imaginary cartels that control referees.</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1776193766000</v>
+        <v>1776272079000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043970652697211186</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF42PP_XcAEKunC.jpg', 'type': 'photo', 'id': '2044130916491030529'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF42PP_XAAA-k6v.jpg', 'type': 'photo', 'id': '2044130916491001856'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Cle Etc.', 'screenName': 'Cle_Etc', 'followersCount': 186, 'favouritesCount': 21460, 'friendsCount': 42, 'description': 'Married. Dad. Irish. Musician. Songwriter. Producer. Teacher. Believer. Cynic. Man United supporter. Dyslexic. Dreamer. Likes a laugh.'}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1798,68 +1825,73 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2044130108303085904</t>
+          <t>2044433219693466085</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46126.96488425926</v>
+        <v>46127.87128472222</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2044132642241568996</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044132642241568996</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors MY POWER SOUP. पावर सूप. I’M KING OF THE WORLD. @LeaderOkkes @UniofOxford @OUPAcademic @Harvard @Stanford @Cambridge_Uni @Yale @WHU_1893 @universityofky @MIT @techreview @WashInstitute @ForeignPolicy @ForeignAffairs @CFR_org @ChathamHouse @BrookingsInst @McKinsey_MGI @TelAvivUni https://t.co/Gv1O15jASP</t>
+          <t>To find the trending news on Real estate, finance, and Technology for April 15, check the news links and the video link below:
+https://t.co/AuS5pOClPI
+https://t.co/uOBF8Ce7As
+https://t.co/0Q3Pd23x0U
+https://t.co/QMIfzjAAnq
+#INTLBM  #Sohar #EToro #EmiratesNBD #Sobha #Headlines</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1776194174000</v>
+        <v>1776260321000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF43yDhasAE0J8P.jpg', 'type': 'photo', 'id': '2044132613951238145'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF43yDZWAAA220e.jpg', 'type': 'photo', 'id': '2044132613917376512'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'International Business Magazine', 'screenName': 'ibmag_magazine', 'followersCount': 1537, 'favouritesCount': 2080, 'friendsCount': 1003, 'description': 'International Business Magazine is a Dubai, UAE based publication.'}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1872,64 +1904,65 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2044130932110626901</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>46126.96960648148</v>
+        <v>46127.73519675926</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/ibmag_magazine/status/2044410083262734349</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044410083262734349</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2044133212385874152</t>
+          <t>2043999660285862211</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044133212385874152</t>
+          <t>https://x.com/ibmag_magazine/status/2043999660285862211</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @UniofOxford MY POWER SOUP. MIJN KRACHTSOEP. I’M KING OF THE WORLD. @LeaderOkkes @DefenceU @DefesaGovBr @DefenceHQ @Defensoria_Peru @DefensaSV @Defensagob @Defensie @DefensieMin @DefensieStas @DHQNigeria @kdfinfo @RwandaMoD  @DefensoriaCol @ArmedForcesJO @CanadianForces @IDF @Armees_Gouv https://t.co/j9UW8NkvCJ</t>
+          <t>To find the trending news on Corporate, Technology, Banking and Finance for #April14, check the links below:
+https://t.co/wCnnEeLf7A
+https://t.co/5jczPIqAT3
+https://t.co/X0IupL4wiw
+https://t.co/amPUbrkpdI
+#Intlbm #telecoms #Investment #MiddleEast #Banking #Finance #Innovation</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1776194310000</v>
+        <v>1776162469000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2043999660285862211</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44TxYXQAALIb0.jpg', 'type': 'photo', 'id': '2044133193196978176'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44TxXWgAA_cP6.jpg', 'type': 'photo', 'id': '2044133193192734720'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'International Business Magazine', 'screenName': 'ibmag_magazine', 'followersCount': 1537, 'favouritesCount': 2080, 'friendsCount': 1003, 'description': 'International Business Magazine is a Dubai, UAE based publication.'}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1942,64 +1975,62 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2044132642241568996</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" s="2" t="n">
-        <v>46126.97118055556</v>
+        <v>46126.60265046296</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2044133751009997207</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044133751009997207</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @UniofOxford @DefenceU MIN KRAFTSOPPA. MY POWER SOUP. @LeaderOkkes @BankofAmerica @bankofengland @bankofcanada @BankofIndia_IN @bankofthailand @BankOfTanzania @bankofmaldives @BcodeVenezuela @Banxico @BancoMundialLAC @Bancolombia @el_BID @BancoMundial @BancoCentralBR @BancoCentral_AR @BancoCentralRD https://t.co/tHfR0Eljxf</t>
+          <t>Emirates NBD has announced a strategic partnership with Sobha Realty to provide integrated home financing solutions for buyers of the premium luxury developer’s off-plan residential developments across Dubai.
+Read more on https://t.co/966sAK8POe
+#GCnews #emirates #MENA https://t.co/B6wVnQqtgg</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1776194439000</v>
+        <v>1776255595000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44y-vasAANkaM.jpg', 'type': 'photo', 'id': '2044133729359278080'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF44y-RWQAA5RfD.jpg', 'type': 'photo', 'id': '2044133729233158144'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8h57OawAA3WNa.jpg', 'type': 'photo', 'id': '2044390034883919872'}]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Gulf Construction', 'screenName': 'Gulf_const', 'followersCount': 3304, 'favouritesCount': 338, 'friendsCount': 334, 'description': 'We are an authoritative, respected journal with unmatched coverage of the Gulf region’s building and construction industries.'}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2008,138 +2039,135 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2044133212385874152</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" s="2" t="n">
-        <v>46126.97267361111</v>
+        <v>46127.68049768519</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/Gulf_const/status/2044390258528395378</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044390258528395378</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044017573616893963</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/Gulf_const/status/2044017573616893963</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei @NYSE @BentleyMotors @UniofOxford A MINHA SOPA DE PODER. MY POWER SOUP. I’M KING OF THE WORLD. @LeaderOkkes @airasia_indo @IAF_MCC @CebuPacificAir @airasia @usairforce @airtelindia @British_Airways @KenyaAirways @etihad @flysaa @EmiratesNBD_AE @emirates @AmericanAir @AirCanada @airserbia @SaudiAirlinesEn @X https://t.co/8qnHpREKqV</t>
+          <t>Mered, the award-winning developer based in UAE, has announced that main piling operations are now progressing at Riviera Residences, a waterfront residential tower in Abu Dhabi, Al Reem Island.
+Read more on https://t.co/xGW6cvJ1Nc
+#GCnews #developer #UAE #residences https://t.co/bFrmFMn6HS</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1776194550000</v>
+        <v>1776166740000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044017573616893963</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF45OSkbEAAvVjg.jpg', 'type': 'photo', 'id': '2044134198538342400'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF45OTeXYAA1oKr.jpg', 'type': 'photo', 'id': '2044134198781370368'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFxca_0aMAAamjh.jpg', 'type': 'photo', 'id': '2043609949796970496'}]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Gulf Construction', 'screenName': 'Gulf_const', 'followersCount': 3304, 'favouritesCount': 338, 'friendsCount': 334, 'description': 'We are an authoritative, respected journal with unmatched coverage of the Gulf region’s building and construction industries.'}</t>
         </is>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>2</v>
-      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>2044133751009997207</t>
-        </is>
-      </c>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" s="2" t="n">
-        <v>46126.97395833334</v>
+        <v>46126.65208333333</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134219362779352</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2044134219362779352</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2044134999616549139</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/LeaderOkkes/status/2044134999616549139</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@RoyalFamily @MonarchieBe @koninklijkhuis @KensingtonRoyal @X @DefensieMin @FratellidItalia @GiorgiaMeloni @Pontifex @MarkJCarney @EmmanuelMacron @PrimeministerGR @netanyahu @LulaOficial @JMilei @Jaemyung_Lee @chrisluxonmp @ParmelinG @scotgov @SwissGov @lemondefr @TheEconomist @iaeaorg @wef @wto @IMFNews @WorldBankGroup @Davos @nikkei MY INTERNATIONAL RECIPE. MEUM RECEPTUM INTERNATIONALE. EGO SUM: ÖKKEŞ. @LeaderOkkes @nvidia @amazon @Apple @aramco @Broadcom @Tesla @Walmart @Walmart @Disney @Meta @NetflixKR @EliLillyandCo @jpmorgan @exxonmobil @Oracle @Roche @AstraZeneca @Shell @MorganStanley @lorealparisfr https://t.co/WRKhLq07T0</t>
+          <t>شكرا Emirates NBD بنك الإمارات دبي الوطني
+على دعمكم الإنساني في نجاح أنشطة المؤسسة لدعم الأسر المحتاجة..
+#متبرعين_خير_للناس
+#مؤسسة_خير_للناس https://t.co/5PUxmmX1mn</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1776194736000</v>
+        <v>1776252503000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2021899533345841203</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF45710WwAAMkZ5.jpg', 'type': 'photo', 'id': '2044134981094522880'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HF4572xasAA1gCB.jpg', 'type': 'photo', 'id': '2044134981350633472'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8VrwnXkAApAXH.jpg', 'type': 'photo', 'id': '2044376597378076672'}]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'THE REAL KING OF THE WORLD: ÖKKEŞ ŞAHİN', 'screenName': 'LeaderOkkes', 'followersCount': 1, 'favouritesCount': 1722, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'خير للناس للتنمية', 'screenName': 'khir_llnas', 'followersCount': 3, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2148,130 +2176,107 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2044134219362779352</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" s="2" t="n">
-        <v>46126.97611111111</v>
+        <v>46127.64471064815</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/khir_llnas/status/2044377290952364098</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044377290952364098</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044440524782764312</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044064867896963237</t>
+          <t>https://x.com/khir_llnas/status/2044440524782764312</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>أعزائي ..
-السبب الوحيد للارتفاعات في الاسواق 
-هو دخول سيولة قوية ( بغض النظر عن الآلية) 
-تتزامن مع نتائج الشركات
-وهي الفترة التي لا يفوتها السوق أبداً
-لا في سراء ولا في ضراء 
-عُدْ إلي بعد أسبوعين،
-حتى نتحدث عن " زلزال المنطق "
-أضف الى ذلك .. أنا بِنْت ☹️</t>
+          <t>تبرع الآن
+https://t.co/sk7px2ePBH https://t.co/lsrrrAISd0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1776178016000</v>
+        <v>1776267579000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044440524782764312</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9PwRYXUAAfgil.jpg', 'type': 'photo', 'id': '2044440446567403520'}]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3885, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
+          <t>{'name': 'خير للناس للتنمية', 'screenName': 'khir_llnas', 'followersCount': 3, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2607</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" s="2" t="n">
-        <v>46126.78259259259</v>
+        <v>46127.81920138889</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>2044071581186699505</t>
-        </is>
-      </c>
+          <t>2044363346460172688</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/alnuaimi_bader/status/2044071581186699505</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>@ChirinAsadi ما شاء الله عليكم اخت شيرين. دائماً تثبتين بُعد النظر والفهم العميق للأسواق. أتوقع تألُّق قطاع البنوك عندنا في الإمارات وحتى قطاع العقارات بتكون نتائجه مميزة بإذن الله تعالى.</t>
-        </is>
-      </c>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="n">
-        <v>1776179616000</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2044064867896963237</t>
-        </is>
-      </c>
+        <v>1776313989514</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2279,68 +2284,51 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'bader_alain', 'screenName': 'alnuaimi_bader', 'followersCount': 47, 'favouritesCount': 5559, 'friendsCount': 217, 'description': 'Power of simplicity'}</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2044064867896963237</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>46126.80111111111</v>
+        <v>46128.35636011574</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044363346460172688</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2044082310447018168</t>
+          <t>2044363346460172688</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/ChirinAsadi/status/2044082310447018168</t>
+          <t>https://x.com/Sems3499/status/2044363346460172688</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>@alnuaimi_bader اعتقد بنك دبي الامارات الوطني ENBD استفاد من اللخبطة التي حصلت في مارس
-بينما كان دبي الاسلامي DIB محافظاً في الانتقاء</t>
+          <t>@nurkanaydogan Enbd bankalarında çalışanlar için 1. Şık olduğunu düşünüyorum (:</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1776182174000</v>
+        <v>1776249178000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2044064867896963237</t>
+          <t>2044358706846941680</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2350,7 +2338,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'Chirin Al Asadi', 'screenName': 'ChirinAsadi', 'followersCount': 3885, 'favouritesCount': 2850, 'friendsCount': 237, 'description': 'كل الكتابات والافكار هنا 👇🏻أصلية.. أغرد بأفكاري الخاصة بي .. أيضا: قرارك الاستثماري يخصك وحدك🤍 لا تأخذ بأرائي - اسأل مستشارك'}</t>
+          <t>{'name': 'Sem', 'screenName': 'Sems3499', 'followersCount': 4, 'favouritesCount': 275, 'friendsCount': 7, 'description': ''}</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2363,54 +2351,57 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>49</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2044071581186699505</t>
+          <t>2044358706846941680</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46126.83071759259</v>
+        <v>46127.60622685185</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is there any updates or changes regarding Installment deferment for the personal loan due to current geopolitical circumstances,</t>
+          <t>@EmiratesNBD_AE 
+You kept pushing to take the Share Credit Card,finally I applied and then you rejected citing “internal policies” despite having higher eligibility than required.
+Now your agents are calling and saying it’s a miss &amp;amp; to resubmit documents.
+Are you serious?</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1776182192000</v>
+        <v>1776250630000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2420,7 +2411,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'आदियोगी', 'screenName': 'SunnyLusty', 'followersCount': 78, 'favouritesCount': 224, 'friendsCount': 38, 'description': 'Not related to any Political Party, but can’t close eyes if someone tries to fool, It’s can be any1'}</t>
+          <t>{'name': 'Preetam Chakraborty', 'screenName': 'iRonyForChange', 'followersCount': 42, 'favouritesCount': 1281, 'friendsCount': 193, 'description': 'Work &amp; live in 🇦🇪 | Strong political opinions | Anti-establishment'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2442,41 +2433,41 @@
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" s="2" t="n">
-        <v>46126.83092592593</v>
+        <v>46127.62303240741</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/SunnyLusty/status/2044082383205609853</t>
+          <t>https://x.com/iRonyForChange/status/2044369434362753181</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2044085223952900599</t>
+          <t>2044371163166466284</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2044085223952900599</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2044371163166466284</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>@SunnyLusty Hello, we have replied to you privately.</t>
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #997789 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1776182869000</v>
+        <v>1776251042000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2486,7 +2477,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174047, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174063, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2503,189 +2494,188 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2044082383205609853</t>
+          <t>2044369434362753181</t>
         </is>
       </c>
       <c r="P30" s="2" t="n">
-        <v>46126.83876157407</v>
+        <v>46127.62780092593</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/amsh75/status/1962127907049930843</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>سؤال:
-ماهو افضل بنك يشتري مديونية ؟!
-قرض عقاري + قرض شخصي .
-@alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE</t>
+          <t>Sobha Realty is making off-plan investing in Dubai more accessible.
+In partnership with Emirates NBD, Sobha Realty introduces flexible financing solutions, giving investors easier access to high-potential opportunities.
+#DubaiInvestors #OffPlanDubai #RealEstateInvesting #Dubai https://t.co/yHBmK8RVEk</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1756642722000</v>
+        <v>1776246435000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7_CgOb0AAEGFF.jpg', 'type': 'photo', 'id': '2044351699348082688'}]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'علي محمد الضبعان', 'screenName': 'amsh75', 'followersCount': 32674, 'favouritesCount': 2853, 'friendsCount': 6053, 'description': 'حاصل على وسام الملك عبدالعزيز من الدرجة الثالثة/ مدير فرع @Trahum_sa بالمنطقة الشرقية/ عضو لجنة الاسكان التنموي بالمنطقة الشرقية / رئيس مجلس إدارة @tadom_sa'}</t>
+          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" s="2" t="n">
-        <v>45900.67965277778</v>
+        <v>46127.57447916667</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/titledeednews/status/2044351837869105398</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044351837869105398</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1962458003224854945</t>
+          <t>2044042548185010299</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/KhalidSaeedR/status/1962458003224854945</t>
+          <t>https://x.com/titledeednews/status/2044042548185010299</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>@amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE انا ابحث ايضا عن شراء المديونيه قرض عقاري قرض شخصي،،،</t>
+          <t>Al Habtoor Group is committing over AED 5 billion to a new commercial tower in Dubai. Another strong indicator of sustained demand for Grade A office space and long-term market confidence.
+#DubaiRealEstate #CommercialRealEstate #InvestInDubai #DubaiBrokers #RealEstateNews https://t.co/kHUr6Xe7wr</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1756721423000</v>
+        <v>1776172694000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044042548185010299</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3loHrbsAAWgHC.jpg', 'type': 'photo', 'id': '2044042283314819072'}]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'خالد سعيد اليْمِنِي (أبو مشاري)', 'screenName': 'KhalidSaeedR', 'followersCount': 11096, 'favouritesCount': 6906, 'friendsCount': 1130, 'description': 'صحافي ومذيع  تلفزيوني   ومقدم حفلات رسميه،،،\nأخصائي وممارس العلاقات العامه،،'}</t>
+          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>1</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1962127907049930843</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" s="2" t="n">
-        <v>45901.59054398148</v>
+        <v>46126.72099537037</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/HarshGada76429/status/2038970719238045794</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله من خلال تجربتي مع البنك السعودي الفرنسي لا انصح ابدا بشراء مديونية منه اتفقت مع الموظف على اعادة تمويل وكنت في بنك الرياض علي قرض شخصي وعقاري اتفقت مع الموظف بعد ماشاف راتبي والعقار المرهون لبنك الرياض قيمته ٣ مليون  قدروه عمارة ٢٥ شقة المهم موظف البنك الفرنسي</t>
+          <t>@RBLBankCares
+@rblbank
+I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
+Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1776180604000</v>
+        <v>1774963476000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2695,68 +2685,67 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 21, 'description': ''}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1962458003224854945</t>
-        </is>
-      </c>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>46126.8125462963</v>
+        <v>46112.72541666667</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044076340891009154</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE موظف البنك الفرنسي قال نعطيك اعادة تمويل ويطلع لك فائض بالشخصي٧٥٠٠٠ وفعلا تحولت لي والعقاري قال يفيض لك٢٥٥٠٠٠ وسحب علي وماعاد يرد وحتى اليوم فوق ١٠ مرات احاول ارفع شكوى من التطبيق مايقبلون الشكوى 
-اصلا</t>
+          <t>@RBLBankCares @rblbank I haven't got the resolution yet 
+On technical terms you are denying me the voucher
+What about last 3 years of harassment where you guys were denying for voucher which i have earned by reaching milestone?
+@EmiratesNBD_AE   be careful with tie up with
+RBL Bank</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1776180751000</v>
+        <v>1776247575000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2766,7 +2755,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 21, 'description': ''}</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2783,50 +2772,50 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
-        <v>46126.81424768519</v>
+        <v>46127.58767361111</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/HarshGada76429/status/2044356621351149946</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2044077090039873867</t>
+          <t>2044364006027403737</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077090039873867</t>
+          <t>https://x.com/RBLBankCares/status/2044364006027403737</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE وحاليا بعد ماكان عندي قرض عقاري في بنك الرياض راح ارجعه مليون٦٠٠ ألف على ١٥ سنةصرت مديون للبنك الفرنسي مليونين ٣٠٠ ألف والصك مرهون عندهم وكل الي سوه سددو لبنك الرياض مليون ٧٠الف قيمة السداد المبكر فقط والفائض الي وعدني فيه سحب علي ومايرد</t>
+          <t>@HarshGada76429 Hello, our representative will get in touch with you at the earliest to address your query. Regards, RBL Bank.</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1776180930000</v>
+        <v>1776249336000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2038970719238045794</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2836,11 +2825,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'RBL Bank Cares', 'screenName': 'RBLBankCares', 'followersCount': 15138, 'favouritesCount': 107, 'friendsCount': 1, 'description': 'Welcome to the official service handle of RBL Bank for addressing your queries. The Bank’s social media guidelines are available on: https://t.co/4latICF1Kx'}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2853,50 +2842,51 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2044076340891009154</t>
+          <t>2044356621351149946</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46126.81631944444</v>
+        <v>46127.60805555555</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2044077341328957795</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044077341328957795</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE والله كاننا نتعامل مع عصابة مو موظف بنك لي ١٧ سنة اتعامل مع البنوك عمري ماشفت تعامل مثل البنك الفرنسي</t>
+          <t>@ENBDdeals
+Took a Takaful policy from ENBD back in 2012. 15 year policy. Was supposed to mature in 2027. Policy was issued from Aman insurances. ENBD was distributor. Being told now to contact Aman insurance directly. Aman is as good as closed. ENBD is not taking responsibility.</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1776180989000</v>
+        <v>1776235930000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2906,11 +2896,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Akbar Syed', 'screenName': 'metakixakbar', 'followersCount': 0, 'favouritesCount': 88, 'friendsCount': 25, 'description': ''}</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2923,50 +2913,46 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2044077090039873867</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" s="2" t="n">
-        <v>46126.81700231481</v>
+        <v>46127.45289351852</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2044078376982319373</t>
+          <t>2044310308068425734</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044078376982319373</t>
+          <t>https://x.com/ENBDdeals/status/2044310308068425734</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>@KhalidSaeedR @amsh75 @alrajhibank @BSF_sa @alinma @BankAlbilad @snbalahli @GulfIntlBank @EmiratesNBD_AE @BankAlJazira @RiyadBank @alawwalsab @SAIBLIVE فوق ١٠ مرات ارفع شكاوي هذا الرد</t>
+          <t>@metakixakbar Quoting case #997567 in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1776181236000</v>
+        <v>1776236533000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2976,7 +2962,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'محمد', 'screenName': 'attas_2010', 'followersCount': 2342, 'favouritesCount': 3675, 'friendsCount': 4836, 'description': 'لا إله إلا الله محمد رسول الله\nتابعني وأتابعك'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39129, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2993,52 +2979,51 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2044078181662019702</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46126.81986111111</v>
+        <v>46127.45987268518</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/attas_2010/status/2044075725334954107</t>
+          <t>https://x.com/metakixakbar/status/2044307778140025041</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2044084483222127002</t>
+          <t>2044310246277967968</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/BSF_help/status/2044084483222127002</t>
+          <t>https://x.com/ENBDdeals/status/2044310246277967968</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>عميلنا العزيز ، نود التوضيح بأن منصات التواصل الاجتماعي مخصصة للاستفسارات العامة فقط.
-ولضمان خصوصيتكم وحماية بياناتكم، نرجو عدم مشاركة أي معلومات شخصية أو مصرفية (مثل رقم الهوية، رقم الحساب، كلمة المرور، رقم الجوال أو الأرقام السرية) عبر هذه المنصات.
-يرجى استخدام البريد الإلكتروني أو القنوات الرسمية للبنك لمعالجة الطلبات بأمان وسرية تامة.</t>
+          <t>@metakixakbar We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at
+ social@emiratesnbd.com</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1776182692000</v>
+        <v>1776236518000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1962127907049930843</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3048,11 +3033,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'BSF Help', 'screenName': 'BSF_help', 'followersCount': 56031, 'favouritesCount': 1, 'friendsCount': 1, 'description': 'مرحبًا بكم في الحساب الرسمي BSF Help، المصدر المعتمد للإجابة على استفساراتكم المصرفية. تابعوا حسابنا @BSF_sa لمعرفة آخر الأخبار'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39129, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3065,52 +3050,50 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2044075725334954107</t>
+          <t>2044307778140025041</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46126.83671296296</v>
+        <v>46127.45969907408</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/Eisa_Shj/status/2044283005183857003</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE and @SobhaRealtyDXB partner to offer integrated home financing solutions for off-plan projects in #Dubai .
-#EmiratesNBD #SobhaRealty #UAE #Dubairealestate #realestate
-https://t.co/ukweMYki3P</t>
+          <t>ماعرف ليش اغلب الناس لين الحين تفتح عندهم و هم من اكثر البنوك في تعقيد الامور الحمدالله على نعمه ENBD الصراحة🦦</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1776173826000</v>
+        <v>1776230024000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044283005183857003</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3120,7 +3103,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'عـيـســى الأمـيــري', 'screenName': 'Eisa_Shj', 'followersCount': 74, 'favouritesCount': 40742, 'friendsCount': 404, 'description': 'Don’t be sorry, BE BETTER ✨'}</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3130,55 +3113,53 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>80</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" s="2" t="n">
-        <v>46126.73409722222</v>
+        <v>46127.38453703704</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044047297034760542</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2044047297034760542</t>
+          <t>2044301025142513927</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2044060507603382318</t>
+          <t>2039084064070623329</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/biztoday_intl/status/2044060507603382318</t>
+          <t>https://x.com/AliAhmedk66633/status/2039084064070623329</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>#DaherAircraft strengthens its customer support and distributor Network by adding the Kodiak to Columbia Air’s portfolio.
-@DAHER_official #aircraft #aviation #NicolasChabbert #MelissaDuzguner
-https://t.co/tFtCpJWMU9</t>
+          <t>@EmiratesNBD_KSA اسوء تجربة من البنك في خدمة العملاء ولا ادارة التحصيل الي اسلوبه زي الزفت تخيلو طلبت خطاب عدم مومانعه  من شراء المديونية لك وشو يسوي البنك يتصل على البنك الثاني ويتاكد متى تتغير النسبه ويتاخر الطلب لي ثلاث ايام وانا اتصل على ادارة التحصيل وخدمه العملاء اخر شي</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1776176976000</v>
+        <v>1774990499000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2044060507603382318</t>
+          <t>2039084064070623329</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3188,11 +3169,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'Biz Today Intl', 'screenName': 'biztoday_intl', 'followersCount': 469, 'favouritesCount': 969, 'friendsCount': 107, 'description': "Biz Today is the World's preeminent 24-hour English language business, economics, technology and finance to travel, fashion and lifestyle publication"}</t>
+          <t>{'name': 'Ali Ahmed', 'screenName': 'AliAhmedk66633', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 6, 'description': ''}</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3205,46 +3186,46 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>157</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" s="2" t="n">
-        <v>46126.77055555556</v>
+        <v>46113.03818287037</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044301025142513927</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044301025142513927</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/oras_2030/status/2044301025142513927</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Emirates NBD And Sobha Realty Partner To Offer Integrated Home Financing Solutions For Off-Plan Projects In Dubai https://t.co/fVBST6NQ7A</t>
+          <t>@AliAhmedk66633 @EmiratesNBD_KSA هل تنصح اخ علي@ انقل راتبي عندهم عشان قرض شخصي لان نسبتهم اقل من البنوك الاخرى؟</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1776168712000</v>
+        <v>1776234320000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2039084064070623329</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3254,7 +3235,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'oras2030', 'screenName': 'oras_2030', 'followersCount': 0, 'favouritesCount': 133, 'friendsCount': 126, 'description': 'سبحان الله وبحمده سبحان الله العظيم'}</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -3271,46 +3252,50 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2039084064070623329</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="n">
-        <v>46126.67490740741</v>
+        <v>46127.43425925926</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044025847523487886</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2044025847523487886</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2044038581161996359</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/dcgguide/status/2044038581161996359</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EWEC Opens Q2 2026 Clean Energy Certificates Auction To Empower Organisations To Lead Global Energy Transition https://t.co/wXSWsOlKcV</t>
+          <t>Emirates Islamic launches AED1m campaign for SME customers  https://t.co/7gX7HHRcOh</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1776171748000</v>
+        <v>1776269241000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2044038581161996359</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3320,7 +3305,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93486, 'favouritesCount': 19465, 'friendsCount': 106588, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1108, 'favouritesCount': 23739, 'friendsCount': 301, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -3333,73 +3318,60 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" s="2" t="n">
-        <v>46126.7100462963</v>
+        <v>46127.8384375</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/gold_hadas/status/2044447495619547616</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044447495619547616</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044631075935199685</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/gold_hadas/status/2044631075935199685</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>القيمة السوقية لأكبر 10 شركات عامة في الإمارات تبلغ 692.3 مليار دولار في 2026، تتصدرها "الشركة العالمية القابضة" مستحوذة وحدها على نحو 34% من إجمالي القيمة السوقية.
-@ihc__official
-@TAQAGroup
-@ADNOCGas
-@FABConnects
-@EmiratesNBD_AE
-@eAndUAE
-@DEWAOfficial
-@emaardubai
-@OfficialADCB
-@adhuae
-@ADX_AE
-@DFMalerts
-#الإمارات #أدنوك #الطاقة #IHC  #الشبكة_الاقتصادية</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1776172925000</v>
+        <v>1776313010000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044631075935199685</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3mvnXaMAAc5dn.jpg', 'type': 'photo', 'id': '2044043511591481344'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'الشبكة الاقتصادية', 'screenName': 'Net_eqtisad', 'followersCount': 347, 'favouritesCount': 645, 'friendsCount': 24, 'description': 'أرقام..احصائيات..اقتصاد واكثر!'}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1108, 'favouritesCount': 23739, 'friendsCount': 301, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3416,58 +3388,58 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" s="2" t="n">
-        <v>46126.72366898148</v>
+        <v>46128.34502314815</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044043515546800261</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2044043515546800261</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2044029975376855339</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/Net_eqtisad/status/2044029975376855339</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>التقى سمو الشيخ خالد بن محمد بن زايد آل نهيان قادة شركات صينية، في إطار تعزيز الشراكة الاستراتيجية بين البلدين.
-📌 ركزت اللقاءات على استكشاف فرص جديدة للتعاون الاقتصادي والتنموي، بما يدعم توسيع الاستثمارات وتعزيز العلاقات الثنائية.
-#الإمارات #الصين #الاستثمار #الاقتصاد #الشبكة_الاقتصادية</t>
+          <t>الإمارات الإسلامي @emiratesislamic  يعزز قطاع الأعمال بحملة للشركات الصغيرة
+#الإمارات #دبي #بنوك #شركات #مشاريع_صغيرة #تمويل #اقتصاد #استثمار #نمو #entalarabiya
+https://t.co/XNTvseOsQ0</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1776169697000</v>
+        <v>1776243957000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2044029975376855339</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3abgLagAAnLi2.jpg', 'type': 'photo', 'id': '2044029971925204992'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'الشبكة الاقتصادية', 'screenName': 'Net_eqtisad', 'followersCount': 347, 'favouritesCount': 645, 'friendsCount': 24, 'description': 'أرقام..احصائيات..اقتصاد واكثر!'}</t>
+          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15614, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -3477,65 +3449,65 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>82</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" s="2" t="n">
-        <v>46126.68630787037</v>
+        <v>46127.54579861111</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/EntAlArabiya/status/2044341445717610661</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044341445717610661</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044366042470977758</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/EntAlArabiya/status/2044366042470977758</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Emirates NBD and Sobha Realty partner to offer integrated home financing solutions for off-plan projects in Dubai 
-#EmiratesNBD #SobhaRealty #Dubai #UAE #Business #Partnership @SobhaRealtyDXB #OneVilleNews
-https://t.co/rQ8bwNlb8E via @onevillenews https://t.co/uuh2N7Ktl1</t>
+          <t>شراكة بين RGB وBNC Publishing لتعزيز الوصول إلى المحتوى الصحي الموثوق في المنطقة @EntMagazineME  
+#الإمارات #صحة #توعية #طب #إعلام #شركات #محتوى #رفاهية #ابتكار #entalarabiya
+https://t.co/PFB5U9YnOG</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1776167865000</v>
+        <v>1776249821000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044366042470977758</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF3Tb09bMAAglq0.jpg', 'type': 'photo', 'id': '2044022280922279936'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
+          <t>{'name': 'Entrepreneur العربية', 'screenName': 'EntAlArabiya', 'followersCount': 15614, 'favouritesCount': 5008, 'friendsCount': 796, 'description': 'لمتابعة آخر أخبار عالم ريادة الأعمال في منطقة الشرق الأوسط وشمال إفريقيا، الحساب الرسمي لمجلة Entrepreneur العربية'}</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -3545,65 +3517,63 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>138</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" s="2" t="n">
-        <v>46126.66510416667</v>
+        <v>46127.61366898148</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2044022292972482932</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2044022292972482932</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2043769833955917928</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/OneVilleNews/status/2043769833955917928</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>“Ya Biladi”… A Song That Feels Like Home, Bringing the UAE’s Spirit to Life 
-#YaBiladi #UAE #Dubai #Song #HussainAlJassmi @7sainaljassmi #محمد_بن_زايد #الامارات_العربية_المتحدة 
-https://t.co/TqZCzfMs1b via @onevillenews https://t.co/lrW3u4M1bq</t>
+          <t>Emirates Islamic Drives SME Growth And Engagement Through AED 1 Million Business Banking Campaign https://t.co/lYSRNGGq3N</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1776107674000</v>
+        <v>1776243753000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2043769833955917928</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFztt94bcAAnViP.jpg', 'type': 'photo', 'id': '2043769704880500736'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'One Ville News', 'screenName': 'OneVilleNews', 'followersCount': 45, 'favouritesCount': 8, 'friendsCount': 39, 'description': 'All of One Ville, all in one place.'}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93487, 'favouritesCount': 19475, 'friendsCount': 106586, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -3613,53 +3583,53 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" s="2" t="n">
-        <v>46125.96844907408</v>
+        <v>46127.5434375</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/dcgguide/status/2044340590037655768</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044340590037655768</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044619960383848830</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/Zawya/status/2044002065840521609</t>
+          <t>https://x.com/dcgguide/status/2044619960383848830</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>While regional tensions are driving higher volatility and risk premiums, the #banking sector in the GCC remains fundamentally sound, with Saudi and UAE institutions still offering upside even under adverse scenarios, according to CI Capital https://t.co/BjQ424Gns3</t>
+          <t>Soulland Arrives In Dubai, Marking Its First Entry Into The Middle East https://t.co/lNcIEXHcGK</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1776163042000</v>
+        <v>1776310360000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044619960383848830</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3669,63 +3639,65 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'Zawya', 'screenName': 'Zawya', 'followersCount': 26278, 'favouritesCount': 259, 'friendsCount': 94, 'description': 'https://t.co/zY3tN9MLkQ, by @LSEGplc, is a leading source of regional news and intelligence. Retweets are not endorsements.'}</t>
+          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93487, 'favouritesCount': 19475, 'friendsCount': 106586, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
         </is>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" s="2" t="n">
-        <v>46126.60928240741</v>
+        <v>46128.31435185186</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2044003893114232972</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/nabilal_rawi/status/2044003893114232972</t>
+          <t>https://x.com/emiratesislamic/status/2044294653097156714</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>@Zawya Emirates NBD and ADCB demonstrate the UAE's institutional strength. Free zones and global market access create a financial anchor for entrepreneurs navigating regional volatility.</t>
+          <t>من “يوماً ما” إلى يوم الانتقال!
+التمويل السكني من الإمارات الإسلامي يجعل حلم امتلاك منزلك حقيقة، مع المرونة والوضوح في كل خطوة من رحلتك.
+استمتع بحلول تمويلية مصممة خصيصاً لك، ودعم متكامل طوال الطريق، لتصبح تجربة امتلاك المنزل سلسة وميسرة.</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1776163478000</v>
+        <v>1776232801000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2044002065840521609</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3735,11 +3707,11 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'Nabil Smarter', 'screenName': 'nabilal_rawi', 'followersCount': 30, 'favouritesCount': 16977, 'friendsCount': 335, 'description': 'المستقبل ليس مكاناً نكسبه، بل مكاناً يجب أن نحميه.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -3752,66 +3724,61 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>2044002065840521609</t>
-        </is>
-      </c>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" s="2" t="n">
-        <v>46126.6143287037</v>
+        <v>46127.41667824074</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044294656716836969</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2043984421192077650</t>
+          <t>https://x.com/emiratesislamic/status/2044294656716836969</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Travel more, earn more miles ✈️
-Earn bonus Skywards Miles on Emirates Holidays bookings when you pay with your Emirates NBD card. Offer valid until 30 April 2026. T&amp;amp;Cs apply.
-https://t.co/HWEZythYdM https://t.co/z5yAeQRQdC</t>
+          <t>ابدأ رحلتك نحو منزل أحلامك اليوم.
+https://t.co/lQDtk9615Y</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1776158836000</v>
+        <v>1776232801000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2043984421192077650</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF2w_zAWYAA52Xp.jpg', 'type': 'photo', 'id': '2043984415965995008'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39131, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3820,51 +3787,58 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2044294653097156714</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="n">
-        <v>46126.56060185185</v>
+        <v>46127.41667824074</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044294659795513346</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/GidwaniHero/status/2044143965486948528</t>
+          <t>https://x.com/emiratesislamic/status/2044294659795513346</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>@HHShkMohd @ENBDdeals @FABConnects @MashreqTweets @emiratesislamic 
-Dear uae government what is daily lime to deposit in machine if I have 100k to deposit and machine is slow and behind me standing In Q Are arguing what to do who deposit black money no one question them why</t>
+          <t>From “one day” to move-in day.
+Emirates Islamic Home Finance helps turn home ownership into reality, with the flexibility and clarity you need at every step.
+With tailored finance solutions and guided support throughout,
+Your home journey starts here.
+https://t.co/XwkOLamNf0</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1776196874000</v>
+        <v>1776232802000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2044143965486948528</t>
+          <t>2044294653097156714</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3874,7 +3848,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{'name': 'Hero Gidwani', 'screenName': 'GidwaniHero', 'followersCount': 19, 'favouritesCount': 24, 'friendsCount': 154, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3891,128 +3865,133 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2044294656716836969</t>
+        </is>
+      </c>
       <c r="P50" s="2" t="n">
-        <v>46127.00085648148</v>
+        <v>46127.41668981482</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/RotanaLive/status/2043039035585700343</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ليلة استثنائية حلق فيها صقر الغناء في #موسم_جدة 🦅
-والجمهور ولعها حماس من أول لحظة لآخرها 🔥
-#رابح_صقر
-#روتانا_لايف
-@RabehSaqer 
-@JEDCalendar 
-@EmiratesNBD_KSA https://t.co/2PHoXVNSf7</t>
+          <t>@emiratesislamic has announced the launch of a new Business Banking campaign aimed at supporting 3SME customers and strengthening #business resilience across the #UAE.
+Running until June 30, 2026, the campaign allows businesses to participate by increasing and maintaining their average balances in their Business Banking Accounts.
+The initiative offers a total prize pool of AED1 million and will reward 55 winners over three months, providing multiple opportunities for customers to win cash prizes while encouraging sustainable growth.
+🔗Read more HERE: https://t.co/j0Wq0RjPdm</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1775933438000</v>
+        <v>1776237111000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2043038860767068160/img/roy7XPjYQBFoKXUJ.jpg', 'type': 'video', 'id': '2043038860767068160'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7bgFgb0AArMEW.jpg', 'type': 'photo', 'id': '2044312625153298432'}]</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'Rotana Live', 'screenName': 'RotanaLive', 'followersCount': 193531, 'favouritesCount': 7072, 'friendsCount': 149, 'description': 'روتانا لايف الحساب الرسمي لحفلات روتانا | Rotana events https://t.co/wTAoLH4wPm'}</t>
+          <t>{'name': 'Entrepreneur Middle East', 'screenName': 'EntMagazineME', 'followersCount': 178522, 'favouritesCount': 30182, 'friendsCount': 622, 'description': 'The official Twitter of Entrepreneur Middle East: inspiring, informing, and celebrating entrepreneurs in the Middle East, and beyond.'}</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>106</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" s="2" t="n">
-        <v>46123.95182870371</v>
+        <v>46127.4665625</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/EntMagazineME/status/2044312732879728677</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044312732879728677</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2043855961165623417</t>
+          <t>2044354972473766389</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/FirasAlin3va/status/2043855961165623417</t>
+          <t>https://x.com/EntMagazineME/status/2044354972473766389</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>@RotanaLive @RabehSaqer @JEDCalendar @EmiratesNBD_KSA أداء ساحر لطيور الغناء في موسم جدة!</t>
+          <t>RGB (@RGBDubai), a #Dubai-based broadcasting and content production company known for its cutting-edge output and expertise in branding and identity since 2006, and the creator of The Health Community—a digital platform focused on verified medical knowledge—has entered a strategic media partnership with Dubai-headquartered regional media company BNC Publishing.
+The collaboration aims to expand access to credible, expert-led health content across the Middle East, leveraging Entrepreneur’s bilingual platforms and established regional audience.
+Designed as more than a content platform, The Health Community seeks to create a connected ecosystem where reliable #healthcare knowledge can be shared in ways that are practical and accessible for everyday life.
+Under the partnership, Entrepreneur Middle East (@EntMagazineME) and Entrepreneur Al Arabiya will collaborate with RGB to develop bilingual editorial features, #expert insights, and multimedia storytelling that elevate conversations around prevention, wellbeing, and human performance across the region.
+Read more HERE: https://t.co/KBGmbzdXAG</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1776128208000</v>
+        <v>1776247182000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2043039035585700343</t>
+          <t>2044354972473766389</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF8B64ZaYAECgQU.jpg', 'type': 'photo', 'id': '2044354866932506625'}]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{'name': 'فراس علي', 'screenName': 'FirasAlin3va', 'followersCount': 27, 'favouritesCount': 189, 'friendsCount': 8, 'description': 'أنا لاعب كرة قدم ملتزم وأحب التحدي والتركيز على تطوير مهاراتي دائماً.'}</t>
+          <t>{'name': 'Entrepreneur Middle East', 'screenName': 'EntMagazineME', 'followersCount': 178522, 'favouritesCount': 30182, 'friendsCount': 622, 'description': 'The official Twitter of Entrepreneur Middle East: inspiring, informing, and celebrating entrepreneurs in the Middle East, and beyond.'}</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -4022,67 +4001,64 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2043039035585700343</t>
-        </is>
-      </c>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" s="2" t="n">
-        <v>46126.20611111111</v>
+        <v>46127.583125</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Really struggling to get hold of @emiratesislamic I’ve called the international line and emailed and really need to get hold of someone. Please help 😭</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/zGFXn2y3iT</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1776165319000</v>
+        <v>1776274926000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r2SlXIAA7IEH.jpg', 'type': 'photo', 'id': '2044471336295145472'}]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{'name': 'Zahara Sadiq', 'screenName': 'ZaharaMMalik', 'followersCount': 741, 'favouritesCount': 827, 'friendsCount': 564, 'description': 'Impact Investing | Entrepreneur | Driven by Building Bridges Globally | Serial Tea Drinker | Part Time Wisdom Coach'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -4099,46 +4075,51 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
       <c r="P53" s="2" t="n">
-        <v>46126.63563657407</v>
+        <v>46127.90423611111</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://x.com/ZaharaMMalik/status/2044011613422834071</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2044023053797953761</t>
+          <t>2044471342880170391</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2044023053797953761</t>
+          <t>https://x.com/emiratesislamic/status/2044471342880170391</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>@ZaharaMMalik Dear Zahara,we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+https://t.co/RWuJWfhfUm</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1776168046000</v>
+        <v>1776274927000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4165,60 +4146,62 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2044011613422834071</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="P54" s="2" t="n">
-        <v>46126.66719907407</v>
+        <v>46127.90424768518</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044471339784810653</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044471339784810653</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042145058133307907</t>
+          <t>https://x.com/emiratesislamic/status/2044322412007735394</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>@emiratesislamic I have already cleared a personal loan and approached your Phone Banking &amp;amp; WhatsApp channel for issue of NIL LIABILITY LETTER..but no concrete response .Not feasible to obtain through your application as well.Can u please check&amp;amp; revert ASAP. Thank You.</t>
+          <t>Invest in gold and silver, easily and digitally with the EI + Mobile Banking App
+⭐️Access the Wealth tab through the EI + Mobile Banking App and start investing securely and seamlessly.
+⭐️Shariah-compliant offering https://t.co/lsN56x6Joc</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1775720297000</v>
+        <v>1776239419000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kZnMXwAAJGag.jpg', 'type': 'photo', 'id': '2044322409541517312'}]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -4231,55 +4214,57 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>205</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" s="2" t="n">
-        <v>46121.48491898148</v>
+        <v>46127.49327546296</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2042152553400385940</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2042152553400385940</t>
+          <t>https://x.com/emiratesislamic/status/2044471327159996698</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/PtTMEJsQ5k</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1775722084000</v>
+        <v>1776274923000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF9r1lyXAAANAJs.jpg', 'type': 'photo', 'id': '2044471324270067712'}]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -4301,50 +4286,50 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>2042145058133307907</t>
-        </is>
-      </c>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" s="2" t="n">
-        <v>46121.50560185185</v>
+        <v>46127.90420138889</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2042853514049917277</t>
+          <t>2044471329382900119</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2042853514049917277</t>
+          <t>https://x.com/emiratesislamic/status/2044471329382900119</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>@emiratesislamic So far nobody has contacted me in connection with this query nor any mail from your end .</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+https://t.co/FsXr2qXw7K</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1775889206000</v>
+        <v>1776274924000</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4354,11 +4339,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -4371,50 +4356,53 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>74</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2042152553400385940</t>
+          <t>2044471327159996698</t>
         </is>
       </c>
       <c r="P57" s="2" t="n">
-        <v>46123.43988425926</v>
+        <v>46127.90421296296</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2043560931511189651</t>
+          <t>2044322414310367621</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043560931511189651</t>
+          <t>https://x.com/emiratesislamic/status/2044322414310367621</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>⭐️Certified gold bars meeting London Bullion Market Association (LBMA) and Dubai Good Delivery (DGD) standards
+⭐️Certified silver bars compliant with UAE Good Delivery (UAE GD) standards
+Terms and conditions apply.
+https://t.co/w5RtLlrqm8</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1776057868000</v>
+        <v>1776239419000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4428,7 +4416,7 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -4441,60 +4429,63 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>143</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2042853514049917277</t>
+          <t>2044322412007735394</t>
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>46125.39199074074</v>
+        <v>46127.49327546296</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>@emiratesislamic How many days more you require to issue a NIL LIABILITY LETTER...?</t>
+          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
+EI + للخدمات المصرفية عبر الهاتف المتحرك
+⭐️ادخل إلى منصة "الثروات" في تطبيق + EI  للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان.
+⭐️منتج متوافق مع أحكام الشريعة الإسلامية https://t.co/CZe51naJfQ</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1776150922000</v>
+        <v>1776239416000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7kY9tWoAAk87F.jpg', 'type': 'photo', 'id': '2044322398405566464'}]</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>{'name': 'TS Aswani Kumar', 'screenName': 'aswanikumartst5', 'followersCount': 10, 'favouritesCount': 181, 'friendsCount': 25, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -4507,54 +4498,53 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2043560931511189651</t>
-        </is>
-      </c>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
       <c r="P59" s="2" t="n">
-        <v>46126.46900462963</v>
+        <v>46127.49324074074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://x.com/aswanikumartst5/status/2043951228640747823</t>
+          <t>https://x.com/emiratesislamic/status/2044322401052250291</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2043955058459467807</t>
+          <t>2044322403761697193</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2043955058459467807</t>
+          <t>https://x.com/emiratesislamic/status/2044322403761697193</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>@aswanikumartst5 Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>⭐️سبائك ذهب معتمدة ومطابقة لمعايير جمعية سوق لندن للسبائك ودبي للتسليم الجيد
+⭐️سبائك فضة معتمدة ومتوافقة مع معايير الإمارات للتسليم الجيد
+تطبق الشروط والأحكام.
+https://t.co/WN0tZk19JS</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1776151835000</v>
+        <v>1776239417000</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2042145058133307907</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4581,430 +4571,16 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>116</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>2043951228640747823</t>
+          <t>2044322401052250291</t>
         </is>
       </c>
       <c r="P60" s="2" t="n">
-        <v>46126.47957175926</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2043932263390310621</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2043932263390310621</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>How do you usually pay for your expenses?
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2043932263390310621</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" s="2" t="n">
-        <v>46126.41666666666</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263390310621</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2043932263390310621</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Money grows best when given time, balance, and the right mix.
-Spreading investments and thinking long term can help create steadier progress along the way.
-Small steps today can support stronger outcomes tomorrow.</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" s="2" t="n">
-        <v>46126.41666666666</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043917165502316982</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>نظرتك الأسبوعية… لحياة أكثر وعياً واتزاناً مالياً.
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-Your Weekly Perspective. A step toward a more mindful financial week.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic https://t.co/48pYcSntb5</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1776142801000</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2043917165502316982</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HFw707XWcAAVI5E.jpg', 'type': 'photo', 'id': '2043574111394230272'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HFw71ETXwAAPour.jpg', 'type': 'photo', 'id': '2043574113793458176'}]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" s="2" t="n">
-        <v>46126.37501157408</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2043932266456367150</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932266456367150</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>To know more:
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1776146401000</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="n">
-        <v>46126.41667824074</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263725854816</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2043932263725854816</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263386157239</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>ينمو المال بشكل أفضل مع الوقت، والتوازن، والتنوّع المناسب.
-تنويع الاستثمارات والتفكير على المدى الطويل يساعدان على تحقيق استقرار أكبر.
-خطوات صغيرة اليوم قد تصنع نتائج أقوى في المستقبل.
-للمزيد: 
-https://t.co/mgtIcQsyLZ https://t.co/Eh7yupmtiG</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2043932263386157239</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2043692933543550976/pu/img/DwmJr4WPQRT9Ka0q.jpg', 'type': 'video', 'id': '2043692933543550976'}]</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" s="2" t="n">
-        <v>46126.41666666666</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2043932263449006494</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>كيف تدفع نفقاتك عادةً؟
-#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1776146400000</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2043932263449006494</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18415, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" s="2" t="n">
-        <v>46126.41666666666</v>
+        <v>46127.49325231482</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,7 +555,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -568,11 +568,11 @@
         <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>560089</t>
+          <t>578257</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -638,7 +638,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>112</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -709,7 +709,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -780,7 +780,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -900,7 +900,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -917,7 +917,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -932,25 +932,158 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2046263546024165797</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2046263546024165797</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+https://t.co/sNYXzG1RYE</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1776702221000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2046263546024165797</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195570, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2</v>
+      </c>
+      <c r="M8" t="n">
+        <v>34</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>7222</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="n">
+        <v>46132.84978009259</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2046263546024165797</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2046216696818745580</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/DurovPD/status/2046216696818745580</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>I’m buying more Bitcoin and Toncoin</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1776691052000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2046216696818745580</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'name': 'Pavel Durov (Parody)', 'screenName': 'DurovPD', 'followersCount': 196121, 'favouritesCount': 3798, 'friendsCount': 4672, 'description': 'TON is making digital ownership easy for billions. Pavel Durov Parody • Just a Memes'}</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>119</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>929</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>26870</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="2" t="n">
+        <v>46132.72050925926</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2046418526051684674</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>2046418526051684674</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>#EmiratesNBD @EmiratesNBD_AE Sent Me An Account Statement,They Owe Me 200000AED Which They Won't Pay.@HHShkMohd @MohamedBinZayed
 #Lebanese #Banks Stole My Money @FransabankGroup @EmmanuelMacron.
@@ -959,269 +1092,206 @@
 I Am Just Too Tired To Give Up</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>1776739171000</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>2046418526051684674</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>{'name': 'M.G.', 'screenName': 'yallaweb', 'followersCount': 597, 'favouritesCount': 13, 'friendsCount': 446, 'description': 'Digital Marketer,Startup Founder, Almost Homeless Accidental Activist Against Corrupt Corporations,zionistLobby WarCrimes,GayLobby Pedophiles &amp; CIA Cockroaches.'}</t>
         </is>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="n">
+        <v>46133.27744212963</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://x.com/yallaweb/status/2046418526051684674</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2046418526051684674</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2046433498962026756</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/Mario_thomas_y/status/2046433498962026756</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>@yallaweb Were you able to file a legal complaint @yallaweb ?</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1776742741000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2046418526051684674</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'name': 'Mario Thomas', 'screenName': 'Mario_thomas_y', 'followersCount': 1643, 'favouritesCount': 2658, 'friendsCount': 236, 'description': 'Victim of Elon scams.'}</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" s="2" t="n">
-        <v>46133.27744212963</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2046418526051684674</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>46133.31876157408</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>https://x.com/yallaweb/status/2046418526051684674</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2046418526051684674</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>2046311476127023142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>https://x.com/yallaweb/status/2046311476127023142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>#God I Hate Slow #Internet,it's Killer Of  #Productivity
 Had 1000Mbps In #MexicoCity,But #GenocidalJews &amp;amp; #GenocidalGays Did    #Sabotage That,As They Thought My #highspeed Can Hinder/Expose/Endanger Their Crimes &amp;amp; Conspiracies.
 #EconomicSiege #Mexico #CDMX #Islamophobia #USA</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F12" t="n">
         <v>1776713649000</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>2046311476127023142</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>{'name': 'M.G.', 'screenName': 'yallaweb', 'followersCount': 597, 'favouritesCount': 13, 'friendsCount': 446, 'description': 'Digital Marketer,Startup Founder, Almost Homeless Accidental Activist Against Corrupt Corporations,zionistLobby WarCrimes,GayLobby Pedophiles &amp; CIA Cockroaches.'}</t>
         </is>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" s="2" t="n">
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="n">
         <v>46132.98204861111</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2046263546024165797</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2046263546024165797</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
-https://t.co/sNYXzG1RYE</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1776702221000</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2046263546024165797</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195559, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" t="n">
-        <v>34</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>7024</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" s="2" t="n">
-        <v>46132.84978009259</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://x.com/khaleejtimes/status/2046263546024165797</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2046263546024165797</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2046216696818745580</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>https://x.com/DurovPD/status/2046216696818745580</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>I’m buying more Bitcoin and Toncoin</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1776691052000</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2046216696818745580</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>{'name': 'Pavel Durov (Parody)', 'screenName': 'DurovPD', 'followersCount': 196123, 'favouritesCount': 3798, 'friendsCount': 4672, 'description': 'TON is making digital ownership easy for billions. Pavel Durov Parody • Just a Memes'}</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>118</v>
-      </c>
-      <c r="K11" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" t="n">
-        <v>35</v>
-      </c>
-      <c r="M11" t="n">
-        <v>891</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>25793</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" s="2" t="n">
-        <v>46132.72050925926</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2046264235852718127</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>2046264189786714117</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>https://x.com/preeminentdxb/status/2046264189786714117</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>A quiet shift, but a powerful one.
 The gap between intent and ownership in Dubai just got smaller, and more predictable.
@@ -1229,230 +1299,161 @@
 #MarketMaturity #DubaiRealEstate #PropertyInvestment https://t.co/F1CLT9HxwK</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>1776702375000</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2046264189786714117</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKavSW8AAvugA.jpg', 'type': 'photo', 'id': '2046264166428635136'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbQLWYAAjRuc.png', 'type': 'photo', 'id': '2046264175257608192'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbh8WgAAvC6X.png', 'type': 'photo', 'id': '2046264180026540032'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKbz0W4AAHPcf.png', 'type': 'photo', 'id': '2046264184824848384'}]</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" s="2" t="n">
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="2" t="n">
         <v>46132.8515625</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2046264235852718127</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2046264235852718127</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that's reducing friction, improving transparency, and making long-term planning far more structure https://t.co/ykGWWmVfrC</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>1776702386000</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2046264189786714117</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKda4WYAEW_JB.png', 'type': 'photo', 'id': '2046264212490444801'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKdvYXUAAyguF.png', 'type': 'photo', 'id': '2046264217993433088'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKeRWWcAEerrb.jpg', 'type': 'photo', 'id': '2046264227111792641'}]</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
-        </is>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2046264189786714117</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n">
-        <v>46132.85168981482</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2046264235852718127</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2046264235852718127</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/preeminentdxb/status/2046264235852718127</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Backed by Emirates NBD and Dubai Holding Real Estate, this move signals a maturing market: one that's reducing friction, improving transparency, and making long-term planning far more structure https://t.co/ykGWWmVfrC</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1776702386000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2046264189786714117</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKda4WYAEW_JB.png', 'type': 'photo', 'id': '2046264212490444801'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKdvYXUAAyguF.png', 'type': 'photo', 'id': '2046264217993433088'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXKeRWWcAEerrb.jpg', 'type': 'photo', 'id': '2046264227111792641'}]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'name': 'Preeminent Properties', 'screenName': 'preeminentdxb', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 2, 'description': "Unveiling UAE's finest real estate, where trust and satisfaction meet"}</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2046264189786714117</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>46132.85168981482</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>https://x.com/naveenthumala/status/2046198033738785046</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2046198033738785046</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>2046198033738785046</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>https://x.com/naveenthumala/status/2046198033738785046</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>If someone experienced gulf banking understands  the importance of Emirates NBD acquiring RBL bank stake
 #RBLBank</t>
         </is>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" t="n">
         <v>1776686602000</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>2046198033738785046</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>{'name': 'Naveen Reddy', 'screenName': 'naveenthumala', 'followersCount': 20, 'favouritesCount': 1498, 'friendsCount': 127, 'description': 'Remember you will die'}</t>
         </is>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" s="2" t="n">
-        <v>46132.66900462963</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2046190505554321598</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>2046190505554321598</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>@DFMalerts 
-I have old account with DFM and now dormant. 
-I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
-I have the full details. I need your help to update my investor’s account.</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>1776684807000</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2046190505554321598</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>{'name': 'vision', 'screenName': 'ja2030ah', 'followersCount': 86, 'favouritesCount': 12, 'friendsCount': 597, 'description': 'وطني وقيادته خط أحمر'}</t>
-        </is>
-      </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
@@ -1467,12 +1468,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" s="2" t="n">
-        <v>46132.64822916667</v>
+        <v>46132.66900462963</v>
       </c>
     </row>
     <row r="16">
@@ -1525,7 +1526,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1535,14 +1536,14 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M16" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>857177</t>
+          <t>870622</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -1608,7 +1609,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>143</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1662,7 +1663,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1679,7 +1680,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>140</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1694,139 +1695,138 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2046190505554321598</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2046190505554321598</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://x.com/ja2030ah/status/2046190505554321598</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>@DFMalerts 
+I have old account with DFM and now dormant. 
+I talked to Emirates NBD Securities , they said to contact Dubai Financial Market. 
+I have the full details. I need your help to update my investor’s account.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1776684807000</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2046190505554321598</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'name': 'vision', 'screenName': 'ja2030ah', 'followersCount': 86, 'favouritesCount': 12, 'friendsCount': 597, 'description': 'وطني وقيادته خط أحمر'}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="2" t="n">
+        <v>46132.64822916667</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2046171931813011938</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>2046171931813011938</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://x.com/ENBDdeals/status/2046171931813011938</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Turn your bills into rewards
 Get AED 500 worth of noon credits + AED 500 welcome bonus when you apply for an Emirates NBD noon One Visa Credit Card.
 Apply Now: https://t.co/vPejTs11gM https://t.co/w4kHA8AtSA</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F20" t="n">
         <v>1776680379000</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2046171931813011938</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGV2hzyXYAAiJn2.jpg', 'type': 'photo', 'id': '2046171928918974464'}]</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39176, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39178, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" s="2" t="n">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="n">
         <v>46132.59697916666</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2046171233243541979</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>2046171233243541979</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>https://x.com/ATwo2/status/2046171233243541979</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>1776680212000</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>{'name': 'عبدالله ثاني الغاوي', 'screenName': 'ATwo2', 'followersCount': 444, 'favouritesCount': 4901, 'friendsCount': 480, 'description': 'رياضي، اقتصادي، #crypto$'}</t>
-        </is>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2045093015459352679</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="n">
-        <v>46132.59504629629</v>
       </c>
     </row>
     <row r="21">
@@ -1842,21 +1842,21 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2046175033328890208</t>
+          <t>2046171233243541979</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2046175033328890208</t>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>@ATwo2 مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
+          <t>@EmiratesNBD_AE شو ها العروض مع احترامي لكم. لا تستغلون حماة الوطن بهكذا عروض مخجله</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1776681118000</v>
+        <v>1776680212000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1870,11 +1870,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174304, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'عبدالله ثاني الغاوي', 'screenName': 'ATwo2', 'followersCount': 442, 'favouritesCount': 4901, 'friendsCount': 480, 'description': 'رياضي، اقتصادي، #crypto$'}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1887,48 +1887,46 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2046171233243541979</t>
+          <t>2045093015459352679</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46132.6055324074</v>
+        <v>46132.59504629629</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
+          <t>https://x.com/ATwo2/status/2046171233243541979</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2046061240511082734</t>
+          <t>2046171233243541979</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2046061240511082734</t>
+          <t>2046175033328890208</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/she7ii88/status/2046061240511082734</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2046175033328890208</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE هذا عرض صدق ؟! 
-٦% ؟! سلامات البنوك الاسلاميه المرابحه الثابته ٢.٧% ؟! 
-ولو سمحتوا علم الامارات و لبس القوات المسلحه ... ليست دعايه</t>
+          <t>@ATwo2 مرحبًا، هل يمكننا معرفة سبب عدم رضاك؟ سيكون من المفيد جدًا إذا كان بإمكانك مشاركة المزيد من التفاصيل حول ذلك ورقم اتصالك معنا عبر الرسائل الخاصة.</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1776653988000</v>
+        <v>1776681118000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1942,7 +1940,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'Rashed Sem', 'screenName': 'she7ii88', 'followersCount': 9, 'favouritesCount': 303, 'friendsCount': 49, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174305, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1959,61 +1957,61 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>71</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2045093015459352679</t>
+          <t>2046171233243541979</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46132.29152777778</v>
+        <v>46132.6055324074</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2046166030557614556</t>
+          <t>2046167018303602898</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2046166030557614556</t>
+          <t>2046167018303602898</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
-https://t.co/sNYXzG1RYE</t>
+          <t>Excited to announce Mr Vijay Bains, Group Head of ESG &amp;amp; CSO at Emirates NBD, as a plenary speaker for Climate Finance 2.0 at the Global Sustainability &amp;amp; CSR Forum!
+With 20+ years in sustainable finance &amp;amp; leadership in ESG councils, Vijay brings unmatched expertise. Don’t miss it! https://t.co/ApxeVy3ABX</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1776678972000</v>
+        <v>1776679207000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2046166030557614556</t>
+          <t>2046167018303602898</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVyD6AaAAAN0zx.jpg', 'type': 'photo', 'id': '2046167017145892864'}]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195559, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
+          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2023,177 +2021,43 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" s="2" t="n">
-        <v>46132.58069444444</v>
+        <v>46132.58341435185</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
+          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2046166030557614556</t>
+          <t>2046167018303602898</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2046265860453761085</t>
+          <t>2046118862736003268</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/Cricket_bazball/status/2046265860453761085</t>
+          <t>https://x.com/ArabiaCSR/status/2046118862736003268</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
-        <is>
-          <t>🚨 End of Mike Hesson 🚨
-- PCB has decided to sack Mike Hesson from the role of Pakistan team’s head coach and has decided to appoint Ottis Gibson as the new head coach for white-ball cricket. (Geo news) https://t.co/nvlKVuP4il</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>1776702773000</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2046265860453761085</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXL9DraAAMigd2.jpg', 'type': 'photo', 'id': '2046265855529582595'}]</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>{'name': 'junaid', 'screenName': 'Cricket_bazball', 'followersCount': 145, 'favouritesCount': 174812, 'friendsCount': 258, 'description': 'Cricket • Stats • Not affiliated with anyone'}</t>
-        </is>
-      </c>
-      <c r="J24" t="n">
-        <v>27</v>
-      </c>
-      <c r="K24" t="n">
-        <v>8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>34</v>
-      </c>
-      <c r="M24" t="n">
-        <v>680</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>32444</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" s="2" t="n">
-        <v>46132.85616898148</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2046167018303602898</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>2046167018303602898</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Excited to announce Mr Vijay Bains, Group Head of ESG &amp;amp; CSO at Emirates NBD, as a plenary speaker for Climate Finance 2.0 at the Global Sustainability &amp;amp; CSR Forum!
-With 20+ years in sustainable finance &amp;amp; leadership in ESG councils, Vijay brings unmatched expertise. Don’t miss it! https://t.co/ApxeVy3ABX</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>1776679207000</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2046167018303602898</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVyD6AaAAAN0zx.jpg', 'type': 'photo', 'id': '2046167017145892864'}]</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
-        </is>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" s="2" t="n">
-        <v>46132.58341435185</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://x.com/ArabiaCSR/status/2046167018303602898</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2046167018303602898</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2046118862736003268</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://x.com/ArabiaCSR/status/2046118862736003268</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
         <is>
           <t>Arabia CSR Network – Driving sustainability and responsible business across the MENA region.
 Through research, insights, and collaboration, we empower organisations to create meaningful CSR impact and shape a sustainable future.
@@ -2201,68 +2065,336 @@
 https://t.co/FXjp8HUpNf https://t.co/gpTUlQf79R</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>1776667726000</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2046118862736003268</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVGQ4CakAAF6bs.jpg', 'type': 'photo', 'id': '2046118861444124672'}]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
+        <v>46132.45053240741</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2046166030557614556</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2046166030557614556</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Emirates NBD extends fee waivers, 0% interest on credit card transfers for UAE customers
+https://t.co/sNYXzG1RYE</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1776678972000</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2046166030557614556</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1195570, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>2</v>
+      </c>
+      <c r="M25" t="n">
+        <v>52</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>8417</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
+        <v>46132.58069444444</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://x.com/khaleejtimes/status/2046166030557614556</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2046166030557614556</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2046265860453761085</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/Cricket_bazball/status/2046265860453761085</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>🚨 End of Mike Hesson 🚨
+- PCB has decided to sack Mike Hesson from the role of Pakistan team’s head coach and has decided to appoint Ottis Gibson as the new head coach for white-ball cricket. (Geo news) https://t.co/nvlKVuP4il</t>
+        </is>
+      </c>
       <c r="F26" t="n">
-        <v>1776667726000</v>
+        <v>1776702773000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2046118862736003268</t>
+          <t>2046265860453761085</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGVGQ4CakAAF6bs.jpg', 'type': 'photo', 'id': '2046118861444124672'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGXL9DraAAMigd2.jpg', 'type': 'photo', 'id': '2046265855529582595'}]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Arabia CSR Network', 'screenName': 'ArabiaCSR', 'followersCount': 3122, 'favouritesCount': 2298, 'friendsCount': 595, 'description': 'We are one of the very first multi-stakeholder platforms contributing to CSR &amp; sustainable development across the Arab world. #HappinessInSustainability'}</t>
+          <t>{'name': 'junaid', 'screenName': 'Cricket_bazball', 'followersCount': 145, 'favouritesCount': 174810, 'friendsCount': 258, 'description': 'Cricket • Stats • Not affiliated with anyone'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>824</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" s="2" t="n">
-        <v>46132.45053240741</v>
+        <v>46132.85616898148</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
+https://t.co/H82MnfRa04</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1776647481000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>46132.21621527777</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2046033950339166455</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2046443612029030400</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/Kyodonews_JBN/status/2046443612029030400</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Cognizant Propels AI Workforce Training with Cognizant Skillspring™: New Talent Transformation Platform Designed to Accelerate Clients' Workforce AI Readiness【Cognizant Technology Solutions Corporation】
+https://t.co/19NBuCknq7</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1776745152000</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2046443612029030400</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="n">
+        <v>46133.34666666666</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://x.com/ADIBTweets/status/2044321422282240384</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>قد تكون رسالة من “قريب”... لكنها احتيال. 
 أجب واربح 
@@ -2280,387 +2412,257 @@
 مسابقة_مصرف_أبوظبي_الإسلامي</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F29" t="n">
         <v>1776239183000</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HF7jf0ba0AAZFPu.jpg', 'type': 'photo', 'id': '2044321416661880832'}]</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137562, 'favouritesCount': 2888, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>392</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'name': 'ADIB Tweets', 'screenName': 'ADIBTweets', 'followersCount': 137559, 'favouritesCount': 2890, 'friendsCount': 104, 'description': 'حياكم في الحساب الرسمي لمصرف أبوظبي الإسلامي، شركة مساهمة عامة. Welcome to Abu Dhabi Islamic Bank Public Joint Stock Company official account'}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>396</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>69</v>
       </c>
-      <c r="M27" t="n">
-        <v>205</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>1429049</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" s="2" t="n">
+      <c r="M29" t="n">
+        <v>206</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1444459</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="2" t="n">
         <v>46127.49054398148</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>2045175695169732901</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2045175695169732901</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>لماذ البنك لايتحمل المسوؤلية إذا تم اختراق الحساب الشخصي وتم سحب مبلغ من المال بدون اي ادارة امن الحسابات او عن طريق ارسال OTP ويدعي انه تم التحويل بالفعل والبنك غير قادر علي فعل شيي و يجب ان يتحمل صاحب الحساب تكاليف اصدار بطاقة جديده و تحمل المبلغ المسحوب و كأن الحسابات الشخصية سبيل متاح لاي عملية إحتيال وعلي صاحب الحساب تحمل كامل المسؤلية والبنك الذي من المفترض هو المؤتمن علي هذا المال لايتحمل إي مسؤلية.. علي فكره انتم من البنوك التي لاتهتم بحمايه العميل لكن هناك بنوك مثل الامارات الإسلامي له كل الشكر والامتنان لانه حدث معي عمليه احتيال و خلال اسبوع تحمل البنك المبلغ وتم إيداعه في حسابي وتم اصدار بطاقة جديده بدون اي تكلفة.
 كل الشكر الي بنك الإمارات الإسلامي @emiratesislamic</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F30" t="n">
         <v>1776442857000</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J30" t="n">
         <v>3</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="P28" s="2" t="n">
+      <c r="P30" s="2" t="n">
         <v>46129.84788194444</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046125857643606493</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>@mohmd_moh مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F31" t="n">
         <v>1776669394000</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>2045175695169732901</t>
         </is>
       </c>
-      <c r="P29" s="2" t="n">
+      <c r="P31" s="2" t="n">
         <v>46132.46983796296</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>2046224051438526663</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>https://x.com/mohmd_moh/status/2046224051438526663</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>الشكر الجزيل لكم .  ليس لدي اي مشكلة حاليا أنا فقط ذكرت ماحدث معي للإشادة بكم علي سرعة الحل المقدم من طرفكم وسرعة استجابتكم وتحملكم المسؤلية تجاه العملاء .
 تعامل راقي وليس هدفكم المكسب فقط ولكن هدفكم الاول هو ارضاء العميل وهذا ذكاء منكم لأنكم بهذا الأسلوب سوف تكسبوا ثقة العملاء وبالتالي زيادة العملاء ويأتي المكسب مضاعف لاحقا . 
 كلمة حق تقال ان نهج الإمارات الإسلامي يستحق ان يقتدي به جميع البنوك.</t>
         </is>
       </c>
-      <c r="F30" t="n">
+      <c r="F32" t="n">
         <v>1776692805000</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>2044321422282240384</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>{'name': 'Mohamed Mohamed', 'screenName': 'mohmd_moh', 'followersCount': 195, 'favouritesCount': 6659, 'friendsCount': 1287, 'description': ''}</t>
         </is>
       </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>2046125857643606493</t>
         </is>
       </c>
-      <c r="P30" s="2" t="n">
+      <c r="P32" s="2" t="n">
         <v>46132.74079861111</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2046033950339166455</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2046033950339166455</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Emirates NBD、Dar Global向け2億5,000万米ドルのシンジケート・タームローンを実行し、世界的な成長と事業拡大を加速【Dar Global】
-https://t.co/H82MnfRa04</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1776647481000</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2046033950339166455</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" s="2" t="n">
-        <v>46132.21621527777</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046033950339166455</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2046033950339166455</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2046417468009447750</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/Kyodonews_JBN/status/2046417468009447750</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Thunes Launches Real-Time Payments into New Zealand【Thunes】
-https://t.co/quS53PS2oK</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>1776738919000</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>2046417468009447750</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>{'name': 'KYODONEWS JBN', 'screenName': 'Kyodonews_JBN', 'followersCount': 22, 'favouritesCount': 6, 'friendsCount': 2, 'description': '株式会社共同通信社 ジャパンビジネス広報センター'}</t>
-        </is>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" s="2" t="n">
-        <v>46133.27452546296</v>
       </c>
     </row>
     <row r="33">
@@ -2706,7 +2708,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523002, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522996, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2723,7 +2725,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
@@ -2772,7 +2774,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12525, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12526, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2843,7 +2845,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523002, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522996, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2860,7 +2862,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>228</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -2913,7 +2915,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12525, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
+          <t>{'name': 'Rakesh Mavath', 'screenName': 'RakeshMavath', 'followersCount': 367, 'favouritesCount': 12526, 'friendsCount': 3077, 'description': 'Running two startups: one guarantees your rent @takeem_ai, the other guarantees your dignity. Still waiting for my guaranteed 8 hours of sleep.'}</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2983,7 +2985,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 523002, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
+          <t>{'name': 'Aadit Sheth', 'screenName': 'aaditsh', 'followersCount': 522996, 'favouritesCount': 32071, 'friendsCount': 588, 'description': 'Co-founder, The Narrative Company. We help Fortune 500 C-suite engineer their biggest moments. Also write Neatprompts, 100K+ subscribers.'}</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -3000,7 +3002,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3073,7 +3075,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>69</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
@@ -3137,7 +3139,11 @@
       <c r="M39" t="n">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O39" t="inlineStr">
         <is>
           <t>2046215312949879234</t>
@@ -3206,7 +3212,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>56</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
@@ -3273,7 +3279,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>47</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3288,93 +3294,163 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2046106592232214645</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2046106592232214645</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+https://t.co/y7eSpGNdfk</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1776664801000</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2046106592232214645</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="2" t="n">
+        <v>46132.41667824074</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106592114856006</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>الاستثمار ليس معقداً، بل يحتاج إلى تخطيط ذكي.
 مع منصة الثروات الرقمية من الإمارات الإسلامي، يمكنك البدء بثقة عبر تجربة رقمية سلسة ومتوافقة مع الشريعة الإسلامية، صُممت لمساعدتك على:
 ✔️ الوصول إلى مجموعة واسعة من خيارات الاستثمار المتوافقة مع الشريعة الإسلامية</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F43" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="J43" t="n">
         <v>1</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" s="2" t="n">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="2" t="n">
         <v>46132.41667824074</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>2046106595369615672</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106595369615672</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>✔️ متابعة استثماراتك لحظة بلحظة
 ✔️ الحصول على إرشادات ذكية لدعم قراراتك المالية
@@ -3384,143 +3460,143 @@
 https://t.co/PgcKVmrsKA</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F44" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J44" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="P43" s="2" t="n">
+      <c r="P44" s="2" t="n">
         <v>46132.41667824074</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Investing doesn’t have to be complicated. It just has to be well-planned. With Emirates Islamic Digital Wealth, start investing confidently through a seamless, Shariah-compliant digital experience designed to help you:
 ✔️ Access a range of Shariah-compliant investment options</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F45" t="n">
         <v>1776664802000</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J45" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
         <is>
           <t>2046106595369615672</t>
         </is>
       </c>
-      <c r="P44" s="2" t="n">
+      <c r="P45" s="2" t="n">
         <v>46132.41668981482</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106598221746656</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>2046106600142725209</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046106600142725209</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>✔️ Track your investments in real time
 ✔️ Get smart insights to guide your decisions
@@ -3530,142 +3606,147 @@
 https://t.co/BZed26iXDD</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F46" t="n">
         <v>1776664802000</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>2046106592114856006</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
         <is>
           <t>2046106598221746656</t>
         </is>
       </c>
-      <c r="P45" s="2" t="n">
+      <c r="P46" s="2" t="n">
         <v>46132.41668981482</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2046106592232214645</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2046106592232214645</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046106592232214645</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Legitimate delivery companies don’t ask for extra payments through unsecured links.
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1776664801000</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2046106592232214645</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" s="2" t="n">
-        <v>46132.41667824074</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>https://x.com/emiratesislamic/status/2046215312949879234</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2046215315273486655</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary valet parking
+✈️ Complimentary airport lounge access
+💳 Metal Card with unique design
+And much more!
+📅 Offer valid till 31 May 2026
+https://t.co/Rcpj14D3rn</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1776690722000</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2046215312949879234</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>46132.71668981481</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>2046215063929749703</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215061186683019</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>حصرياً للإماراتيين. تقدم بطلب بطاقة إماراتي الائتمانية واحصل على مكافأة ترحيبية تصل الى 150,000 ميل من أميال سمارت مايلز بقيمة 1,500 درهم
 ✅ بدون رسوم عضوية سنوية
@@ -3673,68 +3754,68 @@
 🍔 خصم لغاية %50 على طلبات https://t.co/X996FmddPk</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>1776690662000</v>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGWdwRrWMAARNF5.jpg', 'type': 'photo', 'id': '2046215058414252032'}]</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="J48" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" s="2" t="n">
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" s="2" t="n">
         <v>46132.71599537037</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>2046215063929749703</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>2046215063929749703</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2046215063929749703</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>🚗 خدمة صف السيارات
 🛫 الدخول إلى صالات المطارات
@@ -3744,123 +3825,48 @@
 https://t.co/WJhVBxsiSW</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F49" t="n">
         <v>1776690662000</v>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
         <is>
           <t>2046215061186683019</t>
         </is>
       </c>
-      <c r="P48" s="2" t="n">
+      <c r="P49" s="2" t="n">
         <v>46132.71599537037</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2046215315273486655</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2046215315273486655</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046215315273486655</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>🚗 Complimentary valet parking
-✈️ Complimentary airport lounge access
-💳 Metal Card with unique design
-And much more!
-📅 Offer valid till 31 May 2026
-https://t.co/Rcpj14D3rn</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1776690722000</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>2046215312949879234</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>46132.71668981481</v>
       </c>
     </row>
     <row r="50">
@@ -4166,17 +4172,409 @@
           <t>2046200685037830312</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>1776746213445</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="2" t="n">
+        <v>46133.35895190972</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1776671148000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
         <is>
           <t>2045418169452695808</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="P55" s="2" t="n">
+        <v>46132.49013888889</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2046181231432495104</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046181231432495104</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>@emiratesislamic ردكم لم يحرك ساكن 
+ إنجاز المعاملة إلى اليوم صفر</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1776682596000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2046133214998114511</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>46132.62263888889</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2046200685037830312</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1776687234000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2046181231432495104</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>46132.67631944444</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
+شكرا من القلب مرة اخرى .</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1776584832000</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'name': 'اماراتى وافتخر', 'screenName': 'firstdiver4ever', 'followersCount': 934, 'favouritesCount': 4615, 'friendsCount': 1841, 'description': 'الله ثم الوطن ثم رئيس الدوله'}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="2" t="n">
+        <v>46131.49111111111</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2046164985571598514</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>@firstdiver4ever عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1776678723000</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2045771180469272971</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>46132.5778125</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2045418169452695808</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>https://x.com/alsajwani1/status/2045418169452695808</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>@emiratesislamic ولكن إلى اليوم لم يتم إنهاء الإجراء 
 مع الأسف لايوجد متابعة لطلب من الفرع
@@ -4186,702 +4584,213 @@
 متى ستنتهي المأساة؟ https://t.co/rFW4GdBPlY</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="F60" t="n">
         <v>1776500668000</v>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGLI-x3aUAA7Qsp.jpg', 'type': 'photo', 'id': '2045418161642819584'}]</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="J60" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
         <is>
           <t>2045035981535912006</t>
         </is>
       </c>
-      <c r="P54" s="2" t="n">
+      <c r="P60" s="2" t="n">
         <v>46130.51699074074</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2046200685037830312</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2046154630548402178</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://x.com/alsajwani1/status/2046154630548402178</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1776676254000</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2044702429464441285</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
         <is>
           <t>2046133214998114511</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046133214998114511</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="P61" s="2" t="n">
+        <v>46132.54923611111</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2046200645498130445</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
 رسالتك الخاصه.</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>1776671148000</v>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="F62" t="n">
+        <v>1776687225000</v>
+      </c>
+      <c r="G62" t="inlineStr">
         <is>
           <t>2044702429464441285</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J55" t="n">
-        <v>2</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>2045418169452695808</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>46132.49013888889</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2046200685037830312</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2046181231432495104</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://x.com/alsajwani1/status/2046181231432495104</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>@emiratesislamic ردكم لم يحرك ساكن 
- إنجاز المعاملة إلى اليوم صفر</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1776682596000</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2044702429464441285</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>2046133214998114511</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>46132.62263888889</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2046200685037830312</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2046200685037830312</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200685037830312</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1776687234000</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2044702429464441285</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2046181231432495104</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>46132.67631944444</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2046200645498130445</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
         <is>
           <t>2046154630548402178</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://x.com/alsajwani1/status/2046154630548402178</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أنا اريد إنهاء الإجراء ولا اريد رد كلمات</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1776676254000</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2044702429464441285</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2046133214998114511</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>46132.54923611111</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2046200645498130445</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2046200645498130445</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200645498130445</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1776687225000</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2044702429464441285</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2046154630548402178</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="n">
+      <c r="P62" s="2" t="n">
         <v>46132.67621527778</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2046200603928338537</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2046139112361717905</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://x.com/alsajwani1/status/2046139112361717905</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>@emiratesislamic 
-منذ أسبوع قدمت على طلب كسر الوديعة وتسديد قيمة القرض  من الوديعة فرعكم في 06 مول في الشارقة ومن أسبوع وموظفين الفرع لا علم لهم بالإجراء ويتواصلون عبر الإميل مع الإدارة لمعرفة الخطوات والإدارة لاحياة لمن تنادي
-هل تتوقعون من هذه الخدمة تدخلون في حلبة المنافسة</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1776672554000</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2046139112361717905</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>{'name': 'عبدالصاحب السجواني', 'screenName': 'alsajwani1', 'followersCount': 622, 'favouritesCount': 55, 'friendsCount': 2015, 'description': '\u200fمدرب ومستشار ريادة الأعمال  trainer and adviser Entrepreneurs'}</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" s="2" t="n">
-        <v>46132.50641203704</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2046200603928338537</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2046200603928338537</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046200603928338537</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>@alsajwani1 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1776687215000</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2046139112361717905</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2046139112361717905</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>46132.67609953704</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2046164985571598514</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://x.com/firstdiver4ever/status/2045771180469272971</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>@emiratesislamic أتقدم لجميع العاملين في مصرف الإمارات الإسلامي بجزيل الشكر والتقدير على جهودهم وعملهم الدؤوب الذي قاموا به ، حيث تم مشكلتي في زمن قياسي بالوقت الذي كان من المفروض ان يتم انجازه خلال سبعة ايام عمل .
-شكرا من القلب مرة اخرى .</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1776584832000</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>{'name': 'اماراتى وافتخر', 'screenName': 'firstdiver4ever', 'followersCount': 934, 'favouritesCount': 4614, 'friendsCount': 1841, 'description': 'الله ثم الوطن ثم رئيس الدوله'}</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" s="2" t="n">
-        <v>46131.49111111111</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2046164985571598514</t>
+          <t>2046125792552222931</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2046164985571598514</t>
+          <t>2045083218303402442</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046164985571598514</t>
+          <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
-        <is>
-          <t>@firstdiver4ever عزيزنا المتعامل، يسرنا أن نعرب لك عن جزيل شكرنا لهذه الكلمات الطيبة. كما أننا نقدر الوقت والجهد الذي بذلته لارسال هذا التقدير.</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1776678723000</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2045771180469272971</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>46132.5778125</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2046125792552222931</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083218303402442</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
         <is>
           <t>Get a chance to win a total of AED 1,000,000 in cash prizes.
 55 businesses will be winners. Will you be one of them?
@@ -4889,8 +4798,74 @@
 💸 Second cash prize: AED 100,000 each (2 winners) https://t.co/V52QeTxHT6</t>
         </is>
       </c>
+      <c r="F63" t="n">
+        <v>1776420809000</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGYWVTWUAEdJxW.jpg', 'type': 'photo', 'id': '2045083215245758465'}]</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>2</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" s="2" t="n">
+        <v>46129.59269675926</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2045520833406464393</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203/status/2045520833406464393</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>@emiratesislamic Before few days u stopped the otp which was protecting our account from any fake or steeling money then we star receiving  withdraw from our account without permission I think u stolen our money</t>
+        </is>
+      </c>
       <c r="F64" t="n">
-        <v>1776420809000</v>
+        <v>1776525145000</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -4899,16 +4874,16 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGGYWVTWUAEdJxW.jpg', 'type': 'photo', 'id': '2045083215245758465'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -4917,16 +4892,20 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
       <c r="P64" s="2" t="n">
-        <v>46129.59269675926</v>
+        <v>46130.80028935185</v>
       </c>
     </row>
     <row r="65">
@@ -4942,155 +4921,85 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>2046125792552222931</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1776669378000</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
           <t>2045520833406464393</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://x.com/gassann20203/status/2045520833406464393</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>@emiratesislamic Before few days u stopped the otp which was protecting our account from any fake or steeling money then we star receiving  withdraw from our account without permission I think u stolen our money</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1776525145000</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
       <c r="P65" s="2" t="n">
-        <v>46130.80028935185</v>
+        <v>46132.46965277778</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2046125792552222931</t>
+          <t>2046125833811615920</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2046125792552222931</t>
+          <t>2045083221952532551</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046125792552222931</t>
+          <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
-        <is>
-          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1776669378000</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2045520833406464393</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="n">
-        <v>46132.46965277778</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2046125833811615920</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2045083221952532551</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2045083221952532551</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
         <is>
           <t>💸 Monthly cash prizes: from AED 5,000 up to AED 25,000 (52 winners)
 Valid until 30 June 2026.
@@ -5098,8 +5007,78 @@
 https://t.co/FsXr2qXw7K</t>
         </is>
       </c>
+      <c r="F66" t="n">
+        <v>1776420810000</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="n">
+        <v>46129.59270833333</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2045521200613560345</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://x.com/gassann20203/status/2045521200613560345</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>@emiratesislamic It's fake prize from 15 year u have account with u never ever I trusted u and today after removing otp u start steel the money from account</t>
+        </is>
+      </c>
       <c r="F67" t="n">
-        <v>1776420810000</v>
+        <v>1776525232000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5113,7 +5092,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -5130,16 +5109,16 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2045083218303402442</t>
+          <t>2045083221952532551</t>
         </is>
       </c>
       <c r="P67" s="2" t="n">
-        <v>46129.59270833333</v>
+        <v>46130.8012962963</v>
       </c>
     </row>
     <row r="68">
@@ -5155,155 +5134,85 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
+          <t>2046125833811615920</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1776669388000</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2045083218303402442</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
           <t>2045521200613560345</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>https://x.com/gassann20203/status/2045521200613560345</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>@emiratesislamic It's fake prize from 15 year u have account with u never ever I trusted u and today after removing otp u start steel the money from account</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1776525232000</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>{'name': 'gazan', 'screenName': 'gassann20203', 'followersCount': 36, 'favouritesCount': 17, 'friendsCount': 35, 'description': 'Bloch chain expert'}</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>2045083221952532551</t>
-        </is>
-      </c>
       <c r="P68" s="2" t="n">
-        <v>46130.8012962963</v>
+        <v>46132.46976851852</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2046125833811615920</t>
+          <t>2046106592135831614</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2046125833811615920</t>
+          <t>2046106592135831614</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2046125833811615920</t>
+          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
-        <is>
-          <t>@gassann20203 Dear customer, we will connect with you on private messaging to serve you better</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1776669388000</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2045083218303402442</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>2045521200613560345</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>46132.46976851852</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2046106592135831614</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2046106592135831614</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046106592135831614</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
         <is>
           <t>شركات التوصيل الموثوقة لا تطلب دفعات إضافية عبر روابط غير آمنة.
 لا تقع في الفخ. احذر الاحتيال.
@@ -5311,43 +5220,43 @@
 https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
-      <c r="F70" t="n">
+      <c r="F69" t="n">
         <v>1776664801000</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>2046106592135831614</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18454, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" s="2" t="n">
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" s="2" t="n">
         <v>46132.41667824074</v>
       </c>
     </row>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P109"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,35 +517,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047809819265110291</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047809819265110291</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
+          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
+راتبك 80 الف درهم فيما فوق 
+رصيدك مينزلش عن 500 الف درهم 
+كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1776999913000</v>
+        <v>1777070882000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047809819265110291</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -555,7 +558,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'KARIM 🎩', 'screenName': 'karim_alharby', 'followersCount': 8056, 'favouritesCount': 31929, 'friendsCount': 441, 'description': 'Perfumer &amp; owner @ https://t.co/k1MCEdWq9g'}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -568,126 +571,130 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46136.29528935185</v>
+        <v>46137.11668981481</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047692986402643994</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047692986402643994</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1776999691000</v>
+        <v>1777043026000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047692986402643994</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGrd61bXUAAXvdG.jpg', 'type': 'photo', 'id': '2047692983437316096'}]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39175, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" s="2" t="n">
-        <v>46136.2927199074</v>
+        <v>46136.79428240741</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047692986402643994</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2047534633697308773</t>
+          <t>2046851288172810389</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047534633697308773</t>
+          <t>https://x.com/ENBDdeals/status/2046851288172810389</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>@abhiseksonusonu We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to livsocialconnect@liv.me and tag the case reference number #1001503 in the subject line.</t>
+          <t>باقة ورد لكل لحظة مميزة مع فلاورد 💐
+احصل على خصم 20% على تنسيقات الورود الأنيقة، حصريًا عبر تطبيق تستاهل.
+لمعرفة المزيد:
+https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777005272000</v>
+        <v>1776842350000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2046851288172810389</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGfgZjWWYAARtsk.jpg', 'type': 'photo', 'id': '2046851285253513216'}]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174340, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39175, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -700,65 +707,51 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2047511223839908158</t>
-        </is>
-      </c>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" s="2" t="n">
-        <v>46136.35731481481</v>
+        <v>46134.47164351852</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047432576336351289</t>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2047432576336351289</t>
+          <t>2047712208696614977</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2047432576336351289</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047432576336351289</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2042645533164999079</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>⎐كُـود⎐كوبِون⎐خـِصم⎐
-e1HcWgcAZOk
-⎐نون⎐
-⊵CBB54⊴
-⎐باث▬اند▬بودي⎐
-Af8p⊴
-⎐مفارش▬الحبيب⎐
-⊵sm29⊴
-⎐نمشي⎐
-⊵BLK13⊴
-^^^^
-ENbd</t>
+          <t>سيارة حلمك تقدر تتملكها
+جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1776980940000</v>
+        <v>1775839620000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2047432576336351289</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -768,11 +761,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Sarah', 'screenName': 'Sarah23386430', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 0, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -785,56 +778,46 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" s="2" t="n">
-        <v>46136.07569444444</v>
+        <v>46122.86597222222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047432576336351289</t>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2047432576336351289</t>
+          <t>2047712208696614977</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2047545552334676401</t>
+          <t>2047712208696614977</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/Sarah23386430/status/2047545552334676401</t>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>⎐كُـود⎐كوبِون⎐خـِصم⎐
-WAccobSuJbc
-⎐نون⎐
-⊵CBB54⊴
-⎐درعه⎐
-⊵Bf78⊴
-⎐سنبل⎐
-D46⊴
-⎐تُيموُ⎐
-⊵tea37⊴
-CdFw</t>
+          <t>@EmiratesNBD_KSA اود تقديم قرض كيف أتواصل معكم</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777007875000</v>
+        <v>1777047609000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2047545552334676401</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -844,11 +827,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Sarah', 'screenName': 'Sarah23386430', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 0, 'description': ''}</t>
+          <t>{'name': 'Barigi', 'screenName': 'Barigiin7m', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 103, 'description': ''}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -859,127 +842,138 @@
       <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2042645533164999079</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="n">
-        <v>46136.38744212963</v>
+        <v>46136.84732638889</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/jazz29210933/status/2047406903240565091</t>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2047406903240565091</t>
+          <t>2047712208696614977</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2047364023784529957</t>
+          <t>2047714668169339163</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047364023784529957</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047714668169339163</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>We've reported AED 8.2 billion in profit before tax for Q1, up 6% year on year, driven by solid growth, resilient margins and record non-funded income. 
-https://t.co/oVickxRJGZ
-حققنا 8.2 مليار درهم أرباحًا قبل الضريبة في الربع الأول، بزيادة 6% مقارنة بالفترة ذاتها من العام السابق، مدعومة بنمو قوي، وهوامش ربح مرنة، ونمو قياسي في الدخل غير الممول.
-https://t.co/q7H1c2ANA3</t>
+          <t>@Barigiin7m يرجي مراجعه التفاصيل وكيفيه التقديم من خلال هذا الرابط
+https://t.co/QV8KdPce6H</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1776964596000</v>
+        <v>1777048196000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2047364023784529957</t>
+          <t>2042645533164999079</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmyup-WMAA4jS3.png', 'type': 'video', 'id': '2047363884437094400'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174340, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2047712208696614977</t>
+        </is>
+      </c>
       <c r="P7" s="2" t="n">
-        <v>46135.88652777778</v>
+        <v>46136.85412037037</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/jazz29210933/status/2047406903240565091</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2047406903240565091</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2047406903240565091</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/jazz29210933/status/2047406903240565091</t>
+          <t>https://x.com/RakshtVaghasiya/status/2032450113100984492</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE https://t.co/HdUJGMSnZV</t>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1776974819000</v>
+        <v>1773408842000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2047364023784529957</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGnZuU4WUAEw5rB.jpg', 'type': 'photo', 'id': '2047406895518863361'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Aslam Khan', 'screenName': 'jazz29210933', 'followersCount': 293, 'favouritesCount': 168, 'friendsCount': 321, 'description': 'Free Palestine, Free USA from \nIsraHell Mafia, Anti MAGA, Anti Fat Pedophile Felon Trump, Anti blood sucking billionaires.                    \n💚 Green Party 💚'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -992,62 +986,56 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2047364023784529957</t>
-        </is>
-      </c>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>46136.00484953704</v>
+        <v>46094.73196759259</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/trk86380/status/2047367010003063072</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2047367010003063072</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2032452730443256247</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2046943784525599100</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2032452730443256247</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ليلة زواجك، مثل ما تتمنّى وأكثر 💍✨
-قدم على التمويل الشخصي وبهامش ربح تنافسي من #بنك_الامارات_دبي_الوطني 💙
-للتفاصيل:https://t.co/5oaojOqJ8v https://t.co/6LHBU3Yt0q</t>
+          <t>@RakshtVaghasiya We sincerely regret for the inconvenience To be able to assist further, we kindly request you to kindly share your registered mobile number through direct message, We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1776864403000</v>
+        <v>1773409466000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2046943757950480384/pu/img/mi4I-rg9GSJC7_ep.jpg', 'type': 'video', 'id': '2046943757950480384'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17361, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1057,53 +1045,57 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>942</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2032450113100984492</t>
+        </is>
+      </c>
       <c r="P9" s="2" t="n">
-        <v>46134.72688657408</v>
+        <v>46094.73918981481</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/trk86380/status/2047367010003063072</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2047367010003063072</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2047263845274484876</t>
+          <t>2032457337122791694</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/AzzamAlAseel/status/2047263845274484876</t>
+          <t>https://x.com/RakshtVaghasiya/status/2032457337122791694</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA كيف التواصل معكم بخصوص شراء مديونية؟</t>
+          <t>@EmiratesNBD_KSA 0561891252</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1776940711000</v>
+        <v>1773410565000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1113,7 +1105,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'عزّام الأصيــل', 'screenName': 'AzzamAlAseel', 'followersCount': 0, 'favouritesCount': 15, 'friendsCount': 70, 'description': 'لا ديمومة لشيء ..'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1130,50 +1122,50 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>45</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2032452730443256247</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46135.61008101852</v>
+        <v>46094.75190972222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/trk86380/status/2047367010003063072</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2047367010003063072</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2047267674904826221</t>
+          <t>2032458133151342720</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047267674904826221</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2032458133151342720</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@AzzamAlAseel مرحبا, يرجى إرسال رقم هاتفك و رقم الهوية عبر الخاص ليمكننا مساعدتك, شكرا</t>
+          <t>@RakshtVaghasiya We have shared your details with the concerned team, and they will contact you shortly.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1776941624000</v>
+        <v>1773410754000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1183,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17361, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1193,57 +1185,57 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>115</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2047263845274484876</t>
+          <t>2032457337122791694</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46135.62064814815</v>
+        <v>46094.75409722222</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/trk86380/status/2047367010003063072</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2047367010003063072</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2047367010003063072</t>
+          <t>2035964859116879927</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/trk86380/status/2047367010003063072</t>
+          <t>https://x.com/RakshtVaghasiya/status/2035964859116879927</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA @AzzamAlAseel ردو خاص</t>
+          <t>@EmiratesNBD_KSA No one contacted yet. This is not acceptable at all from brand like Emirates NBD. Extremely disappointed.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1776965308000</v>
+        <v>1774246823000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1253,7 +1245,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'تركي القرشي', 'screenName': 'trk86380', 'followersCount': 0, 'favouritesCount': 660, 'friendsCount': 313, 'description': ''}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1270,50 +1262,50 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>71</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2047267674904826221</t>
+          <t>2032458133151342720</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46135.89476851852</v>
+        <v>46104.43082175926</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/trk86380/status/2047367010003063072</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2047367010003063072</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2047368892855578654</t>
+          <t>2035976151764549748</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047368892855578654</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@trk86380 مرحبا شكرا لتواصلك معنا تم الرد عبر رسائل الخاص</t>
+          <t>@RakshtVaghasiya Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1776965756000</v>
+        <v>1774249515000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2046943784525599100</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1323,11 +1315,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17361, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1340,50 +1332,51 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2047367010003063072</t>
+          <t>2035964859116879927</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46135.8999537037</v>
+        <v>46104.46197916667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/ARbinQA/status/2047337655638073470</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2047337655638073470</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2047270522849812926</t>
+          <t>2038625938133471268</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/business/status/2047270522849812926</t>
+          <t>https://x.com/RakshtVaghasiya/status/2038625938133471268</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Emirates President Tim Clark struck a defiant tone in his first media appearance since the war in Iran forced the world’s largest airline to curtain operations, saying demand is strong enough to rebound https://t.co/pDJ8RYrmJD</t>
+          <t>@EmiratesNBD_KSA Dispute request #22407819581 was raised on 23rd March'26 and After that I received call from NBD representative &amp;amp; I explained my dispute. But after that no communication or response received from NBD.
+I am really frustrated by response from such reputed bank.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1776942303000</v>
+        <v>1774881274000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2047270522849812926</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1393,137 +1386,137 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'Bloomberg', 'screenName': 'business', 'followersCount': 10010588, 'favouritesCount': 5518, 'friendsCount': 110, 'description': 'The first word in business news | Watch Live: https://t.co/nHEpHOAfg3 | Newsletters: https://t.co/nWaCxHTiks | Podcasts: https://t.co/096e9xMJF7'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>19890</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2035976151764549748</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="n">
-        <v>46135.62850694444</v>
+        <v>46111.77400462963</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/ARbinQA/status/2047337655638073470</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2047337655638073470</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2047337655638073470</t>
+          <t>2038628104541774071</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/ARbinQA/status/2047337655638073470</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038628104541774071</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@business #Redundancy #COVID @emirates @EmiratesSupport @EmiratesNBD_AE @DXB @DXBMediaOffice @HamdanMohammed @MohamedBinZayed @HHShkMohd @MOHRE_UAE @AbuDhabi_ADM @abudhabitv @abudhabitv @khaleejtimes @gulf_news @OPECSecretariat @OPECnews @OPECFundAr @GCC #GCC @mofauae Still awaitingsupport https://t.co/kYgfHEitVf</t>
+          <t>@RakshtVaghasiya Hi Rakshit, we have already escalated the matter and our team will contact you as soon as possible.</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1776958309000</v>
+        <v>1774881790000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2047270522849812926</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmavuWXsAAQepw.jpg', 'type': 'photo', 'id': '2047337650302988288'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmavueWsAAzCO4.jpg', 'type': 'photo', 'id': '2047337650336477184'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'A R', 'screenName': 'ARbinQA', 'followersCount': 2, 'favouritesCount': 458, 'friendsCount': 0, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2047270522849812926</t>
+          <t>2038625938133471268</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46135.81376157407</v>
+        <v>46111.77997685185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345158077702559</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2041172230642471397</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345158077702559</t>
+          <t>https://x.com/RakshtVaghasiya/status/2041172230642471397</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Банки ОАЭ в 2026: где реально открыть счёт 🏦
-RAKBANK и Mashreq — чаще открывают малому бизнесу; 
-Emirates NBD — при наличии офиса и оборотов; 
-Wio — быстро, но с лимитами.
-Частые причины отказа: крипто, нет сайта, размытый бизнес, рисковые юрисдикции.</t>
+          <t>@EmiratesNBD_KSA This is really frustrating from NBD. Nothing has progressed. No meaningful action yet ... Really disappointed from Emirates NBD</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1776960098000</v>
+        <v>1775488357000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1533,7 +1526,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Andris Kaushelis', 'screenName': 'AndrisKaushelis', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 2, 'description': '➡ Регистрация и сопровождение бизнеса в ОАЭ\n➡ Emirates ID\n➡ Индивидуальный подход\nРуководитель офиса @mirsatori в ОАЭ\nЗапись на консультацию ⬇'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1550,47 +1543,50 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2038628104541774071</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="n">
-        <v>46135.83446759259</v>
+        <v>46118.80042824074</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345158077702559</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2047345180924137800</t>
+          <t>2041173077455667467</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345180924137800</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2041173077455667467</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Банк оценивает риски, а не только компанию.
-Как вы оцениваете свои шансы на открытие счёта в ОАЭ сейчас?</t>
+          <t>@RakshtVaghasiya Hello, a follow-up on your request has been sent, and you will be contacted as soon as possible.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1776960103000</v>
+        <v>1775488559000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1600,11 +1596,11 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Andris Kaushelis', 'screenName': 'AndrisKaushelis', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 2, 'description': '➡ Регистрация и сопровождение бизнеса в ОАЭ\n➡ Emirates ID\n➡ Индивидуальный подход\nРуководитель офиса @mirsatori в ОАЭ\nЗапись на консультацию ⬇'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1617,51 +1613,50 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>92</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2041172230642471397</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46135.83452546296</v>
+        <v>46118.80276620371</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2047345158077702559</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2047345158077702559</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2046982948507767088</t>
+          <t>2046954276312777137</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/AndrisKaushelis/status/2046982948507767088</t>
+          <t>https://x.com/RakshtVaghasiya/status/2046954276312777137</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Travel ban в ОАЭ: долг может остановить вас в аэропорту ✈️
-Даже задолженность от 15 000 AED может привести к запрету на выезд: кредитор подаёт в суд, и данные попадают в систему без уведомлений.</t>
+          <t>@EmiratesNBD_KSA Still no one contacted me.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1776873740000</v>
+        <v>1776866904000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2046982948507767088</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1671,7 +1666,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Andris Kaushelis', 'screenName': 'AndrisKaushelis', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 2, 'description': '➡ Регистрация и сопровождение бизнеса в ОАЭ\n➡ Emirates ID\n➡ Индивидуальный подход\nРуководитель офиса @mirsatori в ОАЭ\nЗапись на консультацию ⬇'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1688,50 +1683,50 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2041173077455667467</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="n">
-        <v>46134.83495370371</v>
+        <v>46134.75583333334</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/asu_dixit/status/2047342848086094191</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2047342848086094191</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2047342848086094191</t>
+          <t>2046956528205259220</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/asu_dixit/status/2047342848086094191</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2046956528205259220</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hooow long we r taking for an disinvestment ?4 years!!
-Even @115, Private bank PE ⬆️180/220. 
-Priceto converge 90-135 -&amp;gt;115/120
-Boost for the 35% remaining stake + 10lakh cr sentiment ⏫. 
-@PMOIndia @nsitharaman @SecyDIPAM @DasShaktikanta @EmiratesNBD_AE @nsitharamanoffc</t>
+          <t>@RakshtVaghasiya Hello Rakshit, thanks for writing to us please note that a follow-up request has been sent, and you will be contacted as soon as possible.</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1776959547000</v>
+        <v>1776867441000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2047342848086094191</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1741,11 +1736,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'Asutosh Dixit', 'screenName': 'asu_dixit', 'followersCount': 378, 'favouritesCount': 6859, 'friendsCount': 1475, 'description': 'Software Engineer 💻 and interested in travel ✈️, people👨🏻\u200d🦰, books📚, food🍛, investment 📈 ,spirituality. ❤️ beats fr India 🇮🇳 and views🗣 r personal.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1758,51 +1753,50 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2046954276312777137</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="n">
-        <v>46135.82809027778</v>
+        <v>46134.76204861111</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/asu_dixit/status/2047342848086094191</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2047342848086094191</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2046795354205823361</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/asu_dixit/status/2046795354205823361</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Dear @idco_odisha @MohanMOdisha @CMO_Odisha @SampadSwainBJP 
-Congratulations! 
-We must actively support AMNS new iron ore mines and make them production ready
-Help put slurry pipes. 
-Help taking ores - refine in other states.
-Acquire land @Kendrapada site. It can be useful.</t>
+          <t>@EmiratesNBD_KSA Same reply every time but no concrete solutions. Just a pathetic approach..</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1776829014000</v>
+        <v>1777050832000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2046795354205823361</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1812,11 +1806,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Asutosh Dixit', 'screenName': 'asu_dixit', 'followersCount': 378, 'favouritesCount': 6859, 'friendsCount': 1475, 'description': 'Software Engineer 💻 and interested in travel ✈️, people👨🏻\u200d🦰, books📚, food🍛, investment 📈 ,spirituality. ❤️ beats fr India 🇮🇳 and views🗣 r personal.'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1829,58 +1823,60 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2046956528205259220</t>
+        </is>
+      </c>
       <c r="P20" s="2" t="n">
-        <v>46134.31729166667</v>
+        <v>46136.88462962963</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047322098696163735</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2047322098696163735</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2047322098696163735</t>
+          <t>2047728007276544227</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047322098696163735</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047728007276544227</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Emirates NBD, in line with the resilient operating environment in the UAE, reported a profit before tax of AED8.2 billion ($2.23 billion) for the first quarter of 2026.
-Read more on https://t.co/Nn6AqaDch6
-#ABCNews #Profit #Growth #StrategicInvestment #UAE https://t.co/Q0uOolHeF2</t>
+          <t>@RakshtVaghasiya Thanks for writing to us, we have already escalated the matter and our team will contact you as soon as possible.</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1776954600000</v>
+        <v>1777051376000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2047322098696163735</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlvjm4bcAAWkyh.jpg', 'type': 'photo', 'id': '2047290163139932160'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1897,180 +1893,188 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2047725724354633861</t>
+        </is>
+      </c>
       <c r="P21" s="2" t="n">
-        <v>46135.77083333334</v>
+        <v>46136.89092592592</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047322098696163735</t>
+          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2047322098696163735</t>
+          <t>2047692228684878061</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2047329655724581037</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047329655724581037</t>
+          <t>https://x.com/AbdulrhmanRF/status/2046820251229159879</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>DMCC has announced the launch of One Uptown Place and Two Uptown Place, two new premium commercial towers within its flagship Uptown Dubai district, representing the latest milestone in the district’s expansion.
-Read more on https://t.co/K2EMlFIFzy
-#ABCNews #CommercialTowers https://t.co/zPgztC8nQE</t>
+          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
+ @EmiratesNBD_KSA</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1776956402000</v>
+        <v>1776834950000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2047329655724581037</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlx9DGacAA7ZCb.jpg', 'type': 'photo', 'id': '2047292799234764800'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
+          <t>{'name': 'Abed', 'screenName': 'AbdulrhmanRF', 'followersCount': 2023, 'favouritesCount': 19524, 'friendsCount': 1152, 'description': 'A simple guy who likes محمد عبده /Tech/TV/Movies/روجر فيدرير Roger Federer // الهلال 💙 Al Hilal SFC'}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>305</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" s="2" t="n">
-        <v>46135.79168981482</v>
+        <v>46134.38599537037</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/EMD0958/status/2047327801745842508</t>
+          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2047327801745842508</t>
+          <t>2047692228684878061</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2047327620354994312</t>
+          <t>2046821489882624075</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/Forsan_UAE/status/2047327620354994312</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2046821489882624075</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>بدخل يصل لـ14.4 مليار درهم بنمو 13%، وودائع بلغت 44 مليار درهم بزيادة قدرها 6%.. #بنك_الإمارات_دبي_الوطني يواصل تألقه بنتائج قياسية خلال الربع الأول من 2026 https://t.co/RGczynJXtC</t>
+          <t>@AbdulrhmanRF مرحبا, تم الرد على الخاص.</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1776955916000</v>
+        <v>1776835245000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2047327620354994312</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmRndRaYAARh_E.jpg', 'type': 'photo', 'id': '2047327612675186688'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'فرسان الإمارات', 'screenName': 'Forsan_UAE', 'followersCount': 625430, 'favouritesCount': 302, 'friendsCount': 80, 'description': 'الدفاع عن الوطن واجب مقدس، وشرف تعشقه قلوب أبناء زايد'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>780</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2046820251229159879</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="n">
-        <v>46135.78606481481</v>
+        <v>46134.38940972222</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/EMD0958/status/2047327801745842508</t>
+          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2047327801745842508</t>
+          <t>2047692228684878061</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2047327801745842508</t>
+          <t>2047663017521774593</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/EMD0958/status/2047327801745842508</t>
+          <t>https://x.com/buib102/status/2047663017521774593</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>@Forsan_UAE @EmiratesNBD_AE https://t.co/4ASu117jo9</t>
+          <t>@EmiratesNBD_KSA @AbdulrhmanRF حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
+متى توصل الحواله ؟</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1776955960000</v>
+        <v>1777035881000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2047327620354994312</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2080,11 +2084,11 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'EMDHoresman', 'screenName': 'EMD0958', 'followersCount': 183, 'favouritesCount': 188, 'friendsCount': 3185, 'description': ''}</t>
+          <t>{'name': 'kal', 'screenName': 'buib102', 'followersCount': 3, 'favouritesCount': 131, 'friendsCount': 50, 'description': 'ا'}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2097,128 +2101,130 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2047327620354994312</t>
+          <t>2046821489882624075</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46135.78657407407</v>
+        <v>46136.71158564815</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/Forbes_MENA_/status/2047302322716340460</t>
+          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2047302322716340460</t>
+          <t>2047692228684878061</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2047302322716340460</t>
+          <t>2047665248799195623</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/Forbes_MENA_/status/2047302322716340460</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047665248799195623</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>FAB, Emirates NBD, and ADCB have posted combined Q1 2026 net profits of $4 billion, reaffirming the UAE banking sector’s strength despite persistent regional headwinds. Here’s how the nation’s top 3 banks navigated a turbulent quarter.
-#Forbes 
-For More Details: https://t.co/6pj7bhaQHT</t>
+          <t>@buib102 مرحباً، شكرا لتواصلك معنا. يُرجى إرسال التفاصيل الخاصه بطلبك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1776949885000</v>
+        <v>1777036413000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2047302322716340460</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl6nC7WsAADnIL.jpg', 'type': 'photo', 'id': '2047302316835909632'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Forbes Middle East', 'screenName': 'Forbes_MENA_', 'followersCount': 19664, 'favouritesCount': 182, 'friendsCount': 6, 'description': "The Homepage of The World's Business Leaders.\nFollow @ForbesME for breaking news and latest updates in Arabic."}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2047663017521774593</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="n">
-        <v>46135.71626157407</v>
+        <v>46136.71774305555</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/Forbes_MENA_/status/2047302322716340460</t>
+          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2047302322716340460</t>
+          <t>2047692228684878061</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2047331247572001247</t>
+          <t>2047671039249846621</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/Forbes_MENA_/status/2047331247572001247</t>
+          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>At the Abu Dhabi Global Entrepreneurship Festival, Nader Nassar, Founder and CEO of Hlthera and Board Member of the Forbes Middle East Youth Council, says the event is one of the most significant initiatives for entrepreneurs in the UAE, bringing together founders, accelerator programs, and knowledge-sharing opportunities in one place.</t>
+          <t>@EmiratesNBD_KSA عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1776956781000</v>
+        <v>1777037794000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2047331247572001247</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmTrsYXMAAJ5gB.jpg', 'type': 'video', 'id': '2047325722478256128'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Forbes Middle East', 'screenName': 'Forbes_MENA_', 'followersCount': 19664, 'favouritesCount': 182, 'friendsCount': 6, 'description': "The Homepage of The World's Business Leaders.\nFollow @ForbesME for breaking news and latest updates in Arabic."}</t>
+          <t>{'name': 'رغد الحربي', 'screenName': 'i_rh9590', 'followersCount': 113, 'favouritesCount': 1989, 'friendsCount': 1338, 'description': '-'}</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -2228,72 +2234,71 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2047665248799195623</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="n">
-        <v>46135.79607638889</v>
+        <v>46136.73372685185</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/CyberxGlobal/status/2047320011086389312</t>
+          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2047320011086389312</t>
+          <t>2047692228684878061</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2047320011086389312</t>
+          <t>2047673420695920899</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/CyberxGlobal/status/2047320011086389312</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047673420695920899</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Speaker Announcement – CyberX Egypt 2026
-We’re excited to welcome Hisham Mohamed Aly, Chief Information Security Officer at Emirates NBD Egypt as a featured speaker at CyberX Egypt 2026.
-🗓 18 May 2026
-📍New Cairo, Egypt
- Apply now: https://t.co/bFrDYoxMSe
-#CyberXEgypt https://t.co/gIEqC0W76B</t>
+          <t>@i_rh9590 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1776954102000</v>
+        <v>1777038362000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2047320011086389312</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmKL3naEAAKNd4.jpg', 'type': 'photo', 'id': '2047319442129031168'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'CyberxGlobal', 'screenName': 'CyberxGlobal', 'followersCount': 49, 'favouritesCount': 61, 'friendsCount': 15, 'description': 'CYBERX GLOBAL is a dedicated series for Cyber Security, OT &amp; ICS Conferences and Seminars in Middle East, Africa, India and South East Asia.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2306,65 +2311,64 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2047671039249846621</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="n">
-        <v>46135.76506944445</v>
+        <v>46136.74030092593</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/CyberxGlobal/status/2047320011086389312</t>
+          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2047320011086389312</t>
+          <t>2047692228684878061</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2047318648508035212</t>
+          <t>2047692228684878061</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/CyberxGlobal/status/2047318648508035212</t>
+          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Media Partner Announcement - CyberX Indonesia 2026    
-We are proud to announce Gazet International Magazine as a media partner for CyberX Indonesia 2026
-🗓 28 April 2026 
-📍 Fairmont Hotel, Jakarta, Indonesia    
-Secure your spot now: https://t.co/veR16zImuE
-#CyberXIndonesia https://t.co/ghuwCuRQz7</t>
+          <t>@EmiratesNBD_KSA الووووو .</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1776953777000</v>
+        <v>1777042846000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2047318648508035212</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmIuXabIAA5OE6.jpg', 'type': 'photo', 'id': '2047317835756806144'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'CyberxGlobal', 'screenName': 'CyberxGlobal', 'followersCount': 49, 'favouritesCount': 61, 'friendsCount': 15, 'description': 'CYBERX GLOBAL is a dedicated series for Cyber Security, OT &amp; ICS Conferences and Seminars in Middle East, Africa, India and South East Asia.'}</t>
+          <t>{'name': 'forty', 'screenName': 'fortyxxl88', 'followersCount': 1, 'favouritesCount': 43, 'friendsCount': 50, 'description': ''}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2373,50 +2377,54 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2047673420695920899</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="n">
-        <v>46135.76130787037</v>
+        <v>46136.79219907407</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2047306816560705775</t>
+          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2047306816560705775</t>
+          <t>2047692228684878061</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2047306816560705775</t>
+          <t>2047692437317988536</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2047306816560705775</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047692437317988536</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Emirates NBD Q1 profit rises 3%, beats estimates https://t.co/ZnaITHVNDR</t>
+          <t>@fortyxxl88 مرحبا شكرا لتواصلك معنا . يُرجى إرسال التفاصيل الخاصه بطلبك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1776950956000</v>
+        <v>1777042895000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2047306816560705775</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2426,7 +2434,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12442, 'favouritesCount': 443407, 'friendsCount': 8658, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2443,46 +2451,50 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2047692228684878061</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n">
-        <v>46135.72865740741</v>
+        <v>46136.7927662037</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2047306816560705775</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2047306816560705775</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2047469626863358363</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2047469626863358363</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Iraq’s “Man in the Shadows”: Intelligence Chief Emerges as Consensus PM Candidate | Search 4 Dinar https://t.co/qRHYc2we70</t>
+          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1776989773000</v>
+        <v>1777042618000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2047469626863358363</t>
+          <t>2046820251229159879</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2492,7 +2504,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12442, 'favouritesCount': 443407, 'friendsCount': 8658, 'description': ''}</t>
+          <t>{'name': 'forty', 'screenName': 'fortyxxl88', 'followersCount': 1, 'favouritesCount': 43, 'friendsCount': 50, 'description': ''}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2505,63 +2517,64 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2047673420695920899</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="n">
-        <v>46136.17792824074</v>
+        <v>46136.78956018519</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/hspropertydubai/status/2047296929651130678</t>
+          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2047296929651130678</t>
+          <t>2047678055070757117</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2047296929651130678</t>
+          <t>2047678055070757117</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/hspropertydubai/status/2047296929651130678</t>
+          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Want to invest in Dubai off-plan projects with less cash? 🔑
-Thanks to Emirates NBD, Emaar, Nakheel, and Dubai Holding, you can now use a mortgage during construction.
-Plan your future more clearly and invest smartly.
-#InvestInDubai #Emaar #DubaiRealEstate #OffPlanInvesting https://t.co/jepcUuYehh</t>
+          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1776948599000</v>
+        <v>1777039467000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2047296929651130678</t>
+          <t>2047678055070757117</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047296827842813952/img/8FjyJ1uk5TJBoqYQ.jpg', 'type': 'video', 'id': '2047296827842813952'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'H&amp;S Real Estate', 'screenName': 'hspropertydubai', 'followersCount': 1093, 'favouritesCount': 3, 'friendsCount': 236, 'description': 'H&amp;S Real Estate is the No. 1 firm in Dubai for off-plan real estate investment.\n\n+971 526 902 884'}</t>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2578,64 +2591,62 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" s="2" t="n">
-        <v>46135.70137731481</v>
+        <v>46136.75309027778</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/hspropertydubai/status/2047296929651130678</t>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2047296929651130678</t>
+          <t>2047666831612149831</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2046926039549702580</t>
+          <t>2047620964712693908</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/hspropertydubai/status/2046926039549702580</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047620964712693908</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>⸻
-“If your money isn’t growing, you’re losing purchasing power.” 💡
-In Dubai, no income tax, no capital gains tax, and active capital. Yields 6%-12%, off-plan appreciation 15%-40%.
-Global capital asks, “Where does my money perform better?” The answer: Dubai.
-#InvestInDubai https://t.co/vgNlslTiHR</t>
+          <t>You get an unexpected payment request. What do you do?
+Stay Safe, Stay Vigilant. #UnitedAgainstFraud
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1776860172000</v>
+        <v>1777025855000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2046926039549702580</t>
+          <t>2047620964712693908</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2046925950642946048/img/x2C_wP0TfnP7gCF0.jpg', 'type': 'video', 'id': '2046925950642946048'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'H&amp;S Real Estate', 'screenName': 'hspropertydubai', 'followersCount': 1093, 'favouritesCount': 3, 'friendsCount': 236, 'description': 'H&amp;S Real Estate is the No. 1 firm in Dubai for off-plan real estate investment.\n\n+971 526 902 884'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2648,46 +2659,46 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>314</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" s="2" t="n">
-        <v>46134.67791666667</v>
+        <v>46136.59554398148</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/ArgaamPlus/status/2047291417643340140</t>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2047291417643340140</t>
+          <t>2047666831612149831</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2047291417643340140</t>
+          <t>2047666831612149831</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/ArgaamPlus/status/2047291417643340140</t>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Emirates NBD Q1 2026 up 3% YoY to AED 6.40 billion</t>
+          <t>@EmiratesNBD_AE Is this biggest joke ?</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1776947285000</v>
+        <v>1777036791000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2047291417643340140</t>
+          <t>2047620964712693908</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2697,11 +2708,11 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Argaam Plus', 'screenName': 'ArgaamPlus', 'followersCount': 29012, 'favouritesCount': 19, 'friendsCount': 7, 'description': "Market data, analysis, and commentary from Saudi Arabia's leading business news provider. \n\nArabic Account: @Argaam"}</t>
+          <t>{'name': 'Ayesha.amala', 'screenName': 'AmalaAyesha', 'followersCount': 39, 'favouritesCount': 20, 'friendsCount': 135, 'description': ''}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2710,60 +2721,65 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2047620964712693908</t>
+        </is>
+      </c>
       <c r="P33" s="2" t="n">
-        <v>46135.68616898148</v>
+        <v>46136.72211805556</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney/status/2047271389288083759</t>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2047271389288083759</t>
+          <t>2047666831612149831</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2047271389288083759</t>
+          <t>2047668962998034824</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney/status/2047271389288083759</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047668962998034824</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>حقق Emirates NBD أرباحًا قبل الضريبة 8.2 مليار درهم (+6%) في الربع الأول 2026، مع إيرادات 14.4 مليار وأصول تتجاوز 1.2 تريليون. النمو مدعوم بالتوسع والرقمنة، مع أداء قوي أيضًا لـ Emirates Islamic. https://t.co/JrTGPuxva9</t>
+          <t>@AmalaAyesha Hi Ayesha, Please find the below link for more details. Thanks- Zubair 
+https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1776942510000</v>
+        <v>1777037299000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2047271389288083759</t>
+          <t>2047620964712693908</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGled5zXoAEVx_z.jpg', 'type': 'photo', 'id': '2047271373442097153'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'رؤيا مال وأعمال', 'screenName': 'royamoney', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'نرصد سوق المال والأعمال ببساطة.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2780,57 +2796,60 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2047666831612149831</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="n">
-        <v>46135.63090277778</v>
+        <v>46136.72799768519</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney/status/2047271389288083759</t>
+          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2047271389288083759</t>
+          <t>2047647028012876081</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2047295679458906286</t>
+          <t>2047647028012876081</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/royamoney/status/2047295679458906286</t>
+          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>أعلن نقيب أصحاب محلات الحلي والمجوهرات، ربحي علان، عن قرار النقابة بوقف نشر التسعيرة اليومية الموحدة لمصاغات الذهب من عيار 14 اعتبارا من يوم السبت، وذلك بعد مرور قرابة عام على طرحه في الأسواق الأردنية.
-تفاصيل: https://t.co/1sqjpxockw https://t.co/UM0sp4YPt0</t>
+          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting https://t.co/w2yAiSn6ht or the App https://t.co/ps8Dxgg3Bm</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1776948301000</v>
+        <v>1777032069000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2047295679458906286</t>
+          <t>2047647028012876081</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl0hkfXsAA-dTZ.jpg', 'type': 'photo', 'id': '2047295625696358400'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq0Hv-XgAII1HC.jpg', 'type': 'photo', 'id': '2047647025823449090'}]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'رؤيا مال وأعمال', 'screenName': 'royamoney', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'نرصد سوق المال والأعمال ببساطة.'}</t>
+          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18752, 'favouritesCount': 2497, 'friendsCount': 1471, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2847,57 +2866,56 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" s="2" t="n">
-        <v>46135.69792824074</v>
+        <v>46136.66746527778</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047274925501673582</t>
+          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2047274925501673582</t>
+          <t>2047647028012876081</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2047274925501673582</t>
+          <t>2047616654280953919</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047274925501673582</t>
+          <t>https://x.com/NovoCinemas/status/2047616654280953919</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>يختصر عليك وينجز أمورك بضغطة زر
-نفذ عملياتك البنكية اليومية بكل سهولة وأمان من تطبيق ENBD X📱💙 https://t.co/jJAfEGoiC2</t>
+          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. Watch it now at Novo Cinemas. Book on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/ycxZoinbXq</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1776943353000</v>
+        <v>1777024827000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2047274925501673582</t>
+          <t>2047616654280953919</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlhsgUXsAAU8uO.jpg', 'type': 'photo', 'id': '2047274922834112512'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqYfrJWAAAgCku.jpg', 'type': 'photo', 'id': '2047616650518593536'}]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17361, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18752, 'favouritesCount': 2497, 'friendsCount': 1471, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2910,66 +2928,65 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" s="2" t="n">
-        <v>46135.64065972222</v>
+        <v>46136.58364583334</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/TradeArabia/status/2047275289659539631</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2047275289659539631</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2047275289659539631</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/TradeArabia/status/2047275289659539631</t>
+          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Emirates NBD reported a profit before tax of AED8.2 billion ($2.23 billion) for the first quarter of 2026, up 6% yoy, driven by strong balance sheet growth, resilient margins and record non-funded income growth.
-Read more on https://t.co/SIUcQ2s7tw
-#Tradearabia #emirates #finance https://t.co/48rJKsVpNb</t>
+          <t>Very disappointed with @ENBDdeals 
+I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1776943440000</v>
+        <v>1777027909000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2047275289659539631</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlGt4Ra4AEuMpi.jpg', 'type': 'photo', 'id': '2047245259630108673'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'Trade Arabia', 'screenName': 'TradeArabia', 'followersCount': 16376, 'favouritesCount': 199, 'friendsCount': 48, 'description': "Trade Arabia is the leading portal for business information and trade news covering the Middle East. 'Like' us on \nhttps://t.co/PrFoU4Ciw4"}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -2982,130 +2999,130 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" s="2" t="n">
-        <v>46135.64166666667</v>
+        <v>46136.61931712963</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/TradeArabia/status/2047275289659539631</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2047275289659539631</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2047305740419826118</t>
+          <t>2047629581159477750</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/TradeArabia/status/2047305740419826118</t>
+          <t>https://x.com/ren_fernz/status/2047629581159477750</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gulf women continue to strengthen their presence in the development journey of GCC countries, supported by a young population base and growing participation in the labour market
-Read more on https://t.co/xjqrqS1PA5
-#Tradearabia #Gulf #womenempowerment https://t.co/BJl4kbM156</t>
+          <t>I tried to contact in Jan and Feb on WhatsApp but was unable to contact with customer service in Feb it was due to ramdan . Last I came back to pay the bills and I saw the outstanding balance is again more . I saw the transaction history there is nothing but when I contact CS</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1776950700000</v>
+        <v>1777027909000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2047305740419826118</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlHAAXbwAAlAZC.jpg', 'type': 'photo', 'id': '2047245571040460800'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'Trade Arabia', 'screenName': 'TradeArabia', 'followersCount': 16376, 'favouritesCount': 199, 'friendsCount': 48, 'description': "Trade Arabia is the leading portal for business information and trade news covering the Middle East. 'Like' us on \nhttps://t.co/PrFoU4Ciw4"}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2047629578990936518</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="n">
-        <v>46135.72569444445</v>
+        <v>46136.61931712963</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/GulfIndustryOn/status/2047269260817465622</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2047269260817465622</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2047269260817465622</t>
+          <t>2047629583571186141</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/GulfIndustryOn/status/2047269260817465622</t>
+          <t>https://x.com/ren_fernz/status/2047629583571186141</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dubai South has signed a strategic memorandum of understanding with Emirates NBD, a leading banking group, to support SMEs within Dubai South and facilitate access to a range of banking services.
-Read more on https://t.co/PxdboQNv0C
-#GINews #Aviation #Logistics #MoU #SMEs #Dubai https://t.co/siQn4bnEq2</t>
+          <t>They mentioned I got a penalty of late payment fees charges of 230AED +11AED vat. I asked them check if I got previously, so agent told me to check the application but on application there is nothing shown. So she told to check the Estatement.</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1776942002000</v>
+        <v>1777027910000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2047269260817465622</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkplJpbAAAP2-n.jpg', 'type': 'photo', 'id': '2047213223838154752'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'Gulf Industry Online', 'screenName': 'GulfIndustryOn', 'followersCount': 103, 'favouritesCount': 18, 'friendsCount': 184, 'description': 'Gulf Industry is a "window" into the Gulf\'s manufacturing trading and export sectors providing news, views analysis and information.'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3118,190 +3135,203 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2047629581159477750</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="n">
-        <v>46135.62502314815</v>
+        <v>46136.6193287037</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/GulfIndustryOn/status/2047269260817465622</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2047269260817465622</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2047182427521708183</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/GulfIndustryOn/status/2047182427521708183</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Raimondi Middle East marks a significant milestone in the UAE with more than 100 cranes currently operating across the country.
-Read more on https://t.co/hQ3MYMFkmz
-#GINews #Cranes #Milestones #Dubai https://t.co/2QWz8jFb4j</t>
+          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1776921300000</v>
+        <v>1777027911000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2047182427521708183</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkLOa3a8AA10px.jpg', 'type': 'photo', 'id': '2047179847974449152'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'Gulf Industry Online', 'screenName': 'GulfIndustryOn', 'followersCount': 103, 'favouritesCount': 18, 'friendsCount': 184, 'description': 'Gulf Industry is a "window" into the Gulf\'s manufacturing trading and export sectors providing news, views analysis and information.'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2047629583571186141</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="n">
-        <v>46135.38541666666</v>
+        <v>46136.61934027778</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/alsawaeid_al/status/2047269288839426260</t>
+          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2047269288839426260</t>
+          <t>2047629586435817682</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2047256583240073652</t>
+          <t>2047629588675575900</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2047256583240073652</t>
+          <t>https://x.com/ren_fernz/status/2047629588675575900</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>بنك الإمارات دبي الوطني يحقق نتائج قياسية خلال الربع الأول من عام 2026. https://t.co/pfSai48QFX</t>
+          <t>Was yesterday and they won’t able to do for Jan and Feb. My question is why don’t the @ENBDdeals application show the late fees charges applied on my card?? If I knew I would have not made the repeated mistake. I wanted to close my ADCB Bank but as I wanted to pay the CC bills</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1776938980000</v>
+        <v>1777027911000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2047256583240073652</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlQ8cZaQAAFjpn.jpg', 'type': 'photo', 'id': '2047256504961744896'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'Dubai Media Office', 'screenName': 'DXBMediaOffice', 'followersCount': 2331848, 'favouritesCount': 2, 'friendsCount': 161, 'description': 'الحساب الرسمي للمكتب الإعلامي لحكومة دبي\n\nThe official account of the Government of Dubai Media Office'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="J41" t="n">
         <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>4539</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2047629586435817682</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="n">
-        <v>46135.5900462963</v>
+        <v>46136.61934027778</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/alsawaeid_al/status/2047269288839426260</t>
+          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2047269288839426260</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2047269288839426260</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/alsawaeid_al/status/2047269288839426260</t>
+          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>@DXBMediaOffice @EmiratesNBD_AE https://t.co/S9u750ekZh</t>
+          <t>Breaking News 📢 Dubai Real Estate Just Entered a New Era 🌇
+▪️50/50 Strategy: Pay 50% and leverage ENBD financing for the rest.
+▪️Project Readiness: Available on premium projects at least 30% complete.
+▪️Maximum Liquidity: Grow your portfolio without tying up all your cash. https://t.co/e4xRBY8CCu</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1776942009000</v>
+        <v>1777027644000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2047256583240073652</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC9aIAAcfHM.jpg', 'type': 'photo', 'id': '2047628390761635840'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC8acAAmIIP.jpg', 'type': 'photo', 'id': '2047628390757462016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLDCaEAAgV9I.jpg', 'type': 'photo', 'id': '2047628390782603264'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC7awAA0pEW.jpg', 'type': 'photo', 'id': '2047628390753288192'}]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'هكر اخلاقي _ مؤسسة الصقر الخفي', 'screenName': 'alsawaeid_al', 'followersCount': 97162, 'favouritesCount': 2126, 'friendsCount': 51, 'description': '#هكر_اخلاقي واستشاري مختص في مجال التقنيات الحديثة ، و حل قضايا #الابتزاز | معتمد وموثوق في وزارة التجارة .\nرقم : 7053508417'}</t>
+          <t>{'name': 'D&amp;B Properties', 'screenName': 'dandbdubai', 'followersCount': 589, 'favouritesCount': 930, 'friendsCount': 828, 'description': 'Multi-Award Winning Real Estate Brokerage in Dubai\nSales | Leasing | Off-Plan | Commercial | Asset Management | Valuations &amp; Advisory | Holiday Homes'}</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -3318,66 +3348,63 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>2047256583240073652</t>
-        </is>
-      </c>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" s="2" t="n">
-        <v>46135.62510416667</v>
+        <v>46136.61625</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/BinsalamahTariq/status/2047264777831862651</t>
+          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2047264777831862651</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2047264777831862651</t>
+          <t>2046932416754012230</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/BinsalamahTariq/status/2047264777831862651</t>
+          <t>https://x.com/dandbdubai/status/2046932416754012230</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Emirates NBD, the region’s 4th largest lender by market capitalization, posted a 3% year-on-year (YoY) rise in first quarter 2026 net profit to AED 6.4 billion ($1.74 billion)
-The result beat analysts’ mean estimate of AED 5.69 billion
-https://t.co/7Ieq9hEQ2y https://t.co/B8gBsDKXAX</t>
+          <t>Proud to call the UAE home 🇦🇪
+The UAE continues to inspire, build, and lead and we’re proud to be part of that story.
+Here’s to growth, innovation, and everything ahead
+#UAE #ProudOfUAE #UAENationalPride #Dubai #DubaiLife https://t.co/bnUJHbF5lp</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1776940934000</v>
+        <v>1776861692000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2047264777831862651</t>
+          <t>2046932416754012230</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlYJ2sWkAAfYr8.jpg', 'type': 'photo', 'id': '2047264431940210688'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2046932359065591808/img/bJGTr1dd5W2_rytA.jpg', 'type': 'video', 'id': '2046932359065591808'}]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'Tariq BinSalamah', 'screenName': 'BinsalamahTariq', 'followersCount': 1166, 'favouritesCount': 890, 'friendsCount': 133, 'description': 'Authorized Capital Market Practitioner'}</t>
+          <t>{'name': 'D&amp;B Properties', 'screenName': 'dandbdubai', 'followersCount': 589, 'favouritesCount': 930, 'friendsCount': 828, 'description': 'Multi-Award Winning Real Estate Brokerage in Dubai\nSales | Leasing | Off-Plan | Commercial | Asset Management | Valuations &amp; Advisory | Holiday Homes'}</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -3386,126 +3413,126 @@
         <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>37</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" s="2" t="n">
-        <v>46135.61266203703</v>
+        <v>46134.69550925926</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/BinsalamahTariq/status/2047264777831862651</t>
+          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2047264777831862651</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2047204158361452915</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/BinsalamahTariq/status/2047204158361452915</t>
+          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SABIC Agri-Nutrients Q1 2026 reports 24% YoY &amp;amp; QoQ growth in profitability attributed to higher selling price despite reduced quantities.. https://t.co/XDaNdBks8o</t>
+          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1776926481000</v>
+        <v>1777021162000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2047204158361452915</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkg9OnXYAA-8mQ.jpg', 'type': 'photo', 'id': '2047203741883916288'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'Tariq BinSalamah', 'screenName': 'BinsalamahTariq', 'followersCount': 1166, 'favouritesCount': 890, 'friendsCount': 133, 'description': 'Authorized Capital Market Practitioner'}</t>
+          <t>{'name': 'Kang Hori', 'screenName': 'XSilverMermaidX', 'followersCount': 172, 'favouritesCount': 3163, 'friendsCount': 162, 'description': '🔬💼👩🏻\u200d💻🇦🇪'}</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" s="2" t="n">
-        <v>46135.44538194445</v>
+        <v>46136.54122685185</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2047256960563810466</t>
+          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2047256960563810466</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2047256960563810466</t>
+          <t>2047606015684718778</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2047256960563810466</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047606015684718778</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Emirates NBD reports strong results in Q1 2026. https://t.co/bdt7wIIuTc</t>
+          <t>@XSilverMermaidX We have replied to your message in private</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1776939070000</v>
+        <v>1777022291000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2047256960563810466</t>
+          <t>2047601280143724646</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlRT18asAAIrl4.jpg', 'type': 'photo', 'id': '2047256906956451840'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': 'Dubai Media Office', 'screenName': 'DXBMediaOffice', 'followersCount': 2331848, 'favouritesCount': 2, 'friendsCount': 161, 'description': 'الحساب الرسمي للمكتب الإعلامي لحكومة دبي\n\nThe official account of the Government of Dubai Media Office'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -3515,274 +3542,243 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>4207</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2047601280143724646</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="n">
-        <v>46135.59108796297</v>
+        <v>46136.55429398148</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2047256960563810466</t>
+          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2047256960563810466</t>
+          <t>2047512157030645934</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2047277766769545352</t>
+          <t>2047512157030645934</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/HHShkMohd/status/2047277766769545352</t>
+          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Under the directives of the President of the UAE, we launch a new government model. Within two years, 50% of government sectors, services, and operations will run on Agentic AI, making the UAE the first government globally to operate at this scale through autonomous systems.
-AI is no longer a tool. It analyses, decides, executes, and improves in real time. It will become our executive partner to enhance services, accelerate decisions, and raise efficiency.
-This transformation has a clear timeline. Two years. Performance across government will be measured by speed of adoption, quality of implementation, and mastery of AI in redesigning government work.
-We are investing in our people. Every federal employee will be trained to master AI, building one of the world’s strongest capabilities in AI-driven government.
-Implementation will be overseen by Sheikh Mansour bin Zayed, with a dedicated taskforce chaired by Mohammad Al Gergawi driving execution.
-The world is changing. Technology is accelerating. Our principle remains constant. People come first. Our goal is a government that is faster, more responsive, and more impactful.</t>
+          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1776944030000</v>
+        <v>1776999913000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2047277766769545352</t>
+          <t>2047512157030645934</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlkRYOakAASWH_.jpg', 'type': 'photo', 'id': '2047277755340066816'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlkRYCbIAInaJr.jpg', 'type': 'photo', 'id': '2047277755289772034'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlkRYCaIAAG5YS.jpg', 'type': 'photo', 'id': '2047277755289706496'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlkRYJb0AAbm_7.jpg', 'type': 'photo', 'id': '2047277755319177216'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'HH Sheikh Mohammed', 'screenName': 'HHShkMohd', 'followersCount': 10024706, 'favouritesCount': 1, 'friendsCount': 68, 'description': 'الحساب الرسمي لصاحب السمو الشيخ محمد بن راشد آل مكتوم  | Official account of His Highness Sheikh Mohammed bin Rashid Al Maktoum'}</t>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>844</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>968</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>2106</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>11167</v>
+        <v>0</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>1785324</t>
+          <t>44</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" s="2" t="n">
-        <v>46135.64849537037</v>
+        <v>46136.29528935185</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2047228305686876507</t>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2047228305686876507</t>
+          <t>2047564934997762494</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2047228305686876507</t>
+          <t>2047367142367191224</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2047228305686876507</t>
+          <t>https://x.com/zachrose51/status/2047367142367191224</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Emirates NBD reported record Q1 2026 results, with total income reaching AED14.4 billion ($3.92 billion), up 21% year-on-year and 13% quarter-on-quarter, driven by strong asset growth and record non-funded income.
-Profit before tax rose 6% year-on-year to AED8.2 billion, while net profit increased 3% annually and 27% quarterly to AED6.4 billion ($1.74 billion), reflecting resilient margins and solid balance sheet performance.
-@EmiratesNBD_AE 
-#EmiratesNBD #UAE #Banking #Finance #Earnings</t>
+          <t>We just killed cold email: Introducing Draftboard.
+The world’s first AI Sales Director that outperforms any human.
+Comment your website and we’ll find you intros to 10 dream prospects for free. https://t.co/DK7wDKVQl7</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1776932238000</v>
+        <v>1776965339000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2047228305686876507</t>
+          <t>2047367142367191224</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGk3SqFWgAAGj6x.jpg', 'type': 'photo', 'id': '2047228299290509312'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047366826984972288/img/qZKW_Emc0-7B9Jot.jpg', 'type': 'video', 'id': '2047366826984972288'}]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'Economy Middle East', 'screenName': 'Economy_ME', 'followersCount': 4471, 'favouritesCount': 207, 'friendsCount': 12, 'description': '#EconomyMiddleEast Summit 2026\nThe Economy of Tomorrow: The UAE Emerges Stronger 🇦🇪\n📅 May 21, 2026\n📍 Rosewood, Abu Dhabi\nRegister now ⬇️'}</t>
+          <t>{'name': 'Zach Roseman', 'screenName': 'zachrose51', 'followersCount': 690, 'favouritesCount': 10161, 'friendsCount': 485, 'description': 'Cold outbound is dead. Building the fix @Draftboard - map warm intro paths from your network to your prospects. Ex-CEO Mosaic Group (acq. by Bending Spoons)'}</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>573</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>94</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>1132</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>780455</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" s="2" t="n">
-        <v>46135.51201388889</v>
+        <v>46135.89512731481</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2047228305686876507</t>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2047228305686876507</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2047325047803527361</t>
-        </is>
-      </c>
+          <t>2047564934997762494</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2047325047803527361</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Ajman’s Department of Tourism Development has announced a package of initiatives to support tourism activities, attract investment and strengthen the competitiveness of the emirate’s tourism sector, under the directives of H.H. Sheikh Ammar bin Humaid Al Nuaimi, Crown Prince of Ajman and Chairman of the Ajman Executive Council.
-The package aligns with the Crown Prince’s vision to develop the tourism business environment and strengthen the sector’s sustainability and resilience in the face of various challenges.
-The measures include exemptions and facilitation initiatives covering operations, licensing and marketing, aimed at supporting tourism establishments, improving operational efficiency and boosting competitiveness.
-#Ajman #Tourism #UAE</t>
-        </is>
-      </c>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="n">
-        <v>1776955303000</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2047325047803527361</t>
-        </is>
-      </c>
+        <v>1777084592387</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGmPRllWkAAQ5LL.jpg', 'type': 'photo', 'id': '2047325037925928960'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'Economy Middle East', 'screenName': 'Economy_ME', 'followersCount': 4471, 'favouritesCount': 207, 'friendsCount': 12, 'description': '#EconomyMiddleEast Summit 2026\nThe Economy of Tomorrow: The UAE Emerges Stronger 🇦🇪\n📅 May 21, 2026\n📍 Rosewood, Abu Dhabi\nRegister now ⬇️'}</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>8</v>
-      </c>
-      <c r="M48" t="n">
-        <v>4</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" s="2" t="n">
-        <v>46135.77896990741</v>
+        <v>46137.27537484954</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016/status/2047245588618465658</t>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2047245588618465658</t>
+          <t>2047564934997762494</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2047245588618465658</t>
+          <t>2047564934997762494</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016/status/2047245588618465658</t>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>💰 سجل بنك بنود الإمارات (Emirates NBD)، أكبر البنوك أصولاً في دبي، ارتفاعاً في صافي أرباحه للربع الأول من عام 2026.
-قفز صافي الأرباح بنسبة 3% ليصل إلى 6.4 مليار درهم إماراتي (1.7 مليار دولار)، مدعوماً بنمو الإيداع والإقراض، بينما ارتفع إجمالي الدخل 21% مسجلاً 14.4 مليار درهم.
-#اقتصاد #الخليج #بنوك #الإمارات</t>
+          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1776936358000</v>
+        <v>1777012497000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2047245588618465658</t>
+          <t>2047367142367191224</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGlHAhMXgAAU3WA.jpg', 'type': 'photo', 'id': '2047245579852414976'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'فايز المالكي', 'screenName': 'Fyan2016', 'followersCount': 262, 'favouritesCount': 10399, 'friendsCount': 1796, 'description': 'مهندس.. ماجستير ادارة اعمال تنفيذية.. مهتم بالعقار والديكور والتقنيات الزراعية الحديثة والطبيعة والفيزياء واشياء اخرى'}</t>
+          <t>{'name': 'Zach Roseman', 'screenName': 'zachrose51', 'followersCount': 690, 'favouritesCount': 10161, 'friendsCount': 485, 'description': 'Cold outbound is dead. Building the fix @Draftboard - map warm intro paths from your network to your prospects. Ex-CEO Mosaic Group (acq. by Bending Spoons)'}</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3799,63 +3795,66 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2047564727421964462</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="n">
-        <v>46135.55969907407</v>
+        <v>46136.4409375</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016/status/2047245588618465658</t>
+          <t>https://x.com/hkayyal/status/2047530498705195395</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2047245588618465658</t>
+          <t>2047530498705195395</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2047382489803461045</t>
+          <t>2047530181221613706</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/Fyan2016/status/2047382489803461045</t>
+          <t>https://x.com/hkayyal/status/2047530181221613706</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>🌍 مسؤول إيراني يزعم أن طهران بدأت بتلقي إيرادات رسوم العبور من مضيق هرمز
-نقلت وكالة "تسنيم" عن نائب رئيس البرلمان الإيراني، حميد رضا حاجي بابائي، أن أول إيرادات الرسوم المفروضة على المضيق قد أودعت في حساب البنك المركزي.
-في سياق متصل، كشفت بيانات ملاحية عن عبور 187 سفينة وناقلة نفط المضيق منذ إغلاقه في 4 مارس الماضي، بمتوسط 4 سفن يومياً، منها 23% مسجلة في الصين.
-#الخليج #الشرق_الأوسط #اقتصاد #جيوسياسة #طاقة</t>
+          <t>🧵 Gulf Fintech Daily — April 24, 2026
+AI as infrastructure. Sovereign capital as catalyst. 5 stories 👇
+#GulfFintech #MENA #FinTech</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1776968998000</v>
+        <v>1777004211000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2047382489803461045</t>
+          <t>2047530181221613706</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGnDhajWQAAyt9N.jpg', 'type': 'photo', 'id': '2047382484447281152'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{'name': 'فايز المالكي', 'screenName': 'Fyan2016', 'followersCount': 262, 'favouritesCount': 10399, 'friendsCount': 1796, 'description': 'مهندس.. ماجستير ادارة اعمال تنفيذية.. مهتم بالعقار والديكور والتقنيات الزراعية الحديثة والطبيعة والفيزياء واشياء اخرى'}</t>
+          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 689, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3864,54 +3863,53 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" s="2" t="n">
-        <v>46135.93747685185</v>
+        <v>46136.34503472222</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047246858716930242</t>
+          <t>https://x.com/hkayyal/status/2047530498705195395</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2047246858716930242</t>
+          <t>2047530498705195395</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2047246858716930242</t>
+          <t>2047530498705195395</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047246858716930242</t>
+          <t>https://x.com/hkayyal/status/2047530498705195395</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>للأسف البنك من أسوء من تعامل مع الأزمة والظروف
-صافي الأرباح لم يسجل نمواً مقارنة بالفترة ذاتها من
-العام الماضي على الطرف الأخر سجل دبي الوطني نمواً
-في صافي الربح مقارنة بالفترة ذاتها من العام الماضي
-رغم الأزمة تفوق ENBD على FAB و سجل أرقاماً قياسية .</t>
+          <t>3️⃣ Dubai South × Emirates NBD sign MoU for streamlined SME banking access.
+Corporate account opening + tailored banking within the free zone.
+94% of UAE businesses are SMEs. Financial onboarding friction is being systematically removed.
+#Dubai #SME #D33</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1776936661000</v>
+        <v>1777004286000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2047246858716930242</t>
+          <t>2047530181221613706</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3921,7 +3919,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2980, 'favouritesCount': 130246, 'friendsCount': 6668, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
+          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 689, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3934,50 +3932,54 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>302</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2047530181221613706</t>
+        </is>
+      </c>
       <c r="P51" s="2" t="n">
-        <v>46135.56320601852</v>
+        <v>46136.34590277778</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047246858716930242</t>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2047246858716930242</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2047502441709797406</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/abd11ulla/status/2047502441709797406</t>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>زعيم الشرق الأوسط 🌍 ، محمد بن زايد ( بوخالد ) 🇦🇪 .</t>
+          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1776997597000</v>
+        <v>1776999691000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2047502441709797406</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3987,63 +3989,63 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2980, 'favouritesCount': 130246, 'friendsCount': 6668, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>66</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" s="2" t="n">
-        <v>46136.2684837963</v>
+        <v>46136.2927199074</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://x.com/TheNationalNews/status/2047226752414421132</t>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2047226752414421132</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2047226752414421132</t>
+          <t>2047534633697308773</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/TheNationalNews/status/2047226752414421132</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047534633697308773</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>First Abu Dhabi Bank and Emirates NBD report strong first-quarter earnings despite war uncertainty https://t.co/IoAlA6QA7W</t>
+          <t>@abhiseksonusonu We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to livsocialconnect@liv.me and tag the case reference number #1001503 in the subject line.</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1776931868000</v>
+        <v>1777005272000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2047226752414421132</t>
+          <t>2047511223839908158</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4053,215 +4055,217 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{'name': 'The National', 'screenName': 'TheNationalNews', 'followersCount': 1078357, 'favouritesCount': 3463, 'friendsCount': 206, 'description': "The world has borders. Our stories don't."}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>1112</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2047511223839908158</t>
+        </is>
+      </c>
       <c r="P53" s="2" t="n">
-        <v>46135.50773148148</v>
+        <v>46136.35731481481</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://x.com/researchUSAI/status/2047227343916368335</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2047227343916368335</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2047227343916368335</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://x.com/researchUSAI/status/2047227343916368335</t>
+          <t>https://x.com/JDunlap1974/status/2029505253947629989</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>🇦🇪
-While Gulf economies reel from Hormuz woes..
-First Abu Dhabi Bank and Emirates NBD post strong Q1 earnings amid regional war uncertainty
-Iran's conflict closes Strait of Hormuz, slashes Gulf exports, spikes energy prices and hits jet fuel in China, India, South Korea; yet UAE lenders thrive
-Resilient banks signal UAE stability as 30-nation push led by UK, France aims to reopen strait, but IEA flags history's biggest energy threat if tensions drag</t>
+          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1776932009000</v>
+        <v>1772706733000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2047227343916368335</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2029505138055139328/pu/img/WpN4JWq99VF-NMQD.jpg', 'type': 'video', 'id': '2029505138055139328'}]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>{'name': 'U.S.A.I. 🇺🇸', 'screenName': 'researchUSAI', 'followersCount': 1418, 'favouritesCount': 7656, 'friendsCount': 1, 'description': "🚨 BREAKING: THE WORLD'S MOST GREATEST"}</t>
+          <t>{'name': 'JOSH DUNLAP', 'screenName': 'JDunlap1974', 'followersCount': 373876, 'favouritesCount': 120459, 'friendsCount': 44620, 'description': '🇺🇲 MAYOR OF MAGADONIA 🇺🇲 ✝️ CHRISTIAN ✝️ MAGA\n📣 📣BREAKING NEWS FIRST HERE 📣📣'}</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1256</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" s="2" t="n">
-        <v>46135.50936342592</v>
+        <v>46086.60570601852</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://x.com/researchUSAI/status/2047227343916368335</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2047227343916368335</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2047548010788532657</t>
+          <t>2029530832042393630</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://x.com/researchUSAI/status/2047548010788532657</t>
+          <t>https://x.com/iDenville/status/2029530832042393630</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>🇮🇳🇵🇰 UP ATS nabs two terrorists tied to Pakistani gangsters, ISI
-https://t.co/k9HOKr157I</t>
+          <t>@JDunlap1974 Now audit North Carolina's primaries!!  This is Lakeshia Alston, the woman who ran for election as a REPUBLICAN and won!! https://t.co/vQrXOOfnIW</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1777008462000</v>
+        <v>1772712831000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2047548010788532657</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGpZjs3XkAE0U-R.jpg', 'type': 'photo', 'id': '2047547450466996225'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGpZjs7WIAAE5qH.jpg', 'type': 'photo', 'id': '2047547450483679232'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCpXbMYbwAEvTXt.jpg', 'type': 'photo', 'id': '2029530706775621633'}]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>{'name': 'U.S.A.I. 🇺🇸', 'screenName': 'researchUSAI', 'followersCount': 1418, 'favouritesCount': 7656, 'friendsCount': 1, 'description': "🚨 BREAKING: THE WORLD'S MOST GREATEST"}</t>
+          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23509, 'favouritesCount': 181621, 'friendsCount': 23653, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
+          <t>5793</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2029505253947629989</t>
+        </is>
+      </c>
       <c r="P55" s="2" t="n">
-        <v>46136.39423611111</v>
+        <v>46086.67628472222</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://x.com/timesofdubai_/status/2047222852135621054</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2047222852135621054</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2047222852135621054</t>
+          <t>2047834245423395027</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://x.com/timesofdubai_/status/2047222852135621054</t>
+          <t>https://x.com/stelpetla/status/2047834245423395027</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubai South and Emirates NBD sign a strategic partnership to support businesses, enhance financial solutions, and drive economic growth across Dubai’s dynamic ecosystem.
-#DubaiSouth #EmiratesNBD #DubaiEconomy #BusinessGrowth #UAE #Innovation #SMEs #Entrepreneurs #FutureDubai https://t.co/PU7c1kWtMA</t>
+          <t>@iDenville @JDunlap1974 How are they allowed to enter a bank? I’m not allowed to go in my bank wearing sunglasses or a hat.</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1776930938000</v>
+        <v>1777076705000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2047222852135621054</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkyVJiaIAEMiJn.jpg', 'type': 'photo', 'id': '2047222844535480321'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>{'name': 'Times of Dubai', 'screenName': 'timesofdubai_', 'followersCount': 65, 'favouritesCount': 250, 'friendsCount': 12, 'description': 'Latest Dubai &amp; Gulf news, breaking news, exclusive insights &amp; everything in between!  A part of GH Media Network LLC'}</t>
+          <t>{'name': 'Stella Pet 🇺🇸', 'screenName': 'stelpetla', 'followersCount': 685, 'favouritesCount': 27507, 'friendsCount': 1544, 'description': 'GenX/Jersey Girl. 🇺🇸 Mayflower Descendant, DAR. 12th generation American. Trump X 3'}</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -4270,50 +4274,54 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2029530832042393630</t>
+        </is>
+      </c>
       <c r="P56" s="2" t="n">
-        <v>46135.49696759259</v>
+        <v>46137.18408564815</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://x.com/NikunjSOF/status/2047219745053917579</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2047219745053917579</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2047219745053917579</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://x.com/NikunjSOF/status/2047219745053917579</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>The paperwork is nearly finished. By the first week of June, Emirates NBD will officially become the majority owner, and RBL Bank will begin operating as a foreign-owned subsidiary. While it is difficult to predict exactly how aggressive the new management will be or what their specific plans are, having such a strong promoter will definitely help RBL Bank’s stability and growth.</t>
+          <t>@stelpetla @JDunlap1974 Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1776930197000</v>
+        <v>1777076951000</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2047219745053917579</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4323,7 +4331,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>{'name': 'CA Nikunj', 'screenName': 'NikunjSOF', 'followersCount': 486, 'favouritesCount': 1777, 'friendsCount': 247, 'description': 'Equity &amp; Mutual Fund | Direct/ indirect Tax | Chartered Accountant\n\nhttps://t.co/13qe7OF4yb\n\nDM or email at nrchowdhary@gmail.com'}</t>
+          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23509, 'favouritesCount': 181621, 'friendsCount': 23653, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
         </is>
       </c>
       <c r="J57" t="n">
@@ -4336,62 +4344,67 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2047834245423395027</t>
+        </is>
+      </c>
       <c r="P57" s="2" t="n">
-        <v>46135.4883912037</v>
+        <v>46137.18693287037</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://x.com/NikunjSOF/status/2047219745053917579</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2047219745053917579</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2047215759290769819</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://x.com/NikunjSOF/status/2047215759290769819</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>E2E Networks is a Service Provider (Cloud): They buy GPUs, host them in their own data centers, and "rent" the power to customers on a monthly/hourly basis.
-Netweb Technologies is a Manufacturer (OEM): They design and build the physical supercomputers and AI servers. They make money by "selling" the hardware and software directly to companies or the government to own.
-In simple terms: Netweb is the car manufacturer (selling the vehicle), while E2E is the taxi service (renting the ride).</t>
+          <t>🇦🇪 We salute the nation’s heroes 
+We value your commitment and have designed exclusive banking benefits for your peace of mind.
+📈 Attractive finance profit rates
+🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1776929247000</v>
+        <v>1777048987000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2047215759290769819</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>{'name': 'CA Nikunj', 'screenName': 'NikunjSOF', 'followersCount': 486, 'favouritesCount': 1777, 'friendsCount': 247, 'description': 'Equity &amp; Mutual Fund | Direct/ indirect Tax | Chartered Accountant\n\nhttps://t.co/13qe7OF4yb\n\nDM or email at nrchowdhary@gmail.com'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J58" t="n">
@@ -4404,50 +4417,55 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>39</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" s="2" t="n">
-        <v>46135.47739583333</v>
+        <v>46136.86327546297</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersWorld/status/2047218961809277291</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047717990762782723</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersWorld/status/2047218961809277291</t>
+          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Emirates NBD posts quarterly profit rise in first results since Iran conflict https://t.co/v7FHKB736C https://t.co/v7FHKB736C</t>
+          <t>⏳Payment holidays
+🎁 Exclusive prizes with Kunooz Millionaire Account
+Terms and conditions apply.
+Know more
+https://t.co/OfDhWyedzP
+#EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1776930010000</v>
+        <v>1777048988000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4457,73 +4475,79 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>{'name': 'Reuters World', 'screenName': 'ReutersWorld', 'followersCount': 1026838, 'favouritesCount': 10, 'friendsCount': 161, 'description': 'Your source for top international news and analysis.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2963</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2047717988195852322</t>
+        </is>
+      </c>
       <c r="P59" s="2" t="n">
-        <v>46135.48622685186</v>
+        <v>46136.86328703703</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersWorld/status/2047218961809277291</t>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2047227568915403232</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://x.com/doraxtalk/status/2047227568915403232</t>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>@ReutersWorld Ok</t>
+          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
+Read more on https://t.co/I3d8g2xghd
+#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1776932062000</v>
+        <v>1777014900000</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2047218961809277291</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl1UAxasAAkYXs.jpg', 'type': 'photo', 'id': '2047296492281704448'}]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>{'name': 'Dora', 'screenName': 'doraxtalk', 'followersCount': 945, 'favouritesCount': 2651, 'friendsCount': 988, 'description': 'Comentando sobre tudo!'}</t>
+          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
         </is>
       </c>
       <c r="J60" t="n">
@@ -4540,61 +4564,58 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2047218961809277291</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
       <c r="P60" s="2" t="n">
-        <v>46135.50997685185</v>
+        <v>46136.46875</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047215137723973688</t>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2047215137723973688</t>
+          <t>2047575014564921667</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2047215137723973688</t>
+          <t>2047597663634457003</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047215137723973688</t>
+          <t>https://x.com/ABCinGCC/status/2047597663634457003</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>بنك ENBD: نقوم بدعم العملاء عبر إجراءات تشمل إعفاءات أو تأجيل الرسوم لمساعدة الشركات على التكيف مع الظروف الحالية
-#العربية_Business https://t.co/KdnwaQVmL6</t>
+          <t>UAE-based @AziziGroup  Developments has announced that construction at Beach Oasis II - its vibrant mixed-use community in the dynamic, rapidly growing Dubai Studio City - has reached 43% completion.
+Read more on https://t.co/Y5AVR722nO
+#ABCNews #Developments #BeachOasis #UAE https://t.co/eVcDwo33OV</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1776929098000</v>
+        <v>1777020300000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2047215137723973688</t>
+          <t>2047597663634457003</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkrUNxXQAA-hXR.jpg', 'type': 'video', 'id': '2047214999056076800'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl180kaQAAsBhe.jpg', 'type': 'photo', 'id': '2047297193380560896'}]</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>{'name': 'العربية Business', 'screenName': 'AlArabiya_Bn', 'followersCount': 1995738, 'favouritesCount': 0, 'friendsCount': 53, 'description': 'المصدر الرئيسي لأخبار الاقتصاد والأعمال في الشرق الأوسط @AlArabiya'}</t>
+          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -4604,198 +4625,208 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
       <c r="P61" s="2" t="n">
-        <v>46135.4756712963</v>
+        <v>46136.53125</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047215137723973688</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2047215137723973688</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2047465543267917851</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047465543267917851</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>كيف أنقذت شوكولاتة #KitKat شركة #نستله من فضيحة؟
-#العربية_Business https://t.co/xo2EwMOJwN</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1776988800000</v>
+        <v>1777028400000</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2047465543267917851</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047324941092007936/img/vchuMfCc1dPFfYyF.jpg', 'type': 'video', 'id': '2047324941092007936'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp7wFoXwAAtDsB.jpg', 'type': 'photo', 'id': '2047585046668754944'}]</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>{'name': 'العربية Business', 'screenName': 'AlArabiya_Bn', 'followersCount': 1995738, 'favouritesCount': 0, 'friendsCount': 53, 'description': 'المصدر الرئيسي لأخبار الاقتصاد والأعمال في الشرق الأوسط @AlArabiya'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" s="2" t="n">
-        <v>46136.16666666666</v>
+        <v>46136.625</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047631643901390924</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047193752767193369</t>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>This is the ‘snowball effect’ your savings love.
-Guess and drop your answer below.
-#ENBDRiddleOfTheWeek #GrowYourMoney #SmartSaving https://t.co/FZ9IMHLqZg</t>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+https://t.co/ZafvBWp0Cl</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1776924000000</v>
+        <v>1777028401000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGfmSCYWYAAeGEP.jpg', 'type': 'photo', 'id': '2046857753214214144'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174340, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2047631640168374617</t>
+        </is>
+      </c>
       <c r="P63" s="2" t="n">
-        <v>46135.41666666666</v>
+        <v>46136.62501157408</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2047202084769206665</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047202084769206665</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Worst bank ever iam following up since 1 year for cancellation of wealth account still nothing</t>
+          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
+تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
+📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1776925986000</v>
+        <v>1777048970000</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0l1oXYAEHNu8.jpg', 'type': 'photo', 'id': '2047717911482032129'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0mAsWkAIOAAv.jpg', 'type': 'photo', 'id': '2047717914451546114'}]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>{'name': 'Abid Khan', 'screenName': '77dd14cbca18474', 'followersCount': 0, 'favouritesCount': 9, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J64" t="n">
@@ -4812,50 +4843,50 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2047193752767193369</t>
-        </is>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" s="2" t="n">
-        <v>46135.43965277778</v>
+        <v>46136.8630787037</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047556140431556611</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2047206058129559636</t>
+          <t>2047556140431556611</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047206058129559636</t>
+          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1001012 for us to assist you better. Thanks.</t>
+          <t>You have an unpaid fine – click here
+Do not fall for the traps. Stay alert to scams.
+#EIAgainstFraud with Emirates Islamic.
+#TogetherAgainstFraud
+https://t.co/y7eSpGNdfk</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1776926934000</v>
+        <v>1777010400000</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047556140431556611</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4865,11 +4896,11 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174340, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K65" t="n">
         <v>0</v>
@@ -4882,64 +4913,67 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2047202084769206665</t>
-        </is>
-      </c>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" s="2" t="n">
-        <v>46135.450625</v>
+        <v>46136.41666666666</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I did before also no results we will doing also now. Check your email</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1776927207000</v>
+        <v>1777034682000</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047657988064727443</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FHDWUAA0A9i.jpg', 'type': 'photo', 'id': '2047657975595028480'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FZ7WkAAuMQK.jpg', 'type': 'photo', 'id': '2047657980661764096'}]</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>{'name': 'Abid Khan', 'screenName': '77dd14cbca18474', 'followersCount': 0, 'favouritesCount': 9, 'friendsCount': 21, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -4952,50 +4986,52 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2047206058129559636</t>
-        </is>
-      </c>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
       <c r="P66" s="2" t="n">
-        <v>46135.45378472222</v>
+        <v>46136.69770833333</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://x.com/77dd14cbca18474/status/2047207203501973938</t>
+          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2047213444760273209</t>
+          <t>2047717920193622257</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047213444760273209</t>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>@77dd14cbca18474 We sincerely apologize for the inconvenience caused to you. We will review your email and will take necessary action and update you via email as soon as possible. Thanks</t>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+https://t.co/N2GRIcHWnS
+#الإمارات_الإسلامي #أبطال_الوطن</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1776928695000</v>
+        <v>1777048971000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5005,7 +5041,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174340, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J67" t="n">
@@ -5022,66 +5058,71 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>213</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2047207203501973938</t>
+          <t>2047717917324710124</t>
         </is>
       </c>
       <c r="P67" s="2" t="n">
-        <v>46135.47100694444</v>
+        <v>46136.86309027778</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2047212376362234309</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2047212376362234309</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2047212376362234309</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2047212376362234309</t>
+          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dubai South and Emirates NBD have just signed an MoU to make SME banking in UAE faster, smoother, and more accessible! This is a massive step forward for the Ease of Doing Business in UAE.
-https://t.co/IBP0r0ZWHq
-#dubaisouth #smebanking https://t.co/aJmPeuMCjZ</t>
+          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
+📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
+💳 بطاقة خصم للأبناء
+⭐عروض وخصومات حصرية
+🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
+🏆جوائز نقدية يومية وشهرية
+علمهم صغار!
+تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1776928440000</v>
+        <v>1777034676000</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2047212376362234309</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkomqsagAAL8el.jpg', 'type': 'photo', 'id': '2047212150377316352'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-Dy9W4AA2EvQ.jpg', 'type': 'photo', 'id': '2047657953021321216'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-ECIWoAAdlCp.jpg', 'type': 'photo', 'id': '2047657957093974016'}]</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 0, 'favouritesCount': 16, 'friendsCount': 29, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5090,66 +5131,64 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" s="2" t="n">
-        <v>46135.46805555555</v>
+        <v>46136.69763888889</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2047212376362234309</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2047212376362234309</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2046938769685938442</t>
+          <t>2047657962978558100</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2046938769685938442</t>
+          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>The @DIFC has officially announced a roadmap to become the world’s first AI-native financial center. 
-https://t.co/9ElZqfVH4o
-#FinancialNews #fintech https://t.co/Wuonrb13Ou</t>
+          <t>لمعرفة المزيد، يرجى زيارة https://t.co/Dacednep0G</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1776863207000</v>
+        <v>1777034676000</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2046938769685938442</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGgv7-QbYAASlaK.jpg', 'type': 'photo', 'id': '2046938738010578944'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 0, 'favouritesCount': 16, 'friendsCount': 29, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
@@ -5158,66 +5197,74 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2047657960227176876</t>
+        </is>
+      </c>
       <c r="P69" s="2" t="n">
-        <v>46134.71304398148</v>
+        <v>46136.69763888889</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047208852995846566</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2047208852995846566</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2047208852995846566</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://x.com/ABCinGCC/status/2047208852995846566</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dubai South has signed a strategic memorandum of understanding with Emirates NBD to support SMEs within Dubai South and facilitate access to a range of banking services.
-Read more on https://t.co/7bjytqRTXn
-#ABCNews #MoU #Aviation #Logistics #RealEstate #SMEs https://t.co/ACLvudmI0H</t>
+          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
+📱 Access to a dedicated mobile app
+💳 Complimentary Debit Card for youth
+🏆 Daily &amp;amp; monthly cash prizes
+🎁 A birthday reward of AED 100 for your child
+⭐ Exclusive offers &amp;amp; discounts
+Start them young! https://t.co/cHbCHEecyD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1776927600000</v>
+        <v>1777034678000</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2047208852995846566</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGgyYMkaEAAZins.jpg', 'type': 'photo', 'id': '2046941421912068096'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EiyXYAAScez.jpg', 'type': 'photo', 'id': '2047657965860118528'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EwlWwAAzeCE.jpg', 'type': 'photo', 'id': '2047657969563648000'}]</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -5226,132 +5273,141 @@
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2047657962978558100</t>
+        </is>
+      </c>
       <c r="P70" s="2" t="n">
-        <v>46135.45833333334</v>
+        <v>46136.69766203704</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199400414650716</t>
+          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2047199400414650716</t>
+          <t>2047657972390560162</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2047193752767172824</t>
+          <t>2047657974936604881</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047193752767172824</t>
+          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>هذا هو «تأثير كرة الثلج» الذي تحبه مدخراتك.
-خمن الإجابة واكتبها في التعليقات أدناه.
-#لغز_الأسبوع_ENBD #نمِّ_أموالك #ادخار_ذكي https://t.co/7DKysuXUir</t>
+          <t>Terms &amp;amp; condition apply.
+To know more, please visit https://t.co/Um2N1hjaxk</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1776924000000</v>
+        <v>1777034679000</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2047193752767172824</t>
+          <t>2047657960227176876</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGhKElnXsAAucKZ.jpg', 'type': 'photo', 'id': '2046967473317064704'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174340, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2047657972390560162</t>
+        </is>
+      </c>
       <c r="P71" s="2" t="n">
-        <v>46135.41666666666</v>
+        <v>46136.69767361111</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199400414650716</t>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2047199400414650716</t>
+          <t>2047632173461561410</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2047199400414650716</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199400414650716</t>
+          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Compound Interest</t>
+          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1776925346000</v>
+        <v>1777028525000</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2047193752767172824</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmaBXUAEX6Xi.jpg', 'type': 'photo', 'id': '2047632159343595521'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmlvW4AErjsf.jpg', 'type': 'photo', 'id': '2047632162489294849'}]</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1149, 'favouritesCount': 19748, 'friendsCount': 1783, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -5364,64 +5420,60 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>2047193752767172824</t>
-        </is>
-      </c>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
       <c r="P72" s="2" t="n">
-        <v>46135.43224537037</v>
+        <v>46136.62644675926</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://x.com/AletihadEn/status/2047197832806072615</t>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2047197832806072615</t>
+          <t>2047632173461561410</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2047197832806072615</t>
+          <t>2047632173461561410</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://x.com/AletihadEn/status/2047197832806072615</t>
+          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emirates NBD reports Dh8.2 billion profit before tax in Q1 2026, up 6% YoY 
-Total income increased 21% year-on-year and 13% quarter-on-quarter to Dh14.4 billion, supported by strong asset growth and a sharp rise in non-funded income, which surged 42% year-on-year to Dh4.9 billion.
-Net profit stood at Dh6.4 billion, up 27% quarter-on-quarter but down 3% year-on-year, reflecting overall solid performance during the period.
-Read more: https://t.co/5WKoAM1fAJ 
-#AletihadNewsCenter #UAE #banking  @ENBDdeals</t>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026.
+Terms &amp;amp; conditions apply.
+https://t.co/Hgg0TFDsUE https://t.co/MBZ0YjVgiN</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1776924973000</v>
+        <v>1777028527000</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2047197832806072615</t>
+          <t>2047632164863250935</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmm5VWkAAB2mi.jpg', 'type': 'photo', 'id': '2047632167748931584'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmnGiWkAAtXIq.jpg', 'type': 'photo', 'id': '2047632171293118464'}]</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>{'name': 'Aletihad English', 'screenName': 'AletihadEn', 'followersCount': 1100, 'favouritesCount': 9, 'friendsCount': 12, 'description': 'Aletihad English - Aletihad News Center'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J73" t="n">
@@ -5438,61 +5490,66 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2047632164863250935</t>
+        </is>
+      </c>
       <c r="P73" s="2" t="n">
-        <v>46135.42792824074</v>
+        <v>46136.62646990741</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://x.com/AletihadEn/status/2047197832806072615</t>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2047197832806072615</t>
+          <t>2047632125583605871</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2047548139230671074</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://x.com/AletihadEn/status/2047548139230671074</t>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>#AlAin hosts major #UAE agriculture exhibition
-#AletihadNewsCenter #AbuDhabi @ADNECGroup @MoCCaEUAE @adnecalain</t>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1777008492000</v>
+        <v>1777028514000</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2047548139230671074</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047546481000038400/img/zOIjTWyqBPM179P7.jpg', 'type': 'video', 'id': '2047546481000038400'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjnLXwAAvwdB.jpg', 'type': 'photo', 'id': '2047632111335620608'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjyyXAAAadnx.jpg', 'type': 'photo', 'id': '2047632114451939328'}]</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>{'name': 'Aletihad English', 'screenName': 'AletihadEn', 'followersCount': 1100, 'favouritesCount': 9, 'friendsCount': 12, 'description': 'Aletihad English - Aletihad News Center'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" t="n">
         <v>0</v>
@@ -5505,56 +5562,61 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>37</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
       <c r="P74" s="2" t="n">
-        <v>46136.39458333333</v>
+        <v>46136.62631944445</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199350926070265</t>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2047199350926070265</t>
+          <t>2047632125583605871</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2047199350926070265</t>
+          <t>2047632125583605871</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://x.com/SelmaRomola/status/2047199350926070265</t>
+          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Compound Interest</t>
+          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
+🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير.
+يسري العرض لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.
+https://t.co/909hzRsLZr https://t.co/Ff41FuCAen</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1776925335000</v>
+        <v>1777028516000</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkG7WcAEveRR.jpg', 'type': 'photo', 'id': '2047632119858360321'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkUZWQAEKDDE.jpg', 'type': 'photo', 'id': '2047632123473838081'}]</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>{'name': 'Selma Romola', 'screenName': 'SelmaRomola', 'followersCount': 1149, 'favouritesCount': 19748, 'friendsCount': 1783, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J75" t="n">
@@ -5571,65 +5633,67 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>2047193752767193369</t>
+          <t>2047632116649689120</t>
         </is>
       </c>
       <c r="P75" s="2" t="n">
-        <v>46135.43211805556</v>
+        <v>46136.62634259259</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://x.com/gulfhindinews/status/2047193081275916312</t>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2047193081275916312</t>
+          <t>2047631643926483032</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2047193081275916312</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://x.com/gulfhindinews/status/2047193081275916312</t>
+          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emirates NBD ने कमाई में बनाया रिकॉर्ड, 2026 की पहली तिमाही में 14.4 अरब दिरहम की इनकम, मुनाफ़ा भी बढ़ा
-https://t.co/rdoDZ4ySML https://t.co/QqRyIX35EU https://t.co/pGXfJonLfe</t>
+          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
+استمتع أيضاً بالمزايا الحصرية:
+📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
+🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1776923840000</v>
+        <v>1777028400000</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2047193081275916312</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkXQkaW0AAm4zV.jpg', 'type': 'photo', 'id': '2047193079036170240'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp1V6aW8AAL6dm.jpg', 'type': 'photo', 'id': '2047577999910825984'}]</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>{'name': 'GulfHindi.com', 'screenName': 'gulfhindinews', 'followersCount': 16612, 'favouritesCount': 110, 'friendsCount': 119, 'description': 'UAE, सउदी अरब, कुवैत, क़तर, बहरीन, ओमान और येमन की ख़बरें हिंदी में. Download APP: https://t.co/ilPRB3y2jq also join us on https://t.co/RwcIcNAEJY'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -5638,61 +5702,64 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>41</t>
         </is>
       </c>
       <c r="O76" t="inlineStr"/>
       <c r="P76" s="2" t="n">
-        <v>46135.41481481482</v>
+        <v>46136.625</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://x.com/gulfhindinews/status/2047193081275916312</t>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2047193081275916312</t>
+          <t>2047631643926483032</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2047530365670068310</t>
+          <t>2047631643926483032</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://x.com/gulfhindinews/status/2047530365670068310</t>
+          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Bangladesh Radar System: भारत की सीमा पर बांग्लादेश ने लगाए आधुनिक राडार, सिलीगुड़ी कॉरिडोर और नॉर्थ-ईस्ट पर असर
-https://t.co/uMdCDhHp0b https://t.co/nz8WbUG2Wy https://t.co/RPvuBXb4Yk</t>
+          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
+🔒 تغطية تكافلية
+يسري العرض لغاية 30 أبريل 2026.
+تطبق الشروط والأحكام.
+https://t.co/WVHANHvCwT</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1777004255000</v>
+        <v>1777028401000</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2047530365670068310</t>
+          <t>2047631639946093018</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGpKBGkXAAA3-CW.jpg', 'type': 'photo', 'id': '2047530363396751360'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>{'name': 'GulfHindi.com', 'screenName': 'gulfhindinews', 'followersCount': 16612, 'favouritesCount': 110, 'friendsCount': 119, 'description': 'UAE, सउदी अरब, कुवैत, क़तर, बहरीन, ओमान और येमन की ख़बरें हिंदी में. Download APP: https://t.co/ilPRB3y2jq also join us on https://t.co/RwcIcNAEJY'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J77" t="n">
@@ -5709,61 +5776,63 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2047631639946093018</t>
+        </is>
+      </c>
       <c r="P77" s="2" t="n">
-        <v>46136.34554398148</v>
+        <v>46136.62501157408</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047196564540502492</t>
+          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2047196564540502492</t>
+          <t>2047556140511162463</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2047196564540502492</t>
+          <t>2047556140511162463</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://x.com/AlArabiya_Bn/status/2047196564540502492</t>
+          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>افتتاحية خضراء لكافة المؤشرات الكويتية والإماراتية باستثناء مؤشر أبو ظبي..
-📌 ارتفاع أرباح دو الفصلية 15% إلى 834 مليون درهم
-📌 ارتفاع أرباح بنك ENBD الفصلية 3% إلى 6.4 مليار درهم
-@Noufhijazi_bn
-#افتتاح_الأسواق
-#العربية_Business https://t.co/dWhxxqe7Bt</t>
+          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
+لا تقع في الفخ. احذر الاحتيال.
+#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
+https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1776924670000</v>
+        <v>1777010400000</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2047196564540502492</t>
+          <t>2047556140511162463</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGkabKkXoAAyNBd.jpg', 'type': 'video', 'id': '2047196052474757120'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>{'name': 'العربية Business', 'screenName': 'AlArabiya_Bn', 'followersCount': 1995738, 'favouritesCount': 0, 'friendsCount': 53, 'description': 'المصدر الرئيسي لأخبار الاقتصاد والأعمال في الشرق الأوسط @AlArabiya'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J78" t="n">
@@ -5773,2143 +5842,159 @@
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>1750</t>
+          <t>59</t>
         </is>
       </c>
       <c r="O78" t="inlineStr"/>
       <c r="P78" s="2" t="n">
-        <v>46135.42442129629</v>
+        <v>46136.41666666666</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2047182474049106165</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2038970719238045794</t>
+          <t>2047541041612427486</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://x.com/HarshGada76429/status/2038970719238045794</t>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
-        <is>
-          <t>@RBLBankCares
-@rblbank
-I have been a loyal customer for last 3yrs using your world safari credit card I have achieved the milestone but missed the redemption date by 7 days 
-Request you to send me new redemption link for 10000rs voucher or I will have to end the relationship now</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>1774963476000</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2038970719238045794</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 1, 'friendsCount': 21, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>4</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" s="2" t="n">
-        <v>46112.72541666667</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2047182474049106165</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2047182474049106165</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Pathetic services and poor client retention services by RBL Bank
-@RBLBankCares 
-@EmiratesNBD_AE</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1776921311000</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2038970719238045794</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>{'name': 'Harsh Gada', 'screenName': 'HarshGada76429', 'followersCount': 0, 'favouritesCount': 1, 'friendsCount': 21, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>1</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>2038970719238045794</t>
-        </is>
-      </c>
-      <c r="P80" s="2" t="n">
-        <v>46135.38554398148</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>https://x.com/HarshGada76429/status/2047182474049106165</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2047182474049106165</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2047184999158599844</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>https://x.com/RBLBankCares/status/2047184999158599844</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>@HarshGada76429 Hello, our representative will get in touch with you at the earliest to address your query. Regards, RBL Bank.</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>1776921913000</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2038970719238045794</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>{'name': 'RBL Bank Cares', 'screenName': 'RBLBankCares', 'followersCount': 15185, 'favouritesCount': 107, 'friendsCount': 1, 'description': 'Welcome to the official service handle of RBL Bank for addressing your queries. The Bank’s social media guidelines are available on: https://t.co/4latICF1Kx'}</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>2047182474049106165</t>
-        </is>
-      </c>
-      <c r="P81" s="2" t="n">
-        <v>46135.39251157407</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>https://x.com/abd11ulla/status/2047178753684762646</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2047178753684762646</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2047178753684762646</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>https://x.com/abd11ulla/status/2047178753684762646</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>لا مقارنة بين بنك أبوظبي الأول و الإمارات دبي الوطني
-ENBD أثبت تفوقه المصرفي في أخر 3 أعوام على FAB</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>1776920424000</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2047178753684762646</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2980, 'favouritesCount': 130246, 'friendsCount': 6668, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>1</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>2</v>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" s="2" t="n">
-        <v>46135.37527777778</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>https://x.com/abd11ulla/status/2047178753684762646</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2047178753684762646</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2047199345783754795</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>https://x.com/ahmedalwahedi/status/2047199345783754795</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>@abd11ulla تداوم عندهم اظاهر
-مافي نفس اديب وابوظبي التجاري 😌</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>1776925333000</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2047178753684762646</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>{'name': 'أحمد الواحدي', 'screenName': 'ahmedalwahedi', 'followersCount': 4658, 'favouritesCount': 580, 'friendsCount': 241, 'description': 'من سلالة بني أميه 🇦🇪🧑\u200d🧑\u200d🧒\u200d🧒'}</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>1</v>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>2047178753684762646</t>
-        </is>
-      </c>
-      <c r="P83" s="2" t="n">
-        <v>46135.43209490741</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>https://x.com/abd11ulla/status/2047170067444760649</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2047170067444760649</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2047170067444760649</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>https://x.com/abd11ulla/status/2047170067444760649</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>ماشاءالله 👏🏻 أفضل بنك في الإمارات ENBD 🇦🇪</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>1776918353000</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2047170067444760649</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>{'name': 'Abdulla', 'screenName': 'abd11ulla', 'followersCount': 2980, 'favouritesCount': 130246, 'friendsCount': 6668, 'description': 'The Emirates ( UAE ) = 🗺️'}</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>0</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>1</v>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" s="2" t="n">
-        <v>46135.35130787037</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>https://x.com/khaleejtimes/status/2047177092182557003</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2047177092182557003</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2047177092182557003</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>https://x.com/khaleejtimes/status/2047177092182557003</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Dubai’s Emirates NBD announces record income of Dh14.4 billion in Q1
-https://t.co/UGoB2fsGs4</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>1776920028000</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2047177092182557003</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>{'name': 'Khaleej Times', 'screenName': 'khaleejtimes', 'followersCount': 1196389, 'favouritesCount': 43, 'friendsCount': 1565, 'description': "The official Twitter feed of Khaleej Times, the UAE's first and leading English daily\nhttps://t.co/bKx3o3oPhX"}</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>1</v>
-      </c>
-      <c r="L85" t="n">
-        <v>8</v>
-      </c>
-      <c r="M85" t="n">
-        <v>66</v>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>5910</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" s="2" t="n">
-        <v>46135.37069444444</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>https://x.com/Bosscollion/status/2047136949702631667</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2047136949702631667</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2047136949702631667</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>https://x.com/Bosscollion/status/2047136949702631667</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Wasl Village Deposit machine/ATM is not working from Wednesday night 22.04.2026. Please SEND A TEAM TO FIX IT! https://t.co/YDRya1jkz8</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>1776910457000</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2047136949702631667</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047136882778357760/img/8MXFYgV4POjG6vNG.jpg', 'type': 'video', 'id': '2047136882778357760'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGjkJg_bMAAS77l.jpg', 'type': 'photo', 'id': '2047136882765803520'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGjkJg9akAEYmc4.jpg', 'type': 'photo', 'id': '2047136882757373953'}]</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>{'name': 'Mr. Wanjaa', 'screenName': 'Bosscollion', 'followersCount': 182, 'favouritesCount': 2125, 'friendsCount': 832, 'description': '🌎 World Renowned influencer 🧠Mindset Changer 🏯Renowned Real Estate Developer 📈Business strategist🤴🏾Kingdom Citizen.'}</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" s="2" t="n">
-        <v>46135.25991898148</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>https://x.com/Bosscollion/status/2047136949702631667</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2047136949702631667</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2047169802033111484</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047169802033111484</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>@Bosscollion Hello, thank you for your feedback, we have escalated the case to the team further.</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>1776918290000</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>2047136949702631667</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174340, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>2047136949702631667</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="n">
-        <v>46135.35057870371</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>https://x.com/Bosscollion/status/2047136949702631667</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2047136949702631667</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2047373452387164658</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>https://x.com/Bosscollion/status/2047373452387164658</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>It’s great to have faith for yourself, to believe for your dreams, speak victory over your life. But God didn’t give you faith just for you. You can be the one that steps up and believes for a friend. @JurrienTimber 
-#COYG https://t.co/vsuVNKk4cH</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>1776966844000</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2047373452387164658</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGm7TO_acAArRUv.jpg', 'type': 'photo', 'id': '2047373444732579840'}]</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>{'name': 'Mr. Wanjaa', 'screenName': 'Bosscollion', 'followersCount': 182, 'favouritesCount': 2125, 'friendsCount': 832, 'description': '🌎 World Renowned influencer 🧠Mindset Changer 🏯Renowned Real Estate Developer 📈Business strategist🤴🏾Kingdom Citizen.'}</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
-        <v>46135.9125462963</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>https://x.com/MarketNews_Feed/status/2047162941082882185</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2047162941082882185</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2047162941082882185</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>https://x.com/MarketNews_Feed/status/2047162941082882185</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>*EMIRATES NBD 1Q OPER INCOME 14.4B DIRHAMS, EST. 13.16B DIRHAMS ...</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>1776916654000</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>2047162941082882185</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>{'name': 'MarketNewsFeed', 'screenName': 'MarketNews_Feed', 'followersCount': 6506, 'favouritesCount': 691, 'friendsCount': 4, 'description': 'The number 1 ranked news aggregator voted unanimously  (by me). All financial and tech headlines in one place. Sources are cited in TG - @MarketFeed'}</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" s="2" t="n">
-        <v>46135.33164351852</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>https://x.com/MarketNews_Feed/status/2047162941082882185</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2047162941082882185</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>2047546370731426247</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>https://x.com/MarketNews_Feed/status/2047546370731426247</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>*VOLVO 1Q ADJ. OPER PROFIT SEK12.17B, EST. SEK11.59B ...</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>1777008071000</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2047546370731426247</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>{'name': 'MarketNewsFeed', 'screenName': 'MarketNews_Feed', 'followersCount': 6506, 'favouritesCount': 691, 'friendsCount': 4, 'description': 'The number 1 ranked news aggregator voted unanimously  (by me). All financial and tech headlines in one place. Sources are cited in TG - @MarketFeed'}</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" s="2" t="n">
-        <v>46136.38971064815</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>https://x.com/diegobloomberg/status/2047162845263978833</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2047162845263978833</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>2047162845263978833</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>https://x.com/diegobloomberg/status/2047162845263978833</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>*EMIRATES NBD 1Q OPER INCOME 14.4B DIRHAMS, EST. 13.16B DIRHAMS</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>1776916631000</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2047162845263978833</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>{'name': 'diego bloomberg', 'screenName': 'diegobloomberg', 'followersCount': 1411, 'favouritesCount': 2, 'friendsCount': 6, 'description': 'Fastest news on X. Premium financial headlines at zero cost— Diego wants to keep finance free, fast, and friendly. Activate notifications to stay ahead.'}</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" s="2" t="n">
-        <v>46135.33137731482</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>https://x.com/diegobloomberg/status/2047162845263978833</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2047162845263978833</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>2047545804903068015</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>https://x.com/diegobloomberg/status/2047545804903068015</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>*TSMC EXTENDS GAIN TO 5% AS TAIWAN LIFTS SINGLE STOCK CAP</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>1777007936000</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>2047545804903068015</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>{'name': 'diego bloomberg', 'screenName': 'diegobloomberg', 'followersCount': 1411, 'favouritesCount': 2, 'friendsCount': 6, 'description': 'Fastest news on X. Premium financial headlines at zero cost— Diego wants to keep finance free, fast, and friendly. Activate notifications to stay ahead.'}</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>6</v>
-      </c>
-      <c r="M92" t="n">
-        <v>6</v>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>3415</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" s="2" t="n">
-        <v>46136.38814814815</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>https://x.com/gold_hadas/status/2047447622948901334</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2047447622948901334</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>2047447622948901334</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>https://x.com/gold_hadas/status/2047447622948901334</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Emirates Islamic operating profit rises 7% to $299.52mln in Q1 https://t.co/9TvssUjSYZ</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>1776984527000</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2047447622948901334</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1116, 'favouritesCount': 24023, 'friendsCount': 295, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>0</v>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="n">
-        <v>0</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" s="2" t="n">
-        <v>46136.11721064815</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>https://x.com/gold_hadas/status/2047447622948901334</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2047447622948901334</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>2047518920312041838</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>https://x.com/gold_hadas/status/2047518920312041838</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>The three Abrahamic religions Islam, Christianity and Judaism are encountering a new type of money in the form of cryptocurrency https://t.co/bmRU4TyL6g</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>1777001526000</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2047518920312041838</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1116, 'favouritesCount': 24023, 'friendsCount': 295, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>0</v>
-      </c>
-      <c r="K94" t="n">
-        <v>0</v>
-      </c>
-      <c r="L94" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" s="2" t="n">
-        <v>46136.31395833333</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>https://x.com/IshwarT74378521/status/2047120928795247018</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2047120928795247018</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>2023349339113107783</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>https://x.com/IdbiFor/status/2023349339113107783</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>Representatives of All India IDBI Bank Officers met  Mr. @BaburaoGolla MP Rajya Sabha, @YSR Congress Party from #AndhraPradesh .
-Honouable MP informed that he will take up the issue of IDBI Privatisation immediately and raise this issue in parliament. 
-#SaveIDBI
-#StopPrivatisation
-@Oaktree @RBI @supriya_sule @RajeevRai</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>1771239049000</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2023349339113107783</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HBRhgDcacAATOmz.jpg', 'type': 'photo', 'id': '2023349335904382976'}]</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>{'name': 'Together for IDBI', 'screenName': 'IdbiFor', 'followersCount': 2379, 'favouritesCount': 7619, 'friendsCount': 157, 'description': 'An awareness initiative run by United Forum of IDBI Officers and Employees.\n\nWe oppose privatization. \n\n#StopPrivatization'}</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>21</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>81</v>
-      </c>
-      <c r="M95" t="n">
-        <v>84</v>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>1923</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" s="2" t="n">
-        <v>46069.61862268519</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>https://x.com/IshwarT74378521/status/2047120928795247018</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2047120928795247018</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>2023696356918149472</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>https://x.com/IshwarT74378521/status/2023696356918149472</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>@IdbiFor @BaburaoGolla @RahulGandhi @PawanKalyan @GauravGogoiAsm @FFH_TO @EmiratesNBD_AE @FinMinIndia @DFS_India @SecyDIPAM @bsindia @INCIndia Save IDBI</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>1771321784000</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2023349339113107783</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>{'name': 'IshwarTiwari', 'screenName': 'IshwarT74378521', 'followersCount': 1, 'favouritesCount': 110, 'friendsCount': 68, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>1</v>
-      </c>
-      <c r="K96" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" t="n">
-        <v>2</v>
-      </c>
-      <c r="M96" t="n">
-        <v>2</v>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>2023349339113107783</t>
-        </is>
-      </c>
-      <c r="P96" s="2" t="n">
-        <v>46070.57620370371</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>https://x.com/IshwarT74378521/status/2047120928795247018</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2047120928795247018</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>2047120928795247018</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>https://x.com/IshwarT74378521/status/2047120928795247018</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>@IdbiFor @BaburaoGolla @RahulGandhi @PawanKalyan @GauravGogoiAsm @FFH_TO @EmiratesNBD_AE @FinMinIndia @DFS_India @SecyDIPAM @bsindia @INCIndia Save IDBI</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>1776906637000</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>2023349339113107783</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>{'name': 'IshwarTiwari', 'screenName': 'IshwarT74378521', 'followersCount': 1, 'favouritesCount': 110, 'friendsCount': 68, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>2023696356918149472</t>
-        </is>
-      </c>
-      <c r="P97" s="2" t="n">
-        <v>46135.21570601852</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2047287763796427063</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>2047287763796427063</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Starting early and staying consistent can help your money grow over time. Small steps today can support a more secure and confident financial future.
-#Finwell #FinancialWellbeing #EmiratesIslamic #Investing https://t.co/7rh6hiRrKq</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>1776946414000</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>2047287763796427063</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047287721278783488/pu/img/1XDZTp3BhshZyriP.jpg', 'type': 'video', 'id': '2047287721278783488'}]</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" s="2" t="n">
-        <v>46135.67608796297</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047287763796427063</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2047287763796427063</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
         <is>
           <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
 من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
 #فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
         </is>
       </c>
-      <c r="F99" t="n">
+      <c r="F79" t="n">
         <v>1777006800000</v>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>2047541041612427486</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047358056963473408/pu/img/J1OcKdI5JfoHlVrB.jpg', 'type': 'video', 'id': '2047358056963473408'}]</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
         <v>1</v>
       </c>
-      <c r="K99" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" s="2" t="n">
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>3</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" s="2" t="n">
         <v>46136.375</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073402364</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2047193753073402364</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>2047193753073402364</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073402364</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Your spending isn’t random… it has patterns.
-Check your last 10 transactions.
-Look for repeats, not amounts.
-You’ll quickly see what’s costing you the most, 
-it’s habits, not purchases.
-#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
-https://t.co/XvyZgR87nM</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>1776924000000</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>2047193753073402364</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2047541041612427486</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2047541045768962304</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
+Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
+#ProudOfUAE</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1777006801000</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2047541041612427486</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" s="2" t="n">
-        <v>46135.41666666666</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2047249884101673033</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>2047249881757085701</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047249881757085701</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>تعكس النتائج المالية للإمارات الإسلامي للربع الأول من عام 2026 مرونة القطاع المالي في الدولة وجاهزيته لمواكبة المتغيرات والتحديات الراهنة. https://t.co/0CC4kCWK5A</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>1776937382000</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>2047249881757085701</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047249829034606592/pu/img/L09wsSrWqyKvM73G.jpg', 'type': 'video', 'id': '2047249829034606592'}]</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>1</v>
-      </c>
-      <c r="K101" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" s="2" t="n">
-        <v>46135.57155092592</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2047249884101673033</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>2047249884101673033</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>وقد ارتفع الربح التشغيلي بنسبة %7 على أساس سنوي ليصل إلى 1.1 مليار درهم إماراتي، كما نما إجمالي الدخل بنسبة %6 على أساس سنوي.
-https://t.co/gvo0477mob</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>1776937383000</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>2047249881757085701</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>1</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>2047249881757085701</t>
-        </is>
-      </c>
-      <c r="P102" s="2" t="n">
-        <v>46135.5715625</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047249884101673033</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2047249884101673033</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>2047249946475160040</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047249946475160040</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>Emirates Islamic’s financial results for the first quarter of 2026 reflect the nation’s financial resilience and preparedness through the current environment. Operating Profit was up by 7% y-o-y to AED 1.1 billion and total income grew 6% y-o-y.
-https://t.co/s9M3UfTGFW https://t.co/DymCZHgrV1</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>1776937397000</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>2047249881757085701</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047249892804857856/pu/img/DlhEWBM_8yLjhOal.jpg', 'type': 'video', 'id': '2047249892804857856'}]</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr">
-        <is>
-          <t>2047249884101673033</t>
-        </is>
-      </c>
-      <c r="P103" s="2" t="n">
-        <v>46135.57172453704</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2047241499490807897</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>2046584718758707650</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>https://x.com/UpendraS83806/status/2046584718758707650</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>@emiratesislamic My client transferred payment from your bank but still not credited into my account.
-Please advise.</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>1776778795000</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>2046584718758707650</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>{'name': 'Upendra Singh', 'screenName': 'UpendraS83806', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 13, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>1</v>
-      </c>
-      <c r="K104" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" s="2" t="n">
-        <v>46133.73605324074</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2047241499490807897</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>2046878598796112328</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2046878598796112328</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>@UpendraS83806 Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>1776848861000</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>2046584718758707650</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>1</v>
-      </c>
-      <c r="K105" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr">
-        <is>
-          <t>2046584718758707650</t>
-        </is>
-      </c>
-      <c r="P105" s="2" t="n">
-        <v>46134.54700231482</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2047241499490807897</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>2046976426990268451</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>https://x.com/UpendraS83806/status/2046976426990268451</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>@emiratesislamic Please check your inbox.</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>1776872185000</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>2046584718758707650</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>{'name': 'Upendra Singh', 'screenName': 'UpendraS83806', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 13, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>1</v>
-      </c>
-      <c r="K106" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr">
-        <is>
-          <t>2046878598796112328</t>
-        </is>
-      </c>
-      <c r="P106" s="2" t="n">
-        <v>46134.81695601852</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2047241499490807897</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>2047241499490807897</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047241499490807897</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>@UpendraS83806 Dear Customer, Thanks for getting in touch. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>1776935384000</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>2046584718758707650</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr">
-        <is>
-          <t>2046976426990268451</t>
-        </is>
-      </c>
-      <c r="P107" s="2" t="n">
-        <v>46135.54842592592</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2047193753073357199</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>2047193753073357199</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>إنفاقك ليس مجرد أرقام عشوائية، هنالك نمط خفي في معاملاتك ينتظر أن تكتشفه.
-راجع آخر 10 معاملات لديك،
-وابحث عن التكرار لا عن المبالغ،
-وستكتشف سريعاً ما يستنزف أموالك أكثر.
-فالأمر يتعلق بالعادات، لا بالمشتريات.</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>1776924000000</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>2047193753073357199</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v>1</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" s="2" t="n">
-        <v>46135.41666666666</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047193753073357199</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2047193753073357199</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>2047193755975917822</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047193755975917822</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>#نظرتك_المالية #التثقيف_المالي #الإمارات_الإسلامي
-https://t.co/mgtIcQsyLZ</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>1776924001000</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>2047193753073357199</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18449, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>2047193753073357199</t>
-        </is>
-      </c>
-      <c r="P109" s="2" t="n">
-        <v>46135.41667824074</v>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2047541041612427486</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="n">
+        <v>46136.37501157408</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P80"/>
+  <dimension ref="A1:P74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,7 +558,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'KARIM 🎩', 'screenName': 'karim_alharby', 'followersCount': 8056, 'favouritesCount': 31929, 'friendsCount': 441, 'description': 'Perfumer &amp; owner @ https://t.co/k1MCEdWq9g'}</t>
+          <t>{'name': 'KARIM 🎩', 'screenName': 'karim_alharby', 'followersCount': 8064, 'favouritesCount': 31929, 'friendsCount': 441, 'description': 'Perfumer &amp; owner @ https://t.co/k1MCEdWq9g'}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -571,11 +571,11 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -586,92 +586,300 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2047712208696614977</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2042645533164999079</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2042645533164999079</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>سيارة حلمك تقدر تتملكها
+جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1775839620000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2042645533164999079</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1796</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="2" t="n">
+        <v>46122.86597222222</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2047712208696614977</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2047712208696614977</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA اود تقديم قرض كيف أتواصل معكم</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1777047609000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2042645533164999079</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'name': 'Barigi', 'screenName': 'Barigiin7m', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 103, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2042645533164999079</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>46136.84732638889</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2047712208696614977</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2047714668169339163</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047714668169339163</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>@Barigiin7m يرجي مراجعه التفاصيل وكيفيه التقديم من خلال هذا الرابط
+https://t.co/QV8KdPce6H</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1777048196000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2042645533164999079</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2047712208696614977</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>46136.85412037037</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2047692986402643994</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>2047692986402643994</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
 Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F6" t="n">
         <v>1777043026000</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2047692986402643994</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGrd61bXUAAXvdG.jpg', 'type': 'photo', 'id': '2047692983437316096'}]</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39175, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39176, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" s="2" t="n">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="n">
         <v>46136.79428240741</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2047692986402643994</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2046851288172810389</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://x.com/ENBDdeals/status/2046851288172810389</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>باقة ورد لكل لحظة مميزة مع فلاورد 💐
 احصل على خصم 20% على تنسيقات الورود الأنيقة، حصريًا عبر تطبيق تستاهل.
@@ -679,252 +887,44 @@
 https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F7" t="n">
         <v>1776842350000</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>2046851288172810389</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGfgZjWWYAARtsk.jpg', 'type': 'photo', 'id': '2046851285253513216'}]</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39175, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39176, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" s="2" t="n">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="2" t="n">
         <v>46134.47164351852</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2047712208696614977</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2042645533164999079</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2042645533164999079</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>سيارة حلمك تقدر تتملكها
-جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1775839620000</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2042645533164999079</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1795</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" s="2" t="n">
-        <v>46122.86597222222</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2047712208696614977</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2047712208696614977</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA اود تقديم قرض كيف أتواصل معكم</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1777047609000</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2042645533164999079</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>{'name': 'Barigi', 'screenName': 'Barigiin7m', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 103, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2042645533164999079</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>46136.84732638889</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2047712208696614977</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2047714668169339163</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047714668169339163</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>@Barigiin7m يرجي مراجعه التفاصيل وكيفيه التقديم من خلال هذا الرابط
-https://t.co/QV8KdPce6H</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1777048196000</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2042645533164999079</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2047712208696614977</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>46136.85412037037</v>
       </c>
     </row>
     <row r="8">
@@ -1035,7 +1035,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1908,12 +1908,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1975,12 +1975,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2045,12 +2045,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2116,12 +2116,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2186,12 +2186,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2256,12 +2256,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2326,31 +2326,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2047691273159528852</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA الووووو .</t>
+          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1777042846000</v>
+        <v>1777042618000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2390,41 +2390,41 @@
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46136.79219907407</v>
+        <v>46136.78956018519</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047692228684878061</t>
+          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2047692228684878061</t>
+          <t>2047678055070757117</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2047692437317988536</t>
+          <t>2047678055070757117</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047692437317988536</t>
+          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>@fortyxxl88 مرحبا شكرا لتواصلك معنا . يُرجى إرسال التفاصيل الخاصه بطلبك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
+          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1777042895000</v>
+        <v>1777039467000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047678055070757117</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17365, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2451,184 +2451,181 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2047692228684878061</t>
-        </is>
-      </c>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" s="2" t="n">
-        <v>46136.7927662037</v>
+        <v>46136.75309027778</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047666831612149831</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047620964712693908</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047620964712693908</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>1777042618000</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2046820251229159879</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>{'name': 'forty', 'screenName': 'fortyxxl88', 'followersCount': 1, 'favouritesCount': 43, 'friendsCount': 50, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2047673420695920899</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="n">
-        <v>46136.78956018519</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2047678055070757117</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>2047678055070757117</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>1777039467000</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>2047678055070757117</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" s="2" t="n">
-        <v>46136.75309027778</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2047666831612149831</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2047620964712693908</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047620964712693908</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
         <is>
           <t>You get an unexpected payment request. What do you do?
 Stay Safe, Stay Vigilant. #UnitedAgainstFraud
 https://t.co/YpRWtBZrhq</t>
         </is>
       </c>
+      <c r="F30" t="n">
+        <v>1777025855000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2047620964712693908</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174354, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="n">
+        <v>46136.59554398148</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2047666831612149831</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2047666831612149831</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Is this biggest joke ?</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1777036791000</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2047620964712693908</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'name': 'Ayesha.amala', 'screenName': 'AmalaAyesha', 'followersCount': 39, 'favouritesCount': 20, 'friendsCount': 135, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2047620964712693908</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46136.72211805556</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2047666831612149831</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2047668962998034824</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2047668962998034824</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>@AmalaAyesha Hi Ayesha, Please find the below link for more details. Thanks- Zubair 
+https://t.co/YpRWtBZrhq</t>
+        </is>
+      </c>
       <c r="F32" t="n">
-        <v>1777025855000</v>
+        <v>1777037299000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2642,11 +2639,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174354, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2655,50 +2652,55 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2047666831612149831</t>
+        </is>
+      </c>
       <c r="P32" s="2" t="n">
-        <v>46136.59554398148</v>
+        <v>46136.72799768519</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is this biggest joke ?</t>
+          <t>Very disappointed with @ENBDdeals 
+I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1777036791000</v>
+        <v>1777027909000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2047620964712693908</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2708,7 +2710,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Ayesha.amala', 'screenName': 'AmalaAyesha', 'followersCount': 39, 'favouritesCount': 20, 'friendsCount': 135, 'description': ''}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2721,55 +2723,50 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2047620964712693908</t>
-        </is>
-      </c>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>46136.72211805556</v>
+        <v>46136.61931712963</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2047668962998034824</t>
+          <t>2047629581159477750</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047668962998034824</t>
+          <t>https://x.com/ren_fernz/status/2047629581159477750</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>@AmalaAyesha Hi Ayesha, Please find the below link for more details. Thanks- Zubair 
-https://t.co/YpRWtBZrhq</t>
+          <t>I tried to contact in Jan and Feb on WhatsApp but was unable to contact with customer service in Feb it was due to ramdan . Last I came back to pay the bills and I saw the outstanding balance is again more . I saw the transaction history there is nothing but when I contact CS</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1777037299000</v>
+        <v>1777027909000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2047620964712693908</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2779,11 +2776,11 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -2796,16 +2793,16 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2047629578990936518</t>
         </is>
       </c>
       <c r="P34" s="2" t="n">
-        <v>46136.72799768519</v>
+        <v>46136.61931712963</v>
       </c>
     </row>
     <row r="35">
@@ -2866,7 +2863,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
@@ -2943,372 +2940,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
+          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2047629586435817682</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2047629578990936518</t>
+          <t>2047628468545110433</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
+          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
-        <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>1777027909000</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>2047629578990936518</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" s="2" t="n">
-        <v>46136.61931712963</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2047629586435817682</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>2047629581159477750</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629581159477750</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>I tried to contact in Jan and Feb on WhatsApp but was unable to contact with customer service in Feb it was due to ramdan . Last I came back to pay the bills and I saw the outstanding balance is again more . I saw the transaction history there is nothing but when I contact CS</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>1777027909000</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2047629578990936518</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>2047629578990936518</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="n">
-        <v>46136.61931712963</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2047629586435817682</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2047629583571186141</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629583571186141</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>They mentioned I got a penalty of late payment fees charges of 230AED +11AED vat. I asked them check if I got previously, so agent told me to check the application but on application there is nothing shown. So she told to check the Estatement.</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1777027910000</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2047629578990936518</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>2047629581159477750</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="n">
-        <v>46136.6193287037</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2047629586435817682</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>2047629586435817682</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>As I was late to university I thought just downloading and then going through so I just opened and saw that I have been charged on JAN and Feb and so I contacted ENBD CS again and asked them to revert the previous charges and they told me they can only remove for April which</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>1777027911000</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2047629578990936518</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>2047629583571186141</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="n">
-        <v>46136.61934027778</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629586435817682</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2047629586435817682</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>2047629588675575900</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>https://x.com/ren_fernz/status/2047629588675575900</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Was yesterday and they won’t able to do for Jan and Feb. My question is why don’t the @ENBDdeals application show the late fees charges applied on my card?? If I knew I would have not made the repeated mistake. I wanted to close my ADCB Bank but as I wanted to pay the CC bills</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>1777027911000</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2047629578990936518</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4057, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>2047629586435817682</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="n">
-        <v>46136.61934027778</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2047628468545110433</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2047628468545110433</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
         <is>
           <t>Breaking News 📢 Dubai Real Estate Just Entered a New Era 🌇
 ▪️50/50 Strategy: Pay 50% and leverage ENBD financing for the rest.
@@ -3316,68 +2966,68 @@
 ▪️Maximum Liquidity: Grow your portfolio without tying up all your cash. https://t.co/e4xRBY8CCu</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F37" t="n">
         <v>1777027644000</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>2047628468545110433</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC9aIAAcfHM.jpg', 'type': 'photo', 'id': '2047628390761635840'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC8acAAmIIP.jpg', 'type': 'photo', 'id': '2047628390757462016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLDCaEAAgV9I.jpg', 'type': 'photo', 'id': '2047628390782603264'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC7awAA0pEW.jpg', 'type': 'photo', 'id': '2047628390753288192'}]</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>{'name': 'D&amp;B Properties', 'screenName': 'dandbdubai', 'followersCount': 589, 'favouritesCount': 930, 'friendsCount': 828, 'description': 'Multi-Award Winning Real Estate Brokerage in Dubai\nSales | Leasing | Off-Plan | Commercial | Asset Management | Valuations &amp; Advisory | Holiday Homes'}</t>
         </is>
       </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" s="2" t="n">
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="2" t="n">
         <v>46136.61625</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>https://x.com/dandbdubai/status/2047628468545110433</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2047628468545110433</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>2046932416754012230</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://x.com/dandbdubai/status/2046932416754012230</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Proud to call the UAE home 🇦🇪
 The UAE continues to inspire, build, and lead and we’re proud to be part of that story.
@@ -3385,518 +3035,384 @@
 #UAE #ProudOfUAE #UAENationalPride #Dubai #DubaiLife https://t.co/bnUJHbF5lp</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F38" t="n">
         <v>1776861692000</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>2046932416754012230</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2046932359065591808/img/bJGTr1dd5W2_rytA.jpg', 'type': 'video', 'id': '2046932359065591808'}]</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>{'name': 'D&amp;B Properties', 'screenName': 'dandbdubai', 'followersCount': 589, 'favouritesCount': 930, 'friendsCount': 828, 'description': 'Multi-Award Winning Real Estate Brokerage in Dubai\nSales | Leasing | Off-Plan | Commercial | Asset Management | Valuations &amp; Advisory | Holiday Homes'}</t>
         </is>
       </c>
-      <c r="J43" t="n">
+      <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" s="2" t="n">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="n">
         <v>46134.69550925926</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>2047601280143724646</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>2047601280143724646</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F39" t="n">
         <v>1777021162000</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>2047601280143724646</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>{'name': 'Kang Hori', 'screenName': 'XSilverMermaidX', 'followersCount': 172, 'favouritesCount': 3163, 'friendsCount': 162, 'description': '🔬💼👩🏻\u200d💻🇦🇪'}</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="J39" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" s="2" t="n">
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="2" t="n">
         <v>46136.54122685185</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>2047601280143724646</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>2047606015684718778</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2047606015684718778</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>@XSilverMermaidX We have replied to your message in private</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F40" t="n">
         <v>1777022291000</v>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>2047601280143724646</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="inlineStr">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174354, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2047601280143724646</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>46136.55429398148</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2047564934997762494</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>1777091876819</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="2" t="n">
+        <v>46137.35968540509</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2047564934997762494</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2047564934997762494</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1777012497000</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2047367142367191224</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'name': 'Zach Roseman', 'screenName': 'zachrose51', 'followersCount': 697, 'favouritesCount': 10161, 'friendsCount': 485, 'description': 'Cold outbound is dead. Building the fix @Draftboard - map warm intro paths from your network to your prospects. Ex-CEO Mosaic Group (acq. by Bending Spoons)'}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>2047601280143724646</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="n">
-        <v>46136.55429398148</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2047512157030645934</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>2047512157030645934</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1776999913000</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2047512157030645934</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" s="2" t="n">
-        <v>46136.29528935185</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2047564934997762494</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2047367142367191224</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>https://x.com/zachrose51/status/2047367142367191224</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>We just killed cold email: Introducing Draftboard.
-The world’s first AI Sales Director that outperforms any human.
-Comment your website and we’ll find you intros to 10 dream prospects for free. https://t.co/DK7wDKVQl7</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>1776965339000</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2047367142367191224</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2047366826984972288/img/qZKW_Emc0-7B9Jot.jpg', 'type': 'video', 'id': '2047366826984972288'}]</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>{'name': 'Zach Roseman', 'screenName': 'zachrose51', 'followersCount': 690, 'favouritesCount': 10161, 'friendsCount': 485, 'description': 'Cold outbound is dead. Building the fix @Draftboard - map warm intro paths from your network to your prospects. Ex-CEO Mosaic Group (acq. by Bending Spoons)'}</t>
-        </is>
-      </c>
-      <c r="J47" t="n">
-        <v>573</v>
-      </c>
-      <c r="K47" t="n">
-        <v>152</v>
-      </c>
-      <c r="L47" t="n">
-        <v>94</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1132</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>780455</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" s="2" t="n">
-        <v>46135.89512731481</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2047564934997762494</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="n">
-        <v>1777084592387</v>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" s="2" t="n">
-        <v>46137.27537484954</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2047564934997762494</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2047564934997762494</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1777012497000</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2047367142367191224</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>{'name': 'Zach Roseman', 'screenName': 'zachrose51', 'followersCount': 690, 'favouritesCount': 10161, 'friendsCount': 485, 'description': 'Cold outbound is dead. Building the fix @Draftboard - map warm intro paths from your network to your prospects. Ex-CEO Mosaic Group (acq. by Bending Spoons)'}</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>2047564727421964462</t>
         </is>
       </c>
-      <c r="P49" s="2" t="n">
+      <c r="P42" s="2" t="n">
         <v>46136.4409375</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>https://x.com/hkayyal/status/2047530498705195395</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>2047530498705195395</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>2047530181221613706</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>https://x.com/hkayyal/status/2047530181221613706</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>🧵 Gulf Fintech Daily — April 24, 2026
 AI as infrastructure. Sovereign capital as catalyst. 5 stories 👇
 #GulfFintech #MENA #FinTech</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F43" t="n">
         <v>1777004211000</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>2047530181221613706</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 689, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 690, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
         <v>6</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>2</v>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" s="2" t="n">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="2" t="n">
         <v>46136.34503472222</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>https://x.com/hkayyal/status/2047530498705195395</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>2047530498705195395</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>2047530498705195395</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>https://x.com/hkayyal/status/2047530498705195395</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>3️⃣ Dubai South × Emirates NBD sign MoU for streamlined SME banking access.
 Corporate account opening + tailored banking within the free zone.
@@ -3904,12 +3420,490 @@
 #Dubai #SME #D33</t>
         </is>
       </c>
+      <c r="F44" t="n">
+        <v>1777004286000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2047530181221613706</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 690, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2047530181221613706</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>46136.34590277778</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2047512157030645934</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2047512157030645934</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1776999913000</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2047512157030645934</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" s="2" t="n">
+        <v>46136.29528935185</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2047511223839908158</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2047511223839908158</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1776999691000</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2047511223839908158</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="n">
+        <v>46136.2927199074</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2047511223839908158</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2047534633697308773</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2047534633697308773</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>@abhiseksonusonu We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to livsocialconnect@liv.me and tag the case reference number #1001503 in the subject line.</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1777005272000</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2047511223839908158</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174354, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2047511223839908158</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>46136.35731481481</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2047835274818748466</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2029505253947629989</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/JDunlap1974/status/2029505253947629989</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1772706733000</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2029505253947629989</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2029505138055139328/pu/img/WpN4JWq99VF-NMQD.jpg', 'type': 'video', 'id': '2029505138055139328'}]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'name': 'JOSH DUNLAP', 'screenName': 'JDunlap1974', 'followersCount': 373925, 'favouritesCount': 120459, 'friendsCount': 44620, 'description': '🇺🇲 MAYOR OF MAGADONIA 🇺🇲 ✝️ CHRISTIAN ✝️ MAGA\n📣 📣BREAKING NEWS FIRST HERE 📣📣'}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>16</v>
+      </c>
+      <c r="K48" t="n">
+        <v>14</v>
+      </c>
+      <c r="L48" t="n">
+        <v>279</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1256</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>11957</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" s="2" t="n">
+        <v>46086.60570601852</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2047835274818748466</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2029530832042393630</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/iDenville/status/2029530832042393630</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>@JDunlap1974 Now audit North Carolina's primaries!!  This is Lakeshia Alston, the woman who ran for election as a REPUBLICAN and won!! https://t.co/vQrXOOfnIW</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1772712831000</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2029505253947629989</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCpXbMYbwAEvTXt.jpg', 'type': 'photo', 'id': '2029530706775621633'}]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23517, 'favouritesCount': 181621, 'friendsCount': 23656, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>7</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>9</v>
+      </c>
+      <c r="M49" t="n">
+        <v>13</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>6300</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2029505253947629989</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>46086.67628472222</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2047835274818748466</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2047834245423395027</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/stelpetla/status/2047834245423395027</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>@iDenville @JDunlap1974 How are they allowed to enter a bank? I’m not allowed to go in my bank wearing sunglasses or a hat.</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1777076705000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2029505253947629989</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'name': 'Stella Pet 🇺🇸', 'screenName': 'stelpetla', 'followersCount': 685, 'favouritesCount': 27506, 'friendsCount': 1544, 'description': 'GenX/Jersey Girl. 🇺🇸 Mayflower Descendant, DAR. 12th generation American. Trump X 3'}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2029530832042393630</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>46137.18408564815</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2047835274818748466</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2047835274818748466</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>@stelpetla @JDunlap1974 Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
+        </is>
+      </c>
       <c r="F51" t="n">
-        <v>1777004286000</v>
+        <v>1777076951000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2047530181221613706</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3919,7 +3913,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 689, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
+          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23517, 'favouritesCount': 181621, 'friendsCount': 23656, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
         </is>
       </c>
       <c r="J51" t="n">
@@ -3932,71 +3926,74 @@
         <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2047530181221613706</t>
+          <t>2047834245423395027</t>
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>46136.34590277778</v>
+        <v>46137.18693287037</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
+Also, enjoy exclusive benefits:
+📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
+🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1776999691000</v>
+        <v>1777028400000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp7wFoXwAAtDsB.jpg', 'type': 'photo', 'id': '2047585046668754944'}]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J52" t="n">
         <v>1</v>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -4006,46 +4003,50 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>31</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" s="2" t="n">
-        <v>46136.2927199074</v>
+        <v>46136.625</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2047534633697308773</t>
+          <t>2047631643901390924</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047534633697308773</t>
+          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>@abhiseksonusonu We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to livsocialconnect@liv.me and tag the case reference number #1001503 in the subject line.</t>
+          <t>✈️Payment holiday up to 6 months 
+🔒 Complimentary Takaful coverage
+Offer valid until 30 April 2026.
+T&amp;amp;Cs apply.
+https://t.co/ZafvBWp0Cl</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1777005272000</v>
+        <v>1777028401000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4055,7 +4056,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174349, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -4072,316 +4073,40 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="P53" s="2" t="n">
-        <v>46136.35731481481</v>
+        <v>46136.62501157408</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
+          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2047835274818748466</t>
+          <t>2047631640168374617</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2029505253947629989</t>
+          <t>2047717988195852322</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://x.com/JDunlap1974/status/2029505253947629989</t>
+          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
-        <is>
-          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1772706733000</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2029505138055139328/pu/img/WpN4JWq99VF-NMQD.jpg', 'type': 'video', 'id': '2029505138055139328'}]</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>{'name': 'JOSH DUNLAP', 'screenName': 'JDunlap1974', 'followersCount': 373876, 'favouritesCount': 120459, 'friendsCount': 44620, 'description': '🇺🇲 MAYOR OF MAGADONIA 🇺🇲 ✝️ CHRISTIAN ✝️ MAGA\n📣 📣BREAKING NEWS FIRST HERE 📣📣'}</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>16</v>
-      </c>
-      <c r="K54" t="n">
-        <v>14</v>
-      </c>
-      <c r="L54" t="n">
-        <v>279</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1256</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>11940</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" s="2" t="n">
-        <v>46086.60570601852</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2047835274818748466</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2029530832042393630</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2029530832042393630</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>@JDunlap1974 Now audit North Carolina's primaries!!  This is Lakeshia Alston, the woman who ran for election as a REPUBLICAN and won!! https://t.co/vQrXOOfnIW</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1772712831000</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCpXbMYbwAEvTXt.jpg', 'type': 'photo', 'id': '2029530706775621633'}]</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23509, 'favouritesCount': 181621, 'friendsCount': 23653, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>6</v>
-      </c>
-      <c r="K55" t="n">
-        <v>3</v>
-      </c>
-      <c r="L55" t="n">
-        <v>9</v>
-      </c>
-      <c r="M55" t="n">
-        <v>13</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>5793</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="n">
-        <v>46086.67628472222</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2047835274818748466</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2047834245423395027</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://x.com/stelpetla/status/2047834245423395027</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>@iDenville @JDunlap1974 How are they allowed to enter a bank? I’m not allowed to go in my bank wearing sunglasses or a hat.</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1777076705000</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>{'name': 'Stella Pet 🇺🇸', 'screenName': 'stelpetla', 'followersCount': 685, 'favouritesCount': 27507, 'friendsCount': 1544, 'description': 'GenX/Jersey Girl. 🇺🇸 Mayflower Descendant, DAR. 12th generation American. Trump X 3'}</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>2029530832042393630</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="n">
-        <v>46137.18408564815</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2047835274818748466</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2047835274818748466</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>@stelpetla @JDunlap1974 Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1777076951000</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23509, 'favouritesCount': 181621, 'friendsCount': 23653, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>1</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2047834245423395027</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>46137.18693287037</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2047717990762782723</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2047717988195852322</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
         <is>
           <t>🇦🇪 We salute the nation’s heroes 
 We value your commitment and have designed exclusive banking benefits for your peace of mind.
@@ -4389,68 +4114,204 @@
 🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="F54" t="n">
         <v>1777048987000</v>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>2047717988195852322</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
         <v>1</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>1</v>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" s="2" t="n">
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="2" t="n">
         <v>46136.86327546297</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2047575014564921667</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2047575014564921667</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
+Read more on https://t.co/I3d8g2xghd
+#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1777014900000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2047575014564921667</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl1UAxasAAkYXs.jpg', 'type': 'photo', 'id': '2047296492281704448'}]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 356, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>46136.46875</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2047575014564921667</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2047597663634457003</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/ABCinGCC/status/2047597663634457003</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>UAE-based @AziziGroup  Developments has announced that construction at Beach Oasis II - its vibrant mixed-use community in the dynamic, rapidly growing Dubai Studio City - has reached 43% completion.
+Read more on https://t.co/Y5AVR722nO
+#ABCNews #Developments #BeachOasis #UAE https://t.co/eVcDwo33OV</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1777020300000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2047597663634457003</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl180kaQAAsBhe.jpg', 'type': 'photo', 'id': '2047297193380560896'}]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 356, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" s="2" t="n">
+        <v>46136.53125</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>2047717990762782723</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>2047717990762782723</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>⏳Payment holidays
 🎁 Exclusive prizes with Kunooz Millionaire Account
@@ -4460,419 +4321,140 @@
 #EmiratesIslamic #FrontlineHeroes</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="F57" t="n">
         <v>1777048988000</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>2047717988195852322</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
         <is>
           <t>2047717988195852322</t>
         </is>
       </c>
-      <c r="P59" s="2" t="n">
+      <c r="P57" s="2" t="n">
         <v>46136.86328703703</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2047575014564921667</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2047575014564921667</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on https://t.co/I3d8g2xghd
-#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1777014900000</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2047575014564921667</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl1UAxasAAkYXs.jpg', 'type': 'photo', 'id': '2047296492281704448'}]</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" s="2" t="n">
-        <v>46136.46875</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2047575014564921667</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2047597663634457003</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2047597663634457003</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>UAE-based @AziziGroup  Developments has announced that construction at Beach Oasis II - its vibrant mixed-use community in the dynamic, rapidly growing Dubai Studio City - has reached 43% completion.
-Read more on https://t.co/Y5AVR722nO
-#ABCNews #Developments #BeachOasis #UAE https://t.co/eVcDwo33OV</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1777020300000</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2047597663634457003</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl180kaQAAsBhe.jpg', 'type': 'photo', 'id': '2047297193380560896'}]</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 355, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" s="2" t="n">
-        <v>46136.53125</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1777028400000</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp7wFoXwAAtDsB.jpg', 'type': 'photo', 'id': '2047585046668754944'}]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" s="2" t="n">
-        <v>46136.625</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2047631643901390924</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;amp;Cs apply.
-https://t.co/ZafvBWp0Cl</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1777028401000</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>46136.62501157408</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>2047717988195852322</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>2047717917324710124</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
 تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
 📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="F58" t="n">
         <v>1777048970000</v>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>2047717917324710124</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0l1oXYAEHNu8.jpg', 'type': 'photo', 'id': '2047717911482032129'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0mAsWkAIOAAv.jpg', 'type': 'photo', 'id': '2047717914451546114'}]</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" s="2" t="n">
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="2" t="n">
         <v>46136.8630787037</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>2047556140431556611</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>2047556140431556611</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>You have an unpaid fine – click here
 Do not fall for the traps. Stay alert to scams.
@@ -4881,68 +4463,144 @@
 https://t.co/y7eSpGNdfk</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="F59" t="n">
         <v>1777010400000</v>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>2047556140431556611</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" s="2" t="n">
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="2" t="n">
         <v>46136.41666666666</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2047717920193622257</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2047717920193622257</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>🏦 بدون رسوم إجراءات
+⏳ تأجيل الأقساط
+🎁 جوائز حصرية مع حساب كنوز المليونير
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+https://t.co/N2GRIcHWnS
+#الإمارات_الإسلامي #أبطال_الوطن</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1777048971000</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2047717917324710124</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2047717917324710124</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="n">
+        <v>46136.86309027778</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>2047657988064727443</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>2047657988064727443</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
 📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
@@ -4954,144 +4612,68 @@
 تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="F61" t="n">
         <v>1777034682000</v>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>2047657988064727443</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FHDWUAA0A9i.jpg', 'type': 'photo', 'id': '2047657975595028480'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FZ7WkAAuMQK.jpg', 'type': 'photo', 'id': '2047657980661764096'}]</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" s="2" t="n">
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" s="2" t="n">
         <v>46136.69770833333</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2047717917324710124</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2047717920193622257</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-https://t.co/N2GRIcHWnS
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1777048971000</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2047717917324710124</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2047717917324710124</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="n">
-        <v>46136.86309027778</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>2047657972390560162</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>2047657960227176876</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
 📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
@@ -5103,138 +4685,138 @@
 تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="F62" t="n">
         <v>1777034676000</v>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>2047657960227176876</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-Dy9W4AA2EvQ.jpg', 'type': 'photo', 'id': '2047657953021321216'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-ECIWoAAdlCp.jpg', 'type': 'photo', 'id': '2047657957093974016'}]</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" s="2" t="n">
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" s="2" t="n">
         <v>46136.69763888889</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>2047657972390560162</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>2047657962978558100</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>لمعرفة المزيد، يرجى زيارة https://t.co/Dacednep0G</t>
         </is>
       </c>
-      <c r="F69" t="n">
+      <c r="F63" t="n">
         <v>1777034676000</v>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>2047657960227176876</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
         <is>
           <t>2047657960227176876</t>
         </is>
       </c>
-      <c r="P69" s="2" t="n">
+      <c r="P63" s="2" t="n">
         <v>46136.69763888889</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>2047657972390560162</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>2047657972390560162</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Introducing the ALPHA Youth Account, a banking experience that offers:
 📱 Access to a dedicated mobile app
@@ -5245,211 +4827,211 @@
 Start them young! https://t.co/cHbCHEecyD</t>
         </is>
       </c>
-      <c r="F70" t="n">
+      <c r="F64" t="n">
         <v>1777034678000</v>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>2047657960227176876</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EiyXYAAScez.jpg', 'type': 'photo', 'id': '2047657965860118528'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EwlWwAAzeCE.jpg', 'type': 'photo', 'id': '2047657969563648000'}]</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
         <is>
           <t>2047657962978558100</t>
         </is>
       </c>
-      <c r="P70" s="2" t="n">
+      <c r="P64" s="2" t="n">
         <v>46136.69766203704</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>2047657972390560162</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>2047657974936604881</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Terms &amp;amp; condition apply.
 To know more, please visit https://t.co/Um2N1hjaxk</t>
         </is>
       </c>
-      <c r="F71" t="n">
+      <c r="F65" t="n">
         <v>1777034679000</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>2047657960227176876</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
         <is>
           <t>2047657972390560162</t>
         </is>
       </c>
-      <c r="P71" s="2" t="n">
+      <c r="P65" s="2" t="n">
         <v>46136.69767361111</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>2047632173461561410</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>2047632164863250935</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
 Enjoy more rewards:
 💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
         </is>
       </c>
-      <c r="F72" t="n">
+      <c r="F66" t="n">
         <v>1777028525000</v>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>2047632164863250935</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmaBXUAEX6Xi.jpg', 'type': 'photo', 'id': '2047632159343595521'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmlvW4AErjsf.jpg', 'type': 'photo', 'id': '2047632162489294849'}]</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
         <v>1</v>
       </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" s="2" t="n">
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" s="2" t="n">
         <v>46136.62644675926</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>2047632173461561410</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>2047632173461561410</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>🎁 Reward of AED 100 with an ALPHA Youth Account
 And much more.
@@ -5458,140 +5040,140 @@
 https://t.co/Hgg0TFDsUE https://t.co/MBZ0YjVgiN</t>
         </is>
       </c>
-      <c r="F73" t="n">
+      <c r="F67" t="n">
         <v>1777028527000</v>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>2047632164863250935</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmm5VWkAAB2mi.jpg', 'type': 'photo', 'id': '2047632167748931584'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmnGiWkAAtXIq.jpg', 'type': 'photo', 'id': '2047632171293118464'}]</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
         <is>
           <t>2047632164863250935</t>
         </is>
       </c>
-      <c r="P73" s="2" t="n">
+      <c r="P67" s="2" t="n">
         <v>46136.62646990741</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2047632125583605871</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
         <is>
           <t>2047632116649689120</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2047632116649689120</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
 استمتع بالمزيد من المكافآت:
 💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
         </is>
       </c>
-      <c r="F74" t="n">
+      <c r="F68" t="n">
         <v>1777028514000</v>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>2047632116649689120</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjnLXwAAvwdB.jpg', 'type': 'photo', 'id': '2047632111335620608'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjyyXAAAadnx.jpg', 'type': 'photo', 'id': '2047632114451939328'}]</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
         <v>1</v>
       </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" s="2" t="n">
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" s="2" t="n">
         <v>46136.62631944445</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2047632116649689120</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2047632125583605871</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2047632125583605871</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2047632125583605871</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
 🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
@@ -5601,72 +5183,72 @@
 https://t.co/909hzRsLZr https://t.co/Ff41FuCAen</t>
         </is>
       </c>
-      <c r="F75" t="n">
+      <c r="F69" t="n">
         <v>1777028516000</v>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>2047632116649689120</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkG7WcAEveRR.jpg', 'type': 'photo', 'id': '2047632119858360321'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkUZWQAEKDDE.jpg', 'type': 'photo', 'id': '2047632123473838081'}]</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
         <is>
           <t>2047632116649689120</t>
         </is>
       </c>
-      <c r="P75" s="2" t="n">
+      <c r="P69" s="2" t="n">
         <v>46136.62634259259</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>2047631643926483032</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>2047631639946093018</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
 استمتع أيضاً بالمزايا الحصرية:
@@ -5674,68 +5256,68 @@
 🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
         </is>
       </c>
-      <c r="F76" t="n">
+      <c r="F70" t="n">
         <v>1777028400000</v>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>2047631639946093018</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp1V6aW8AAL6dm.jpg', 'type': 'photo', 'id': '2047577999910825984'}]</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
         <v>1</v>
       </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" s="2" t="n">
         <v>46136.625</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>2047631643926483032</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>2047631643926483032</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
 🔒 تغطية تكافلية
@@ -5744,72 +5326,72 @@
 https://t.co/WVHANHvCwT</t>
         </is>
       </c>
-      <c r="F77" t="n">
+      <c r="F71" t="n">
         <v>1777028401000</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>2047631639946093018</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
         <is>
           <t>2047631639946093018</t>
         </is>
       </c>
-      <c r="P77" s="2" t="n">
+      <c r="P71" s="2" t="n">
         <v>46136.62501157408</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>2047556140511162463</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>2047556140511162463</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
 لا تقع في الفخ. احذر الاحتيال.
@@ -5817,183 +5399,183 @@
 https://t.co/ltnxcRlBOA</t>
         </is>
       </c>
-      <c r="F78" t="n">
+      <c r="F72" t="n">
         <v>1777010400000</v>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>2047556140511162463</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" s="2" t="n">
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" s="2" t="n">
         <v>46136.41666666666</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>2047541041612427486</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>2047541041612427486</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
 من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
 #فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
         </is>
       </c>
-      <c r="F79" t="n">
+      <c r="F73" t="n">
         <v>1777006800000</v>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>2047541041612427486</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047358056963473408/pu/img/J1OcKdI5JfoHlVrB.jpg', 'type': 'video', 'id': '2047358056963473408'}]</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
         <v>1</v>
       </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
         <v>3</v>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" s="2" t="n">
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" s="2" t="n">
         <v>46136.375</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>2047541041612427486</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>2047541045768962304</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
 Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
 #ProudOfUAE</t>
         </is>
       </c>
-      <c r="F80" t="n">
+      <c r="F74" t="n">
         <v>1777006801000</v>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>2047541041612427486</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18451, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
         <is>
           <t>2047541041612427486</t>
         </is>
       </c>
-      <c r="P80" s="2" t="n">
+      <c r="P74" s="2" t="n">
         <v>46136.37501157408</v>
       </c>
     </row>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,38 +517,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2047809819265110291</t>
+          <t>2048213606257570300</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2047809819265110291</t>
+          <t>2047936203438362829</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/karim_alharby/status/2047809819265110291</t>
+          <t>https://x.com/AmritMohanty1/status/2047936203438362829</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>حبيت أفتح حساب جولد في بنك المشرق لقيتهم عاوزني ابقى مليونير علشان يبدأو معايا الكلام بسم الله يا سيد الناس خد الشروط..
-راتبك 80 الف درهم فيما فوق 
-رصيدك مينزلش عن 500 الف درهم 
-كان في شرط تالت ورابع قومت فاتح المحفظة وبايس كروت ADCB و ENBD و البنك الأهلي المصري وصليت ركعتين شكر</t>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1777070882000</v>
+        <v>1777101014000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2047809819265110291</t>
+          <t>2047936203438362829</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -558,11 +555,11 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'KARIM 🎩', 'screenName': 'karim_alharby', 'followersCount': 8064, 'favouritesCount': 31929, 'friendsCount': 441, 'description': 'Perfumer &amp; owner @ https://t.co/k1MCEdWq9g'}</t>
+          <t>{'name': 'Amrit Mohanty', 'screenName': 'AmritMohanty1', 'followersCount': 8, 'favouritesCount': 144, 'friendsCount': 136, 'description': 'Everything that’s here are my opinions. Not necessarily shared by reasonable-minded people nor my benevolent corporate overlords!!'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -571,51 +568,50 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>143</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46137.11668981481</v>
+        <v>46137.46543981481</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2047712208696614977</t>
+          <t>2048213606257570300</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2042645533164999079</t>
+          <t>2047939066302267716</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2042645533164999079</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2047939066302267716</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سيارة حلمك تقدر تتملكها
-جديدة ولا مستعملة نمولها لك مع التمويل التأجيري للسيارات من بنك الإمارات دبي الوطني</t>
+          <t>@AmritMohanty1 Hi Amrit! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1001922 in the subject line of the email.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1775839620000</v>
+        <v>1777101696000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2042645533164999079</t>
+          <t>2047936203438362829</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -625,63 +621,67 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174414, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1796</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2047936203438362829</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="n">
-        <v>46122.86597222222</v>
+        <v>46137.47333333334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2047712208696614977</t>
+          <t>2048213606257570300</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2047712208696614977</t>
+          <t>2048213606257570300</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA اود تقديم قرض كيف أتواصل معكم</t>
+          <t>@EmiratesNBD_AE Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777047609000</v>
+        <v>1777167152000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2042645533164999079</t>
+          <t>2047936203438362829</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,11 +691,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Barigi', 'screenName': 'Barigiin7m', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 103, 'description': ''}</t>
+          <t>{'name': 'Amrit Mohanty', 'screenName': 'AmritMohanty1', 'followersCount': 8, 'favouritesCount': 144, 'friendsCount': 136, 'description': 'Everything that’s here are my opinions. Not necessarily shared by reasonable-minded people nor my benevolent corporate overlords!!'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -708,51 +708,58 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2042645533164999079</t>
+          <t>2047939066302267716</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46136.84732638889</v>
+        <v>46138.23092592593</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/Barigiin7m/status/2047712208696614977</t>
+          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2047712208696614977</t>
+          <t>2048234825199526119</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2047714668169339163</t>
+          <t>2048234825199526119</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047714668169339163</t>
+          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>@Barigiin7m يرجي مراجعه التفاصيل وكيفيه التقديم من خلال هذا الرابط
-https://t.co/QV8KdPce6H</t>
+          <t>IDBI बैंक विनिवेश: क्या है ताजा अपडेट? 
+​IDBI बैंक के निजीकरण की प्रक्रिया एक बार फिर चर्चा में है। बाजार में चल रही ताजा रिपोर्ट्स के अनुसार, इस बड़े सौदे से जुड़ी कुछ महत्वपूर्ण बातें सामने आ रही हैं:
+​प्रमुख दावेदार: दुबई का Emirates NBD और कनाडा का Fairfax Group इस रेस में आगे बताए जा रहे हैं। दोनों की नजर बैंक में करीब 60.7% हिस्सेदारी पर है।
+​सरकार और LIC की भूमिका: भारत सरकार और LIC अपनी हिस्सेदारी बेचने की तैयारी में हैं। यह बैंकिंग सेक्टर के सबसे बड़े विनिवेश सौदों में से एक हो सकता है।
+​RBI की जांच जारी: वर्तमान में रिज़र्व बैंक (RBI) संभावित खरीदारों का Fit and Proper टेस्ट कर रहा है। बैंकिंग लाइसेंस के नियमों के तहत यह एक अनिवार्य और कड़ी प्रक्रिया है।
+​लक्ष्य: सरकार इस पूरी प्रक्रिया को अगले वित्त वर्ष तक पूरा करने का प्रयास कर रही है।
+​निष्कर्ष:
+हालांकि चर्चाएं तेज हैं, लेकिन अंतिम निर्णय RBI की मंजूरी और औपचारिक वित्तीय बोलियों के बाद ही होगा। बैंकिंग सेक्टर में यह बदलाव आने वाले समय में काफी दिलचस्प हो सकता है।
+​#IDBIBank #BankingNews #EconomyUpdate #Disinvestment #StockMarketIndia #FinanceNews</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1777048196000</v>
+        <v>1777172211000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2042645533164999079</t>
+          <t>2048234825199526119</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -762,7 +769,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Prabhakar Singh Bais', 'screenName': 'theprabhakars', 'followersCount': 1985, 'favouritesCount': 1251, 'friendsCount': 0, 'description': '40+ yrs in markets | Philanthropist | \nFounder @ BullBearDigest 🚀 |\nHelping India invest with confidence 🇮🇳'}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -779,61 +786,56 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2047712208696614977</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" s="2" t="n">
-        <v>46136.85412037037</v>
+        <v>46138.28947916667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
+          <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2047692986402643994</t>
+          <t>2048234825199526119</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2047692986402643994</t>
+          <t>2048200640648876058</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
+          <t>https://x.com/theprabhakars/status/2048200640648876058</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
-Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
+          <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777043026000</v>
+        <v>1777164061000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2047692986402643994</t>
+          <t>2048200640648876058</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGrd61bXUAAXvdG.jpg', 'type': 'photo', 'id': '2047692983437316096'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39176, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Prabhakar Singh Bais', 'screenName': 'theprabhakars', 'followersCount': 1985, 'favouritesCount': 1251, 'friendsCount': 0, 'description': '40+ yrs in markets | Philanthropist | \nFounder @ BullBearDigest 🚀 |\nHelping India invest with confidence 🇮🇳'}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -843,66 +845,63 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>38</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" s="2" t="n">
-        <v>46136.79428240741</v>
+        <v>46138.19515046296</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2047692986402643994</t>
+          <t>2048231285999759759</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2046851288172810389</t>
+          <t>2048231285999759759</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2046851288172810389</t>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>باقة ورد لكل لحظة مميزة مع فلاورد 💐
-احصل على خصم 20% على تنسيقات الورود الأنيقة، حصريًا عبر تطبيق تستاهل.
-لمعرفة المزيد:
-https://t.co/quzlzhDcXR https://t.co/Pj8RmtMYOK</t>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1776842350000</v>
+        <v>1777171367000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2046851288172810389</t>
+          <t>2048231285999759759</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGfgZjWWYAARtsk.jpg', 'type': 'photo', 'id': '2046851285253513216'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39176, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'multibagg.ai', 'screenName': 'MultibaggAI', 'followersCount': 2840, 'favouritesCount': 400, 'friendsCount': 1, 'description': 'Fastest market news, earnings, reports, exchange filings to your feed.'}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -915,51 +914,50 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" s="2" t="n">
-        <v>46134.47164351852</v>
+        <v>46138.27971064814</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2048231285999759759</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2048250566065922366</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2032450113100984492</t>
+          <t>https://x.com/MultibaggAI/status/2048250566065922366</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>BIRET: PPFAS MUTUAL FUND ACQUIRED 2,16,71,826 SHARES (2.61%) OF BROOKFIELD INDIA REAL ESTATE TRUST ON 22 APR 2026, RAISING ITS STAKE FROM 7.70% TO 9.56% OF EQUITY (TOTAL SHARES 82,98,80,869).</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1773408842000</v>
+        <v>1777175964000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2048250566065922366</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -969,11 +967,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'multibagg.ai', 'screenName': 'MultibaggAI', 'followersCount': 2840, 'favouritesCount': 400, 'friendsCount': 1, 'description': 'Fastest market news, earnings, reports, exchange filings to your feed.'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -986,56 +984,80 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>46094.73196759259</v>
+        <v>46138.33291666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/phd_capital/status/2048039331512864848</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2048039331512864848</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2032452730443256247</t>
+          <t>2048039331512864848</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2032452730443256247</t>
+          <t>https://x.com/phd_capital/status/2048039331512864848</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya We sincerely regret for the inconvenience To be able to assist further, we kindly request you to kindly share your registered mobile number through direct message, We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>#RBLBANK (#RBLBank) FY26 — The Turnaround is Real. Q4 Profit surges +233% YoY. Total Business crosses ₹2.5 Lakh Cr. The Emirates NBD era begins. 
+RBL Bank has delivered a pivotal "clean-up" year, exiting FY26 as a leaner, stronger, and significantly more valuable institution. While the profit surge is eye-popping, the real headline is the transformation into a foreign bank subsidiary, setting a massive valuation floor for the stock.
+Key Numbers:
+• Q4 PAT: ₹230 Cr (+233% YoY surge)
+• Annual PAT: ₹822 Cr (+18% YoY)
+• Total Business: ₹2.50 Lakh Cr (+24% YoY)
+• Gross NPA: 1.45% (Significant improvement from 1.88% QoQ)
+• CASA Ratio: 33.60% (Up from 30.90% QoQ)
+What's genuinely exciting:
+✅ The "Emirates NBD" Floor: The proposed $3 Billion acquisition for a 74% stake transforms RBL into a foreign bank subsidiary and provides immediate strategic alpha.
+✅ Asset Quality Triumph: GNPA at 1.45% and Net NPA at 0.39%. The legacy unsecured and microfinance (JLG) stress is effectively in the rearview mirror.
+✅ Deposit Granularity: Retail deposits (&lt;₹3 Cr) grew 16%, proving the bank is successfully rebuilding a stable, lower-cost funding base.
+✅ De-risking the Book: Reduced unsecured exposure (Cards/PL) to 24% from 28%. A safer, more balanced lending profile for the new cycle.
+✅ Liquidity Fortress: An LCR of 130% provides ample headroom for the next leg of credit deployment.
+What demands scrutiny:
+❌ NIM Erosion: Net Interest Margin (NIM) fell to 4.41% (a 5-quarter low). The rising cost of deposits is currently eating into the lending spread.
+❌ Operating RoE: Despite the profit jump, RoE remains in the mid-single digits (~5.5%). Capital efficiency needs to scale toward 10%+ in FY27.
+❌ FDI Regulatory Risk: The $3B deal still awaits final government/RBI clearance; any delay remains a sentiment wildcard.
+❌ Unsecured Slippages: While the overall share is down, fresh slippages in the retail book still require a hawk’s eye as the portfolio seasons.
+The number nobody is talking about
+RBL’s CASA jump of 26% QoQ (to ₹46,723 Cr). While most mid-cap banks are struggling to hold on to low-cost deposits, RBL managed a massive sequential surge. This suggests the branch-led sourcing strategy is finally working, providing the fuel needed to defend margins in FY27.
+The thesis is compelling
+RBL Bank is a classic "Deep Value Turnaround" play. With asset quality now better than several PSU peers and a global giant (Emirates NBD) coming in at a premium valuation, the structural re-rating has just begun.
+₹2.5 Lakh Cr Business. 233% Profit Surge. Asset quality is clean, now the focus shifts to Margin expansion.
+#RBLBank #BankingSector #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch #NiftyBank #TurnaroundStory</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1773409466000</v>
+        <v>1777125602000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2048039331512864848</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGwY6vXbAAAJqnv.jpg', 'type': 'photo', 'id': '2048039327972917248'}]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'PHD CAPITAL', 'screenName': 'phd_capital', 'followersCount': 215, 'favouritesCount': 48, 'friendsCount': 1, 'description': 'PHD CAPITAL A SEBI Registered Corporate Research Analyst in Kolkata, West Bengal. Our Goal To Help People For Their Financial Future.'}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1052,50 +1074,48 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2032450113100984492</t>
-        </is>
-      </c>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" s="2" t="n">
-        <v>46094.73918981481</v>
+        <v>46137.75002314815</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/phd_capital/status/2048039331512864848</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2048039331512864848</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2032457337122791694</t>
+          <t>2048071146399252689</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2032457337122791694</t>
+          <t>https://x.com/BindassPrasad/status/2048071146399252689</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 0561891252</t>
+          <t>@phd_capital Are you stupid?
+The mumbers are cooked up.
+🤷🤦🏼‍♂️🤡</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1773410565000</v>
+        <v>1777133187000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2048039331512864848</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1105,11 +1125,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Prasad', 'screenName': 'BindassPrasad', 'followersCount': 253, 'favouritesCount': 69170, 'friendsCount': 136, 'description': 'Against all extremism that abuses, exploits, or oppresses people — no exceptions.  \nCore principle: Live, let live, and love- the only universal truth!'}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1122,64 +1142,88 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2032452730443256247</t>
+          <t>2048039331512864848</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46094.75190972222</v>
+        <v>46137.8378125</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/phd_capital/status/2048039331512864848</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2048039331512864848</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2032458133151342720</t>
+          <t>2048250725990592587</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2032458133151342720</t>
+          <t>https://x.com/phd_capital/status/2048250725990592587</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya We have shared your details with the concerned team, and they will contact you shortly.</t>
+          <t>#CANFINHOME (#CanFinHomes) FY26 — The Efficiency Engine Hits Top Gear. Q4 Profit surges +31% QoQ. Annual PAT crosses ₹1,000 Cr. RoA expands to a stellar 3.29%.
+Can Fin Homes has delivered an "outstanding" masterclass in margin management. By navigating the interest rate cycle with surgical precision, they’ve turned a falling rate environment into a profit-generating machine, posting record highs across all key return metrics.
+Key Numbers:
+•  Annual PAT: ₹1,086 Cr (+27% YoY)
+•  Q4 PAT: ₹346 Cr (+31% QoQ — Massive recovery)
+•  Net Interest Margin (NIM): 3.93% (Up from 3.64% YoY)
+•  Q4 RoA: 3.29% (Industry-leading)
+•  Annual RoE: 18.16%
+What’s genuinely exciting:
+✅ The NIM Masterclass: Annual NIMs improved to 3.93%, driven by faster repricing of liabilities. In a shifting rate cycle, Can Fin proved they have the fastest reflexes in the HFC space.
+✅ Elite Return Metrics: A quarterly RoA of 3.29% and RoE of 23.12% are figures usually reserved for the highest-quality private banks, not just HFCs.
+✅ The SENP Pivot: Their strategic shift toward the Self-Employed Non-Professional (SENP) segment (now 31% of the book) is the "secret sauce" driving superior yields.
+✅ Liquidity Fortress: With a Liquidity Coverage Ratio (LCR) of 563.5%, they aren't just safe; they are effectively "shocks-proof."
+✅ Disbursement Momentum: 23% YoY growth in disbursements (₹10,531 Cr) shows the demand engine is firing despite intense competition.
+What demands scrutiny:
+❌ The "BT-Out" Problem: High pre-payment rates (₹1,700 Cr/quarter) are dragging absolute AUM growth. They are winning on profits but losing the "volume" war to bank takeovers.
+❌ Management Vacuum: The resignation of Dy MD Vikram Saha introduces a degree of leadership transition at a critical growth juncture.
+❌ Regional Friction: Slower recovery in Karnataka and Telangana due to regulatory (e-Khata) issues remains a localized drag.
+❌ Single-Digit Asset Growth: Despite 23% disbursement growth, net AUM grew only 10%—the leak in the bucket (pre-payments) needs plugging.
+The number nobody is talking about
+Can Fin’s Annual Spread of 2.86%. While the industry is fighting for basis points, Can Fin widened its spread by 31 bps in a single year. This isn't just luck; it’s a result of having 62% of borrowings repo-linked, allowing them to capture rate cut benefits almost instantly while the loan book reprices more slowly.
+The thesis is compelling
+Can Fin Homes remains the "Quality Compounder" for those who value efficiency over raw scale. It is currently valued as an inexpensive play despite having the highest RoA/RoE profile in its peer group. If they can normalize pre-payments and hit the 15% AUM target in FY27, a valuation re-rating is almost a mathematical certainty.
+₹1,086 Cr Profit. 2.58% Annual RoA. Best-in-class underwriting. The housing recovery is here, and Can Fin is the efficiency king.
+#CanFinHomes #HFC #HousingFinance #StockMarketIndia #FundamentalAnalysis #Investing #PHDCapital #EquityResearch</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1773410754000</v>
+        <v>1777176002000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2048250725990592587</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGzZLg3bEAAWNeQ.jpg', 'type': 'photo', 'id': '2048250722370916352'}]</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'PHD CAPITAL', 'screenName': 'phd_capital', 'followersCount': 215, 'favouritesCount': 48, 'friendsCount': 1, 'description': 'PHD CAPITAL A SEBI Registered Corporate Research Analyst in Kolkata, West Bengal. Our Goal To Help People For Their Financial Future.'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1188,64 +1232,71 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2032457337122791694</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" s="2" t="n">
-        <v>46094.75409722222</v>
+        <v>46138.33335648148</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/EdgeOverHype/status/2047998474441146821</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047998474441146821</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2035964859116879927</t>
+          <t>2047998393419722766</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2035964859116879927</t>
+          <t>https://x.com/EdgeOverHype/status/2047998393419722766</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA No one contacted yet. This is not acceptable at all from brand like Emirates NBD. Extremely disappointed.</t>
+          <t>$RBLBANK PAT up 234% YoY sounds massive.
+#RBLBank #PrivateBanks
+But dig in — most of that jump came from lower provisions (₹678 Cr vs ₹785 Cr) and a very low base last year, not a core income explosion.
+Meanwhile, NIM dropped to 4.41% — lowest in 5 quarters. The bank is earning less from each rupee it lends.
+The real story nobody's talking about yet:
+Emirates NBD is about to take 60-74% stake for ~$3 Bn. RBI + CCI approved. This bank is weeks away from becoming a foreign bank subsidiary.
+→ Loans up 23% YoY to ₹1.14L Cr
+→ Deposits up 25% to ₹1.39L Cr
+→ Bad loans (GNPA) down sharply: 2.60% → 1.45%
+→ But NIM falling: 4.89% → 4.41%
+I'm watching NIM more than PAT here. Growing loans fast while margins shrink is a pattern that can look great for a few quarters — until it doesn't.
+[1/2]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1774246823000</v>
+        <v>1777115841000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2047998393419722766</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGvzpm8bUAAE_tG.png', 'type': 'photo', 'id': '2047998351724204032'}]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Edge Over Hype', 'screenName': 'EdgeOverHype', 'followersCount': 332, 'favouritesCount': 4, 'friendsCount': 10, 'description': 'Not a guru. Not an advisor. Just a retail investor with 20+ yrs in Indian markets. I share what I notice. Your views welcome. Not SEBI registered.'}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1262,50 +1313,53 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2032458133151342720</t>
-        </is>
-      </c>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" s="2" t="n">
-        <v>46104.43082175926</v>
+        <v>46137.63704861111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/EdgeOverHype/status/2047998474441146821</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047998474441146821</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2035976151764549748</t>
+          <t>2047998474441146821</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
+          <t>https://x.com/EdgeOverHype/status/2047998474441146821</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
+          <t>The Emirates NBD deal changes everything about how to evaluate this bank.
+New parent. New capital. New identity. Possibly new strategy, new risk appetite, new cost structure.
+At this point you're not just buying Q4 results — you're betting on what RBL looks like under foreign ownership.
+Watch: Can NIM stabilize above 4.3% next 2 quarters? That's the real test of whether this growth is profitable or just aggressive.
+Would you buy $RBLBANK for the turnaround story — or does the ownership change make it too uncertain to bet on right now?
+For educational purposes only. Not SEBI registered investment advice.
+Bookmark 🔖 Follow + 🔔
+[2/2]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1774249515000</v>
+        <v>1777115860000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2047998393419722766</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1315,7 +1369,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Edge Over Hype', 'screenName': 'EdgeOverHype', 'followersCount': 332, 'favouritesCount': 4, 'friendsCount': 10, 'description': 'Not a guru. Not an advisor. Just a retail investor with 20+ yrs in Indian markets. I share what I notice. Your views welcome. Not SEBI registered.'}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1332,51 +1386,52 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>73</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2035964859116879927</t>
+          <t>2047998393419722766</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46104.46197916667</v>
+        <v>46137.63726851852</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/EdgeOverHype/status/2047998474441146821</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047998474441146821</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2038625938133471268</t>
+          <t>2048001688121078067</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2038625938133471268</t>
+          <t>https://x.com/EdgeOverHype/status/2048001688121078067</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Dispute request #22407819581 was raised on 23rd March'26 and After that I received call from NBD representative &amp;amp; I explained my dispute. But after that no communication or response received from NBD.
-I am really frustrated by response from such reputed bank.</t>
+          <t>One more thing worth noting —
+Credit card receivables and personal loans actually shrank this quarter. The 23% loan growth is coming from other retail segments.
+That's a deliberate cleanup. Whether it sticks under new management is the question.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1774881274000</v>
+        <v>1777116627000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2047998393419722766</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1386,11 +1441,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Edge Over Hype', 'screenName': 'EdgeOverHype', 'followersCount': 332, 'favouritesCount': 4, 'friendsCount': 10, 'description': 'Not a guru. Not an advisor. Just a retail investor with 20+ yrs in Indian markets. I share what I notice. Your views welcome. Not SEBI registered.'}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1403,64 +1458,65 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2035976151764549748</t>
+          <t>2047998474441146821</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46111.77400462963</v>
+        <v>46137.64614583334</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2047948728103800903</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047948728103800903</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2038628104541774071</t>
+          <t>2047948728103800903</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038628104541774071</t>
+          <t>https://x.com/EmiratesNBD_EGY/status/2047948728103800903</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hi Rakshit, we have already escalated the matter and our team will contact you as soon as possible.</t>
+          <t>Emirates NBD celebrates Sinai Liberation Day, honoring Egypt’s strength and enduring spirit.
+Tax Registration Number: 204-897-319 https://t.co/qXPkhBDY06</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1774881790000</v>
+        <v>1777104000000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2047948728103800903</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq2VyoXsAAVdRq.jpg', 'type': 'photo', 'id': '2047649466077917184'}]</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_EGY', 'followersCount': 2957, 'favouritesCount': 1, 'friendsCount': 3, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في جمهورية مصر العربية - Welcome to the official account for Emirates NBD in Egypt.'}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1473,50 +1529,49 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2038625938133471268</t>
-        </is>
-      </c>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" s="2" t="n">
-        <v>46111.77997685185</v>
+        <v>46137.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/moneycontrolcom/status/2048029415465242975</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2048029415465242975</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2041172230642471397</t>
+          <t>2048029415465242975</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2041172230642471397</t>
+          <t>https://x.com/moneycontrolcom/status/2048029415465242975</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA This is really frustrating from NBD. Nothing has progressed. No meaningful action yet ... Really disappointed from Emirates NBD</t>
+          <t>#Banking | RBL Bank expects Emirates NBD deal closure in Q1 FY27, hinges on govt approval
+@malvisundaresan with details: 
+https://t.co/rvjEkgafEY 
+#RBLBank #Emirates</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1775488357000</v>
+        <v>1777123237000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2048029415465242975</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1526,137 +1581,136 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Moneycontrol', 'screenName': 'moneycontrolcom', 'followersCount': 1510241, 'favouritesCount': 1319, 'friendsCount': 261, 'description': 'Sign up for #MCPro for the most useful insights on markets, companies, and the economy. https://t.co/wm1FjFCCPR'}</t>
         </is>
       </c>
       <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2038628104541774071</t>
-        </is>
-      </c>
+          <t>2232</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" s="2" t="n">
-        <v>46118.80042824074</v>
+        <v>46137.72265046297</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/moneycontrolcom/status/2048029415465242975</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2048029415465242975</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2041173077455667467</t>
+          <t>2048241225577422968</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2041173077455667467</t>
+          <t>https://x.com/moneycontrolcom/status/2048241225577422968</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hello, a follow-up on your request has been sent, and you will be contacted as soon as possible.</t>
+          <t>🚨 #BREAKING | Washington, D.C.: An armed man carrying multiple weapons charged a security checkpoint at the White House Correspondents’ Dinner before being “taken down” by the U.S. Secret Service, President Donald Trump said.
+One officer was shot but survived due to a bulletproof vest. “I just spoke to the officer, and he’s doing great,” Trump added.
+⚠️ High drama unfolded as the President was evacuated from the event.
+👉 Swipe to watch footage from the scene
+🔗 Updates from the link in comment.
+#DonaldTrump #WhiteHouse #BreakingNews #USNews #SecretService #Security</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1775488559000</v>
+        <v>1777173737000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2048241225577422968</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGzOfs7awAANb6o.jpg', 'type': 'photo', 'id': '2048238974578376704'}, {'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2048239007910502400/img/_IeeQy6lPXo0v3s4.jpg', 'type': 'video', 'id': '2048239007910502400'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGzOjVvbgAESWmV.jpg', 'type': 'photo', 'id': '2048239037073555457'}]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Moneycontrol', 'screenName': 'moneycontrolcom', 'followersCount': 1510241, 'favouritesCount': 1319, 'friendsCount': 261, 'description': 'Sign up for #MCPro for the most useful insights on markets, companies, and the economy. https://t.co/wm1FjFCCPR'}</t>
         </is>
       </c>
       <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2041172230642471397</t>
-        </is>
-      </c>
+          <t>3888</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" s="2" t="n">
-        <v>46118.80276620371</v>
+        <v>46138.3071412037</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/marketalertsz/status/2047956082497323013</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047956082497323013</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2046954276312777137</t>
+          <t>2047956082497323013</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2046954276312777137</t>
+          <t>https://x.com/marketalertsz/status/2047956082497323013</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Still no one contacted me.</t>
+          <t>Company: RBL Bank
+Update Type: Press Release 📰 | Sentiment: Positive 🟢
+Summary: RBL Bank Q4 net profit surged 234% YoY to ₹230 crore. Advances grew 23% and deposits 25% YoY. GNPA improved to 1.45% from 1.88% QoQ. Strategic investment by Emirates NBD P.J.S.C is in the final stages of closure following RBI and CCI approvals. Dividend of ₹1 per share proposed.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1776866904000</v>
+        <v>1777105753000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2047956082497323013</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1666,11 +1720,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Market Alerts By Tijori', 'screenName': 'marketalertsz', 'followersCount': 31042, 'favouritesCount': 6, 'friendsCount': 3, 'description': 'Instant alerts about listed companies by @Tijori1 &amp; @zerodhaonline. \nNote: Summaries are AI-generated and may have inaccuracies.'}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1679,54 +1733,52 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2041173077455667467</t>
-        </is>
-      </c>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" s="2" t="n">
-        <v>46134.75583333334</v>
+        <v>46137.52028935185</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/marketalertsz/status/2047956082497323013</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047956082497323013</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2046956528205259220</t>
+          <t>2048029774162051302</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2046956528205259220</t>
+          <t>https://x.com/marketalertsz/status/2048029774162051302</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hello Rakshit, thanks for writing to us please note that a follow-up request has been sent, and you will be contacted as soon as possible.</t>
+          <t>Company: Quality Power Elect.
+Update Type: Important Company Update | Sentiment: Positive 🟢
+Summary: Quality Power secured a significant international order worth approximately INR 48.3 Crore for High Voltage Reactors. The contract, destined for a U.S. Data Centre project, is scheduled for execution within 12 months and involves no promoter or related party interests.</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1776867441000</v>
+        <v>1777123323000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2048029774162051302</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1736,67 +1788,66 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Market Alerts By Tijori', 'screenName': 'marketalertsz', 'followersCount': 31042, 'favouritesCount': 6, 'friendsCount': 3, 'description': 'Instant alerts about listed companies by @Tijori1 &amp; @zerodhaonline. \nNote: Summaries are AI-generated and may have inaccuracies.'}</t>
         </is>
       </c>
       <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2046954276312777137</t>
-        </is>
-      </c>
+          <t>1131</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" s="2" t="n">
-        <v>46134.76204861111</v>
+        <v>46137.72364583334</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047919433033851317</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/Harryhwrqx/status/2047919433033851317</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Same reply every time but no concrete solutions. Just a pathetic approach..</t>
+          <t>1.The SEC has been regulating crypto for 10 years.
+No clear RWA framework. No tokenization path. Just lawsuits.
+Meanwhile, UAE built the entire system in 3 years.
+🧵 Why VARA is what the SEC wishes it could be.</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1777050832000</v>
+        <v>1777097015000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2047919433033851317</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1806,7 +1857,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Harry', 'screenName': 'Harryhwrqx', 'followersCount': 0, 'favouritesCount': 56, 'friendsCount': 16, 'description': "17. Obsessed with RWA tokenization &amp; why blockchains can't verify reality.\nLearning in public. Long UAE."}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1823,50 +1874,52 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2046956528205259220</t>
-        </is>
-      </c>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" s="2" t="n">
-        <v>46136.88462962963</v>
+        <v>46137.41915509259</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2047728007276544227</t>
+          <t>2047919589150110006</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047728007276544227</t>
+          <t>https://x.com/Harryhwrqx/status/2047919589150110006</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Thanks for writing to us, we have already escalated the matter and our team will contact you as soon as possible.</t>
+          <t>2.The SEC treats most tokens as securities.
+That means:
+❌ No clear tokenization pathway for real estate
+❌ Months of legal uncertainty per deal
+❌ Enforcement first, framework second
+Builders don't build where they get sued.
+They move.</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1777051376000</v>
+        <v>1777097053000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2047919433033851317</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1876,11 +1929,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Harry', 'screenName': 'Harryhwrqx', 'followersCount': 0, 'favouritesCount': 56, 'friendsCount': 16, 'description': "17. Obsessed with RWA tokenization &amp; why blockchains can't verify reality.\nLearning in public. Long UAE."}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1893,51 +1946,54 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2047919433033851317</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46136.89092592592</v>
+        <v>46137.41959490741</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047919630182977759</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/AbdulrhmanRF/status/2046820251229159879</t>
+          <t>https://x.com/Harryhwrqx/status/2047919630182977759</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>متى بتفعلون خدمة SAMSUNG PAY ؟
- @EmiratesNBD_KSA</t>
+          <t>3.VARA took a different approach.
+Instead of "is this a security?" — they asked:
+"What does this asset do? Let's build rules around that."
+Result: RWAs get their own category — ARVA tokens.
+Clear rules. Clear pathway. Clear market.</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1776834950000</v>
+        <v>1777097062000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047919433033851317</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1947,63 +2003,73 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'Abed', 'screenName': 'AbdulrhmanRF', 'followersCount': 2023, 'favouritesCount': 19524, 'friendsCount': 1152, 'description': 'A simple guy who likes محمد عبده /Tech/TV/Movies/روجر فيدرير Roger Federer // الهلال 💙 Al Hilal SFC'}</t>
+          <t>{'name': 'Harry', 'screenName': 'Harryhwrqx', 'followersCount': 0, 'favouritesCount': 56, 'friendsCount': 16, 'description': "17. Obsessed with RWA tokenization &amp; why blockchains can't verify reality.\nLearning in public. Long UAE."}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2047919589150110006</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="n">
-        <v>46134.38599537037</v>
+        <v>46137.41969907407</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2046821489882624075</t>
+          <t>2047919733958431202</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2046821489882624075</t>
+          <t>https://x.com/Harryhwrqx/status/2047919733958431202</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>@AbdulrhmanRF مرحبا, تم الرد على الخاص.</t>
+          <t>4.VARA May 2025 Rulebook (v2.0):
+✅ RWA tokens legally defined as ARVA
+✅ Licensed exchanges can list them
+✅ Monthly audits required
+✅ Dubai Land Dept already on-chain
+✅ EU removed UAE from high-risk AML list
+From sandbox → full commercial operation. In one update.</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1776835245000</v>
+        <v>1777097087000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047919433033851317</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2013,11 +2079,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Harry', 'screenName': 'Harryhwrqx', 'followersCount': 0, 'favouritesCount': 56, 'friendsCount': 16, 'description': "17. Obsessed with RWA tokenization &amp; why blockchains can't verify reality.\nLearning in public. Long UAE."}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2030,51 +2096,56 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047919630182977759</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46134.38940972222</v>
+        <v>46137.41998842593</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2047663017521774593</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/buib102/status/2047663017521774593</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA @AbdulrhmanRF حولت اليوم مبلغ مالي اكثر من 20 الف من حسابي لديكم لبنك @alinma
-متى توصل الحواله ؟</t>
+          <t>5.What happened after regulatory clarity?
+→ Mantra: $1B DAMAC deal
+→ Mavryk: $10B UAE pipeline
+→ 40%+ of EU DeFi traders moved to UAE platforms
+→ Emirates NBD actively building crypto services
+Clarity attracts capital.
+Confusion repels it.</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1777035881000</v>
+        <v>1777097106000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047919433033851317</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2084,7 +2155,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'kal', 'screenName': 'buib102', 'followersCount': 3, 'favouritesCount': 131, 'friendsCount': 50, 'description': 'ا'}</t>
+          <t>{'name': 'Harry', 'screenName': 'Harryhwrqx', 'followersCount': 0, 'favouritesCount': 56, 'friendsCount': 16, 'description': "17. Obsessed with RWA tokenization &amp; why blockchains can't verify reality.\nLearning in public. Long UAE."}</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2101,50 +2172,56 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2046821489882624075</t>
+          <t>2047919733958431202</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46136.71158564815</v>
+        <v>46137.42020833334</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/Harryhwrqx/status/2047919811624312884</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2047665248799195623</t>
+          <t>2047919938258776516</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047665248799195623</t>
+          <t>https://x.com/Harryhwrqx/status/2047919938258776516</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@buib102 مرحباً، شكرا لتواصلك معنا. يُرجى إرسال التفاصيل الخاصه بطلبك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
+          <t>6.SEC 2025: Still debating whether ETH is a security.
+VARA 2025: Full RWA issuance framework live.
+Security token infrastructure live.
+AED stablecoin payments live.
+Real estate tokenization operational.
+One regulator is building the future.
+One is still arguing about the past.</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1777036413000</v>
+        <v>1777097136000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047919433033851317</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2154,7 +2231,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Harry', 'screenName': 'Harryhwrqx', 'followersCount': 0, 'favouritesCount': 56, 'friendsCount': 16, 'description': "17. Obsessed with RWA tokenization &amp; why blockchains can't verify reality.\nLearning in public. Long UAE."}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2171,64 +2248,66 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2047663017521774593</t>
+          <t>2047919811624312884</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46136.71774305555</v>
+        <v>46137.42055555555</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/titledeednews/status/2047895879798186062</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047895879798186062</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2047671039249846621</t>
+          <t>2047895879798186062</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/i_rh9590/status/2047671039249846621</t>
+          <t>https://x.com/titledeednews/status/2047895879798186062</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA عندي مشكلة في البطاقة و احاول اسحب منها يطلع ( خطأ في النظام ) مع العلم يوجد بها رصيد ، و خدمة العملاء عندكم للاسف مافي اي تعاون .</t>
+          <t>Dubai Holding and Emirates NBD roll out new off-plan mortgage solutions, lowering entry barriers for buyers.
+More financing = more demand = more deals.
+#DubaiRealEstate #BreakingNews #OffPlanDubai #PropertyInvestment #DubaiBrokers #InvestInDubai https://t.co/6kZs3vX1Ui</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1777037794000</v>
+        <v>1777091400000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047895879798186062</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp2JjBa4AA2WW4.jpg', 'type': 'photo', 'id': '2047578886985408512'}]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'رغد الحربي', 'screenName': 'i_rh9590', 'followersCount': 113, 'favouritesCount': 1989, 'friendsCount': 1338, 'description': '-'}</t>
+          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2241,64 +2320,61 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2047665248799195623</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" s="2" t="n">
-        <v>46136.73372685185</v>
+        <v>46137.35416666666</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/titledeednews/status/2047895879798186062</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047895879798186062</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2047673420695920899</t>
+          <t>2047986478500966671</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047673420695920899</t>
+          <t>https://x.com/titledeednews/status/2047986478500966671</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>@i_rh9590 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
+          <t>Dubai’s ultra-luxury market is still breaking records, even as the market stabilizes.
+#DubaiRealEstate #LuxuryRealEstate #InvestInDubai #PropertyInvestment https://t.co/hSb1kz4cSu</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1777038362000</v>
+        <v>1777113000000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047986478500966671</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp2ZFBa0AAL2Zk.jpg', 'type': 'photo', 'id': '2047579153810247680'}]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17367, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'The Title Deed', 'screenName': 'titledeednews', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 10, 'description': ''}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2311,50 +2387,49 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2047671039249846621</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>46136.74030092593</v>
+        <v>46137.60416666666</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/hkayyal/status/2047892921970794814</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047892921970794814</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2047691273159528852</t>
+          <t>2047892553002012842</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/fortyxxl88/status/2047691273159528852</t>
+          <t>https://x.com/hkayyal/status/2047892553002012842</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA تشترون مديونية قطاع خاص غير معتمد ؟</t>
+          <t>🧵 Gulf Fintech Daily — April 25, 2026
+WhatsApp bans. Wealthtech licenses. B2B credit. Cross-border corridors.
+5 stories shaping Gulf finance today 👇
+#GulfFintech #MENA #FinTech</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1777042618000</v>
+        <v>1777090607000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2046820251229159879</t>
+          <t>2047892553002012842</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2364,11 +2439,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'forty', 'screenName': 'fortyxxl88', 'followersCount': 1, 'favouritesCount': 43, 'friendsCount': 50, 'description': ''}</t>
+          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 691, 'favouritesCount': 2385, 'friendsCount': 948, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2377,54 +2452,53 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2047673420695920899</t>
-        </is>
-      </c>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" s="2" t="n">
-        <v>46136.78956018519</v>
+        <v>46137.34498842592</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
+          <t>https://x.com/hkayyal/status/2047892921970794814</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2047678055070757117</t>
+          <t>2047892921970794814</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2047678055070757117</t>
+          <t>2047892921970794814</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047678055070757117</t>
+          <t>https://x.com/hkayyal/status/2047892921970794814</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE  My issue regarding the credit card payment has now been successfully resolved.I would like to extend my sincere thanks to the bank’s support team for their prompt response and professional assistance throughout the process.Thank you once again.</t>
+          <t>4️⃣ UAE B2B BNPL market hits $1.97B — 23.9% CAGR → $4.66B by 2030.
+Tabby for Business, Tamara, Beehive embedding payment terms in trade platforms.
+ENBD, ADCB, FAB building digital trade finance. SME credit competition intensifies.
+#UAE #BNPL #Fintech</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1777039467000</v>
+        <v>1777090695000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2047678055070757117</t>
+          <t>2047892553002012842</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2434,7 +2508,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 691, 'favouritesCount': 2385, 'friendsCount': 948, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2447,52 +2521,54 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2047892553002012842</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n">
-        <v>46136.75309027778</v>
+        <v>46137.34600694444</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2048143516644016239</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2047620964712693908</t>
+          <t>2048143516644016239</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047620964712693908</t>
+          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>You get an unexpected payment request. What do you do?
-Stay Safe, Stay Vigilant. #UnitedAgainstFraud
-https://t.co/YpRWtBZrhq</t>
+          <t>Emirates Islamic Q1 2026 Results: Operating Profit Rises to Dh1.1 Billion on Higher Financing and Deposits https://t.co/DsNXQRIxdO</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1777025855000</v>
+        <v>1777150441000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2047620964712693908</t>
+          <t>2048143516644016239</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2502,11 +2578,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174354, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1120, 'favouritesCount': 24115, 'friendsCount': 298, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -2515,50 +2591,50 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" s="2" t="n">
-        <v>46136.59554398148</v>
+        <v>46138.03751157408</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/gold_hadas/status/2048143516644016239</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2048143516644016239</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2048247003604222217</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/gold_hadas/status/2048247003604222217</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Is this biggest joke ?</t>
+          <t>Iran gear up for World Cup with friendly against North Macedonia https://t.co/CsUS1iUsqp</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1777036791000</v>
+        <v>1777175114000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2047620964712693908</t>
+          <t>2048247003604222217</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2568,11 +2644,11 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Ayesha.amala', 'screenName': 'AmalaAyesha', 'followersCount': 39, 'favouritesCount': 20, 'friendsCount': 135, 'description': ''}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1120, 'favouritesCount': 24115, 'friendsCount': 298, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -2581,65 +2657,67 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2047620964712693908</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" s="2" t="n">
-        <v>46136.72211805556</v>
+        <v>46138.3230787037</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/AmalaAyesha/status/2047666831612149831</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2047666831612149831</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2047668962998034824</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047668962998034824</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>@AmalaAyesha Hi Ayesha, Please find the below link for more details. Thanks- Zubair 
-https://t.co/YpRWtBZrhq</t>
+          <t>The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨
+✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply. https://t.co/hM1cLA9U4s</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1777037299000</v>
+        <v>1777111200000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2047620964712693908</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGtI1G3WwAEo5Bv.jpg', 'type': 'photo', 'id': '2047810532783079425'}]</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174354, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2656,61 +2734,58 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>2047666831612149831</t>
-        </is>
-      </c>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" s="2" t="n">
-        <v>46136.72799768519</v>
+        <v>46137.58333333334</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
+          <t>https://x.com/emiratesislamic/status/2047978927268696148</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2047629578990936518</t>
+          <t>2047978927268696148</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2047629578990936518</t>
+          <t>2047933629662155095</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
+          <t>https://x.com/emiratesislamic/status/2047933629662155095</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Very disappointed with @ENBDdeals 
-I moved from UAE since Sept 2025 and I’m paying my bills every month by 23rd. Since I’m out of country I won’t be having same time zone and I always see glitch in the ENBD app . I see the outstanding balance keep changing every time</t>
+          <t>احصل على بطاقة ائتمانية من الإمارات الإسلامي واستفد من مزايا خاصة:
+🌟 مكافأة ترحيبية تصل قيمتها إلى 1,000 درهم (قسيمة هدايا من https://t.co/iCieKmtWAq)
+✈️ الدخول إلى صالات المطارات وخدمات الاستقبال والترحيب والتوصيل من وإلى المطار https://t.co/dIBJO6jPay</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1777027909000</v>
+        <v>1777100400000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2047629578990936518</t>
+          <t>2047933629662155095</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGsZrS9WMAAiveF.jpg', 'type': 'photo', 'id': '2047758687184236544'}]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2723,60 +2798,62 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>137</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>46136.61931712963</v>
+        <v>46137.45833333334</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz/status/2047629578990936518</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2047629578990936518</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2047629581159477750</t>
+          <t>2047963827363299676</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/ren_fernz/status/2047629581159477750</t>
+          <t>https://x.com/emiratesislamic/status/2047963827363299676</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I tried to contact in Jan and Feb on WhatsApp but was unable to contact with customer service in Feb it was due to ramdan . Last I came back to pay the bills and I saw the outstanding balance is again more . I saw the transaction history there is nothing but when I contact CS</t>
+          <t>تملّك منزلك الجديد بسهولة مع حلول التمويل السكني المرنة من الإمارات الإسلامي واستمتع بمزايا استثنائية
+تمويل يصل إلى %85 من قيمة العقار
+رسوم إجراءات منخفضة ومعدلات ربح تنافسية https://t.co/skou0cynsQ</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1777027909000</v>
+        <v>1777107600000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2047629578990936518</t>
+          <t>2047963827363299676</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGszxefXMAAMdRU.jpg', 'type': 'photo', 'id': '2047787380661235712'}]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'Ren', 'screenName': 'ren_fernz', 'followersCount': 4059, 'favouritesCount': 6485, 'friendsCount': 862, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J34" t="n">
@@ -2793,64 +2870,63 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>2047629578990936518</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" s="2" t="n">
-        <v>46136.61931712963</v>
+        <v>46137.54166666666</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2047647028012876081</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2047647028012876081</t>
+          <t>2047963832136433706</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
+          <t>https://x.com/emiratesislamic/status/2047963832136433706</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sometimes, all you need is a quiet escape into a great story. 🎞️🤍 Use your Emirates NBD card at Novo Cinemas to enjoy 15% off tickets any day of the week. A simple way to reward yourself with a moment of peace. Book your tickets now by visiting https://t.co/w2yAiSn6ht or the App https://t.co/ps8Dxgg3Bm</t>
+          <t>موافقات سريعة ووثائق رقمية سهلة
+تغطية "تكافل" لك ولعقارك للحماية وراحة البال
+تطبق الشروط والأحكام.
+https://t.co/HswM8pCWkX</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1777032069000</v>
+        <v>1777107601000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2047647028012876081</t>
+          <t>2047963827363299676</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq0Hv-XgAII1HC.jpg', 'type': 'photo', 'id': '2047647025823449090'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18752, 'favouritesCount': 2497, 'friendsCount': 1471, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2863,60 +2939,66 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2047963827363299676</t>
+        </is>
+      </c>
       <c r="P35" s="2" t="n">
-        <v>46136.66746527778</v>
+        <v>46137.54167824074</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2047647028012876081</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2047647028012876081</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2047616654280953919</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/NovoCinemas/status/2047616654280953919</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bro life… but extra chaos 🍻🔥#VaazhaII continues to pull crowds with fun, madness and those “this is so real” moments. Watch it now at Novo Cinemas. Book on https://t.co/w2yAiSn6ht or the Novo App. https://t.co/ycxZoinbXq</t>
+          <t>Step into your new home with ease with flexible Home Finance solutions from Emirates Islamic and enjoy exclusive benefits.
+Financing up to 85% of the property value.  
+Low processing fees and competitive profit rates. https://t.co/Ki4ITc9BJs</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1777024827000</v>
+        <v>1777107602000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2047616654280953919</t>
+          <t>2047963827363299676</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqYfrJWAAAgCku.jpg', 'type': 'photo', 'id': '2047616650518593536'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGszxtjXYAAKzUr.jpg', 'type': 'photo', 'id': '2047787384704557056'}]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'Novo Cinemas', 'screenName': 'NovoCinemas', 'followersCount': 18752, 'favouritesCount': 2497, 'friendsCount': 1471, 'description': 'Offering you A Great Time Out with 2D, 3D &amp; luxury 7-Star VIP experiences. Contact customerservice@novocinemas.com for support.'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2929,59 +3011,63 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2047963832136433706</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="n">
-        <v>46136.58364583334</v>
+        <v>46137.54168981482</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
+          <t>https://x.com/emiratesislamic/status/2047963834812334213</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2047628468545110433</t>
+          <t>2047963834812334213</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2047628468545110433</t>
+          <t>2047963837182156928</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
+          <t>https://x.com/emiratesislamic/status/2047963837182156928</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Breaking News 📢 Dubai Real Estate Just Entered a New Era 🌇
-▪️50/50 Strategy: Pay 50% and leverage ENBD financing for the rest.
-▪️Project Readiness: Available on premium projects at least 30% complete.
-▪️Maximum Liquidity: Grow your portfolio without tying up all your cash. https://t.co/e4xRBY8CCu</t>
+          <t>Quick approvals and easy digital documentation.
+Takaful coverage for yourself and your property.
+Terms &amp;amp; Conditions apply.
+https://t.co/rb0JMWd7zH</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1777027644000</v>
+        <v>1777107602000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2047628468545110433</t>
+          <t>2047963827363299676</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC9aIAAcfHM.jpg', 'type': 'photo', 'id': '2047628390761635840'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC8acAAmIIP.jpg', 'type': 'photo', 'id': '2047628390757462016'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLDCaEAAgV9I.jpg', 'type': 'photo', 'id': '2047628390782603264'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqjLC7awAA0pEW.jpg', 'type': 'photo', 'id': '2047628390753288192'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'D&amp;B Properties', 'screenName': 'dandbdubai', 'followersCount': 589, 'favouritesCount': 930, 'friendsCount': 828, 'description': 'Multi-Award Winning Real Estate Brokerage in Dubai\nSales | Leasing | Off-Plan | Commercial | Asset Management | Valuations &amp; Advisory | Holiday Homes'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2998,59 +3084,63 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2047963834812334213</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="n">
-        <v>46136.61625</v>
+        <v>46137.54168981482</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai/status/2047628468545110433</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2047628468545110433</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2046932416754012230</t>
+          <t>2047933633118228811</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/dandbdubai/status/2046932416754012230</t>
+          <t>https://x.com/emiratesislamic/status/2047933633118228811</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Proud to call the UAE home 🇦🇪
-The UAE continues to inspire, build, and lead and we’re proud to be part of that story.
-Here’s to growth, innovation, and everything ahead
-#UAE #ProudOfUAE #UAENationalPride #Dubai #DubaiLife https://t.co/bnUJHbF5lp</t>
+          <t>💸مكافآت فورية وأميال يمكن استردادها بشكل فوري
+👍 استرداد نقدي، وخصومات، وجولات غولف، وخدمة صف السيارات في مواقع مختارة والمزيد
+يسري العرض لغاية 30 يونيو 2026
+https://t.co/kS1kj9YbcM</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1776861692000</v>
+        <v>1777100401000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2046932416754012230</t>
+          <t>2047933629662155095</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2046932359065591808/img/bJGTr1dd5W2_rytA.jpg', 'type': 'video', 'id': '2046932359065591808'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'D&amp;B Properties', 'screenName': 'dandbdubai', 'followersCount': 589, 'favouritesCount': 930, 'friendsCount': 828, 'description': 'Multi-Award Winning Real Estate Brokerage in Dubai\nSales | Leasing | Off-Plan | Commercial | Asset Management | Valuations &amp; Advisory | Holiday Homes'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -3060,63 +3150,69 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2047933629662155095</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="n">
-        <v>46134.69550925926</v>
+        <v>46137.45834490741</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2047601280143724646</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2047601280143724646</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE  hello, i want to check, is there an issue with the SMS server? I stopped receiving SMS after April 7th</t>
+          <t>Apply for an Emirates Islamic Credit Card and enjoy unmatched rewards:
+🌟 Welcome bonus worth up to AED 1,000 https://t.co/iCieKmtWAq gift voucher
+✈️ Airport lounge access, meet &amp;amp; greet services and airport transfers https://t.co/5nZN3kuFYg</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1777021162000</v>
+        <v>1777100402000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2047601280143724646</t>
+          <t>2047933629662155095</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGsZrh2W0AAevJj.jpg', 'type': 'photo', 'id': '2047758691181449216'}]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'Kang Hori', 'screenName': 'XSilverMermaidX', 'followersCount': 172, 'favouritesCount': 3163, 'friendsCount': 162, 'description': '🔬💼👩🏻\u200d💻🇦🇪'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3133,46 +3229,53 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2047933633118228811</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="n">
-        <v>46136.54122685185</v>
+        <v>46137.45835648148</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/XSilverMermaidX/status/2047601280143724646</t>
+          <t>https://x.com/emiratesislamic/status/2047933636054245884</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2047601280143724646</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2047606015684718778</t>
+          <t>2047933638453366977</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047606015684718778</t>
+          <t>https://x.com/emiratesislamic/status/2047933638453366977</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>@XSilverMermaidX We have replied to your message in private</t>
+          <t>💸 Miles &amp;amp; instant rewards and multiple redemption options
+👍 Cashback, discounts, golf, valet parking at select locations and much more
+Offer valid till 30 June 2026
+https://t.co/hPFzvUt1DS</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1777022291000</v>
+        <v>1777100402000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2047601280143724646</t>
+          <t>2047933629662155095</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3182,7 +3285,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174354, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -3199,164 +3302,186 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>42</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2047601280143724646</t>
+          <t>2047933636054245884</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46136.55429398148</v>
+        <v>46137.45835648148</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2047564934997762494</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>2047835274818748466</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2029505253947629989</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
+          <t>https://x.com/JDunlap1974/status/2029505253947629989</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
+        </is>
+      </c>
       <c r="F41" t="n">
-        <v>1777091876819</v>
-      </c>
-      <c r="G41" t="inlineStr"/>
+        <v>1772706733000</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2029505253947629989</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2029505138055139328/pu/img/WpN4JWq99VF-NMQD.jpg', 'type': 'video', 'id': '2029505138055139328'}]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>{'name': 'JOSH DUNLAP', 'screenName': 'JDunlap1974', 'followersCount': 374495, 'favouritesCount': 120482, 'friendsCount': 44662, 'description': '🇺🇲 MAYOR OF MAGADONIA 🇺🇲 ✝️ CHRISTIAN ✝️ MAGA\n📣 📣BREAKING NEWS FIRST HERE 📣📣'}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>16</v>
+      </c>
+      <c r="K41" t="n">
+        <v>14</v>
+      </c>
+      <c r="L41" t="n">
+        <v>281</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1261</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>12013</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
       <c r="P41" s="2" t="n">
-        <v>46137.35968540509</v>
+        <v>46086.60570601852</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2047564934997762494</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2047564934997762494</t>
+          <t>2029530832042393630</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/zachrose51/status/2047564934997762494</t>
+          <t>https://x.com/iDenville/status/2029530832042393630</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>@coiningmaxi Alright - found some of your customers: PayTabs, Telr, Network International, Magnati, Emirates NBD and Mashreq Bank. Sound right? Going to use these to track down real prospects at your dream customers and map intro paths to them</t>
+          <t>@JDunlap1974 Now audit North Carolina's primaries!!  This is Lakeshia Alston, the woman who ran for election as a REPUBLICAN and won!! https://t.co/vQrXOOfnIW</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1777012497000</v>
+        <v>1772712831000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2047367142367191224</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCpXbMYbwAEvTXt.jpg', 'type': 'photo', 'id': '2029530706775621633'}]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'Zach Roseman', 'screenName': 'zachrose51', 'followersCount': 697, 'favouritesCount': 10161, 'friendsCount': 485, 'description': 'Cold outbound is dead. Building the fix @Draftboard - map warm intro paths from your network to your prospects. Ex-CEO Mosaic Group (acq. by Bending Spoons)'}</t>
+          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23577, 'favouritesCount': 181752, 'friendsCount': 23764, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2047564727421964462</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>46136.4409375</v>
+        <v>46086.67628472222</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal/status/2047530498705195395</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2047530498705195395</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2047530181221613706</t>
+          <t>2047834245423395027</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal/status/2047530181221613706</t>
+          <t>https://x.com/stelpetla/status/2047834245423395027</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>🧵 Gulf Fintech Daily — April 24, 2026
-AI as infrastructure. Sovereign capital as catalyst. 5 stories 👇
-#GulfFintech #MENA #FinTech</t>
+          <t>@iDenville @JDunlap1974 How are they allowed to enter a bank? I’m not allowed to go in my bank wearing sunglasses or a hat.</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1777004211000</v>
+        <v>1777076705000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2047530181221613706</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3366,66 +3491,67 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 690, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
+          <t>{'name': 'Stella Pet 🇺🇸', 'screenName': 'stelpetla', 'followersCount': 684, 'favouritesCount': 27517, 'friendsCount': 1543, 'description': 'GenX/Jersey Girl. 🇺🇸 Mayflower Descendant, DAR. 12th generation American. Trump X 3'}</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2029530832042393630</t>
+        </is>
+      </c>
       <c r="P43" s="2" t="n">
-        <v>46136.34503472222</v>
+        <v>46137.18408564815</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal/status/2047530498705195395</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2047530498705195395</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2047530498705195395</t>
+          <t>2047835274818748466</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/hkayyal/status/2047530498705195395</t>
+          <t>https://x.com/iDenville/status/2047835274818748466</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3️⃣ Dubai South × Emirates NBD sign MoU for streamlined SME banking access.
-Corporate account opening + tailored banking within the free zone.
-94% of UAE businesses are SMEs. Financial onboarding friction is being systematically removed.
-#Dubai #SME #D33</t>
+          <t>@stelpetla @JDunlap1974 Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1777004286000</v>
+        <v>1777076951000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2047530181221613706</t>
+          <t>2029505253947629989</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3435,7 +3561,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'Houssam Kayyal حسام كيال', 'screenName': 'hkayyal', 'followersCount': 690, 'favouritesCount': 2385, 'friendsCount': 946, 'description': 'Managing Partner @ DefineX | Embedded Finance &amp; Digital-Payments Strategist | Ex-CRO @ FOO | Advisor to Banks &amp; Telcos'}</t>
+          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23577, 'favouritesCount': 181752, 'friendsCount': 23764, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -3445,74 +3571,80 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>2047530181221613706</t>
+          <t>2047834245423395027</t>
         </is>
       </c>
       <c r="P44" s="2" t="n">
-        <v>46136.34590277778</v>
+        <v>46137.18693287037</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+          <t>https://x.com/emiratesislamic/status/2047978927205781948</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047978927205781948</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047978927205781948</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047512157030645934</t>
+          <t>https://x.com/emiratesislamic/status/2047978927205781948</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE @LivBank It’s been 4 days since I raised the complaint. My due date is this Monday this delay is unacceptable. Please treat this as urgent and resolve on priority.</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم
+💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية https://t.co/NhNzx3Mewv</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1776999913000</v>
+        <v>1777111200000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2047512157030645934</t>
+          <t>2047978927205781948</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGsnacUXUAA8Ovg.jpg', 'type': 'photo', 'id': '2047773790801711104'}]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3522,63 +3654,63 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>86</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" s="2" t="n">
-        <v>46136.29528935185</v>
+        <v>46137.58333333334</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047918534362030486</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047918530113266095</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/emiratesislamic/status/2047918530113266095</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>@LivBank @EmiratesNBD_AE I deposited cash via ENBD ATM toward my credit card on 21st April but amount got stuck. Complaint already raised, yet the amount is still not credited. My due date is this Monday. Request urgent resolution and credit of funds.</t>
+          <t>من فتح حساب فوري للاستثمارات حسب أحكام الشريعة الإسلامية، يمكنك الآن الحصول على أكثر من 200 خدمة مصرفية عبر تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/KcPGd1gMey</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1776999691000</v>
+        <v>1777096800000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047918530113266095</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqv7peXcAA5cKV.jpg', 'type': 'photo', 'id': '2047642419873673216'}]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 37, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3588,56 +3720,56 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>78</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" s="2" t="n">
-        <v>46136.2927199074</v>
+        <v>46137.41666666666</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/abhiseksonusonu/status/2047511223839908158</t>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047918534362030486</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2047534633697308773</t>
+          <t>2047918534362030486</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2047534633697308773</t>
+          <t>https://x.com/emiratesislamic/status/2047918534362030486</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>@abhiseksonusonu We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to livsocialconnect@liv.me and tag the case reference number #1001503 in the subject line.</t>
+          <t>From instant account opening to shariah-compliant investments, benefit from 200+ banking services via the EI + Mobile Banking App. https://t.co/HS8hXCAAB4</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1777005272000</v>
+        <v>1777096801000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047918530113266095</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqv70cWMAAUdHd.jpg', 'type': 'photo', 'id': '2047642422817992704'}]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174354, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18465, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -3654,1929 +3786,16 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>61</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2047511223839908158</t>
+          <t>2047918530113266095</t>
         </is>
       </c>
       <c r="P47" s="2" t="n">
-        <v>46136.35731481481</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2047835274818748466</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>https://x.com/JDunlap1974/status/2029505253947629989</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Judge overturns election after Democrats caught ballot stuffing. https://t.co/sCEs1CS21j</t>
-        </is>
-      </c>
-      <c r="F48" t="n">
-        <v>1772706733000</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2029505138055139328/pu/img/WpN4JWq99VF-NMQD.jpg', 'type': 'video', 'id': '2029505138055139328'}]</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>{'name': 'JOSH DUNLAP', 'screenName': 'JDunlap1974', 'followersCount': 373925, 'favouritesCount': 120459, 'friendsCount': 44620, 'description': '🇺🇲 MAYOR OF MAGADONIA 🇺🇲 ✝️ CHRISTIAN ✝️ MAGA\n📣 📣BREAKING NEWS FIRST HERE 📣📣'}</t>
-        </is>
-      </c>
-      <c r="J48" t="n">
-        <v>16</v>
-      </c>
-      <c r="K48" t="n">
-        <v>14</v>
-      </c>
-      <c r="L48" t="n">
-        <v>279</v>
-      </c>
-      <c r="M48" t="n">
-        <v>1256</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>11957</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" s="2" t="n">
-        <v>46086.60570601852</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2047835274818748466</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>2029530832042393630</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2029530832042393630</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>@JDunlap1974 Now audit North Carolina's primaries!!  This is Lakeshia Alston, the woman who ran for election as a REPUBLICAN and won!! https://t.co/vQrXOOfnIW</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>1772712831000</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HCpXbMYbwAEvTXt.jpg', 'type': 'photo', 'id': '2029530706775621633'}]</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23517, 'favouritesCount': 181621, 'friendsCount': 23656, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
-        <v>7</v>
-      </c>
-      <c r="K49" t="n">
-        <v>3</v>
-      </c>
-      <c r="L49" t="n">
-        <v>9</v>
-      </c>
-      <c r="M49" t="n">
-        <v>13</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>6300</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="P49" s="2" t="n">
-        <v>46086.67628472222</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2047835274818748466</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>2047834245423395027</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>https://x.com/stelpetla/status/2047834245423395027</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>@iDenville @JDunlap1974 How are they allowed to enter a bank? I’m not allowed to go in my bank wearing sunglasses or a hat.</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
-        <v>1777076705000</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>{'name': 'Stella Pet 🇺🇸', 'screenName': 'stelpetla', 'followersCount': 685, 'favouritesCount': 27506, 'friendsCount': 1544, 'description': 'GenX/Jersey Girl. 🇺🇸 Mayflower Descendant, DAR. 12th generation American. Trump X 3'}</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>2029530832042393630</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="n">
-        <v>46137.18408564815</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2047835274818748466</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2047835274818748466</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>https://x.com/iDenville/status/2047835274818748466</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>@stelpetla @JDunlap1974 Most of the Islamic banking is done through a different system, Bai' al-Sarf.  They have their own banks: Emirates Islamic Bank, Al Rajhi Bank, Abu Dhabi Islamic Bank and more.  They come with apps.</t>
-        </is>
-      </c>
-      <c r="F51" t="n">
-        <v>1777076951000</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>2029505253947629989</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>{'name': 'DenvilleCommunity', 'screenName': 'iDenville', 'followersCount': 23517, 'favouritesCount': 181621, 'friendsCount': 23656, 'description': "Paralegal, Cert. in Veteran's Law. Content Provider for Small  \nBiz - Denville, downtowndenville, Morris County, ProudArmyMom.  \nSee my XArticles - https://t.co/jr1UygtUyx"}</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>2047834245423395027</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="n">
-        <v>46137.18693287037</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Get a guaranteed iPhone 17 when you apply for an Emirates Islamic Personal Finance.
-Also, enjoy exclusive benefits:
-📊 Profit rates starting from 2.59% flat p.a.(approximately equivalent to 4.74% p.a. reducing profit rate)
-🏦 Finance amount of up to AED 4,000,000 https://t.co/QSbM2ZKbuH</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>1777028400000</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp7wFoXwAAtDsB.jpg', 'type': 'photo', 'id': '2047585046668754944'}]</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" s="2" t="n">
-        <v>46136.625</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2047631643901390924</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643901390924</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>✈️Payment holiday up to 6 months 
-🔒 Complimentary Takaful coverage
-Offer valid until 30 April 2026.
-T&amp;amp;Cs apply.
-https://t.co/ZafvBWp0Cl</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>1777028401000</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="n">
-        <v>46136.62501157408</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631640168374617</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2047631640168374617</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>2047717988195852322</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>🇦🇪 We salute the nation’s heroes 
-We value your commitment and have designed exclusive banking benefits for your peace of mind.
-📈 Attractive finance profit rates
-🏦 Zero processing fees https://t.co/Q8zlLDLLW1</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>1777048987000</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>2047717988195852322</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0p_HW8AA45jd.jpg', 'type': 'photo', 'id': '2047717982747422720'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0qJzWcAAnD8P.jpg', 'type': 'photo', 'id': '2047717985616293888'}]</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" s="2" t="n">
-        <v>46136.86327546297</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2047575014564921667</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>2047575014564921667</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Emirates Islamic has reported an operating profit of AED1.1 billion ($299.52 million) for the quarter ending March 31, 2026, 7% growth over the same period last year.
-Read more on https://t.co/I3d8g2xghd
-#ABCNews #Profit #Banking #FinancialInstitution https://t.co/jfJF6uK62j</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>1777014900000</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>2047575014564921667</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl1UAxasAAkYXs.jpg', 'type': 'photo', 'id': '2047296492281704448'}]</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 356, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" s="2" t="n">
-        <v>46136.46875</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2047575014564921667</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2047575014564921667</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>2047597663634457003</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>https://x.com/ABCinGCC/status/2047597663634457003</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>UAE-based @AziziGroup  Developments has announced that construction at Beach Oasis II - its vibrant mixed-use community in the dynamic, rapidly growing Dubai Studio City - has reached 43% completion.
-Read more on https://t.co/Y5AVR722nO
-#ABCNews #Developments #BeachOasis #UAE https://t.co/eVcDwo33OV</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1777020300000</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>2047597663634457003</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGl180kaQAAsBhe.jpg', 'type': 'photo', 'id': '2047297193380560896'}]</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>{'name': 'Arabian Business Community (ABC GCC)', 'screenName': 'ABCinGCC', 'followersCount': 356, 'favouritesCount': 8, 'friendsCount': 180, 'description': 'Official Twitter of the Arabian Business Community (ABC). We’ll be tweeting about business news and popular business categories in the Gulf region.'}</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" s="2" t="n">
-        <v>46136.53125</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2047717990762782723</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>2047717990762782723</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717990762782723</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>⏳Payment holidays
-🎁 Exclusive prizes with Kunooz Millionaire Account
-Terms and conditions apply.
-Know more
-https://t.co/OfDhWyedzP
-#EmiratesIslamic #FrontlineHeroes</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1777048988000</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2047717988195852322</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2047717988195852322</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>46136.86328703703</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717988195852322</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2047717988195852322</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2047717917324710124</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717917324710124</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>🇦🇪 تحية تقدير وامتنان لأبطال الوطن
-تقديراً لإخلاصك وتفانيك في خدمة الوطن، قمنا بتصميم باقة حصرية من المزايا المصرفية لنمنحك راحة البال.
-📈 معدلات أرباح مميزة على التمويل https://t.co/DrYnMIk6Zd</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1777048970000</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2047717917324710124</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0l1oXYAEHNu8.jpg', 'type': 'photo', 'id': '2047717911482032129'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGr0mAsWkAIOAAv.jpg', 'type': 'photo', 'id': '2047717914451546114'}]</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" s="2" t="n">
-        <v>46136.8630787037</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2047556140431556611</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2047556140431556611</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140431556611</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>You have an unpaid fine – click here
-Do not fall for the traps. Stay alert to scams.
-#EIAgainstFraud with Emirates Islamic.
-#TogetherAgainstFraud
-https://t.co/y7eSpGNdfk</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1777010400000</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2047556140431556611</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" s="2" t="n">
-        <v>46136.41666666666</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2047717920193622257</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2047717920193622257</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047717920193622257</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>🏦 بدون رسوم إجراءات
-⏳ تأجيل الأقساط
-🎁 جوائز حصرية مع حساب كنوز المليونير
-تطبق الشروط والأحكام.
-لمعرفة المزيد، تفضل بزيارة
-https://t.co/N2GRIcHWnS
-#الإمارات_الإسلامي #أبطال_الوطن</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1777048971000</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2047717917324710124</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2047717917324710124</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>46136.86309027778</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2047657988064727443</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2047657988064727443</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657988064727443</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/j3JLeVQTou</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1777034682000</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2047657988064727443</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FHDWUAA0A9i.jpg', 'type': 'photo', 'id': '2047657975595028480'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-FZ7WkAAuMQK.jpg', 'type': 'photo', 'id': '2047657980661764096'}]</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" s="2" t="n">
-        <v>46136.69770833333</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2047657972390560162</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2047657960227176876</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657960227176876</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>نقدم لك تجربة مصرفية مميزة مع حساب ALPHA للأبناء، الذي يوفر:
-📱تطبيق للخدمات المصرفية عبر الهاتف المتحرك مخصص لأبنائك
-💳 بطاقة خصم للأبناء
-⭐عروض وخصومات حصرية
-🎁مكافأة بقيمة 100 درهم بمناسبة يوم ميلاد الأبناء
-🏆جوائز نقدية يومية وشهرية
-علمهم صغار!
-تطبق الشروط والأحكام. https://t.co/PUCOpaLwMF</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1777034676000</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>2047657960227176876</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-Dy9W4AA2EvQ.jpg', 'type': 'photo', 'id': '2047657953021321216'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-ECIWoAAdlCp.jpg', 'type': 'photo', 'id': '2047657957093974016'}]</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" s="2" t="n">
-        <v>46136.69763888889</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2047657972390560162</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2047657962978558100</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657962978558100</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>لمعرفة المزيد، يرجى زيارة https://t.co/Dacednep0G</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1777034676000</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2047657960227176876</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>1</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2047657960227176876</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="n">
-        <v>46136.69763888889</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2047657972390560162</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2047657972390560162</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Introducing the ALPHA Youth Account, a banking experience that offers:
-📱 Access to a dedicated mobile app
-💳 Complimentary Debit Card for youth
-🏆 Daily &amp;amp; monthly cash prizes
-🎁 A birthday reward of AED 100 for your child
-⭐ Exclusive offers &amp;amp; discounts
-Start them young! https://t.co/cHbCHEecyD</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1777034678000</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2047657960227176876</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EiyXYAAScez.jpg', 'type': 'photo', 'id': '2047657965860118528'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGq-EwlWwAAzeCE.jpg', 'type': 'photo', 'id': '2047657969563648000'}]</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>1</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2047657962978558100</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="n">
-        <v>46136.69766203704</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657972390560162</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2047657972390560162</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2047657974936604881</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047657974936604881</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Terms &amp;amp; condition apply.
-To know more, please visit https://t.co/Um2N1hjaxk</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>1777034679000</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2047657960227176876</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2047657972390560162</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="n">
-        <v>46136.69767361111</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2047632173461561410</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2047632164863250935</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632164863250935</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more https://t.co/w9nMkMnJJb</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1777028525000</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2047632164863250935</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmaBXUAEX6Xi.jpg', 'type': 'photo', 'id': '2047632159343595521'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmmlvW4AErjsf.jpg', 'type': 'photo', 'id': '2047632162489294849'}]</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>1</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" s="2" t="n">
-        <v>46136.62644675926</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2047632173461561410</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2047632173461561410</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632173461561410</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026.
-Terms &amp;amp; conditions apply.
-https://t.co/Hgg0TFDsUE https://t.co/MBZ0YjVgiN</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1777028527000</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2047632164863250935</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmm5VWkAAB2mi.jpg', 'type': 'photo', 'id': '2047632167748931584'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmnGiWkAAtXIq.jpg', 'type': 'photo', 'id': '2047632171293118464'}]</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2047632164863250935</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="n">
-        <v>46136.62646990741</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2047632116649689120</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2047632116649689120</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد https://t.co/DfoSsbwLQd</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1777028514000</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2047632116649689120</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjnLXwAAvwdB.jpg', 'type': 'photo', 'id': '2047632111335620608'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmjyyXAAAadnx.jpg', 'type': 'photo', 'id': '2047632114451939328'}]</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>1</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" s="2" t="n">
-        <v>46136.62631944445</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632116649689120</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2047632116649689120</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2047632125583605871</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047632125583605871</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني
-🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير.
-يسري العرض لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.
-https://t.co/909hzRsLZr https://t.co/Ff41FuCAen</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1777028516000</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2047632116649689120</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkG7WcAEveRR.jpg', 'type': 'photo', 'id': '2047632119858360321'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HGqmkUZWQAEKDDE.jpg', 'type': 'photo', 'id': '2047632123473838081'}]</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>2047632116649689120</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>46136.62634259259</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2047631643926483032</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2047631639946093018</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631639946093018</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>احصل على iPhone 17 مضمون عند التقدم بطلب تمويل شخصي من الإمارات الإسلامي.
-استمتع أيضاً بالمزايا الحصرية:
-📊 معدلات ربح تبدأ من %2.59 ثابتة سنوياً (ما يعادل تقريباً %4.74 كمعدل متناقص سنوياً).
-🏦 مبلغ تمويلي يصل إلى 4,000,000 درهم https://t.co/eMEYGVmxwY</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1777028400000</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2047631639946093018</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGp1V6aW8AAL6dm.jpg', 'type': 'photo', 'id': '2047577999910825984'}]</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" s="2" t="n">
-        <v>46136.625</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2047631643926483032</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2047631643926483032</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047631643926483032</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>✈️ تأجيل القسط الأول لمدة تصل إلى 6 شهور
-🔒 تغطية تكافلية
-يسري العرض لغاية 30 أبريل 2026.
-تطبق الشروط والأحكام.
-https://t.co/WVHANHvCwT</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1777028401000</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2047631639946093018</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>2047631639946093018</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="n">
-        <v>46136.62501157408</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2047556140511162463</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>2047556140511162463</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047556140511162463</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>عليك غرامة لم تُسدّد بعد – اضغط هنا
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>1777010400000</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2047556140511162463</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" t="n">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" s="2" t="n">
-        <v>46136.41666666666</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>معًا، نُعلي راية الفخر احتفاءً بالإمارات وقيمها الراسخة 🇦🇪
-من قلب فروعنا، اجتمع الموظفون والعملاء في أجواء وطنية جسّدت روح الانتماء والوحدة، وعكست مشاعر الفخر بالوطن.
-#فخورين_بالإمارات https://t.co/b3HOjAP5Rw</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1777006800000</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2047358056963473408/pu/img/J1OcKdI5JfoHlVrB.jpg', 'type': 'video', 'id': '2047358056963473408'}]</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>1</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>3</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" s="2" t="n">
-        <v>46136.375</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541041612427486</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2047541045768962304</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2047541045768962304</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Together, we raise the flag with pride, celebrating the UAE and its enduring values 🇦🇪
-Across our branches, staff and customers came together in a patriotic atmosphere that embodied unity, belonging, and a deep sense of pride in the nation.
-#ProudOfUAE</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1777006801000</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18452, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>0</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>2047541041612427486</t>
-        </is>
-      </c>
-      <c r="P74" s="2" t="n">
-        <v>46136.37501157408</v>
+        <v>46137.41667824074</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,35 +517,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/OhManal72060/status/2048595916316111027</t>
+          <t>https://x.com/OhManal72060/status/2048587742964015122</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2048595916316111027</t>
+          <t>2048587742964015122</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2048595916316111027</t>
+          <t>2048587742964015122</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/OhManal72060/status/2048595916316111027</t>
+          <t>https://x.com/OhManal72060/status/2048587742964015122</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA تم تحويل الراتب لبنكم الموقر ولم يتم صرف الراتب</t>
+          <t>@EmiratesNBD_AE تم تحويل الراتب اليكم ولم ينزل ؟</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1777258302000</v>
+        <v>1777256353000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2048595916316111027</t>
+          <t>2048587742964015122</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -572,56 +572,56 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46139.28590277778</v>
+        <v>46139.26334490741</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/maaalnews_en/status/2048348881016995895</t>
+          <t>https://x.com/OhManal72060/status/2048587742964015122</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2048348881016995895</t>
+          <t>2048587742964015122</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2048348881016995895</t>
+          <t>2048618992814653785</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/maaalnews_en/status/2048348881016995895</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2048618992814653785</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>#Multi #Business Group Secures SAR 15 mln Sharia-compliant Facility from Emirates NBD https://t.co/GDYFPCMaa1 https://t.co/U19XgEelTm</t>
+          <t>@OhManal72060 مرحبا, تم الرد على الخاص.</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1777199404000</v>
+        <v>1777263804000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2048348881016995895</t>
+          <t>2048587742964015122</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG0yc-DW4AA3ieA.jpg', 'type': 'photo', 'id': '2048348878798249984'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'Maaal Economy News', 'screenName': 'maaalnews_en', 'followersCount': 3836, 'favouritesCount': 12, 'friendsCount': 2, 'description': 'Maaal financial and economic news  https://t.co/VzpAj61zvF'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174457, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -636,59 +636,60 @@
       <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2048587742964015122</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="n">
-        <v>46138.60421296296</v>
+        <v>46139.34958333334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/maaalnews_en/status/2048348881016995895</t>
+          <t>https://x.com/EdgeOverHype/status/2048590455336841432</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2048348881016995895</t>
+          <t>2048590455336841432</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2048388611272294507</t>
+          <t>2048590455336841432</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/maaalnews_en/status/2048388611272294507</t>
+          <t>https://x.com/EdgeOverHype/status/2048590455336841432</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vision 2030 Annual Report: PIF’s Assets Under Management Target Raised to SAR 10 Trillion by 2030
-https://t.co/5HdGjJ82lS https://t.co/QzSxNzkVb2</t>
+          <t>$RBLBANK under Emirates NBD ownership — what's your read?
+○ Bullish — new capital + cleanup = re-rating ahead
+○ Cautious — too much uncertainty, wait for FY27 clarity</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777208876000</v>
+        <v>1777257000000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2048388611272294507</t>
+          <t>2048590455336841432</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG1Wlg_WQAA8TUj.jpg', 'type': 'photo', 'id': '2048388608034226176'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Maaal Economy News', 'screenName': 'maaalnews_en', 'followersCount': 3836, 'favouritesCount': 12, 'friendsCount': 2, 'description': 'Maaal financial and economic news  https://t.co/VzpAj61zvF'}</t>
+          <t>{'name': 'Edge Over Hype', 'screenName': 'EdgeOverHype', 'followersCount': 334, 'favouritesCount': 4, 'friendsCount': 10, 'description': 'Not a guru. Not an advisor. Just a retail investor with 20+ yrs in Indian markets. I share what I notice. Your views welcome. Not SEBI registered.'}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -698,53 +699,62 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>33</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" s="2" t="n">
-        <v>46138.7138425926</v>
+        <v>46139.27083333334</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/FiDecoded/status/2048298339524124826</t>
+          <t>https://x.com/EdgeOverHype/status/2048590455336841432</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2048298339524124826</t>
+          <t>2048590455336841432</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048298339524124826</t>
+          <t>2048375682447921445</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/FiDecoded/status/2048298339524124826</t>
+          <t>https://x.com/EdgeOverHype/status/2048375682447921445</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Big news from RBL Bank - Emirates NBD is investing up to $3 billion to acquire a 60% stake, the largest foreign investment in India's financial sector</t>
+          <t>The best companies don't look like winners every quarter.
+They spend on brands, enter new markets, accept lower margins — knowing it'll pay off in 5–10 years.
+Markets hate this. Stock drops. Analysts complain.
+But Thomas Russo calls this the real edge: the "capacity to suffer."
+→ A company willing to sacrifice today's profit for tomorrow's moat is rare
+→ Rarer still: one that does this when the economy is tough, not just when times are easy
+Most investors screen for fast profit growth.
+The actual filter should be: is this company investing through pain — or cutting corners to protect one quarter's numbers?
+The best compounders look uncomfortable in the short term. That's the point.
+#LongTermInvesting #CompoundingWorks</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1777187354000</v>
+        <v>1777205794000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2048298339524124826</t>
+          <t>2048375682447921445</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -754,7 +764,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Finance Decoded', 'screenName': 'FiDecoded', 'followersCount': 4, 'favouritesCount': 0, 'friendsCount': 1, 'description': ''}</t>
+          <t>{'name': 'Edge Over Hype', 'screenName': 'EdgeOverHype', 'followersCount': 334, 'favouritesCount': 4, 'friendsCount': 10, 'description': 'Not a guru. Not an advisor. Just a retail investor with 20+ yrs in Indian markets. I share what I notice. Your views welcome. Not SEBI registered.'}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -767,50 +777,50 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>28</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" s="2" t="n">
-        <v>46138.46474537037</v>
+        <v>46138.6781712963</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/FiDecoded/status/2048298339524124826</t>
+          <t>https://x.com/OhManal72060/status/2048595916316111027</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2048298339524124826</t>
+          <t>2048595916316111027</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048298349963669771</t>
+          <t>2048595916316111027</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/FiDecoded/status/2048298349963669771</t>
+          <t>https://x.com/OhManal72060/status/2048595916316111027</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>This deal will triple RBL Bank's net worth to around ₹42,000 crore, improve its credit rating, and reduce its cost of funds</t>
+          <t>@EmiratesNBD_KSA تم تحويل الراتب لبنكم الموقر ولم يتم صرف الراتب</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777187356000</v>
+        <v>1777258302000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2048298339524124826</t>
+          <t>2048595916316111027</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -820,11 +830,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Finance Decoded', 'screenName': 'FiDecoded', 'followersCount': 4, 'favouritesCount': 0, 'friendsCount': 1, 'description': ''}</t>
+          <t>{'name': 'Manal OH', 'screenName': 'OhManal72060', 'followersCount': 0, 'favouritesCount': 21, 'friendsCount': 25, 'description': ''}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -837,60 +847,56 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2048298339524124826</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" s="2" t="n">
-        <v>46138.46476851852</v>
+        <v>46139.28590277778</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/FiDecoded/status/2048298339524124826</t>
+          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2048298339524124826</t>
+          <t>2048470825146171877</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2048297687934812386</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/FiDecoded/status/2048297687934812386</t>
+          <t>https://x.com/Nidhinkn/status/2048469042315337899</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Big news from RBL Bank - Emirates NBD is investing and will own up to 74% of the bank by Q1 FY27. This means RBL Bank will become a foreign bank in India.</t>
+          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1777187198000</v>
+        <v>1777228053000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2048297687934812386</t>
+          <t>2048469042315337899</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG2ftYnacAADNVo.png', 'type': 'photo', 'id': '2048469007574134784'}]</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Finance Decoded', 'screenName': 'FiDecoded', 'followersCount': 4, 'favouritesCount': 0, 'friendsCount': 1, 'description': ''}</t>
+          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 193, 'friendsCount': 52, 'description': 'Nation First. Bharat.'}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -907,36 +913,805 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" s="2" t="n">
-        <v>46138.46293981482</v>
+        <v>46138.93579861111</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2048470825146171877</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2048469731607281786</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048469731607281786</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>There was no email or sms from @EmiratesNBD_KSA regarding the monthly spend of 3000 SR. The new customers could be aware of this, since you would have informed them. However VAC had mentioned in their app about spending of 100$ and I did spend that. I want the 460SAR refund</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1777228217000</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2048469042315337899</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 193, 'friendsCount': 52, 'description': 'Nation First. Bharat.'}</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2048469042315337899</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>46138.93769675926</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2048470825146171877</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2048470825146171877</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Hello @EmiratesNBD_KSA , I want the amount to refunded to my account. Else I will have to escalate this issue to @SAMA_GOV 
+@EmiratesNBD_AE @VisaCEMEA</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1777228478000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2048469042315337899</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 193, 'friendsCount': 52, 'description': 'Nation First. Bharat.'}</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2048469731607281786</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>46138.9407175926</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2048470825146171877</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2048472558526202097</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048472558526202097</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA @SAMA_GOV @EmiratesNBD_AE @VisaCEMEA I did contact 
+@EmiratesNBD_KSA customer care twice. They closed a ticket today which was open for 20 days. Reference Number 22489659935. It's better you guys can go and loot.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1777228891000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2048469042315337899</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 193, 'friendsCount': 52, 'description': 'Nation First. Bharat.'}</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2048470825146171877</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>46138.94549768518</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2048470825146171877</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2048615227546087604</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2048615227546087604</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>@Nidhinkn Hello, we are sorry to hear that you are experiencing this. Please send your phone number and ID number via private message so that we can assist you. Thank you</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1777262906000</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2048469042315337899</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17399, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2048470825146171877</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>46139.33918981482</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://x.com/Nidhinkn/status/2048472558526202097</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2048472558526202097</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2048616031619309576</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2048616031619309576</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>@Nidhinkn Hello, we are sorry to hear that you are experiencing this. Please send your phone number and ID number via private message so that we can assist you. Thank you</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1777263098000</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2048469042315337899</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174457, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2048472558526202097</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>46139.34141203704</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363390700306583</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2048363390700306583</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2048363366360707433</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363366360707433</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1/6 🧵 
+RBLBANK Q4 FY26 Concall: Moving past headline advances growth. Here are asset quality triggers, transient deposit impacts, and margin trajectories. 
+A concall summary PDF of RBLBANK attached for sharing. 👇
+https://t.co/PUnR70G7tT</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1777202857000</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2048363366360707433</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>{'name': 'CompoundingAI', 'screenName': 'compoundingaiin', 'followersCount': 4899, 'favouritesCount': 2158, 'friendsCount': 43, 'description': 'Institutional Grade AI Market Research Assistant\n\nSubstack : https://t.co/cyPsc6BDHB\n\nJoin our waitlist : https://t.co/YjlV0hX2PR'}</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="2" t="n">
+        <v>46138.64417824074</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363390700306583</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2048363390700306583</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2048363369200300049</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363369200300049</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2/6 
+RBLBANK Card Stress: Credit card write-offs hit a massive ₹590 Cr in Q4, totaling ~₹2,100 Cr for FY26. RBLBANK expects recovery at just ~₹0.15 per rupee over 2-3 years. Card slippages guided to fall to 7-7.5% in H2.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1777202858000</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2048363366360707433</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>{'name': 'CompoundingAI', 'screenName': 'compoundingaiin', 'followersCount': 4899, 'favouritesCount': 2158, 'friendsCount': 43, 'description': 'Institutional Grade AI Market Research Assistant\n\nSubstack : https://t.co/cyPsc6BDHB\n\nJoin our waitlist : https://t.co/YjlV0hX2PR'}</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2048363366360707433</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>46138.64418981481</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363390700306583</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2048363390700306583</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2048363373562339422</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363373562339422</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3/6 
+RBLBANK MFI Protection: Despite market stress, management is highly defensive on its JLG book. A massive 98% of RBLBANK's JLG disbursements and 95% of the standard book are backed by CGFMU guarantees.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1777202859000</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2048363366360707433</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>{'name': 'CompoundingAI', 'screenName': 'compoundingaiin', 'followersCount': 4899, 'favouritesCount': 2158, 'friendsCount': 43, 'description': 'Institutional Grade AI Market Research Assistant\n\nSubstack : https://t.co/cyPsc6BDHB\n\nJoin our waitlist : https://t.co/YjlV0hX2PR'}</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2048363369200300049</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>46138.64420138889</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363390700306583</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2048363390700306583</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2048363380831072653</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363380831072653</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>4/6 
+RBLBANK Deposits: While deposits grew 25% YoY, this includes ~₹5,000 Cr of transient IHC deposits logged in late March/early April. RBLBANK notes term-deposit repricing is nearly complete with only 5-10 bps residual.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>1777202861000</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2048363366360707433</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>{'name': 'CompoundingAI', 'screenName': 'compoundingaiin', 'followersCount': 4899, 'favouritesCount': 2158, 'friendsCount': 43, 'description': 'Institutional Grade AI Market Research Assistant\n\nSubstack : https://t.co/cyPsc6BDHB\n\nJoin our waitlist : https://t.co/YjlV0hX2PR'}</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2048363373562339422</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>46138.64422453703</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363390700306583</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2048363390700306583</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2048363385427988518</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363385427988518</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>5/6 
+RBLBANK Margins: NIM fell 22 bps due to a 50 bps drop in advance yields &amp;amp; surplus liquidity. $
+RBLBANK expects NIM improvement from Q2 as capital inflows reduce leverage to 4x and lower card slippages aid spread.</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1777202862000</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2048363366360707433</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>{'name': 'CompoundingAI', 'screenName': 'compoundingaiin', 'followersCount': 4899, 'favouritesCount': 2158, 'friendsCount': 43, 'description': 'Institutional Grade AI Market Research Assistant\n\nSubstack : https://t.co/cyPsc6BDHB\n\nJoin our waitlist : https://t.co/YjlV0hX2PR'}</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2048363380831072653</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>46138.64423611111</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363390700306583</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2048363390700306583</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2048363390700306583</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://x.com/compoundingaiin/status/2048363390700306583</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>6/6 
+RBLBANK Strategy: Emirates NBD infusion has RBI/CCI nods, pending GOI/SEBI. Also, RBLBANK is targeting a $135B monthly cross-border remittance flow, leveraging tech pipelines for a 23-25% partner bank share.</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1777202863000</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2048363366360707433</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>{'name': 'CompoundingAI', 'screenName': 'compoundingaiin', 'followersCount': 4899, 'favouritesCount': 2158, 'friendsCount': 43, 'description': 'Institutional Grade AI Market Research Assistant\n\nSubstack : https://t.co/cyPsc6BDHB\n\nJoin our waitlist : https://t.co/YjlV0hX2PR'}</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2048363385427988518</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>46138.64424768519</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>https://x.com/EmiratesNBD_AE/status/2048319900381315248</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2048319900381315248</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>2048319900381315248</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2048319900381315248</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Why choose when you can have the best of both worlds.
 Personalized support when you need it and cutting-edge technology when you want it. 
@@ -944,68 +1719,68 @@
 Apply now https://t.co/r4IQZQh7WI https://t.co/lkt4tkv3m1</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F19" t="n">
         <v>1777192494000</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>2048319900381315248</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2048319791635509249/img/wd8ep14TFoSm2Fdz.jpg', 'type': 'video', 'id': '2048319791635509249'}]</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174455, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174457, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" s="2" t="n">
+      <c r="M19" t="n">
+        <v>7</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="2" t="n">
         <v>46138.52423611111</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2048319900381315248</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>2048319900381315248</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>2048250721053593717</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_AE/status/2048250721053593717</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Your motivation will fluctuate.
 Your emotions will shift.
@@ -1017,136 +1792,1239 @@
 #FinancialWellbeing #EmiratesNBD #InvestSmart #FinWell</t>
         </is>
       </c>
-      <c r="F9" t="n">
+      <c r="F20" t="n">
         <v>1777176001000</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>2048250721053593717</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGvXp4DX0AAozRW.jpg', 'type': 'photo', 'id': '2047967569991159808'}]</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174455, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174457, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>2</v>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>355</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" s="2" t="n">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="n">
         <v>46138.33334490741</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://x.com/maaalnews_en/status/2048348881016995895</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2048348881016995895</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2048348881016995895</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://x.com/maaalnews_en/status/2048348881016995895</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>#Multi #Business Group Secures SAR 15 mln Sharia-compliant Facility from Emirates NBD https://t.co/GDYFPCMaa1 https://t.co/U19XgEelTm</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1777199404000</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2048348881016995895</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG0yc-DW4AA3ieA.jpg', 'type': 'photo', 'id': '2048348878798249984'}]</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>{'name': 'Maaal Economy News', 'screenName': 'maaalnews_en', 'followersCount': 3836, 'favouritesCount': 12, 'friendsCount': 2, 'description': 'Maaal financial and economic news  https://t.co/VzpAj61zvF'}</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="2" t="n">
+        <v>46138.60421296296</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://x.com/maaalnews_en/status/2048348881016995895</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2048348881016995895</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2048388611272294507</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://x.com/maaalnews_en/status/2048388611272294507</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Vision 2030 Annual Report: PIF’s Assets Under Management Target Raised to SAR 10 Trillion by 2030
+https://t.co/5HdGjJ82lS https://t.co/QzSxNzkVb2</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1777208876000</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2048388611272294507</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG1Wlg_WQAA8TUj.jpg', 'type': 'photo', 'id': '2048388608034226176'}]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'name': 'Maaal Economy News', 'screenName': 'maaalnews_en', 'followersCount': 3836, 'favouritesCount': 12, 'friendsCount': 2, 'description': 'Maaal financial and economic news  https://t.co/VzpAj61zvF'}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="n">
+        <v>46138.7138425926</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2048329007666528266</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2048329007666528266</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2048329007666528266</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2048329007666528266</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD SHARE Visa Credit Card.
+Apply Now: https://t.co/XpFUmulYZw https://t.co/IA8ruFShHw</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1777194666000</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2048329007666528266</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG0gYJNXcAA7i8_.jpg', 'type': 'photo', 'id': '2048329004684374016'}]</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39189, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
+        <v>46138.549375</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2048329007666528266</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2048329007666528266</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2047692986402643994</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://x.com/ENBDdeals/status/2047692986402643994</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Get an AED 500 Pet Corner Gift Card when you apply for an Emirates NBD noon One Visa Credit Card.
+Apply Now: https://t.co/vPejTs11gM https://t.co/RjpetrwLd9</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1777043026000</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2047692986402643994</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGrd61bXUAAXvdG.jpg', 'type': 'photo', 'id': '2047692983437316096'}]</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39189, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="n">
+        <v>46136.79428240741</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://x.com/safoo6764/status/2048297636403315015</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2048297636403315015</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2048297636403315015</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://x.com/safoo6764/status/2048297636403315015</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA السلام عليكم ورحمة الله وبركاتة 
+لماذا هذا التأخير في بنك الامارات 
+يوجد طلب من يوم الاحد إلى فات 
+والى الان ما ياتي رد عليه 
+جميع البنوك بالمملكة تاني الرد خلال ٤٨ ساعة</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>1777187186000</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2048297636403315015</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>{'name': 'Abu Turki', 'screenName': 'safoo6764', 'followersCount': 36, 'favouritesCount': 27, 'friendsCount': 155, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="2" t="n">
+        <v>46138.46280092592</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://x.com/safoo6764/status/2048297636403315015</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2048297636403315015</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2048500791602720888</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://x.com/safoo6764/status/2048500791602720888</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>سؤالي للكابتن عماد ما الفرق بين الاهلي بالآسيوية والاهلي بالدوري   #اكشن_مع_وليد</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1777235622000</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2048500791602720888</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>{'name': 'Abu Turki', 'screenName': 'safoo6764', 'followersCount': 36, 'favouritesCount': 27, 'friendsCount': 155, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="n">
+        <v>46139.02340277778</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://x.com/Normal_2610/status/2048287911771308484</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2048287911771308484</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2048287911771308484</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/Normal_2610/status/2048287911771308484</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RBL Bank - Expects the Emirates NBD investment to close in Q1 FY27, pending government approvals. The deal is firm and not affected by geopolitical tensions. 
+RBI approval received, working on Government of India and SEBI clearances. 
+RBL Bank's card will be accepted as part of the National Common Mobility Card initiative for Bengaluru's metro and buses.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1777184868000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2048287911771308484</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'Normal Guy', 'screenName': 'Normal_2610', 'followersCount': 17546, 'favouritesCount': 16122, 'friendsCount': 959, 'description': 'Investor | policy | politics | Geopolitics | Defence | AI | Observer &amp; Commentator | Critic | stay curious \n\nवीर भोग्या वसुंधरा'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>19</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2171</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="2" t="n">
+        <v>46138.43597222222</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://x.com/Normal_2610/status/2048287911771308484</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2048287911771308484</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2048611391993496004</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/Normal_2610/status/2048611391993496004</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Wet-bulb temperature is the number india needs to learn fast. 
+when humidity gets high enough, your body can't cool itself even at 35°C. you just overheat. india sits at about 10% urban AC ownership. 
+we're adding 130m new ACs by 2035, mostly powered by coal. cooling ourselves by warming the planet. Real Estate Premium will continue</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1777261991000</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2048611391993496004</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'name': 'Normal Guy', 'screenName': 'Normal_2610', 'followersCount': 17546, 'favouritesCount': 16122, 'friendsCount': 959, 'description': 'Investor | policy | politics | Geopolitics | Defence | AI | Observer &amp; Commentator | Critic | stay curious \n\nवीर भोग्या वसुंधरा'}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="n">
+        <v>33</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>3428</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="n">
+        <v>46139.32859953704</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://x.com/Fyan2016/status/2048291487721345391</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2048291487721345391</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2048291487721345391</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://x.com/Fyan2016/status/2048291487721345391</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>💰 مجموعة الأعمال المتعددة توقع اتفاقية تسهيلات ائتمانية مع بنك الإمارات دبي الوطني (Emirates NBD) بقيمة 15 مليون ريال
+تم استكمال التوقيعات للاتفاقية، التي تعد متوافقة مع أحكام الشريعة الإسلامية، ومنحها مدة 12 شهراً، وتم تقديم سند لأمر يمثل ضماناً بقيمة التمويل.
+الهدف من التسهيل هو دعم أعمال الشركة العامة، وتغطية إصدار خطابات الضمان (الابتدائية والنهائية) وتأمين دفعات المشاريع المختلفة.
+#الأعمال #التمويل #تاسي #البنوك #السعودية #تداول</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1777185720000</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2048291487721345391</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGz-QEdWYAEf5cz.jpg', 'type': 'photo', 'id': '2048291482574938113'}]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'name': 'فايز المالكي', 'screenName': 'Fyan2016', 'followersCount': 272, 'favouritesCount': 10404, 'friendsCount': 1797, 'description': 'مهندس.. ماجستير ادارة اعمال تنفيذية.. مهتم بالعقار والديكور والتقنيات الزراعية الحديثة والطبيعة والفيزياء واشياء اخرى'}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="2" t="n">
+        <v>46138.44583333333</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://x.com/X3_3y3/status/2048286728524284019</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2048286728524284019</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2047936203438362829</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/AmritMohanty1/status/2047936203438362829</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Disappointed with @EmiratesNBD_AE support on reported fraudulent credit card charges. Disputed amounts still show as payable and due date is near. Requested urgent review, temporary credit, and waiver of fees/interest pending investigation. Please assist urgently. #EmiratesNBD</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1777101014000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2047936203438362829</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>{'name': 'Amrit Mohanty', 'screenName': 'AmritMohanty1', 'followersCount': 8, 'favouritesCount': 144, 'friendsCount': 136, 'description': 'Everything that’s here are my opinions. Not necessarily shared by reasonable-minded people nor my benevolent corporate overlords!!'}</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="n">
+        <v>46137.46543981481</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://x.com/X3_3y3/status/2048286728524284019</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2048286728524284019</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2048286728524284019</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://x.com/X3_3y3/status/2048286728524284019</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>@AmritMohanty1 @EmiratesNBD_AE السلام عليكم ممكن تتواصلون معي خاص ؟</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1777184586000</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2047936203438362829</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'name': ':(', 'screenName': 'X3_3y3', 'followersCount': 497, 'favouritesCount': 2101, 'friendsCount': 169, 'description': 'استغفر الله العظيم واتوب اليه { صلى الله على نبينا محمد }'}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2047936203438362829</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46138.43270833333</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://x.com/ArgaamPlus/status/2048284259559874976</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2048284259559874976</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2048284259559874976</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/ArgaamPlus/status/2048284259559874976</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Multi Business Group signed a SAR 15 million Shariah-compliant credit facilities agreement with Emirates NBD.
+Show more: https://t.co/FldwIQXk1i https://t.co/prZbq1JMi8</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1777183997000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2048284259559874976</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGz3riMX0AAIpGd.png', 'type': 'photo', 'id': '2048284257831866368'}]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'name': 'Argaam Plus', 'screenName': 'ArgaamPlus', 'followersCount': 29047, 'favouritesCount': 19, 'friendsCount': 7, 'description': "Market data, analysis, and commentary from Saudi Arabia's leading business news provider. \n\nArabic Account: @Argaam"}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="2" t="n">
+        <v>46138.4258912037</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266647291748727</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2048266647291748727</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2048266314901586424</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266314901586424</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RBL Bank Q4 FY26 results are out.
+Net profit: ₹230 crore — up 234% YoY, 7% QoQ. 
+NII: ₹1,671 crore — up 7% YoY. Operating profit: ₹955 crore — up 11% YoY.
+Good headline numbers. But as always, the ratios tell the fuller story. https://t.co/A0sxjq4y5B</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1777179719000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2048266314901586424</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGznQjwaMAAF71J.jpg', 'type': 'photo', 'id': '2048266202208940032'}]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'name': 'Arjun Jain', 'screenName': 'arjunjain_96', 'followersCount': 164, 'favouritesCount': 680, 'friendsCount': 231, 'description': 'Indian equities, fixed income, and the macro in between. Earnings deep-dives, market frameworks, bond market coverage you won’t find elsewhere. CA (ICAEW) | LBS'}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="2" t="n">
+        <v>46138.37637731482</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266647291748727</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2048266647291748727</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2048266484296614059</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266484296614059</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Growth
+The book is growing well.
+Advances: +23% YoY, +11% QoQ to ₹1.14 lakh crore. Deposits: +25% YoY, +16% QoQ to ₹1.39 lakh crore.
+Crucially, deposits are growing faster than advances - that's a healthy sign. The bank isn't stretching its funding to chase loan growth.
+CASA deposits also jumped 26% QoQ - that's meaningful for cost of funds going forward.</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1777179759000</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2048266314901586424</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'name': 'Arjun Jain', 'screenName': 'arjunjain_96', 'followersCount': 164, 'favouritesCount': 680, 'friendsCount': 231, 'description': 'Indian equities, fixed income, and the macro in between. Earnings deep-dives, market frameworks, bond market coverage you won’t find elsewhere. CA (ICAEW) | LBS'}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2048266314901586424</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>46138.37684027778</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266647291748727</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2048266647291748727</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2048266647291748727</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266647291748727</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Profitability
+NIM at 4.41% - this is the one number to watch.
+It was 4.89% a year ago and 4.63% last quarter. That's 48 bps of compression YoY.
+Management has guided that Q1 FY27 margins will remain similar to Q4. The expectation is that the Emirates NBD capital infusion will then drive expansion.
+Cost-to-income improving - 65.1% vs 66.3% last quarter. Still high, but moving in the right direction.</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1777179798000</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2048266314901586424</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'name': 'Arjun Jain', 'screenName': 'arjunjain_96', 'followersCount': 164, 'favouritesCount': 680, 'friendsCount': 231, 'description': 'Indian equities, fixed income, and the macro in between. Earnings deep-dives, market frameworks, bond market coverage you won’t find elsewhere. CA (ICAEW) | LBS'}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2048266484296614059</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46138.37729166666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266647291748727</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2048266647291748727</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2048266796424405218</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/arjunjain_96/status/2048266796424405218</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Asset quality
+This is where the real progress shows.
+GNPA: 1.45% - down from 2.60% a year ago and 1.88% last quarter. Significant improvement.
+NNPA: 0.39% - improved QoQ from 0.55%. Though slightly higher than 0.29% a year ago, which reflects the write-off cycle working through.
+PCR at 94.9% - nearly fully provided. The balance sheet is well cushioned.
+The asset quality trajectory is clearly improving. The question is whether it sustains.</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1777179833000</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2048266314901586424</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'name': 'Arjun Jain', 'screenName': 'arjunjain_96', 'followersCount': 164, 'favouritesCount': 680, 'friendsCount': 231, 'description': 'Indian equities, fixed income, and the macro in between. Earnings deep-dives, market frameworks, bond market coverage you won’t find elsewhere. CA (ICAEW) | LBS'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2048266647291748727</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>46138.37769675926</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>https://x.com/Fyan2016/status/2048281389733183899</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>2048281389733183899</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>2048281389733183899</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>https://x.com/Fyan2016/status/2048281389733183899</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>💰 أعلنت مجموعة الأعمال المتعددة عن إبرام اتفاقية تسهيلات ائتمانية (متوافقة مع الشريعة) مع بنك الإمارات دبي الوطني (Emirates NBD).
 تغطي الاتفاقية مبلغاً يبلغ 15 مليون ريال سعودي، وتمتد لمدة اثني عشر شهراً، وتهدف لتوفير تسهيلات عامة لخطابات الضمان ومستحقات الدفعات الأولية للمشاريع.
 #تاسي #أعمال #الرياض #تمويل #السعودية #اقتصاد</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F37" t="n">
         <v>1777183313000</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>2048281389733183899</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>{'name': 'فايز المالكي', 'screenName': 'Fyan2016', 'followersCount': 272, 'favouritesCount': 10404, 'friendsCount': 1797, 'description': 'مهندس.. ماجستير ادارة اعمال تنفيذية.. مهتم بالعقار والديكور والتقنيات الزراعية الحديثة والطبيعة والفيزياء واشياء اخرى'}</t>
         </is>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
         <v>1</v>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" s="2" t="n">
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="2" t="n">
         <v>46138.41797453703</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>https://x.com/Fyan2016/status/2048281389733183899</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>2048281389733183899</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>2048468545143550362</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>https://x.com/Fyan2016/status/2048468545143550362</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>🏗️ فوز تحالف "حسن علام" و"البواني" بعقد ضخم لإنشاء المتحف السعودي للفن المعاصر
 أعلنت مجموعة حسن علام القابضة وشركة البواني القابضة عن ترسية عقد بقيمة 1.84 مليار ريال سعودي (ما يعادل 490 مليون دولار) في منطقة الدرعية بالرياض.
@@ -1154,68 +3032,68 @@
 #تاسي #السعودية #رؤية_2030 #الرياض #الدرعية #اقتصاد</t>
         </is>
       </c>
-      <c r="F11" t="n">
+      <c r="F38" t="n">
         <v>1777227934000</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>2048468545143550362</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG2fSBQbgAAIRuz.jpg', 'type': 'photo', 'id': '2048468537447251968'}]</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>{'name': 'فايز المالكي', 'screenName': 'Fyan2016', 'followersCount': 272, 'favouritesCount': 10404, 'friendsCount': 1797, 'description': 'مهندس.. ماجستير ادارة اعمال تنفيذية.. مهتم بالعقار والديكور والتقنيات الزراعية الحديثة والطبيعة والفيزياء واشياء اخرى'}</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M38" t="n">
         <v>2</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>137</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" s="2" t="n">
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="n">
         <v>46138.9344212963</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>2048234825199526119</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>2048234825199526119</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>IDBI बैंक विनिवेश: क्या है ताजा अपडेट? 
 ​IDBI बैंक के निजीकरण की प्रक्रिया एक बार फिर चर्चा में है। बाजार में चल रही ताजा रिपोर्ट्स के अनुसार, इस बड़े सौदे से जुड़ी कुछ महत्वपूर्ण बातें सामने आ रही हैं:
@@ -1228,110 +3106,1158 @@
 ​#IDBIBank #BankingNews #EconomyUpdate #Disinvestment #StockMarketIndia #FinanceNews</t>
         </is>
       </c>
-      <c r="F12" t="n">
+      <c r="F39" t="n">
         <v>1777172211000</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>2048234825199526119</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>{'name': 'Prabhakar Singh Bais', 'screenName': 'theprabhakars', 'followersCount': 1991, 'favouritesCount': 1251, 'friendsCount': 0, 'description': '40+ yrs in markets | Philanthropist | \nFounder @ BullBearDigest 🚀 |\nHelping India invest with confidence 🇮🇳'}</t>
         </is>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" s="2" t="n">
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="2" t="n">
         <v>46138.28947916667</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>https://x.com/theprabhakars/status/2048234825199526119</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>2048234825199526119</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>2048200640648876058</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://x.com/theprabhakars/status/2048200640648876058</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>India and New Zealand are set to sign a Free Trade Agreement (FTA) on 27 April, with the aim to more than double bilateral trade to $5 billion in five years.</t>
         </is>
       </c>
-      <c r="F13" t="n">
+      <c r="F40" t="n">
         <v>1777164061000</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>2048200640648876058</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>{'name': 'Prabhakar Singh Bais', 'screenName': 'theprabhakars', 'followersCount': 1991, 'favouritesCount': 1251, 'friendsCount': 0, 'description': '40+ yrs in markets | Philanthropist | \nFounder @ BullBearDigest 🚀 |\nHelping India invest with confidence 🇮🇳'}</t>
         </is>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>2</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M40" t="n">
         <v>2</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="2" t="n">
+        <v>46138.19515046296</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2048213606257570300</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2047939066302267716</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2047939066302267716</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>@AmritMohanty1 Hi Amrit! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1001922 in the subject line of the email.</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1777101696000</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2047936203438362829</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174458, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2047936203438362829</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>46137.47333333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2048213606257570300</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2048213606257570300</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Thank you. I have emailed from my registered email ID quoting Case #234234532915. Kindly review urgently and confirm no fees/interest will apply while the dispute is under investigation, as the due date is near.</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1777167152000</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2047936203438362829</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'name': 'Amrit Mohanty', 'screenName': 'AmritMohanty1', 'followersCount': 8, 'favouritesCount': 144, 'friendsCount': 136, 'description': 'Everything that’s here are my opinions. Not necessarily shared by reasonable-minded people nor my benevolent corporate overlords!!'}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2047939066302267716</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46138.23092592593</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://x.com/AmritMohanty1/status/2048213606257570300</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2048213606257570300</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2048276060505051242</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2048276060505051242</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>@AmritMohanty1 Thank you for your email, our team will be checking and replying to your email as soon as possible.</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1777182042000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2047936203438362829</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174458, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2048213606257570300</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46138.40326388889</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2048231285999759759</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2048231285999759759</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RBLBANK: BOARD HAS PROPOSED DIVIDEND OF ₹1/SH, EMIRATES NBD STRATEGIC INVESTMENT SAID TO BE NEARING CLOSURE</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1777171367000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2048231285999759759</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'name': 'multibagg.ai', 'screenName': 'MultibaggAI', 'followersCount': 2851, 'favouritesCount': 400, 'friendsCount': 1, 'description': 'Fastest market news, earnings, reports, exchange filings to your feed.'}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="2" t="n">
+        <v>46138.27971064814</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://x.com/MultibaggAI/status/2048231285999759759</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2048231285999759759</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2048617997074612357</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/MultibaggAI/status/2048617997074612357</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Q4 RESULTS DUE 27 APR 2026: VARUN BEVERAGES, ULTRATECH CEMENT AMONG ~45 COS REPORTING; ALSO ADANI TOTAL GAS, AU SMALL FINANCE BANK.</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1777263566000</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2048617997074612357</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'name': 'multibagg.ai', 'screenName': 'MultibaggAI', 'followersCount': 2851, 'favouritesCount': 400, 'friendsCount': 1, 'description': 'Fastest market news, earnings, reports, exchange filings to your feed.'}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" s="2" t="n">
+        <v>46139.3468287037</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2048341326358253773</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2048341316237426944</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341316237426944</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/dwvwUupGPZ</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1777197600000</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2048341316237426944</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGw4PIzWoAAeCHS.jpg', 'type': 'photo', 'id': '2048073763258802176'}]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" s="2" t="n">
-        <v>46138.19515046296</v>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="n">
+        <v>46138.58333333334</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2048341326358253773</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2048341320448495999</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341320448495999</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>#الإمارات_الإسلامي #الخدمات_المصرفية_المميزة #الخدمات_المصرفية_في_الإمارات #بنك_الإمارات_الإسلامي
+https://t.co/q5wl9dV1IU</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1777197601000</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2048341316237426944</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2048341316237426944</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>46138.58334490741</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2048341326358253773</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2048341323271336150</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341323271336150</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Every financial journey deserves personal attention. From your first investment to building generational wealth, Emirates Islamic Priority Banking is by your side. Discover the difference today. https://t.co/Bp7yN0OlQp</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1777197602000</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2048341316237426944</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGw4PU-XUAAfotC.jpg', 'type': 'photo', 'id': '2048073766526210048'}]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2048341320448495999</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>46138.58335648148</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2048341326358253773</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2048341326358253773</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048341326358253773</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>#EmiratesIslamic #PriorityBanking #UAEBanking #EmiratesIslamicBank
+https://t.co/acT9rqpIYf</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1777197603000</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2048341316237426944</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2048341323271336150</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>46138.58336805556</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2048386618873024952</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2048386615450435972</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386615450435972</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية تصل إلى 750 درهم https://t.co/n80kD0Ihou</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1777208400000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2048386615450435972</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2048130646405447680/pu/img/fbayKqiesvYdJ8ch.jpg', 'type': 'video', 'id': '2048130646405447680'}]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" s="2" t="n">
+        <v>46138.70833333334</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2048386618873024952</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2048386618873024952</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن https://t.co/9VLrqeVE7Q
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1777208401000</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2048386615450435972</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2048386615450435972</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>46138.70834490741</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386618873024952</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2048386618873024952</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2048386621989335442</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048386621989335442</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>✨ Up to 6% back, unlimited
+🎁 Up to AED 750 welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.
+Apply now
+https://t.co/8qeNDgv9OP</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1777208402000</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2048386615450435972</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2048386618873024952</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>46138.70835648148</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2048280917039276118</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2048280917039276118</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048280917039276118</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>You don’t need to fix everything at once.
+Focus on one big expense.
+Consistency creates real progress.
+#EIFinancialWellbeing #SmartMoneyMindset #EmiratesIslamic
+https://t.co/XvyZgR87nM</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1777183200000</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2048280917039276118</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" s="2" t="n">
+        <v>46138.41666666666</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048311115751342110</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2048311115751342110</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2048311115751342110</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048311115751342110</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ابدأ بفتح حساب "الثروات الرقمية" على الفور للوصول إلى مجموعة كاملة من الاستثمارات العالمية المتوافقة مع أحكام الشريعة الإسلامية. احصل على إمكانية التداول في الأسهم الدولية والمحلية بالإضافة إلى صناديق الاستثمار العالمية.
+قم بتحميل تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك. https://t.co/WhwAacgo92</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1777190400000</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2048311115751342110</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2048072771121356800/pu/img/_uRKe1KOeBKKAZT3.jpg', 'type': 'video', 'id': '2048072771121356800'}]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="2" t="n">
+        <v>46138.5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048326216122335689</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2048326216122335689</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2048326216122335689</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2048326216122335689</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>دع مدخراتك تنمو بمعدل ربح متوقع يصل إلى %6.00 سنوياً مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. يسري العرض من 1 فبراير ولغاية 30 أبريل 2026. تطبق الشروط والأحكام.
+تفضل بزيارة
+https://t.co/V3u06n9tmn https://t.co/J0Ld7tXCk7</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1777194000000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2048326216122335689</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HGv-j2gXkAAt5uG.jpg', 'type': 'photo', 'id': '2048010347450175488'}]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18466, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>46138.54166666666</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P89"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,108 +517,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932723045966001</t>
+          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2049932723045966001</t>
+          <t>2050382263129620695</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049368082779394430</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2034225964863893587</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Have you received an email about a Golden Visa? Before you get excited, pause for a moment. -You’re looking at three emails - two are legitimate, and one is designed to steal your data. -Can you identify the fraudulent one?
-Share your answer in the comments and stand the chance to win AED 2,000.
-#UnitedAgainstFraud</t>
+          <t>Make Eid surprises even more valuable.
+From silver to gold, discover a smarter way to own or gift something truly precious.
+Watch this episode and tell us:
+How can you buy gold and silver from the bank?
+To participate:
+Follow Emirates NBD
+Tag 3 friends
+Drop your answer below for a chance to win AED 10,000</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1777442401000</v>
+        <v>1773832238000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHAKjlHXsAA394W.jpg', 'type': 'video', 'id': '2049149365818728448'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2034225751092822016/img/ppYucbpuWh6bd_l0.jpg', 'type': 'video', 'id': '2034225751092822016'}]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>85</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="M2" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46141.41667824074</v>
+        <v>46099.63238425926</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932723045966001</t>
+          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2049932723045966001</t>
+          <t>2050382263129620695</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2049932723045966001</t>
+          <t>2050382263129620695</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932723045966001</t>
+          <t>https://x.com/Bushrasabih2/status/2050382263129620695</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD 
-@EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE @Bushrasabih1 👍</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1777577021000</v>
+        <v>1777684200000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'Khushbu Agarwal', 'screenName': 'khushbuag88', 'followersCount': 18, 'favouritesCount': 445, 'friendsCount': 91, 'description': ''}</t>
+          <t>{'name': 'Bu_shaikh🌸❤️', 'screenName': 'Bushrasabih2', 'followersCount': 244, 'favouritesCount': 5862, 'friendsCount': 540, 'description': 'الحمدلله'}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -645,134 +645,134 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2034225964863893587</t>
         </is>
       </c>
       <c r="P3" s="2" t="n">
-        <v>46142.97478009259</v>
+        <v>46144.21527777778</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/menews247/status/2050048522049687732</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2050048522049687732</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2050048522049687732</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/menews247/status/2050048522049687732</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049379193910165928</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Emirates NBD secures $750m AT1 bond in first GCC debt deal since February
-Read the full story ➡ https://t.co/f2uzKriH3Q
-#EmiratesNBD #DubaiFinance #AT1Issuance #GCCMarkets #BankingNews #UAEEconomy https://t.co/zsvXNiOlyY</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777604630000</v>
+        <v>1777445050000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2050048522049687732</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHM8Qh5bgAALRPt.jpg', 'type': 'photo', 'id': '2050048510058528768'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Middle East News 247', 'screenName': 'menews247', 'followersCount': 223, 'favouritesCount': 232, 'friendsCount': 11, 'description': 'News, trends, and insights for the Middle East region.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>102056</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" s="2" t="n">
-        <v>46143.29432870371</v>
+        <v>46141.44733796296</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/menews247/status/2050048522049687732</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2050048522049687732</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2050050326774903170</t>
+          <t>2049468314699825596</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/menews247/status/2050050326774903170</t>
+          <t>https://x.com/STKgenghis/status/2049468314699825596</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DIFC launches public consultation on revised Prescribed Company Regulations
-Read the full story ➡ https://t.co/0lnO6j8o3D
-#DIFC #Dubai #Finance #Regulations #Business #UAE https://t.co/QcfjNZwmDX</t>
+          <t>@EmiratesNBD_AE would not recommend bank that suspends 40 year old accounts wout notification. Only found out when i temp blocked credit card i thought id misplaced. It cant be unblocked because of suspension...
+deprived of services no notification  told KYC take 8-10 buss days 2 get back. So..</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1777605060000</v>
+        <v>1777466298000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2050050326774903170</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHM95n3bQAEh-pM.jpg', 'type': 'photo', 'id': '2050050315547000833'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Middle East News 247', 'screenName': 'menews247', 'followersCount': 223, 'favouritesCount': 232, 'friendsCount': 11, 'description': 'News, trends, and insights for the Middle East region.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -785,113 +785,120 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
       <c r="P5" s="2" t="n">
-        <v>46143.29930555556</v>
+        <v>46141.69326388889</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/Ummayed666/status/2050015444304871835</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2050015444304871835</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2049427338119557617</t>
+          <t>2049469132337561727</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049427338119557617</t>
+          <t>https://x.com/STKgenghis/status/2049469132337561727</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Follow these simple steps to access the Voyager Travel Portal and start exploring.
-Apply Now at https://t.co/UGR3KI4NhM https://t.co/klrBtm1x0Q</t>
+          <t>@EmiratesNBD_AE O and also after emails customer support has yet to issue a complaint number. No logging = no complaint. The perfect system.</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777456528000</v>
+        <v>1777466493000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2049427338119557617</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHEHTXNWIAAAvD9.jpg', 'type': 'video', 'id': '2049427279692943360'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>583644</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2049468314699825596</t>
+        </is>
+      </c>
       <c r="P6" s="2" t="n">
-        <v>46141.58018518519</v>
+        <v>46141.69552083333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/Ummayed666/status/2050015444304871835</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2050015444304871835</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2050015444304871835</t>
+          <t>2049469842646818920</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/Ummayed666/status/2050015444304871835</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049469842646818920</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE سونيويلكم</t>
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1004599 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1777596744000</v>
+        <v>1777466662000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2049427338119557617</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -901,11 +908,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'ummayed.666', 'screenName': 'Ummayed666', 'followersCount': 44, 'favouritesCount': 158, 'friendsCount': 176, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -918,53 +925,50 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2049427338119557617</t>
+          <t>2049469132337561727</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46143.20305555555</v>
+        <v>46141.69747685185</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932465704456686</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2049932465704456686</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2049932465704456686</t>
+          <t>2049470212714737829</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932465704456686</t>
+          <t>https://x.com/STKgenghis/status/2049470212714737829</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD
-@EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE I will give this a try but am not holding my breath.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1777576960000</v>
+        <v>1777466750000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -974,11 +978,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Khushbu Agarwal', 'screenName': 'khushbuag88', 'followersCount': 18, 'favouritesCount': 445, 'friendsCount': 91, 'description': ''}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -991,52 +995,50 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049469842646818920</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46142.97407407407</v>
+        <v>46141.69849537037</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932218081095958</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2049932218081095958</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2049932218081095958</t>
+          <t>2049472842727665850</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/khushbuag88/status/2049932218081095958</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049472842727665850</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email : 2 
-#UnitedAgainstFraud
-#EmiratesNBD</t>
+          <t>@STKgenghis Hi khana! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1004599 in the subject line of the email.</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1777576901000</v>
+        <v>1777467377000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1046,11 +1048,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Khushbu Agarwal', 'screenName': 'khushbuag88', 'followersCount': 18, 'favouritesCount': 445, 'friendsCount': 91, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1063,40 +1065,52 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2049368082779394430</t>
+          <t>2049470212714737829</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46142.9733912037</v>
+        <v>46141.70575231482</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/Froshbankss/status/2049856732021579996</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2049856732021579996</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>2050374137852670288</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2049474377788604862</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>https://x.com/STKgenghis/status/2049474377788604862</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE Done. As I said not holding breath.</t>
+        </is>
+      </c>
       <c r="F10" t="n">
-        <v>1777610059824</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+        <v>1777467743000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1104,51 +1118,67 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2049472842727665850</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="n">
-        <v>46143.35717388889</v>
+        <v>46141.70998842592</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/Froshbankss/status/2049856732021579996</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2049856732021579996</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2049856732021579996</t>
+          <t>2049475517070348292</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/Froshbankss/status/2049856732021579996</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049475517070348292</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@t_Duches @SalmaCocomoney What bank do you use. Hsbc abi DIB abi Emirates NBD abi Mashreq. Na Hsbc I dey use that year😎</t>
+          <t>@STKgenghis Hello, we will check the email and update you shortly.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1777558904000</v>
+        <v>1777468015000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2049851769593921909</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,11 +1188,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': '𝐃𝐚𝐝𝐝𝐲 𝐅𝐞𝐫𝐧𝐚𝐧𝐝𝐞𝐳 ⭐️', 'screenName': 'Froshbankss', 'followersCount': 1962, 'favouritesCount': 7258, 'friendsCount': 1872, 'description': '𝐏𝐥𝐮𝐯𝐢𝐨𝐩𝐡𝐢𝐥𝐞, 𝐀𝐬𝐭𝐫𝐨𝐩𝐡𝐢𝐥𝐞, 𝐄𝐜𝐜𝐞𝐝𝐞𝐧𝐭𝐞𝐬𝐢𝐚𝐬𝐭. Owner of Froshluxe wears, where quality clothings meet good vibes 😎. #CFC🤍💙'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1175,119 +1205,122 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2049851769593921909</t>
+          <t>2049474377788604862</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46142.76509259259</v>
+        <v>46141.71313657407</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/DaCryptoLady_/status/2049878370037497895</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2049878370037497895</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2049758371734229151</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/Universal_USDU/status/2016771897816645888</t>
+          <t>https://x.com/STKgenghis/status/2049758371734229151</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Universal launches USDU - the UAE’s first Central Bank-registered USD stablecoin.
-Issued by an FSRA-regulated entity in @ADGlobalMarket, USDU is supported by banking partners @EmiratesNBD_AE , @MashreqTweets, and @almaryahbank with global distribution via @aquanow, and alignment with the UAE’s AED ecosystem through @AECoin_UAE.
-Built for regulated digital asset settlement.
-🔗Press release: https://t.co/R5ypIoHbxM</t>
+          <t>@EmiratesNBD_AE So once again routed to the 'team'. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1769670864000</v>
+        <v>1777535453000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2016768856669511680/img/KCUOpCUXTpHGeDMT.jpg', 'type': 'video', 'id': '2016768856669511680'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'Universal', 'screenName': 'Universal_USDU', 'followersCount': 124, 'favouritesCount': 23, 'friendsCount': 18, 'description': 'FSRA-regulated ADGM issuer of USDU, a USD-backed stablecoin registered with the Central Bank of the UAE for regulated digital asset settlement.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1575</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2049475517070348292</t>
+        </is>
+      </c>
       <c r="P12" s="2" t="n">
-        <v>46051.46833333333</v>
+        <v>46142.49366898148</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/DaCryptoLady_/status/2049878370037497895</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2049878370037497895</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2049878370037497895</t>
+          <t>2049759572416495861</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/DaCryptoLady_/status/2049878370037497895</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049759572416495861</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Very refined presentation, nice job. 🚀</t>
+          <t>@STKgenghis We are extremely sorry and we have escalated the matter and will reply to your email as soon as possible with an update.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1777564062000</v>
+        <v>1777535739000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1297,11 +1330,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Crypto Lady', 'screenName': 'DaCryptoLady_', 'followersCount': 451185, 'favouritesCount': 115864, 'friendsCount': 38989, 'description': 'Crypto lover💕| $SOL investor | WEB3 Creator | Growth 👩🏽\u200d💻 | DM for Marketing Inquiries &amp; Business | #DYOR'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1314,119 +1347,120 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2049758371734229151</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46142.82479166667</v>
+        <v>46142.49697916667</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049927131657081284</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2049927131657081284</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>🇦🇪 A prestigious milestone strengthening the UAE’s financial leadership
-Visa has officially appointed Emirates NBD as the National Net Settlement Agent in the country.
-Now, all local Visa card transactions will be settled domestically in AED — a strategic step that enhances financial sovereignty and drives digital innovation.
-@EmiratesNBD_AE @Visa</t>
+          <t>@EmiratesNBD_AE Right. So its now almost 14 days with credit card not functioning.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1777558260000</v>
+        <v>1777575688000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKFRgnaEAAYS6w.jpg', 'type': 'photo', 'id': '2049847316266487808'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'سيف الدرعي| Saif alderei', 'screenName': 'saif_aldareei', 'followersCount': 91393, 'favouritesCount': 44750, 'friendsCount': 1461, 'description': 'إماراتي 🇦🇪.. صوت فخر وهوية، أكتب بلسان الوطن وأصون الحق العربي. شغوف بالسياسة والدبلوماسية، دار زايد نهجي ..'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3311</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2049759572416495861</t>
+        </is>
+      </c>
       <c r="P14" s="2" t="n">
-        <v>46142.75763888889</v>
+        <v>46142.95935185185</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2049854802947940358</t>
+          <t>2050063207486587148</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/D10oaa/status/2049854802947940358</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050063207486587148</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@saif_aldareei والله يفرح القلب</t>
+          <t>@STKgenghis Please note that our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1777558444000</v>
+        <v>1777608131000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1436,11 +1470,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Doaa', 'screenName': 'D10oaa', 'followersCount': 69, 'favouritesCount': 869, 'friendsCount': 129, 'description': 'ماعندي اعداء بحياتي غير  اللي ببجي .'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1453,50 +1487,50 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049927131657081284</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46142.75976851852</v>
+        <v>46143.33484953704</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2049854823411933347</t>
+          <t>2050170081574056214</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/BRANDONFI23/status/2049854823411933347</t>
+          <t>https://x.com/STKgenghis/status/2050170081574056214</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@saif_aldareei برافو</t>
+          <t>@EmiratesNBD_AE I dont think you appreciate where this places me through no fault of mine. I have had several subscriptions stopped because card is blocked. A monthly payment didnt go through - i am facing a fine.  OVER TWO WEEKS since i asked for my card to be blocked as a precaution !????</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1777558449000</v>
+        <v>1777633612000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1506,11 +1540,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'نوره الرشيدي', 'screenName': 'BRANDONFI23', 'followersCount': 98, 'favouritesCount': 1100, 'friendsCount': 104, 'description': 'يكفيك في هذه الدنيا أن يتذكرك أحدهم في مكان ما من العالم ثم يبتسم ، ويكفي أن تكون ذكرى جميلة في ذاكرة أحدهم .'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1523,50 +1557,50 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2050063207486587148</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46142.75982638889</v>
+        <v>46143.62976851852</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/saif_aldareei/status/2049854031779045437</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2049854031779045437</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2049914078898925977</t>
+          <t>2050275701312324065</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/wajdi_6/status/2049914078898925977</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050275701312324065</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>شخص #م ترد له طلب  ؟.</t>
+          <t>@STKgenghis We apologize for the inconvenience, our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1777572576000</v>
+        <v>1777658794000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2049914078898925977</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1576,75 +1610,77 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'wajdi سؤال وجواب', 'screenName': 'wajdi_6', 'followersCount': 24288, 'favouritesCount': 166949, 'friendsCount': 8438, 'description': 'قل الله ينجيكم منها ومن كل كرب\n\nمبرمج لغة php والبايثون + تصميم مواقع'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>1884</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2050170081574056214</t>
+        </is>
+      </c>
       <c r="P17" s="2" t="n">
-        <v>46142.92333333333</v>
+        <v>46143.92122685185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2049847042961502428</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2049847042961502428</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2049847042961502428</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2049847042961502428</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Visa appoints Emirates NBD as UAE NNSS agent, enabling faster domestic card settlements in dirhams and boosting payment efficiency.
-https://t.co/yy0VYtPQ4n
-#Visa #EmiratesNBD #DigitalPayments #NNSSAgent #AEDTransactions #GCCBusinessNews @EmiratesNBD_AE https://t.co/GE4ETgCNup</t>
+          <t>@EmiratesNBD_AE Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1777556594000</v>
+        <v>1777682263000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2049847042961502428</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKFAwEb0AA8ePZ.jpg', 'type': 'photo', 'id': '2049847028356993024'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'GCC Business News', 'screenName': 'GCCBusinessNews', 'followersCount': 485, 'favouritesCount': 103, 'friendsCount': 20, 'description': 'GBN is an exclusive business news portal for entrepreneurs, businessmen, and trade enthusiasts of the GCC region.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1661,59 +1697,60 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2050275701312324065</t>
+        </is>
+      </c>
       <c r="P18" s="2" t="n">
-        <v>46142.73835648148</v>
+        <v>46144.1928587963</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2049847042961502428</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2049847042961502428</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2049902278983975149</t>
+          <t>2050427142379282939</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/GCCBusinessNews/status/2049902278983975149</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050427142379282939</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>DIFC opens public consultation on amended Prescribed Company regulations, expanding access and roles for corporate service providers.
-https://t.co/LBv5b09AVg
-#DIFC #PrescribedCompanyRegulations #CorporateServiceProviders #PCRegulations #Dubai #GCCBusinessNews
-@DIFC https://t.co/vvWfJBcX3G</t>
+          <t>@STKgenghis We are extremely sorry and understand your concern. Please note that we are working very closely to resolve your concern and will update you on urgent basis.</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1777569763000</v>
+        <v>1777694900000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2049902278983975149</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHK3PFCaoAEGPHM.jpg', 'type': 'photo', 'id': '2049902250085228545'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'GCC Business News', 'screenName': 'GCCBusinessNews', 'followersCount': 485, 'favouritesCount': 103, 'friendsCount': 20, 'description': 'GBN is an exclusive business news portal for entrepreneurs, businessmen, and trade enthusiasts of the GCC region.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1730,118 +1767,117 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2050374137852670288</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="n">
-        <v>46142.89077546296</v>
+        <v>46144.33912037037</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850698876223572</t>
+          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>2050399772591399146</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>1880843050014089636</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850698876223572</t>
+          <t>https://x.com/CaVivekkhatri/status/1880843050014089636</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>UAE News Highlights – May 2026
-Fuel: Diesel holds at 4.69. Petrol 98: 3.66 | 95: 3.55 | 91: 3.48.
-Security: Central Bank bans WhatsApp for banking; stick to official portals only.
-Finance: Emirates NBD x Visa partnership goes local for faster payments.
-* https://t.co/t0NMTDrBeh</t>
+          <t>Bandhan Bank and RBL Bank 👇
+Both are crap stock - Avoid for Investing 🎯</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1777557465000</v>
+        <v>1737262902000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>1880843050014089636</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKISuZbEAAH7Bt.jpg', 'type': 'photo', 'id': '2049850635680681984'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKIUONbQAAxArj.jpg', 'type': 'photo', 'id': '2049850661400166400'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Desea Home Properties LTD', 'screenName': 'DeseaLtd', 'followersCount': 4, 'favouritesCount': 136, 'friendsCount': 9, 'description': ''}</t>
+          <t>{'name': 'CA Vivek Khatri', 'screenName': 'CaVivekkhatri', 'followersCount': 219632, 'favouritesCount': 52078, 'friendsCount': 161, 'description': 'Daily Threads &amp; Learning Articles | Algo Trader &amp; Investor | Macro l Building Wealth Community l Founder &amp; Partner @Stocki_zen –SEBI RA Firm (INH000017675)'}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>503</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>89863</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" s="2" t="n">
-        <v>46142.7484375</v>
+        <v>45676.37618055556</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850698876223572</t>
+          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>2050399772591399146</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2049850859971100900</t>
+          <t>2050399772591399146</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850859971100900</t>
+          <t>https://x.com/Jami076152121/status/2050399772591399146</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>**Travel: 40+ new daily flights via Air India Express. Entertainment: Rashed Al Majed live at Etihad Arena tonight (7:30 PM).
-Trust the experts for your UAE needs.
-Contact Desea: +971 56 296 8027 | +971 58 533 2900  https://t.co/EQd4bfIpRG</t>
+          <t>@CaVivekkhatri RBL takenover by ENBD(Largest bank in UAE) is a bad investment according to you?</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1777557504000</v>
+        <v>1777688375000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>1880843050014089636</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1851,11 +1887,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Desea Home Properties LTD', 'screenName': 'DeseaLtd', 'followersCount': 4, 'favouritesCount': 136, 'friendsCount': 9, 'description': ''}</t>
+          <t>{'name': "Jami's Nest", 'screenName': 'Jami076152121', 'followersCount': 58, 'favouritesCount': 21722, 'friendsCount': 1447, 'description': 'NMIMS, Entrepreneur,Consumer Guidance society.\nEquityTA, Country music, Health&amp;Fitness Wiz.'}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1868,65 +1904,66 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>1880843050014089636</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46142.74888888889</v>
+        <v>46144.26359953704</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049850698876223572</t>
+          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2049850698876223572</t>
+          <t>2050364684251893892</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2049805562968465634</t>
+          <t>2050364684251893892</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/DeseaLtd/status/2049805562968465634</t>
+          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Numbers don't lie. Abu Dhabi real estate is on the rise. 
-With a projected 12-16% price increase by year-end and unrivaled rental yields, the scarcity premium in Abu Dhabi is real. Secure your 10-year Golden Visa and capitalize on the 96% occupancy rate in high-volume areas. https://t.co/dVu1vBhEJc</t>
+          <t>Personal financing in Saudi Arabia made easy for expats.💸🙏🏻
+Emirates NBD – Dammam Branch | Financial Consultant
+#SaudiArabia #ExpatsInKSA #Financing #PersonalFinance #KSAJobs</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1777546704000</v>
+        <v>1777680009000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2049805562968465634</t>
+          <t>2050364684251893892</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJfKTgakAAuT1P.jpg', 'type': 'photo', 'id': '2049805411046559744'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJfPqia4AEusWM.jpg', 'type': 'photo', 'id': '2049805503128330241'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJfRPibsAAF_Co.jpg', 'type': 'photo', 'id': '2049805530240364544'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJfSbDbMAAATJN.jpg', 'type': 'photo', 'id': '2049805550511403008'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'Desea Home Properties LTD', 'screenName': 'DeseaLtd', 'followersCount': 4, 'favouritesCount': 136, 'friendsCount': 9, 'description': ''}</t>
+          <t>{'name': 'Yasmeen Aljadah', 'screenName': 'yasmeenalja', 'followersCount': 188, 'favouritesCount': 20, 'friendsCount': 33, 'description': 'ياسمين\nمستشارة التمويل الشخصي – بنك الإمارات دبي الوطني فرع الدمام \nأساعدك تختار الحل المناسب لك بكل وضوح وسهولة 💸\n📩 تواصل خاص'}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1939,57 +1976,59 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" s="2" t="n">
-        <v>46142.62388888889</v>
+        <v>46144.16677083333</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2049841391577260274</t>
+          <t>https://x.com/yasmeenalja/status/2050364684251893892</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2049841391577260274</t>
+          <t>2050364684251893892</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2049841391577260274</t>
+          <t>2050357066875748710</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2049841391577260274</t>
+          <t>https://x.com/yasmeenalja/status/2050357066875748710</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Visa, a world leader in digital payments, has appointed Emirates NBD, a leading banking group in the Middle East, North Africa and Türkiye (MENAT) region, as its official National Net Settlement Service (NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement. The collaboration enhances the UAE’s domestic settlement capabilities. 
-@EmiratesNBD_AE I @Visa</t>
+          <t>ياسمين صالح
+📞 0552891984
+🏦 بنك الإمارات دبي – فرع الدمام
+#تمويل #قروض #بدون_تحويل_راتب #السعودية https://t.co/t5wubHztjE</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1777555246000</v>
+        <v>1777678193000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2049841391577260274</t>
+          <t>2050357066875748710</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJ_2S0a0AALy9V.jpg', 'type': 'photo', 'id': '2049841351148359680'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHRU4egWIAAB2vK.jpg', 'type': 'photo', 'id': '2050357059598557184'}]</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Dubai Media Office', 'screenName': 'DXBMediaOffice', 'followersCount': 2333303, 'favouritesCount': 2, 'friendsCount': 161, 'description': 'الحساب الرسمي للمكتب الإعلامي لحكومة دبي\n\nThe official account of the Government of Dubai Media Office'}</t>
+          <t>{'name': 'Yasmeen Aljadah', 'screenName': 'yasmeenalja', 'followersCount': 188, 'favouritesCount': 20, 'friendsCount': 33, 'description': 'ياسمين\nمستشارة التمويل الشخصي – بنك الإمارات دبي الوطني فرع الدمام \nأساعدك تختار الحل المناسب لك بكل وضوح وسهولة 💸\n📩 تواصل خاص'}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -1999,134 +2038,139 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>77</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" s="2" t="n">
-        <v>46142.72275462963</v>
+        <v>46144.14575231481</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2049841391577260274</t>
+          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2049841391577260274</t>
+          <t>2050373118900977885</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2049917788115128436</t>
+          <t>2050373118900977885</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/DXBMediaOffice/status/2049917788115128436</t>
+          <t>https://x.com/STKgenghis/status/2050373118900977885</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>دبي 
-Dubai https://t.co/sKLpKWh8W9</t>
+          <t>@EmiratesNBD_AE I will not be able to use airport lounge access because my card is blocked. 
+No one from your 'team' has reached out. I have no dues. 
+Why should I continue an approx 40 year old relationship? You have denied me access without notification.</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1777573460000</v>
+        <v>1777682020000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2049917788115128436</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2049917711262904320/img/dhK-n_CyMCyeulcq.jpg', 'type': 'video', 'id': '2049917711262904320'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'Dubai Media Office', 'screenName': 'DXBMediaOffice', 'followersCount': 2333303, 'favouritesCount': 2, 'friendsCount': 161, 'description': 'الحساب الرسمي للمكتب الإعلامي لحكومة دبي\n\nThe official account of the Government of Dubai Media Office'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18380, 'friendsCount': 491, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>303</v>
+        <v>0</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>13510</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2050275701312324065</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="n">
-        <v>46142.93356481481</v>
+        <v>46144.19004629629</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/MrDariBoss/status/2049839188913320262</t>
+          <t>https://x.com/sanju_soh1/status/2050225649172832351</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2049839188913320262</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2049839188913320262</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/MrDariBoss/status/2049839188913320262</t>
+          <t>https://x.com/sanju_soh1/status/2050225649172832351</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow DM 📥, great project, let’s collab 💯✨</t>
+          <t>@EmiratesNBD_KSA , I have a credit card that I can't use for international transactions. My complaint was raised and closed without a solution (22667042570). Domestic transactions are also being declined. Are you restricting my usage? https://t.co/3tBz51OQPM</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1777554721000</v>
+        <v>1777646860000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHPdW1aWMAAuulT.jpg', 'type': 'photo', 'id': '2050225639748153344'}]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Mr Dari ₿', 'screenName': 'MrDariBoss', 'followersCount': 353257, 'favouritesCount': 225771, 'friendsCount': 24887, 'description': 'Crypto Shiller ₿ &amp; Web3 Strategist 🎯 | Scaling top blockchain projects 📈 | DM for promo 📩 #DeFiShill #NFT #Binance'}</t>
+          <t>{'name': 'Sohan 🇮🇳 ಸೋಹನ್', 'screenName': 'sanju_soh1', 'followersCount': 170, 'favouritesCount': 1957, 'friendsCount': 382, 'description': 'Proud Bengaluru resident with a vision to make our city the ultimate global gem! Pushing for public transport to create a swift, sustainable urban paradise.'}</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -2139,50 +2183,46 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2016771897816645888</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" s="2" t="n">
-        <v>46142.71667824074</v>
+        <v>46143.78310185186</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2049834695249088852</t>
+          <t>https://x.com/sanju_soh1/status/2050225649172832351</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2049834695249088852</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2049834695249088852</t>
+          <t>2050229504618991913</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2049834695249088852</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050229504618991913</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emirates NBD prices $750mln PNC6 AT1 bond in first GCC public debt sale since Iran war https://t.co/jGs3XiGvP7</t>
+          <t>@sanju_soh1 Hello, we're sorry to hear you're having an unpleasant experience. We're happy to help and resolve it. Please send details of your complaint via private message so we can assist you better.</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1777553650000</v>
+        <v>1777647779000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2049834695249088852</t>
+          <t>2050225649172832351</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2192,7 +2232,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12530, 'favouritesCount': 443589, 'friendsCount': 8661, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17433, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J26" t="n">
@@ -2209,46 +2249,50 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2050225649172832351</t>
+        </is>
+      </c>
       <c r="P26" s="2" t="n">
-        <v>46142.70428240741</v>
+        <v>46143.79373842593</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2049834695249088852</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2049834695249088852</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2049977067987406974</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2049977067987406974</t>
+          <t>https://x.com/patilabhijeet45/status/2050086851621593314</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barak congratulates al-Zaidi on his appointment to form the Iraqi government. | Search 4 Dinar https://t.co/z0JRBfEsxK</t>
+          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1777587594000</v>
+        <v>1777613768000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2049977067987406974</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2258,11 +2302,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12530, 'favouritesCount': 443589, 'friendsCount': 8661, 'description': ''}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14727, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2275,63 +2319,60 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>46143.09715277778</v>
+        <v>46143.40009259259</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/insightsbyfuzz/status/2049836484035793204</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2049836484035793204</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2049836484035793204</t>
+          <t>2050093026182131824</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/insightsbyfuzz/status/2049836484035793204</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050093026182131824</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>🏦 Emirates NBD takes control of RBL Bank
-Emirates NBD invests ₹38,489 crore in  for a 74% stake. This massive capital infusion targets top five private bank status within 3-5 years.
-#RBLBank
-Read more: https://t.co/jql9PSe3AI https://t.co/KAcb3dolMK</t>
+          <t>@patilabhijeet45 Hello Abhijeet, Thanks for reaching us. We have sent you direct message already. Thanks- Zubair</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1777554076000</v>
+        <v>1777615240000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2049836484035793204</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJ7anrXIAEYYGn.jpg', 'type': 'photo', 'id': '2049836477664665601'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'Insights by fuzz', 'screenName': 'insightsbyfuzz', 'followersCount': 16, 'favouritesCount': 18, 'friendsCount': 4, 'description': 'We connect the dots across news, company filings and management commentary to bring you the top insights!\n\nPowered by @ask_fuzz | Part of @RaiseTheBarHQ'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2344,59 +2385,60 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2050086851621593314</t>
+        </is>
+      </c>
       <c r="P28" s="2" t="n">
-        <v>46142.70921296296</v>
+        <v>46143.41712962963</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/insightsbyfuzz/status/2049836484035793204</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2049836484035793204</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2049876238538334431</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/insightsbyfuzz/status/2049876238538334431</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>📉 Vodafone Idea gets ₹23,649 crore AGR relief
-Payments pushed to FY41 aid cash flow but #IDEA faces negative equity and stiff competition. Investors remain skeptical despite the Telecom lifeline.
-#VodafoneIdea
-Read more: https://t.co/6usokRv9XP https://t.co/EdvvQ8j205</t>
+          <t>@EmiratesNBD_AE Thank you , I just replied you in dm</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1777563554000</v>
+        <v>1777646110000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2049876238538334431</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKfkrhXsAAftmm.jpg', 'type': 'photo', 'id': '2049876232913793024'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'Insights by fuzz', 'screenName': 'insightsbyfuzz', 'followersCount': 16, 'favouritesCount': 18, 'friendsCount': 4, 'description': 'We connect the dots across news, company filings and management commentary to bring you the top insights!\n\nPowered by @ask_fuzz | Part of @RaiseTheBarHQ'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14727, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2409,63 +2451,64 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>750</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2050093026182131824</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n">
-        <v>46142.81891203704</v>
+        <v>46143.77442129629</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/SUAL6AN_UAE/status/2049819862168699318</t>
+          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2049819862168699318</t>
+          <t>2050222500295123129</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2049819862168699318</t>
+          <t>2050275958674932182</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/SUAL6AN_UAE/status/2049819862168699318</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050275958674932182</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>🟥 نجاح كبير لصندوق فاندستار لأسهم الإمارات العربية المتحدة ذات الدخل من "الإمارات دبي الوطني لإدارة الأصول" والشركة تطلق صندوقاً جديداً للصكوك العالمية ذات العائد المرتفع. اقرأ المزيد:
-https://t.co/NvmepCllAn…
-Emirates NBD Asset Management highlights success of FundStar UAE Equities Income Fund and expands access to new global high-yield sukuk fund. Read more: 
-https://t.co/ncw3Zv5gtY…</t>
+          <t>@patilabhijeet45 We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1005869 in the subject line.</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1777550113000</v>
+        <v>1777658855000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2049819862168699318</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJsS9abcAA5Oql.jpg', 'type': 'photo', 'id': '2049819853385854976'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': '𝕊𝕦𝕝𝕥𝕒𝕟\uea00🇦🇪 \uea00', 'screenName': 'SUAL6AN_UAE', 'followersCount': 13683, 'favouritesCount': 58599, 'friendsCount': 7789, 'description': 'الله - الوطن -رئيس الدولة 🇦🇪الامارات الحب والعشق الابدي 🇦🇪الامارات وشيوخ الامارات خط احمر 🇦🇪'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2475,121 +2518,125 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>360</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2050222500295123129</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="n">
-        <v>46142.66334490741</v>
+        <v>46143.92193287037</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/SUAL6AN_UAE/status/2049819862168699318</t>
+          <t>https://x.com/MohSSD4/status/2050227480842154486</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2049819862168699318</t>
+          <t>2050227480842154486</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2049896635782844621</t>
+          <t>2050224474650181731</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/SUAL6AN_UAE/status/2049896635782844621</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050224474650181731</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>🚨#عاجل | 
-الرئيس الأميركي دونالد ترامب: 
-سندمرهم مره أخرى وسنعيدهم إيران إلى عصور ماقبل التاريخ. https://t.co/5Cq4JHyjpa</t>
+          <t>قبل أي خطوة، استشر المختصين📱
+تواصل مع المستشار الائتماني في ⁧#بنك_الإمارات_دبي_الوطني⁩ وخذ القرار بثقة✨ https://t.co/lJ3j6amaZa</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1777568417000</v>
+        <v>1777646580000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2049896635782844621</t>
+          <t>2050224474650181731</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2049896572931215360/img/BzRcOzjrIRPnub8p.jpg', 'type': 'video', 'id': '2049896572931215360'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKuIqgXsAAi-Jy.jpg', 'type': 'photo', 'id': '2049892244279242752'}]</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': '𝕊𝕦𝕝𝕥𝕒𝕟\uea00🇦🇪 \uea00', 'screenName': 'SUAL6AN_UAE', 'followersCount': 13683, 'favouritesCount': 58599, 'friendsCount': 7789, 'description': 'الله - الوطن -رئيس الدولة 🇦🇪الامارات الحب والعشق الابدي 🇦🇪الامارات وشيوخ الامارات خط احمر 🇦🇪'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17433, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>376</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" s="2" t="n">
-        <v>46142.87519675926</v>
+        <v>46143.77986111111</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/raynft_/status/2049828036577460592</t>
+          <t>https://x.com/MohSSD4/status/2050227480842154486</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2049828036577460592</t>
+          <t>2050227480842154486</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2049828036577460592</t>
+          <t>2050227480842154486</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/raynft_/status/2049828036577460592</t>
+          <t>https://x.com/MohSSD4/status/2050227480842154486</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Free assistance anytime, drop me a DM.</t>
+          <t>@EmiratesNBD_KSA السلام عليكم، هل يوجد خصومات بالتعاون مع اي شركات مبيعات الاكترونيات قريبا
+فقدناكم بين البنوك الثانية</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1777552062000</v>
+        <v>1777647297000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2050224474650181731</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2599,11 +2646,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'RayNft \uea00', 'screenName': 'raynft_', 'followersCount': 334492, 'favouritesCount': 107856, 'friendsCount': 150720, 'description': 'Pudgy Penguin #3793 • Spreading Awareness in the Web3 Space • Alpha Caller &amp; CM • Degen Crypto enjoyer #NFT 🐧 #Crypto'}</t>
+          <t>{'name': 'Mohammad S.', 'screenName': 'MohSSD4', 'followersCount': 87, 'favouritesCount': 931, 'friendsCount': 161, 'description': "I trust everyone, it's the devil inside them I don't trust\nلايوجد شيء اسمه دين، جنس، لون، اصل او حتى مكان سيء, بل يوجد شخص جيد او شخص سيء"}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2616,50 +2663,51 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2050224474650181731</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46142.68590277778</v>
+        <v>46143.78815972222</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/00Q__/status/2049833166224216504</t>
+          <t>https://x.com/MohSSD4/status/2050227480842154486</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2049833166224216504</t>
+          <t>2050227480842154486</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2049833166224216504</t>
+          <t>2050233737401479508</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/00Q__/status/2049833166224216504</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050233737401479508</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>@Universal_USDU @ADGlobalMarket @EmiratesNBD_AE @MashreqTweets @almaryahbank @aquanow Really solid concept here, open to connect anytime</t>
+          <t>@MohSSD4 مرحباً بك, يمكنك الأن معرفة المزيد عن العروض والخصومات من خلال الضغط على الرابط ادناه.
+https://t.co/ANkkIZKNb4</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1777553285000</v>
+        <v>1777648789000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2050224474650181731</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2669,7 +2717,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Emma Crypto Strategy', 'screenName': '00Q__', 'followersCount': 137467, 'favouritesCount': 113857, 'friendsCount': 126716, 'description': '🚀 Web3 Growth | Early Gem Finder 📈 $SOL $ETH $BSC | Memes &amp; Altcoins | 🌐 100K+ network | High engagement reach | 📩 DM for collaborations'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17433, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2686,147 +2734,136 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2016771897816645888</t>
+          <t>2050227480842154486</t>
         </is>
       </c>
       <c r="P33" s="2" t="n">
-        <v>46142.70005787037</v>
+        <v>46143.80542824074</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049806904768045275</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214078409527791</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2049806904768045275</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2049806904768045275</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049806904768045275</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214078409527791</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Why settle for someone else’s highlights?
-Start your own journey with an Emirates NBD Voyager credit card. Apply today to get up to AED 700 in https://t.co/tewFiex0BH vouchers.
-Access benefits like:
-- AED 300 https://t.co/tewFiex0BH voucher with a new Emirates NBD Voyager World Credit Card
-- AED 700 https://t.co/tewFiex0BH voucher with a new Emirates NBD Voyager World Elite Credit Card
-Offer is valid until 15 May 2026. Apply now.
-Terms and Conditions apply.
-Apply Now: https://t.co/muX7gaxwoT
-النص المرافق للمنشور:
-لماذا تكتفي بمشاهدة اللقطات المميزة للآخرين؟
-ابدأ رحلتك الخاصة مع بطاقة فويجر من بنك الإمارات دبي الوطني. قدّم طلبك اليوم لتحصل على قسائم من https://t.co/tewFiex0BH بقيمة تصل إلى 700 درهم.
-استفد من المزايا التالية:
-- قسيمة https://t.co/tewFiex0BH بقيمة 300 درهم مع بطاقة فويجر وورلد الائتمانية الجديدة من بنك الإمارات دبي الوطني
-- قسيمة https://t.co/tewFiex0BH بقيمة 700 درهم مع بطاقة فويجر وورلد إيليت الائتمانية الجديدة من بنك الإمارات دبي الوطني
-يسري العرض حتى 15 مايو 2026. قدّم طلبك الآن.
-تطبّق الشروط والأحكام.
- تقدم بطلبك الآن: https://t.co/au9YcHMBrP</t>
+          <t>Extremely Disappointed with ENBD @EmiratesNBD_AE Services
+I raised case in Sep 2025. Partial recovery was done by Dec, then the case was closed and new one was reopened. That too got closed in March without full recovery and without my consent.
+Dispute ref. 230952198951</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1777547024000</v>
+        <v>1777644102000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2049806904768045275</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJggwbXwAAQLLo.jpg', 'type': 'photo', 'id': '2049806896278781952'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJgg-eXcAA73o8.jpg', 'type': 'photo', 'id': '2049806900049440768'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Usman Chaudhry', 'screenName': 'iUsmanChaudhary', 'followersCount': 1540, 'favouritesCount': 129646, 'friendsCount': 4628, 'description': 'Oracle Certified Professional (Sr. Software Engineer )\n#Oracle | Oracle University\nاَلْحَمْدُ لِلّٰهِ من جانبازم.'}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" s="2" t="n">
-        <v>46142.62759259259</v>
+        <v>46143.75118055556</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049806904768045275</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214078409527791</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2049806904768045275</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2049799676367343838</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049799676367343838</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214080468938945</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Start your banking journey today with Emirates NBD.
-ابدأ رحلتك المصرفية اليوم مع بنك الإمارات دبي الوطني. https://t.co/tIpnLZ2ain</t>
+          <t>An amount is still pending, and there’s been no proper follow-up or support.
+Expected much better transparency and accountability from a bank. please look into this urgently.
+@EmiratesNBD_AE
+@centralbankuae
+#ENBD #EmiratesNBD #CustomerService #CreditCardFraud #BankingExperience</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1777545300000</v>
+        <v>1777644102000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2049799676367343838</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJZ77wWUAAPXXa.jpg', 'type': 'photo', 'id': '2049799666594631680'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJZ8OjWgAAcd41.jpg', 'type': 'photo', 'id': '2049799671640391680'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Usman Chaudhry', 'screenName': 'iUsmanChaudhary', 'followersCount': 1540, 'favouritesCount': 129646, 'friendsCount': 4628, 'description': 'Oracle Certified Professional (Sr. Software Engineer )\n#Oracle | Oracle University\nاَلْحَمْدُ لِلّٰهِ من جانبازم.'}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2839,46 +2876,54 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>362</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2050214078409527791</t>
+        </is>
+      </c>
       <c r="P35" s="2" t="n">
-        <v>46142.60763888889</v>
+        <v>46143.75118055556</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049819036184391937</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214080468938945</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2049819036184391937</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2049697401896907011</t>
+          <t>2050268003070271682</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049697401896907011</t>
+          <t>https://x.com/centralbankuae/status/2050268003070271682</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE pls note have reached out twice to CS Team, registered complaint on portal plus addressing system glitch while booking a service. Expected response is to support client with booking with manual intervention since there is known system constraint.</t>
+          <t>Dear Consumer
+Thank you for contacting the Central Bank of the UAE. We highly value your inquiries and feedback.
+For any information or to file a complaint, please contact @SanadakUAE, the new Ombudsman Unit for the resolution of consumer complaints against Licensed Financial Institutions and Insurance Companies, by downloading the mobile application or visiting the website: https://t.co/Dptt9dWyCm 
+Best regards,
+Central Bank of the UAE</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1777520916000</v>
+        <v>1777656958000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2049697401896907011</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2888,11 +2933,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'Nishi Janiani', 'screenName': 'nishijaniani', 'followersCount': 23, 'favouritesCount': 11, 'friendsCount': 100, 'description': ''}</t>
+          <t>{'name': 'Central Bank of the UAE', 'screenName': 'centralbankuae', 'followersCount': 6478, 'favouritesCount': 389, 'friendsCount': 213, 'description': 'الحساب الرسمي لمصرف الإمارات العربية المتحدة المركزي The official account of the Central Bank of the UAE'}</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2901,50 +2946,54 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2050214080468938945</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="n">
-        <v>46142.32541666667</v>
+        <v>46143.89997685186</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049819036184391937</t>
+          <t>https://x.com/iUsmanChaudhary/status/2050214080468938945</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2049819036184391937</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2049704090016379117</t>
+          <t>2050236953451188518</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049704090016379117</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050236953451188518</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>@nishijaniani Hi Nishi, thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1004802 in the subject line of the email.</t>
+          <t>@iUsmanChaudhary We regret to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1006207 in the subject line.</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1777522511000</v>
+        <v>1777649555000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2049697401896907011</t>
+          <t>2050214078409527791</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2954,7 +3003,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J37" t="n">
@@ -2967,64 +3016,64 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2049697401896907011</t>
+          <t>2050214080468938945</t>
         </is>
       </c>
       <c r="P37" s="2" t="n">
-        <v>46142.34387731482</v>
+        <v>46143.81429398148</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049819036184391937</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2049819036184391937</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2049819036184391937</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049819036184391937</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050092857025757288</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Email sent.. there seems lot of to and fro exchange instead of getting on call and resolving the issue.</t>
+          <t>To limit online scam risks, just lower your card limits! With ENBD X App, you’re in control – reduce card limits anytime, anywhere! Stay one step ahead of fraud. Stay #UnitedAgainstFraud https://t.co/uTL4FBuhZu</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1777549916000</v>
+        <v>1777615200000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2049697401896907011</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2049776489160126464/img/8bh7b27h1YuvE1BT.jpg', 'type': 'video', 'id': '2049776489160126464'}]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'Nishi Janiani', 'screenName': 'nishijaniani', 'followersCount': 23, 'favouritesCount': 11, 'friendsCount': 100, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J38" t="n">
@@ -3034,57 +3083,53 @@
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>2049704090016379117</t>
-        </is>
-      </c>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" s="2" t="n">
-        <v>46142.66106481481</v>
+        <v>46143.41666666666</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049819036184391937</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2049819036184391937</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2049819866153033762</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049819866153033762</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@nishijaniani Hello, we will check and reply to your email as soon as possible.</t>
+          <t>@EmiratesNBD_AE Is the app down?</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1777550114000</v>
+        <v>1777619949000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2049697401896907011</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3094,11 +3139,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rasha Gh', 'screenName': 'rashagha', 'followersCount': 408, 'favouritesCount': 7742, 'friendsCount': 159, 'description': '🇱🇧\n🤍\n🇦🇪'}</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3111,64 +3156,60 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2049819036184391937</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46142.66335648148</v>
+        <v>46143.47163194444</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/ForsanUrdu/status/2049793228564480371</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2049793228564480371</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2049793228564480371</t>
+          <t>2050118059285737835</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/ForsanUrdu/status/2049793228564480371</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050118059285737835</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ویزا نے امارات این بی ڈی کو NNSS ایجنٹ مقرر کیا، جس سے لین دین مقامی AED میں مکمل ہوں گے۔
-#NNSS
-#UAE #Dubai #EmiratesNBD #NBD #Visa 
-@EmiratesNBD_AE
-@Visa https://t.co/87utaLSJAb</t>
+          <t>@rashagha Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist. Please mention in the email subject social media case #1005963. Thanks- Zubair</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1777543763000</v>
+        <v>1777621209000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2049793228564480371</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJUFFaWIAAPxcr.jpg', 'type': 'photo', 'id': '2049793226735755264'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'فرسان اردو', 'screenName': 'ForsanUrdu', 'followersCount': 5986, 'favouritesCount': 9, 'friendsCount': 4, 'description': 'متحدہ عرب امارات فرسان اردو آپ کا متحدہ عرب امارات سے متعلق درست معلومات کا جامع ذریعہ ہے.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -3185,59 +3226,60 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2050112775310172515</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="n">
-        <v>46142.58984953703</v>
+        <v>46143.48621527778</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/ForsanUrdu/status/2049793228564480371</t>
+          <t>https://x.com/rashagha/status/2050112775310172515</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2049793228564480371</t>
+          <t>2050112775310172515</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2049880451557277983</t>
+          <t>2050118024770822463</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/ForsanUrdu/status/2049880451557277983</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050118024770822463</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>الإمارات کے صدر اور نیوزی لینڈ کے وزیر اعظم نے تعاون اور اقتصادی شراکت داری بڑھانے پر گفتگو کی
-#UAE #NewZealand
-@MohamedBinZayed
-@UAEEmbassyNZ https://t.co/63tY6ZOhvx</t>
+          <t>@rashagha Hi Rasha, thanks for reaching us, and we are extremely sorry for the inconvenience caused to you. Please note that our app is working fine. If you are facing any issue with the app,</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1777564559000</v>
+        <v>1777621201000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2049880451557277983</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKjaHtXAAAzqQw.jpg', 'type': 'photo', 'id': '2049880449548222464'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'فرسان اردو', 'screenName': 'ForsanUrdu', 'followersCount': 5986, 'favouritesCount': 9, 'friendsCount': 4, 'description': 'متحدہ عرب امارات فرسان اردو آپ کا متحدہ عرب امارات سے متعلق درست معلومات کا جامع ذریعہ ہے.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -3250,134 +3292,133 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2050112775310172515</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="n">
-        <v>46142.83054398148</v>
+        <v>46143.48612268519</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/InfoblazeINDIA/status/2049793884012830907</t>
+          <t>https://x.com/MabokM1849/status/2050113341851685008</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2049793884012830907</t>
+          <t>2050113341851685008</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2049793884012830907</t>
+          <t>2049458682694341011</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/InfoblazeINDIA/status/2049793884012830907</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049458682694341011</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal 
-@RBLBank 
-@EmiratesNBD_AE 
-#India #Banking #Dubai
-#UAE #MiddleEast 
-https://t.co/5caG5iFvBn
-Via https://t.co/E6tc2Xk72c https://t.co/cZjuG5eIoY</t>
+          <t>نجاح كبير لصندوق فاندستار لأسهم الإمارات العربية المتحدة ذات الدخل من "الإمارات دبي الوطني لإدارة الأصول" والشركة تطلق صندوقاً جديداً للصكوك العالمية ذات العائد المرتفع. اقرأ المزيد:
+https://t.co/SzbRvQDh6V
+Emirates NBD Asset Management highlights success of FundStar UAE Equities Income Fund and expands access to new global high-yield sukuk fund. Read more: 
+https://t.co/4VjReJkUUu</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1777543919000</v>
+        <v>1777464001000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2049793884012830907</t>
+          <t>2049458682694341011</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJUjfYbwAAqmHz.png', 'type': 'photo', 'id': '2049793749103132672'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHEjz3MWYAANTmN.jpg', 'type': 'photo', 'id': '2049458679326334976'}]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'Infoblaze INDIA', 'screenName': 'InfoblazeINDIA', 'followersCount': 604, 'favouritesCount': 1020, 'friendsCount': 146, 'description': 'India BusinessNews - From authentic sources -Also @InfoblazeME SoutheastAsia @InfoblazeSEA | https://t.co/yiqL8jaTUG  initiative | https://t.co/Osc3c4Gmzn'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>248429</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" s="2" t="n">
-        <v>46142.59165509259</v>
+        <v>46141.66667824074</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/InfoblazeINDIA/status/2049793884012830907</t>
+          <t>https://x.com/MabokM1849/status/2050113341851685008</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2049793884012830907</t>
+          <t>2050113341851685008</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2050032460352647552</t>
+          <t>2050113341851685008</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/InfoblazeINDIA/status/2050032460352647552</t>
+          <t>https://x.com/MabokM1849/status/2050113341851685008</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Business Headlines - Stock Market Triggers India
-01 May 2026  
-#India #Business #Stockmarket #Sensex #Nifty https://t.co/aydeBfT8V0 https://t.co/ihCOivyU9q</t>
+          <t>@EmiratesNBD_AE https://t.co/GZGbjrxpWb</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1777600800000</v>
+        <v>1777620084000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2050032460352647552</t>
+          <t>2049458682694341011</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHMW7TzbgAApwXI.png', 'type': 'photo', 'id': '2050007463567785984'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHMW7T5bEAAcZn-.png', 'type': 'photo', 'id': '2050007463592923136'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'Infoblaze INDIA', 'screenName': 'InfoblazeINDIA', 'followersCount': 604, 'favouritesCount': 1020, 'friendsCount': 146, 'description': 'India BusinessNews - From authentic sources -Also @InfoblazeME SoutheastAsia @InfoblazeSEA | https://t.co/yiqL8jaTUG  initiative | https://t.co/Osc3c4Gmzn'}</t>
+          <t>{'name': 'Dr:Mobark Ali', 'screenName': 'MabokM1849', 'followersCount': 254, 'favouritesCount': 868, 'friendsCount': 896, 'description': 'دكتور / مبارك أخصائي القلب والشريان 🌹'}</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3394,62 +3435,60 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2049458682694341011</t>
+        </is>
+      </c>
       <c r="P43" s="2" t="n">
-        <v>46143.25</v>
+        <v>46143.47319444444</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/letstalkdubai/status/2049793969677291575</t>
+          <t>https://x.com/baro_jwngma/status/2050135845785698585</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2049793969677291575</t>
+          <t>2050135845785698585</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2049793969677291575</t>
+          <t>2050135845785698585</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/letstalkdubai/status/2049793969677291575</t>
+          <t>https://x.com/baro_jwngma/status/2050135845785698585</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>#Sebi approves change of control at #RBL_Bank in #EmiratesNBD stake deal
-@RBLBank
-@EmiratesNBD_AE
-#India #Banking #Dubai
-#UAE #MiddleEast
-https://t.co/P8Ax5vNbhn
-Via https://t.co/xfccX701ON https://t.co/qf4uWzDcTz</t>
+          <t>SEBI approves change in control for Emirates NBD Bank's preferential equity investment in RBL Bank; transaction pending other regulatory approvals.</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1777543940000</v>
+        <v>1777625449000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2049793969677291575</t>
+          <t>2050135845785698585</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJUvWlbIAAojkD.png', 'type': 'photo', 'id': '2049793952900128768'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': "Let's Talk Dubai", 'screenName': 'letstalkdubai', 'followersCount': 625, 'favouritesCount': 5808, 'friendsCount': 197, 'description': 'Dubai Quality Content\nBusiness News - Middle East @infoblazeME | A Cogentelli initiative'}</t>
+          <t>{'name': 'Hello Market', 'screenName': 'baro_jwngma', 'followersCount': 425, 'favouritesCount': 1706, 'friendsCount': 87, 'description': 'Stock Market | Business | Corporate Action | Value Investing | Basic Economics 📈 \n_ (Not SEBI RA)'}</t>
         </is>
       </c>
       <c r="J44" t="n">
@@ -3459,67 +3498,63 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" s="2" t="n">
-        <v>46142.59189814814</v>
+        <v>46143.53528935185</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/letstalkdubai/status/2049793969677291575</t>
+          <t>https://x.com/baro_jwngma/status/2050135845785698585</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2049793969677291575</t>
+          <t>2050135845785698585</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2049867286908191231</t>
+          <t>2050142408357339369</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/letstalkdubai/status/2049867286908191231</t>
+          <t>https://x.com/baro_jwngma/status/2050142408357339369</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dubai Chamber of Commerce and #FedEx discuss supply chain readiness with representatives from 196 companies amid current global developments
-@DxbChamberComm
-#Dubai #SupplyChain
-#MiddleEast
-https://t.co/7hxJYrXqUe https://t.co/KW6iJfq7dE</t>
+          <t>AWL Agri Business targets mid-teens volume growth, steady EBITDA per ton for edible oil, and EBITDA neutrality in food segment until FY27.</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1777561420000</v>
+        <v>1777627014000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2049867286908191231</t>
+          <t>2050142408357339369</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKXavHaEAAeLFC.jpg', 'type': 'photo', 'id': '2049867265986924544'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': "Let's Talk Dubai", 'screenName': 'letstalkdubai', 'followersCount': 625, 'favouritesCount': 5808, 'friendsCount': 197, 'description': 'Dubai Quality Content\nBusiness News - Middle East @infoblazeME | A Cogentelli initiative'}</t>
+          <t>{'name': 'Hello Market', 'screenName': 'baro_jwngma', 'followersCount': 425, 'favouritesCount': 1706, 'friendsCount': 87, 'description': 'Stock Market | Business | Corporate Action | Value Investing | Basic Economics 📈 \n_ (Not SEBI RA)'}</t>
         </is>
       </c>
       <c r="J45" t="n">
@@ -3529,271 +3564,276 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>56</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" s="2" t="n">
-        <v>46142.79421296297</v>
+        <v>46143.55340277778</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/UAE_Forsan/status/2049790865460154569</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050092857025757288</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2049790865460154569</t>
+          <t>2050092857025757288</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2049790865460154569</t>
+          <t>2050141465431462302</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/UAE_Forsan/status/2049790865460154569</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050141465431462302</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Visa, a world leader in digital payments, has appointed Emirates NBD as its official National Net Settlement Service (#NNSS) Agent in the UAE, allowing Visa’s domestic card transactions to be settled by Emirates NBD locally in UAE Dirhams (AED) in lieu of international settlement
-#UAE #Dubai #EmiratesNBD #NBD #Visa 
-@EmiratesNBD_AE 
-@Visa</t>
+          <t>Embrace higher earnings with your salary transfer
+ Transfer your salary to Emirates NBD and earn up to 6% on your balance. Get started today:
+ 1. Open a Millionaire Account, Current Account or Savings Account
+ 2. Transfer your salary of AED 10,000 or more
+ 3. Maintain an average monthly balance of AED 25,000 or more
+ 4. Earn bonus interest with a credit card
+ Terms and conditions apply
+ https://t.co/u4ZGMVsftb</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1777543200000</v>
+        <v>1777626789000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2049790865460154569</t>
+          <t>2050141465431462302</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJG91GXcAAJVeV.jpg', 'type': 'photo', 'id': '2049778808446742528'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHOQzBXW8AAguXa.jpg', 'type': 'video', 'id': '2050141414244200448'}]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Forsan', 'screenName': 'UAE_Forsan', 'followersCount': 32543, 'favouritesCount': 368, 'friendsCount': 3, 'description': 'UAE Forsan media news 🇦🇪'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>151371</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" s="2" t="n">
-        <v>46142.58333333334</v>
+        <v>46143.55079861111</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/UAE_Forsan/status/2049790865460154569</t>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2049790865460154569</t>
+          <t>2050104780245344423</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2049941758008565840</t>
+          <t>2043682357216149641</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/UAE_Forsan/status/2049941758008565840</t>
+          <t>https://x.com/chin2to/status/2043682357216149641</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>In light of current regional developments, the Ministry of Foreign Affairs (#MoFA) announces a travel ban on UAE nationals traveling to the Islamic Republic of Iran, the Lebanese Republic, and the Republic of Iraq. The Ministry calls on all #UAE nationals currently in these countries to expedite their immediate return to the UAE
-@mofauae</t>
+          <t>Finally thought I'll get an @EmiratesNBD_AE Skywards Credit Card, but applying for one is such a hassle. Changed my mind immediately after speaking to them for 2 months.</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1777579175000</v>
+        <v>1776086818000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2049941758008565840</t>
+          <t>2043682357216149641</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHLbHPZXwAAeuni.jpg', 'type': 'photo', 'id': '2049941697845510144'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Forsan', 'screenName': 'UAE_Forsan', 'followersCount': 32543, 'favouritesCount': 368, 'friendsCount': 3, 'description': 'UAE Forsan media news 🇦🇪'}</t>
+          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>395</t>
+          <t>488</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" s="2" t="n">
-        <v>46142.99971064815</v>
+        <v>46125.72706018519</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2049788923015012684</t>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2049788923015012684</t>
+          <t>2050104780245344423</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2049788923015012684</t>
+          <t>2043691745330798829</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2049788923015012684</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2043691745330798829</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Emirates NBD successfully prices a $750 million Additional Tier 1 (AT1) capital issuance, marking the first GCC debt capital markets transaction since late February 2026 and reinforcing investor confidence in the region’s banking sector.
-#EmiratesNBD #GCC #Banking #CapitalMarket https://t.co/4KQWxk0bOP</t>
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #996916 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1777542737000</v>
+        <v>1776089056000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2049788923015012684</t>
+          <t>2043682357216149641</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJQIZRWMAANFls.jpg', 'type': 'photo', 'id': '2049788885559816192'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'World Remittance Action Forum', 'screenName': 'ForumRemittance', 'followersCount': 17, 'favouritesCount': 0, 'friendsCount': 3, 'description': 'Empowering global money transfers | 💸 Fast, secure, and affordable remittance solutions | 🌐 Connecting families worldwide #Remittance #Fintech #GlobalPayments'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
+          <t>452</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2043682357216149641</t>
+        </is>
+      </c>
       <c r="P48" s="2" t="n">
-        <v>46142.57797453704</v>
+        <v>46125.75296296296</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2049788923015012684</t>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2049788923015012684</t>
+          <t>2050104780245344423</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2049796315736084692</t>
+          <t>2050104780245344423</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/ForumRemittance/status/2049796315736084692</t>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Visa appoints Emirates NBD as its official National Net Settlement Service (NNSS) Agent in the UAE, strengthening the country’s digital payments and settlement infrastructure.
-#Visa #EmiratesNBD #UAE #Payments #Fintech #DigitalPayments #Banking #Innovation https://t.co/ksZUWlHn8I</t>
+          <t>@EmiratesNBD_AE I was supposed to get a call for card cancellation in 2 days, been 4 and no one has bothered calling me yet. Trying to save the cancellation targets?</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1777544499000</v>
+        <v>1777618043000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2049796315736084692</t>
+          <t>2043682357216149641</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJW4OOaUAAi0lK.jpg', 'type': 'photo', 'id': '2049796304298201088'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'World Remittance Action Forum', 'screenName': 'ForumRemittance', 'followersCount': 17, 'favouritesCount': 0, 'friendsCount': 3, 'description': 'Empowering global money transfers | 💸 Fast, secure, and affordable remittance solutions | 🌐 Connecting families worldwide #Remittance #Fintech #GlobalPayments'}</t>
+          <t>{'name': 'Chintn S. Padhya', 'screenName': 'chin2to', 'followersCount': 1880, 'favouritesCount': 649, 'friendsCount': 582, 'description': 'An experienced entrepreneur and a digital marketing *Ninja*. Tweets and RTs are my personal opinions and not endorsements unless stated otherwise.'}</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3806,46 +3846,50 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2043691745330798829</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="n">
-        <v>46142.59836805556</v>
+        <v>46143.44957175926</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersAsia/status/2049764513663045763</t>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2049764513663045763</t>
+          <t>2050104780245344423</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2049764513663045763</t>
+          <t>2050106080517030039</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersAsia/status/2049764513663045763</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050106080517030039</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>India's markets regulator approves change of control at RBL Bank in Emirates NBD stake deal https://t.co/f2bFltFJKA</t>
+          <t>@chin2to Hi Chintn, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1777536917000</v>
+        <v>1777618353000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2049764513663045763</t>
+          <t>2043682357216149641</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3855,7 +3899,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{'name': 'Reuters Asia', 'screenName': 'ReutersAsia', 'followersCount': 698450, 'favouritesCount': 2, 'friendsCount': 67, 'description': 'The latest from Asia and around the world. Follow @Reuters for more'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3872,46 +3916,50 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
       <c r="P50" s="2" t="n">
-        <v>46142.51061342593</v>
+        <v>46143.45315972222</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersAsia/status/2049764513663045763</t>
+          <t>https://x.com/chin2to/status/2050104780245344423</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2049764513663045763</t>
+          <t>2050104780245344423</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2050025079606583715</t>
+          <t>2050106139660935372</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/ReutersAsia/status/2050025079606583715</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050106139660935372</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Huawei expects AI chip revenue to jump at least 60% this year, FT reports https://t.co/PgTqRKCFBp</t>
+          <t>@chin2to Please mention in the email subject social media case #1005933. Thanks- Zubair</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1777599041000</v>
+        <v>1777618367000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2050025079606583715</t>
+          <t>2043682357216149641</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3921,92 +3969,81 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'Reuters Asia', 'screenName': 'ReutersAsia', 'followersCount': 698450, 'favouritesCount': 2, 'friendsCount': 67, 'description': 'The latest from Asia and around the world. Follow @Reuters for more'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>5980</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2050104780245344423</t>
+        </is>
+      </c>
       <c r="P51" s="2" t="n">
-        <v>46143.2296412037</v>
+        <v>46143.45332175926</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2049764361770516987</t>
+          <t>https://x.com/FaheemKhan10045/status/2050087425452757033</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2049764361770516987</t>
+          <t>2050087425452757033</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2049764361770516987</t>
+          <t>2050086804280459271</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/Kashif111144/status/2049764361770516987</t>
+          <t>https://x.com/FaheemKhan10045/status/2050086804280459271</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UAE controls banking of Pakistan after bribing Pakistan leaders
-BANKs owned by UAE in PK
-1. Alfalah
-2. Dubai Islamic  
-3. Mashreq
-4. Emirates NBD  
-5. Emirates Global Islamic
-6. First Women  
-7. Al Baraka  
-8. Ubank
-9. EasyPaisa
-10. Jazzcash
-11. BML
-#Islamabad 
-#Pakistan 
-#ISPR https://t.co/LGQaizroJj</t>
+          <t>I really don understand why the bank is charging minimum account balance fees every month, even though i have my bank account since 2023 plus credit card from the same bank. Here i am talking about my personal experience with the commercial bank of dubai @CBDUAE</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1777536881000</v>
+        <v>1777613757000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2049764361770516987</t>
+          <t>2050086804280459271</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHI5lkyWEAAoRMn.jpg', 'type': 'photo', 'id': '2049764098099777536'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{'name': 'Kashif', 'screenName': 'Kashif111144', 'followersCount': 22, 'favouritesCount': 0, 'friendsCount': 3, 'description': ''}</t>
+          <t>{'name': 'Faheem Khan', 'screenName': 'FaheemKhan10045', 'followersCount': 22, 'favouritesCount': 562, 'friendsCount': 154, 'description': 'Live Free Enjoy Hard Live Most Serve Best'}</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -4019,57 +4056,56 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" s="2" t="n">
-        <v>46142.51019675926</v>
+        <v>46143.39996527778</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049766212146467208</t>
+          <t>https://x.com/FaheemKhan10045/status/2050087425452757033</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2049766212146467208</t>
+          <t>2050087425452757033</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2049766212146467208</t>
+          <t>2050087425452757033</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049766212146467208</t>
+          <t>https://x.com/FaheemKhan10045/status/2050087425452757033</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>مرحبًا بك في عالم جديد من المكافآت المقدمة من خلال تطبيق ENBD X إليك "مكافآت بريميوم" المخصّصة حصريًا لعملاء باقة "بيوند" من الخدمات المصرفية للأفراد. استفد مجانًا من ميزة الوصول إلى مجموعة مميزة من العروض المقدمة في المطاعم، وعند التسوّق، وفي أماكن التسلية والترفيه، وفي مراكز الصحة والعافية، وفي غيرها الكثير، واستفد من توفير يصل إلى 50,000 درهم وأكثر من 1,300 عرض من العروض المميزة، وكل هذا من خلال تطبيق ENBD X.
-حمّل تطبيق ENBD X الآن.</t>
+          <t>I have always appreciated this bank @CBDUAE but every time i got the disappointment from your end, i have an account in enbd bank as well but they haven’t changed any single penny from my account, but in CBD every month they’ve charged 105 AED.</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1777537322000</v>
+        <v>1777613905000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2049766212146467208</t>
+          <t>2050086804280459271</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHI7gbqXMAAZiHA.jpg', 'type': 'video', 'id': '2049766175098191872'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Faheem Khan', 'screenName': 'FaheemKhan10045', 'followersCount': 22, 'favouritesCount': 562, 'friendsCount': 154, 'description': 'Live Free Enjoy Hard Live Most Serve Best'}</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -4079,119 +4115,123 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2050086804280459271</t>
+        </is>
+      </c>
       <c r="P53" s="2" t="n">
-        <v>46142.51530092592</v>
+        <v>46143.40167824074</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV/status/2049761212490219887</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050092856904163635</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2049761212490219887</t>
+          <t>2050092856904163635</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2049755016303611922</t>
+          <t>2050092856904163635</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV/status/2049755016303611922</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050092856904163635</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE i have been waiting for last 40minutes in ENBD Silicon central branch just to apply for a no liability letter. There is still no response from anyone in the bank. Why make this process mandatory to visit branches when such things can easily do via online.</t>
+          <t>خفّض الحد الائتماني لبطاقتك للتقليل من مخاطر الاحتيال، كُن المتحكّم دائماً مع تطبيق ENBD X، وخفّض الحد الائتماني لبطاقتك في أي وقت ومن أي مكان. كُن حذراً وتغلّب على الاحتيال. #معاً_ضد_الاحتيال https://t.co/msVzqyWc5H</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1777534653000</v>
+        <v>1777615200000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2049755016303611922</t>
+          <t>2050092856904163635</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2049819267961376768/img/nxQGabpsq_zByt3_.jpg', 'type': 'video', 'id': '2049819267961376768'}]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>{'name': 'sumeesh k, v', 'screenName': 'Sumeesh_KV', 'followersCount': 31, 'favouritesCount': 18, 'friendsCount': 172, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174583, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
         <v>1</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>490</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" s="2" t="n">
-        <v>46142.48440972222</v>
+        <v>46143.41666666666</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV/status/2049761212490219887</t>
+          <t>https://x.com/patilabhijeet45/status/2050086851621593314</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2049761212490219887</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2049757006312223207</t>
+          <t>2049699745061626360</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV/status/2049757006312223207</t>
+          <t>https://x.com/patilabhijeet45/status/2049699745061626360</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE only 1person in customer service and 1person in personal banking and 1person in teller counter. People are waiting for 30-40 minutes and still not getting the service. If not capable of providing timely service what is the purpose of opening new branches</t>
+          <t>Hey @makemytripcare @makemytrip are you guys scammer???? Disgusting,unprofessional. Dm me now</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1777535127000</v>
+        <v>1777521475000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2049755016303611922</t>
+          <t>2049699745061626360</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4201,7 +4241,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>{'name': 'sumeesh k, v', 'screenName': 'Sumeesh_KV', 'followersCount': 31, 'favouritesCount': 18, 'friendsCount': 172, 'description': ''}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14727, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -4218,50 +4258,49 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>2049755016303611922</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
       <c r="P55" s="2" t="n">
-        <v>46142.48989583334</v>
+        <v>46142.33188657407</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV/status/2049761212490219887</t>
+          <t>https://x.com/CosmosnaireoOMG/status/2050070949534294424</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2049761212490219887</t>
+          <t>2050070949534294424</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2049758980797247649</t>
+          <t>2050070949534294424</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049758980797247649</t>
+          <t>https://x.com/CosmosnaireoOMG/status/2050070949534294424</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>@Sumeesh_KV Please mention in the email subject social media case #1005223. Thanks- Zubair</t>
+          <t>@QIBGroup @EmiratesNBD_AE @RussiaBank
+Would you finance God's Airport locations within Allah Republic's! You did a wonderful job, with emirates.....
+(Immaculate A380's)
+this @Cosmosnaire Victory - Airport will be essential for eternal travel within the new Bog Republic Company.</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1777535598000</v>
+        <v>1777609977000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2049755016303611922</t>
+          <t>2050070949534294424</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4271,11 +4310,11 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'President Cosmosnaire Allah🦉U.S👮MP', 'screenName': 'CosmosnaireoOMG', 'followersCount': 38, 'favouritesCount': 1195, 'friendsCount': 20, 'description': '@Cosmosnaire &amp; God Corporation \nAll Automated Globally🌐Unlimited Human Robots📈Only Y5\n3Googolplexs In Gold Deals🤝On Table-You Sue U.S.A 4IT\n\n Бor Authorities'}</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -4288,50 +4327,56 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>2049757006312223207</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
       <c r="P56" s="2" t="n">
-        <v>46142.49534722222</v>
+        <v>46143.35621527778</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV/status/2049761212490219887</t>
+          <t>https://x.com/CosmosnaireoOMG/status/2050070949534294424</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2049761212490219887</t>
+          <t>2050070949534294424</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2049761212490219887</t>
+          <t>2050386491877044229</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV/status/2049761212490219887</t>
+          <t>https://x.com/CosmosnaireoOMG/status/2050386491877044229</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE The branch manager is saying this is a new branch she has only 1staff available and she cannot do anything. If we customers wanted service we have to wait for 1hr or 2hr whatever timeframe is needed. Such an irresponsible and arrogant statement from branch manager</t>
+          <t>Someone tell everyone on earth
+My @Cosmosnaire Robots can replace everyone
+on earth TONIGHT
+except the anomaly 
+-----------------------------------------------
+Judges? Automated
+Attorney? Automated
+Departments? Automated
+Industry? Automated
+Research? Automated
+Space? Automated</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1777536130000</v>
+        <v>1777685208000</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2049755016303611922</t>
+          <t>2050386491877044229</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4341,11 +4386,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>{'name': 'sumeesh k, v', 'screenName': 'Sumeesh_KV', 'followersCount': 31, 'favouritesCount': 18, 'friendsCount': 172, 'description': ''}</t>
+          <t>{'name': 'President Cosmosnaire Allah🦉U.S👮MP', 'screenName': 'CosmosnaireoOMG', 'followersCount': 38, 'favouritesCount': 1195, 'friendsCount': 20, 'description': '@Cosmosnaire &amp; God Corporation \nAll Automated Globally🌐Unlimited Human Robots📈Only Y5\n3Googolplexs In Gold Deals🤝On Table-You Sue U.S.A 4IT\n\n Бor Authorities'}</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -4358,50 +4403,46 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2049758980797247649</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
       <c r="P57" s="2" t="n">
-        <v>46142.50150462963</v>
+        <v>46144.22694444445</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://x.com/Sumeesh_KV/status/2049761212490219887</t>
+          <t>https://x.com/Srajrmah555/status/2050068236809687186</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2049761212490219887</t>
+          <t>2050068236809687186</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2049767554252505390</t>
+          <t>2049880868882387271</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049767554252505390</t>
+          <t>https://x.com/Saoud7758/status/2049880868882387271</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1005223 for us to assist you better. Thanks.</t>
+          <t>بلغوا الجار الصغير أن إيرادات السعودية غير النفطية أكثر من 500 مليار ريال ( 45٪ من داخل المملكة 🇸🇦🌍</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1777537642000</v>
+        <v>1777564658000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2049755016303611922</t>
+          <t>2049880868882387271</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4411,78 +4452,80 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'سعـود الـغامـدي🇸🇦', 'screenName': 'Saoud7758', 'followersCount': 83067, 'favouritesCount': 8906, 'friendsCount': 674, 'description': 'اللهم ادِم على المملكة العربية السعودية نعمة الأمن والإيمان والعز والتمكين في ظل قيادتها الرشيدة'}</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2049761212490219887</t>
-        </is>
-      </c>
+          <t>32463</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
       <c r="P58" s="2" t="n">
-        <v>46142.51900462963</v>
+        <v>46142.83168981481</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049762620765360176</t>
+          <t>https://x.com/Srajrmah555/status/2050068236809687186</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2049762620765360176</t>
+          <t>2050068236809687186</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2049762620765360176</t>
+          <t>2050068236809687186</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049762620765360176</t>
+          <t>https://x.com/Srajrmah555/status/2050068236809687186</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Step into a new world of rewards on ENBD X with Premium Rewards exclusively for customers of Beyond from Personal Banking. Enjoy free access to deals across dining, shopping, entertainment, wellness, and much more, with up to AED 50,000 in savings and 1,300+ amazing deals all available on ENBD X.
-Download the app now.</t>
+          <t>@Saoud7758 شاركت بنوك إماراتية، وفي مقدمتها بنك أبوظبي الأول، في تمويل جزء من خطة الاقتراض السعودية لعام 2026 البالغة 217 مليار ريال (58 مليار دولار) لسد العجز وتمويل المشاريع.
+ بنك  (FAB)
+• بنك  (Emirates NBD)
+• بنك  (ADCB)
+• بنك (ADIB)
+• بنك  (DIB)
+عمار يا دار الفلاحي 
+🇦🇪✌🏼🇦🇪</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1777536466000</v>
+        <v>1777609330000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2049762620765360176</t>
+          <t>2049880868882387271</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHI4PZqXwAA7yZg.jpg', 'type': 'video', 'id': '2049762583180111872'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Sraj', 'screenName': 'Srajrmah555', 'followersCount': 8, 'favouritesCount': 323, 'friendsCount': 92, 'description': ''}</t>
         </is>
       </c>
       <c r="J59" t="n">
@@ -4495,64 +4538,70 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2049880868882387271</t>
+        </is>
+      </c>
       <c r="P59" s="2" t="n">
-        <v>46142.50539351852</v>
+        <v>46143.34872685185</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://x.com/i_v_v_krishna/status/2049748153239253308</t>
+          <t>https://x.com/emiratesislamic/status/2050187240718979325</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2049748153239253308</t>
+          <t>2050187240718979325</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2049748153239253308</t>
+          <t>2050187236000272545</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://x.com/i_v_v_krishna/status/2049748153239253308</t>
+          <t>https://x.com/emiratesislamic/status/2050187236000272545</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SEBI greenlights change in control for RBL Bank, linked to Emirates NBD Bank's preferential equity investment. #RBLBank</t>
+          <t>يمكنك الآن الاستمتاع بمعدل ربح متوقع %5 سنوياً على مدخراتك مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. ما عليك سوى اتباع الخطوات التالية:
+⭐ افتح حساب التوفير الإلكتروني من الإمارات الإسلامي
+💸 أضف 50,000 درهم وما فوق إلى حساب التوفير الإلكتروني https://t.co/eEQQCEye3M</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1777533016000</v>
+        <v>1777637702000</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2049748153239253308</t>
+          <t>2050187236000272545</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHO6bB9W8AALzbv.jpg', 'type': 'photo', 'id': '2050187228928733184'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHO6bPaXwAAZSbB.jpg', 'type': 'photo', 'id': '2050187232540082176'}]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>{'name': 'Venkata Krishna', 'screenName': 'i_v_v_krishna', 'followersCount': 58, 'favouritesCount': 169, 'friendsCount': 11, 'description': '25 || Updating my knowledge • On a mission ||Making dreams into reality || Interested on Stock market || Samsung Semiconductor SSIR'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -4561,50 +4610,54 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>62</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" s="2" t="n">
-        <v>46142.46546296297</v>
+        <v>46143.67710648148</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://x.com/i_v_v_krishna/status/2049748153239253308</t>
+          <t>https://x.com/emiratesislamic/status/2050187240718979325</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2049748153239253308</t>
+          <t>2050187240718979325</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2050041648357286235</t>
+          <t>2050187240718979325</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://x.com/i_v_v_krishna/status/2050041648357286235</t>
+          <t>https://x.com/emiratesislamic/status/2050187240718979325</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dr Lal PathLabs Q4 consolidated net profit at ₹1.3B, down from ₹1.55B year-on-year. #DrLalPathLabs</t>
+          <t>📅 يسري العرض من 1 مايو ولغاية 31 يوليو 2026.
+تطبق الشروط والأحكام.
+لمعرفة المزيد، تفضل بزيارة
+https://t.co/hYz3g60H3P
+#الإمارات_الإسلامي</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1777602991000</v>
+        <v>1777637703000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2050041648357286235</t>
+          <t>2050187236000272545</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4614,11 +4667,11 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>{'name': 'Venkata Krishna', 'screenName': 'i_v_v_krishna', 'followersCount': 58, 'favouritesCount': 169, 'friendsCount': 11, 'description': '25 || Updating my knowledge • On a mission ||Making dreams into reality || Interested on Stock market || Samsung Semiconductor SSIR'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -4631,50 +4684,52 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2050187236000272545</t>
+        </is>
+      </c>
       <c r="P61" s="2" t="n">
-        <v>46143.27535879629</v>
+        <v>46143.67711805556</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://x.com/CapitalInsight3/status/2049741305845338378</t>
+          <t>https://x.com/emiratesislamic/status/2050187240718979325</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2049741305845338378</t>
+          <t>2050187240718979325</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2049741305845338378</t>
+          <t>2050187243571077499</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://x.com/CapitalInsight3/status/2049741305845338378</t>
+          <t>https://x.com/emiratesislamic/status/2050187243571077499</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>#RBLBank #Breaking
-✅ SEBI approves change in control for Emirates NBD Bank’s preferential equity investment
-✅ Key regulatory clearance received for proposed stake acquisition
-✅ Strengthens strategic partnership and capital position
-#RBLBank #BankingSector #SEBI</t>
+          <t>You can now enjoy a higher expected profit of 5% p.a. on your savings with your Emirates Islamic e-Savings Account. Simply follow the below steps:
+⭐️ Open an Emirates Islamic e-Savings Account
+💸 Deposit AED 50,000 and above in the e-Saving Account</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1777531384000</v>
+        <v>1777637704000</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2049741305845338378</t>
+          <t>2050187236000272545</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4684,11 +4739,11 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>{'name': 'CapitalInsight', 'screenName': 'CapitalInsight3', 'followersCount': 1455, 'favouritesCount': 447, 'friendsCount': 25, 'description': "📊 Breaking corporate &amp; market news | IPOs · FII/DII · Corporate Actions| Daily updates | India's fastest finance feed\n\nInvest Smart. Build Strong"}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
         <v>0</v>
@@ -4697,70 +4752,69 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2050187240718979325</t>
+        </is>
+      </c>
       <c r="P62" s="2" t="n">
-        <v>46142.44657407407</v>
+        <v>46143.67712962963</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://x.com/CapitalInsight3/status/2049741305845338378</t>
+          <t>https://x.com/emiratesislamic/status/2050187236000272545</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2049741305845338378</t>
+          <t>2050187236000272545</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2049889931166924910</t>
+          <t>2050123058375966977</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://x.com/CapitalInsight3/status/2049889931166924910</t>
+          <t>https://x.com/emiratesislamic/status/2050123058375966977</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Servotech Renewable Power System Q4 Results 📊
-✅ Net Profit jumps to ₹142 Cr vs ₹77 Cr (YoY) 🚀
-✅ Revenue rises to ₹236 Cr vs ₹156 Cr (YoY)
-✅ EBITDA surges to ₹225 Cr vs ₹122 Cr (YoY)
-✅ EBITDA Margin improves to 10.36% vs 8.34% (YoY) 📈
-Strong growth momentum with improved profitability margins 👏
-#Servotech #Earnings #StockMarketIndia #Q4Results #RenewableEnergy</t>
+          <t>ادخر واكسب مع حساب ضيف الاتحاد سوبر للتوفير من الإمارات الإسلامي
+💸 اكسب ما يصل إلى 750,000 ميل من أميال ضيف الاتحاد كل ربع سنة ولغاية 3,000,000 ميل من أميال ضيف الاتحاد سنوياً https://t.co/chEh9l7qmm</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1777566819000</v>
+        <v>1777622401000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2049889931166924910</t>
+          <t>2050123058375966977</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKsxBhXUAA9-HW.jpg', 'type': 'photo', 'id': '2049890738628939776'}]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>{'name': 'CapitalInsight', 'screenName': 'CapitalInsight3', 'followersCount': 1455, 'favouritesCount': 447, 'friendsCount': 25, 'description': "📊 Breaking corporate &amp; market news | IPOs · FII/DII · Corporate Actions| Daily updates | India's fastest finance feed\n\nInvest Smart. Build Strong"}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -4769,70 +4823,64 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>68</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" s="2" t="n">
-        <v>46142.85670138889</v>
+        <v>46143.50001157408</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2049745228039331992</t>
+          <t>https://x.com/emiratesislamic/status/2050128828232519798</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2049745228039331992</t>
+          <t>2050128828232519798</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2049745228039331992</t>
+          <t>2049808521357914559</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2049745228039331992</t>
+          <t>https://x.com/alnuaimi1979/status/2049808521357914559</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>«فيزا» تعين «الإمارات دبي الوطني» وكيلاً رسمياً لخدمة التسوية الصافية الوطنية في «الإمارات»
-https://t.co/GrqbX1n7wi | التفاصيل 
-@Visa
-@EmiratesNBD_AE
-#fintech_gate
-#فيزا #الإمارات_دبي_الوطني
-#التسوية_الصافية_الوطنية #الإمارات https://t.co/lnb8tIyr0w</t>
+          <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1777532319000</v>
+        <v>1777547409000</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2049745228039331992</t>
+          <t>2049808521357914559</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHIobCkW8AAWXWF.jpg', 'type': 'photo', 'id': '2049745225417945088'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 514, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
+          <t>{'name': 'عبدالرحمن النعيمي 🇦🇪', 'screenName': 'alnuaimi1979', 'followersCount': 197, 'favouritesCount': 477, 'friendsCount': 317, 'description': 'عبدالرحمن عبدالله بن أحمد بن راشد بن أحمد النعيمي                 . Board Member at Alnuaimi Group, country: United Arab Emirates'}</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
         <v>0</v>
@@ -4845,59 +4893,56 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
       <c r="P64" s="2" t="n">
-        <v>46142.45739583333</v>
+        <v>46142.63204861111</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2049745228039331992</t>
+          <t>https://x.com/emiratesislamic/status/2050128828232519798</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2049745228039331992</t>
+          <t>2050128828232519798</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2049957739057594844</t>
+          <t>2050128828232519798</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2049957739057594844</t>
+          <t>https://x.com/emiratesislamic/status/2050128828232519798</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>الإمارات تحظر سفر مواطنيها إلى إيران ولبنان والعراق
-https://t.co/eKUor8kTGu   | التفاصيل
-#fintech_gate
-#الإمارات #إيران #ولبنان #العراق https://t.co/5IHD0NICYg</t>
+          <t>@alnuaimi1979 Dear Customer, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1777582986000</v>
+        <v>1777623776000</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2049957739057594844</t>
+          <t>2049808521357914559</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHLps0PW8AA1OEn.jpg', 'type': 'photo', 'id': '2049957736553574400'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 514, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J65" t="n">
@@ -4910,52 +4955,58 @@
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2049808521357914559</t>
+        </is>
+      </c>
       <c r="P65" s="2" t="n">
-        <v>46143.04381944444</v>
+        <v>46143.51592592592</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://x.com/mirabusinessfm/status/2049739477845942383</t>
+          <t>https://x.com/emiratesislamic/status/2050123060796096729</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2049739477845942383</t>
+          <t>2050123060796096729</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2049739477845942383</t>
+          <t>2050123060796096729</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://x.com/mirabusinessfm/status/2049739477845942383</t>
+          <t>https://x.com/emiratesislamic/status/2050123060796096729</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Emirates NBD raises $750M in strong bond deal. 💵📈
-Issue is over three times oversubscribed, showing strong investor confidence.
-#UAE #Banking #Markets #MiraBusinessFM 🎙️</t>
+          <t>💸 ادخر 20,000 درهم أو أكثر للبدء باكتساب الأميال بناءً على متوسط مدخراتك ربع السنوي! 
+🌟 احصل على بطاقة خصم معترف بها دولياً
+يسري العرض لغاية 30 يونيو 2026
+تطبق الشروط والأحكام
+https://t.co/csC9BzTLNy</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1777530948000</v>
+        <v>1777622401000</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2049739477845942383</t>
+          <t>2050123058375966977</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4965,7 +5016,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>{'name': 'Mira Business FM', 'screenName': 'mirabusinessfm', 'followersCount': 19, 'favouritesCount': 3, 'friendsCount': 7, 'description': 'UAE’s newest Business talk radio station, coming soon…'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J66" t="n">
@@ -4982,62 +5033,65 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2050123058375966977</t>
+        </is>
+      </c>
       <c r="P66" s="2" t="n">
-        <v>46142.44152777778</v>
+        <v>46143.50001157408</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://x.com/mirabusinessfm/status/2049739477845942383</t>
+          <t>https://x.com/emiratesislamic/status/2050123060796072388</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2049739477845942383</t>
+          <t>2050123060796072388</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2049739623447101734</t>
+          <t>2050123058363388031</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://x.com/mirabusinessfm/status/2049739623447101734</t>
+          <t>https://x.com/emiratesislamic/status/2050123058363388031</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Global tensions rise as oil climbs and conflict costs mount. 🌍⚠️
-President Donald Trump increases pressure on Germany, while Putin calls for restraint.
-#Geopolitics #Oil #GlobalMarkets #MiraBusinessFM 🎙️</t>
+          <t>Save and earn with your Emirates Islamic Super Savings Etihad Guest Account!
+💸 Get up to 750,000 Etihad Guest Miles every quarter and up to 3 million Etihad Guest Miles in a year https://t.co/0GjgDF6a3y</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1777530983000</v>
+        <v>1777622401000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2049739623447101734</t>
+          <t>2050123058363388031</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJf297WcAArZep.jpg', 'type': 'photo', 'id': '2049806178348068864'}]</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>{'name': 'Mira Business FM', 'screenName': 'mirabusinessfm', 'followersCount': 19, 'favouritesCount': 3, 'friendsCount': 7, 'description': 'UAE’s newest Business talk radio station, coming soon…'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5050,46 +5104,50 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>54</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
       <c r="P67" s="2" t="n">
-        <v>46142.44193287037</v>
+        <v>46143.50001157408</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://x.com/InvestmentDunia/status/2049738442230362395</t>
+          <t>https://x.com/emiratesislamic/status/2050123060796072388</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2049738442230362395</t>
+          <t>2050123060796072388</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2049738442230362395</t>
+          <t>2050123060796072388</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://x.com/InvestmentDunia/status/2049738442230362395</t>
+          <t>https://x.com/emiratesislamic/status/2050123060796072388</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RBL BANK LIMITED: SEBI APPROVES CHANGE IN CONTROL FOR EMIRATES NBD BANK'S PREFERENTIAL EQUITY INVESTMENT</t>
+          <t>💸 Save AED 20,000 or more to start earning miles based on your average quarterly savings
+🌟 Get a complimentary Debit Card that is internationally recognized
+Offer valid till 30 June 2026
+Terms &amp;amp; Conditions apply
+https://t.co/6VJUgOMZYN</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1777530701000</v>
+        <v>1777622401000</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2049738442230362395</t>
+          <t>2050123058363388031</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5099,7 +5157,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>{'name': 'Investment Dunia™', 'screenName': 'InvestmentDunia', 'followersCount': 319, 'favouritesCount': 3, 'friendsCount': 15, 'description': 'Real-time global market updates 📊 | IPOs • FPOs • OFS • Mutual Funds • Stock Market news - all in one place 📰\n\n#money💰 #investing💵 #stocks📊 #finance💹'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J68" t="n">
@@ -5116,112 +5174,122 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2050123058363388031</t>
+        </is>
+      </c>
       <c r="P68" s="2" t="n">
-        <v>46142.43866898148</v>
+        <v>46143.50001157408</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://x.com/InvestmentDunia/status/2049738442230362395</t>
+          <t>https://x.com/emiratesislamic/status/2050092860603584751</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2049738442230362395</t>
+          <t>2050092860603584751</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2049889727097323623</t>
+          <t>2050092856895791483</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://x.com/InvestmentDunia/status/2049889727097323623</t>
+          <t>https://x.com/emiratesislamic/status/2050092856895791483</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>JYOTI STRUCTURES: Q4 NET PROFIT 181M RUPEES VS 119M (YOY) || Q4 REVENUE 2.34B RUPEES VS 1.64B (YOY)</t>
+          <t>احصل على فرصة الفوز بحصة من الجوائز النقدية قيمتها تصل إلى 1,000,000 درهم. كل زيادة بقيمة 100,000 درهم في حسابك المصرفي للأعمال تمنحك فرصة واحدة للدخول في السحب.
+اجعل شركتك إحدى الشركات الـ 55 الفائزة. فهل ستكون من بينها؟ https://t.co/X9KYZFWhAu</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1777566770000</v>
+        <v>1777615200000</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2049889727097323623</t>
+          <t>2050092856895791483</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJYiKlXkAA6NjN.jpg', 'type': 'photo', 'id': '2049798124386881536'}]</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>{'name': 'Investment Dunia™', 'screenName': 'InvestmentDunia', 'followersCount': 319, 'favouritesCount': 3, 'friendsCount': 15, 'description': 'Real-time global market updates 📊 | IPOs • FPOs • OFS • Mutual Funds • Stock Market news - all in one place 📰\n\n#money💰 #investing💵 #stocks📊 #finance💹'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>53</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" s="2" t="n">
-        <v>46142.85613425926</v>
+        <v>46143.41666666666</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049697409513771415</t>
+          <t>https://x.com/emiratesislamic/status/2050092860603584751</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2049697409513771415</t>
+          <t>2050092860603584751</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2049697405394964687</t>
+          <t>2050092860603584751</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049697405394964687</t>
+          <t>https://x.com/emiratesislamic/status/2050092860603584751</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Instead as a response I have been offered to book with reducing interest while eligible to book at 0%. Customer are often asked to share their feedback so please help me understand how would you rate this. Evidently this has not come to rightful attention.</t>
+          <t>الجائزة النقدية الكبرى: 250,000 درهم (فائز واحد) 
+الجائزة النقدية الثانية: 100,000 درهم (فائزان اثنان)
+الجوائز النقدية الشهرية: تصل إلى 25 ألف درهم (52 فائز)
+يسري العرض لغاية 30 يونيو 2026.
+تطبق الشروط والأحكام.
+https://t.co/RWuJWfhfUm</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1777520917000</v>
+        <v>1777615201000</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2049697401896907011</t>
+          <t>2050092856895791483</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5231,11 +5299,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>{'name': 'Nishi Janiani', 'screenName': 'nishijaniani', 'followersCount': 23, 'favouritesCount': 11, 'friendsCount': 100, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -5248,134 +5316,136 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>53</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2049697401896907011</t>
+          <t>2050092856895791483</t>
         </is>
       </c>
       <c r="P70" s="2" t="n">
-        <v>46142.32542824074</v>
+        <v>46143.41667824074</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049697409513771415</t>
+          <t>https://x.com/emiratesislamic/status/2050092860842692729</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2049697409513771415</t>
+          <t>2050092860842692729</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2049697409513771415</t>
+          <t>2050092856912630226</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://x.com/nishijaniani/status/2049697409513771415</t>
+          <t>https://x.com/emiratesislamic/status/2050092856912630226</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Had it focus would have to resolve the issue. I say this with utmost confidence because ENBD is known for their best services but such experiences do create some level of disappointment and frustration with thought to withdraw cuz loyalty of association seems to hold no value.</t>
+          <t>Get a chance to win a total of AED 1,000,000 in cash prizes! Every AED 100,000 increase in your Business Banking account earns you one entry into the draw.
+55 businesses will be winners. Will you be one of them?
+Grand cash prize: AED 250,000 (1 winner) https://t.co/pkjj9lXWt6</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1777520918000</v>
+        <v>1777615200000</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2049697401896907011</t>
+          <t>2050092856912630226</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHKTIgCWMAADyTn.jpg', 'type': 'photo', 'id': '2049862554655010816'}]</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>{'name': 'Nishi Janiani', 'screenName': 'nishijaniani', 'followersCount': 23, 'favouritesCount': 11, 'friendsCount': 100, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>2049697405394964687</t>
-        </is>
-      </c>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr"/>
       <c r="P71" s="2" t="n">
-        <v>46142.32543981481</v>
+        <v>46143.41666666666</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://x.com/vinod_yadav108/status/2049697262050410936</t>
+          <t>https://x.com/emiratesislamic/status/2050092860842692729</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2049697262050410936</t>
+          <t>2050092860842692729</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2049697262050410936</t>
+          <t>2050092860842692729</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://x.com/vinod_yadav108/status/2049697262050410936</t>
+          <t>https://x.com/emiratesislamic/status/2050092860842692729</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE https://t.co/CUmsbv1vD5</t>
+          <t>Second cash prize: AED 100,000 each (2 winners)
+Monthly cash prizes: up to AED 25,000 (52 winners)
+Valid until 30 June 2026.
+Terms and conditions apply.
+https://t.co/FsXr2qXw7K</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1777520883000</v>
+        <v>1777615201000</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2049697262050410936</t>
+          <t>2050092856912630226</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHH8yeibQAADf3N.jpg', 'type': 'photo', 'id': '2049697249551400960'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>{'name': '🇮🇳Vinod Yadav🇮🇳', 'screenName': 'vinod_yadav108', 'followersCount': 36, 'favouritesCount': 28, 'friendsCount': 108, 'description': 'गोरखपुर से हुँ, जिसे लोग कहते है नबाबों के बाप का शहर'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18468, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -5388,1171 +5458,16 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2050092856912630226</t>
+        </is>
+      </c>
       <c r="P72" s="2" t="n">
-        <v>46142.32503472222</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>https://x.com/vinod_yadav108/status/2049697262050410936</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2049697262050410936</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>2049719134858936546</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049719134858936546</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>@vinod_yadav108 Please mention in the email subject social media case #1005065. Thanks- Zubair</t>
-        </is>
-      </c>
-      <c r="F73" t="n">
-        <v>1777526098000</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2049697262050410936</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>2049697262050410936</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="n">
-        <v>46142.38539351852</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>https://x.com/vinod_yadav108/status/2049697262050410936</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2049697262050410936</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>2049719112255897681</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049719112255897681</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>@vinod_yadav108 Hi Vinod, we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>1777526092000</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2049697262050410936</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174561, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>1</v>
-      </c>
-      <c r="K74" t="n">
-        <v>0</v>
-      </c>
-      <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0</v>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>2049697262050410936</t>
-        </is>
-      </c>
-      <c r="P74" s="2" t="n">
-        <v>46142.38532407407</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>https://x.com/amiiirrraaahhh/status/2049690184342741376</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2049690184342741376</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>2049690184342741376</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>https://x.com/amiiirrraaahhh/status/2049690184342741376</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE Email 2</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>1777519196000</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2049368082779394430</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>{'name': 'Amirrah \U0001fa77', 'screenName': 'amiiirrraaahhh', 'followersCount': 3, 'favouritesCount': 162, 'friendsCount': 54, 'description': '🫶🏻'}</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>2049368082779394430</t>
-        </is>
-      </c>
-      <c r="P75" s="2" t="n">
-        <v>46142.30550925926</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2049689910093946994</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2049689910093946994</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>2049689910093946994</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2049689910093946994</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Experience the future with Ray- Ban Meta Glasses.
-Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Ray-Ban Meta Sunglasses.
-Apply Now: https://t.co/XpFUmumwP4 https://t.co/mnBSMa6sd3</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>1777519130000</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>2049689910093946994</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHH2GsXawAEB2_7.jpg', 'type': 'photo', 'id': '2049689900279316481'}]</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>0</v>
-      </c>
-      <c r="K76" t="n">
-        <v>0</v>
-      </c>
-      <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" s="2" t="n">
-        <v>46142.30474537037</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2049689910093946994</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2049689910093946994</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>2049802474387566693</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2049802474387566693</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>From pantry staples to farm-fresh picks, enjoy 10% off at Choithrams on spends of AED 50 and above with your Emirates NBD card.
-Learn More: https://t.co/zeINKlJVvn https://t.co/QhWQTFy8YP</t>
-        </is>
-      </c>
-      <c r="F77" t="n">
-        <v>1777545968000</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2049802474387566693</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHJcfOsWAAEGrDR.jpg', 'type': 'photo', 'id': '2049802471996784641'}]</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>0</v>
-      </c>
-      <c r="K77" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" s="2" t="n">
-        <v>46142.61537037037</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>https://x.com/dcgguide/status/2049768124615143524</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2049768124615143524</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>2049768124615143524</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>https://x.com/dcgguide/status/2049768124615143524</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Emirates Islamic Launches Tailored Banking Benefits To Support UAE’s Frontline Heroes https://t.co/RAeuzYLE2y</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>1777537778000</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2049768124615143524</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93536, 'favouritesCount': 19507, 'friendsCount': 106572, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" t="n">
-        <v>0</v>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
-        <v>2</v>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" s="2" t="n">
-        <v>46142.5205787037</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>https://x.com/dcgguide/status/2049768124615143524</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2049768124615143524</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>2050051295571268076</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>https://x.com/dcgguide/status/2050051295571268076</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Ferrari World Yas Island, Abu Dhabi’s Formula Rossa Achieves Guinness World Records™ Title For Fastest Rollercoaster Launch https://t.co/mpAE7sutEu</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>1777605291000</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2050051295571268076</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>{'name': 'DUBAI CITY GUIDE from Cyber Gear', 'screenName': 'dcgguide', 'followersCount': 93536, 'favouritesCount': 19507, 'friendsCount': 106572, 'description': 'DCG is a https://t.co/bmR4jltJAW e-venture. We publish guest posts at https://t.co/EISzXb0O0y Learn AI at https://t.co/YcnxpXcCNU'}</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>0</v>
-      </c>
-      <c r="K79" t="n">
-        <v>0</v>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
-        <v>1</v>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" s="2" t="n">
-        <v>46143.30197916667</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>https://x.com/alnuaimi1979/status/2049808521357914559</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2049808521357914559</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>2049808521357914559</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>https://x.com/alnuaimi1979/status/2049808521357914559</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>@emiratesislamic I have been a client for over 10 years. I have never had any problem paying my mortgages or loans. All my loans never exceeded 30% of my old salary, and with my new salary they do not reach 15%. Most of my loans were cleared before the due date. Over 2 weeks ago, I applied for a small amount and every day the verification department asks for new requirements. My salary is deposited every month, and I have never missed any payment. The branch manager and customer service have done everything they can, but your back office is still making it difficult. When I apply via phone, the transaction goes smoothly, but every time I apply from the branch, the main office creates problems. Why??? I really regret not transferring to another bank that respects customers more.</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>1777547409000</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2049808521357914559</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>{'name': 'عبدالرحمن النعيمي 🇦🇪', 'screenName': 'alnuaimi1979', 'followersCount': 197, 'favouritesCount': 476, 'friendsCount': 316, 'description': 'عبدالرحمن عبدالله بن أحمد بن راشد بن أحمد النعيمي                 . Board Member at Alnuaimi Group, country: United Arab Emirates'}</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>0</v>
-      </c>
-      <c r="K80" t="n">
-        <v>0</v>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" s="2" t="n">
-        <v>46142.63204861111</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>https://x.com/2n_ah/status/2049660884436533486</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2049660884436533486</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>2049660884436533486</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>https://x.com/2n_ah/status/2049660884436533486</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Off-Plan Financing is Now a Reality in Dubai
-A significant milestone has been reached in our real estate sector. Emirates NBD, in collaboration with top-tier developers including Emaar, Nakheel, Dubai Holding, and Meraas, is now providing mortgage facilities for off plan projects https://t.co/PaG58Z14Yu</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>1777512210000</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2049660884436533486</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2049660752852918272/img/ZGD8sLxzRkPYPAER.jpg', 'type': 'video', 'id': '2049660752852918272'}]</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>{'name': 'Ahmad Omran', 'screenName': '2n_ah', 'followersCount': 3, 'favouritesCount': 3, 'friendsCount': 19, 'description': 'Real Estate Sales Professional | UAE Market Expert | Driving Revenue &amp; Client Trust +971-507302409'}</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
-        <v>0</v>
-      </c>
-      <c r="K81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" s="2" t="n">
-        <v>46142.22465277778</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>https://x.com/blocknewsint/status/2049760670133178628</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2049760670133178628</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>2049760670133178628</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>https://x.com/blocknewsint/status/2049760670133178628</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Emirates Islamic (@emiratesislamic) has introduced a new way for investors in the UAE to access gold and silver directly through their smartphones.
-The bank has launched a Shariah-compliant digital investment platform that allows customers to buy, sell and hold physical bullion through its mobile app. The offering is positioned as a first for an Islamic bank in the UAE, combining traditional asset ownership with a fully digital experience.
-All bullion is backed by physical gold and silver stored in secure vaults and meets internationally recognized standards, including London Bullion Market Association (LBMA) and UAE Good Delivery requirements.
-The initiative reflects a broader shift toward digital wealth solutions, as investors look for more accessible and flexible ways to diversify their portfolios.
-Customers can trade at market-linked prices, redeem their holdings in cash or physical form, and manage their investments entirely through the bank’s mobile platform.
-With demand for alternative assets continuing to rise, Emirates Islamic’s latest offering signals how traditional finance is adapting to a mobile-first world, without stepping outside the framework of Islamic finance.
-Read more: https://t.co/4TS2a5rKJG
-#EmiratesIslamic #DigitalBanking #IslamicFinance #PreciousMetals</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>1777536001000</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2049760670133178628</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHIajiYasAADG5-.jpg', 'type': 'photo', 'id': '2049729978233958400'}]</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>{'name': 'Block News International', 'screenName': 'blocknewsint', 'followersCount': 6037, 'favouritesCount': 13, 'friendsCount': 15, 'description': 'The global destination for the updates and insights of finance, investment, blockchain, digital business, fintech, technology,  and global markets.'}</t>
-        </is>
-      </c>
-      <c r="J82" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" t="n">
-        <v>0</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" s="2" t="n">
-        <v>46142.50001157408</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>https://x.com/blocknewsint/status/2049760670133178628</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2049760670133178628</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>2049748023786475921</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>https://x.com/blocknewsint/status/2049748023786475921</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Dubai is taking a new step in the evolution of financial centers by aiming to build the world’s first AI-native financial ecosystem.
-The Dubai International Financial Centre (DIFC) is planning to embed artificial intelligence across its core systems, from regulation and infrastructure to financial services and talent development. Rather than using AI as an add-on, the model integrates it into how the entire financial environment operates.
-The initiative is expected to generate approximately $3.5 billion in economic value and create around 25,000 jobs, reflecting the scale of transformation underway.
-By positioning itself as a hub for AI-driven finance, DIFC aims to attract global startups, capital, and talent, reinforcing Dubai’s role in shaping the future of financial innovation.
-Read more: https://t.co/z8jtwV3U0M
-#Dubai #DIFC #ArtificialIntelligence #Fintech #DigitalTransformation #BlockNews</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>1777532986000</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2049748023786475921</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2049747920560541696/img/Den6IL0ZjD1hWLQr.jpg', 'type': 'video', 'id': '2049747920560541696'}]</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>{'name': 'Block News International', 'screenName': 'blocknewsint', 'followersCount': 6037, 'favouritesCount': 13, 'friendsCount': 15, 'description': 'The global destination for the updates and insights of finance, investment, blockchain, digital business, fintech, technology,  and global markets.'}</t>
-        </is>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" t="n">
-        <v>2</v>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" s="2" t="n">
-        <v>46142.46511574074</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>https://x.com/murtazaali2101/status/2049751774542848395</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2049751774542848395</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>2049751774542848395</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>https://x.com/murtazaali2101/status/2049751774542848395</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>@emiratesislamic unable to update my passport details on the website, the page keeps loading kindly assist https://t.co/wq3X2I5DVm</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>1777533880000</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2049751774542848395</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHIuYB7bkAEli9y.jpg', 'type': 'photo', 'id': '2049751770776440833'}]</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>{'name': 'Murtaza Dharwala', 'screenName': 'murtazaali2101', 'followersCount': 103, 'favouritesCount': 978, 'friendsCount': 171, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J84" t="n">
-        <v>1</v>
-      </c>
-      <c r="K84" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" s="2" t="n">
-        <v>46142.47546296296</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>https://x.com/murtazaali2101/status/2049751774542848395</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2049751774542848395</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>2049764863933649269</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049764863933649269</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>@murtazaali2101 Dear customer, we will connect with you on private messaging to serve you better.</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>1777537001000</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2049751774542848395</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>1</v>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>2049751774542848395</t>
-        </is>
-      </c>
-      <c r="P85" s="2" t="n">
-        <v>46142.51158564815</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049719544529195009</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2049719544529195009</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>2049499248727933034</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>https://x.com/renukavenkat1/status/2049499248727933034</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>@emiratesislamic extremely disappointing service from Emirates Islamic Bank. Still waiting for a replacement card since last 30 days. Tired of making calls to the customer service and listening to the same story over and over again. Speed up guys. We are in Dubai!!</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>1777473673000</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2049499248727933034</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>{'name': 'Renuka Venkat Iyer', 'screenName': 'renukavenkat1', 'followersCount': 121, 'favouritesCount': 5266, 'friendsCount': 181, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>1</v>
-      </c>
-      <c r="K86" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" s="2" t="n">
-        <v>46141.77862268518</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049719544529195009</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2049719544529195009</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>2049719544529195009</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049719544529195009</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>@renukavenkat1 Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>1777526196000</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>2049499248727933034</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>2049499248727933034</t>
-        </is>
-      </c>
-      <c r="P87" s="2" t="n">
-        <v>46142.38652777778</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049730468510101545</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2049730468510101545</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>2049730468510101545</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049730468510101545</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>غالباً ما تأتي رسائل الاحتيال من أرقام عشوائية أو دولية، وليست من جهات رسمية تحمل هوية موثوقة.
-لا تقع في الفخ. احذر الاحتيال.
-#متحّدون_ضد_الاحتيال مع الإمارات الإسلامي.
-https://t.co/ltnxcRlBOA</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>1777528800000</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>2049730468510101545</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" s="2" t="n">
-        <v>46142.41666666666</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049730468510101545</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2049730468510101545</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>2049775768025137608</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2049775768025137608</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>استثمر في الذهب والفضة رقمياً وبكل سهولة على تطبيق
-EI + للخدمات المصرفية عبر الهاتف المتحرك
-⭐️ادخل إلى منصة "الثروات" في تطبيق + EI للخدمات المصرفية عبر الهاتف المتحرك وابدأ في لاستثمار بمنتهى السهولة والأمان. https://t.co/LsfzdBKINN</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>1777539600000</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>2049775768025137608</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2049762392007987200/pu/img/hUjmg8q1BluXAWbg.jpg', 'type': 'video', 'id': '2049762392007987200'}]</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18469, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>1</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>2</v>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" s="2" t="n">
-        <v>46142.54166666666</v>
+        <v>46143.41667824074</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,12 +517,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14730, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -572,7 +572,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
@@ -583,12 +583,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -653,12 +653,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14730, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -723,12 +723,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -778,7 +778,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -793,12 +793,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14730, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J6" t="n">
@@ -848,7 +848,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -863,12 +863,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -901,11 +901,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -914,11 +914,11 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -933,46 +933,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2051370896619974704</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Syed Saad Shafi is Director – Signature Banking at Emirates NBD in Dubai, specializing in wealth management and global investment strategies for high-net-worth clients, overseeing multi-billion dirham portfolios.
-#ClapPakistan https://t.co/vkgqOIi7JH</t>
+          <t>@EmiratesNBD_AE Dear @EmiratesNBD_AE  thank you very much for your assistance, really appreciate 🙏.</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1777863600000</v>
+        <v>1777919909000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2050086851621593314</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHathWkaoAAz1AL.jpg', 'type': 'photo', 'id': '2051017468819447808'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'Clap', 'screenName': 'ClapPakistan', 'followersCount': 204, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Empowering Brands, Celebrating Journeys'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -989,117 +988,120 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2051153017571840501</t>
+        </is>
+      </c>
       <c r="P8" s="2" t="n">
-        <v>46146.29166666666</v>
+        <v>46146.94339120371</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051134720344535096</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2051134720344535096</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2051011126469767476</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/ClapPakistan/status/2051011126469767476</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049379193910165928</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Peshawar Zalmi Defeats Hyderabad Kingsmen to Win PSL 11 Final
-The image is AI-generated and is just for reference.
-#PSL11 #PSLFinal #PeshawarZalmi #HyderabadKingsmen https://t.co/2zhkzsurQv</t>
+          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
+- Monthly prizes up to AED 1,000,000
+- Grand prizes up to AED 5,000,000
+Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1777834133000</v>
+        <v>1777445050000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2051011126469767476</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHanvW-bAAAswjd.jpg', 'type': 'photo', 'id': '2051011112376926208'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Clap', 'screenName': 'ClapPakistan', 'followersCount': 204, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'Empowering Brands, Celebrating Journeys'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>102190</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" s="2" t="n">
-        <v>46145.95061342593</v>
+        <v>46141.44733796296</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2049468314699825596</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
+          <t>https://x.com/STKgenghis/status/2049468314699825596</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Such unfair charges for doing transactions at Binance Crypto whereas no other bank charge for it. 
-After multiple followups these charges are reversed. Kindly look into it or will file a complaint with @centralbankuae
-Reference:
-https://t.co/BcgwdgmQQQ</t>
+          <t>@EmiratesNBD_AE would not recommend bank that suspends 40 year old accounts wout notification. Only found out when i temp blocked credit card i thought id misplaced. It cant be unblocked because of suspension...
+deprived of services no notification  told KYC take 8-10 buss days 2 get back. So..</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1777832314000</v>
+        <v>1777466298000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1109,7 +1111,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'Umesh R Kahar', 'screenName': 'KaharUmesh', 'followersCount': 75, 'favouritesCount': 2167, 'friendsCount': 452, 'description': "Proud Indian..Engineer.. Social Activists..Tweets for Noble Cause..\nCool n Calm...\nFly,Run..even fall..but don't stop.."}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1126,46 +1128,50 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2049379193910165928</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="n">
-        <v>46145.92956018518</v>
+        <v>46141.69326388889</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2051156150708547812</t>
+          <t>2049469132337561727</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051156150708547812</t>
+          <t>https://x.com/STKgenghis/status/2049469132337561727</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@KaharUmesh Quoting case 1007249 in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>@EmiratesNBD_AE O and also after emails customer support has yet to issue a complaint number. No logging = no complaint. The perfect system.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1777868709000</v>
+        <v>1777466493000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1175,11 +1181,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1192,51 +1198,50 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2049468314699825596</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46146.35079861111</v>
+        <v>46141.69552083333</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/KaharUmesh/status/2051003496439427421</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2051156048086519884</t>
+          <t>2049469842646818920</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051156048086519884</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049469842646818920</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@KaharUmesh We sincerely regret for the inconvenience To be able to assist further, we kindly request you to reach out to us at
- social@emiratesnbd.com</t>
+          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1004599 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1777868685000</v>
+        <v>1777466662000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1246,11 +1251,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174635, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1263,50 +1268,50 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2051003496439427421</t>
+          <t>2049469132337561727</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46146.35052083333</v>
+        <v>46141.69747685185</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2049470212714737829</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/STKgenghis/status/2049470212714737829</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dubai prouve que ni la religion ni les étrangers sont le problème d’un état. Dubai tient avec 90% d étrangers. Tout le monde se tien à carreau, j’ai vécu une expérience incroyable de service, de sécurité et de kif. Merci @EmiratesNBD_AE</t>
+          <t>@EmiratesNBD_AE I will give this a try but am not holding my breath.</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1777827034000</v>
+        <v>1777466750000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1316,7 +1321,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'yiahhhh', 'screenName': 'TrioMsPaname', 'followersCount': 6, 'favouritesCount': 1798, 'friendsCount': 145, 'description': '❤️💙'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1333,46 +1338,50 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2049469842646818920</t>
+        </is>
+      </c>
       <c r="P13" s="2" t="n">
-        <v>46145.86844907407</v>
+        <v>46141.69849537037</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2050981528298000875</t>
+          <t>2049472842727665850</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981528298000875</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049472842727665850</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>La France est laxiste, personne ne suit les règles ici.</t>
+          <t>@STKgenghis Hi khana! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1004599 in the subject line of the email.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1777827076000</v>
+        <v>1777467377000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1382,11 +1391,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'yiahhhh', 'screenName': 'TrioMsPaname', 'followersCount': 6, 'favouritesCount': 1798, 'friendsCount': 145, 'description': '❤️💙'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1399,50 +1408,50 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2049470212714737829</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46145.86893518519</v>
+        <v>46141.70575231482</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2050981352871264409</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2050981352871264409</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2051032364747280512</t>
+          <t>2049474377788604862</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/TrioMsPaname/status/2051032364747280512</t>
+          <t>https://x.com/STKgenghis/status/2049474377788604862</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1 coup ko encore lui son slogan de mrde @BallyBagayoko</t>
+          <t>@EmiratesNBD_AE Done. As I said not holding breath.</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1777839196000</v>
+        <v>1777467743000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2051032364747280512</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1452,11 +1461,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'yiahhhh', 'screenName': 'TrioMsPaname', 'followersCount': 6, 'favouritesCount': 1798, 'friendsCount': 145, 'description': '❤️💙'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1469,56 +1478,60 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2049472842727665850</t>
+        </is>
+      </c>
       <c r="P15" s="2" t="n">
-        <v>46146.00921296296</v>
+        <v>46141.70998842592</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049475517070348292</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2048469042315337899</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049475517070348292</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I am using @EmiratesNBD_KSA InfiniteCard for 3years. On 01/02/2026 I made a Purchase of 100$ as per the rule of VisaAirportComp @VisaCEMEA to avail LoungeAccess. #ENBD never notified me about the monthly spend req of SAR 3000. They charged me 460 SAR @SAMA_GOV @EmiratesNBD_AE https://t.co/wlpy5fYt7z</t>
+          <t>@STKgenghis Hello, we will check the email and update you shortly.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1777228053000</v>
+        <v>1777468015000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG2ftYnacAADNVo.png', 'type': 'photo', 'id': '2048469007574134784'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1535,46 +1548,52 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2049474377788604862</t>
+        </is>
+      </c>
       <c r="P16" s="2" t="n">
-        <v>46138.93579861111</v>
+        <v>46141.71313657407</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2048469731607281786</t>
+          <t>2049758371734229151</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2048469731607281786</t>
+          <t>https://x.com/STKgenghis/status/2049758371734229151</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>There was no email or sms from @EmiratesNBD_KSA regarding the monthly spend of 3000 SR. The new customers could be aware of this, since you would have informed them. However VAC had mentioned in their app about spending of 100$ and I did spend that. I want the 460SAR refund</t>
+          <t>@EmiratesNBD_AE So once again routed to the 'team'. 
+I will soon travel and will not be able to use my credit card through no fault of my own. 
+Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1777228217000</v>
+        <v>1777535453000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1584,7 +1603,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1594,58 +1613,57 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>40</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049475517070348292</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46138.93769675926</v>
+        <v>46142.49366898148</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2048470825146171877</t>
+          <t>2049759572416495861</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2048470825146171877</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049759572416495861</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Hello @EmiratesNBD_KSA , I want the amount to refunded to my account. Else I will have to escalate this issue to @SAMA_GOV 
-@EmiratesNBD_AE @VisaCEMEA</t>
+          <t>@STKgenghis We are extremely sorry and we have escalated the matter and will reply to your email as soon as possible with an update.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1777228478000</v>
+        <v>1777535739000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1655,11 +1673,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1668,54 +1686,54 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2048469731607281786</t>
+          <t>2049758371734229151</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46138.9407175926</v>
+        <v>46142.49697916667</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2048615227546087604</t>
+          <t>2049927131657081284</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2048615227546087604</t>
+          <t>https://x.com/STKgenghis/status/2049927131657081284</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>@Nidhinkn Hello, we are sorry to hear that you are experiencing this. Please send your phone number and ID number via private message so that we can assist you. Thank you</t>
+          <t>@EmiratesNBD_AE Right. So its now almost 14 days with credit card not functioning.</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1777262906000</v>
+        <v>1777575688000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1725,11 +1743,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17447, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1742,50 +1760,50 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2048470825146171877</t>
+          <t>2049759572416495861</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46139.33918981482</v>
+        <v>46142.95935185185</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2049584024058810569</t>
+          <t>2050063207486587148</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2049584024058810569</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050063207486587148</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA I did send DM with all details of the issue. Also shared my mobile number and ID. I'll wait till tomorrow evening. If there is no response by then, I'll directly escalate this to @SAMA_GOV</t>
+          <t>@STKgenghis Please note that our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1777493885000</v>
+        <v>1777608131000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1795,7 +1813,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1812,50 +1830,50 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2048615227546087604</t>
+          <t>2049927131657081284</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46142.01255787037</v>
+        <v>46143.33484953704</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2049698552998244828</t>
+          <t>2050170081574056214</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2049698552998244828</t>
+          <t>https://x.com/STKgenghis/status/2050170081574056214</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>@Nidhinkn We have already shared your details with our team and asked  to contact you with an update as soon as possible.</t>
+          <t>@EmiratesNBD_AE I dont think you appreciate where this places me through no fault of mine. I have had several subscriptions stopped because card is blocked. A monthly payment didnt go through - i am facing a fine.  OVER TWO WEEKS since i asked for my card to be blocked as a precaution !????</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1777521191000</v>
+        <v>1777633612000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1865,7 +1883,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17447, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J21" t="n">
@@ -1882,51 +1900,50 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>22</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2049584024058810569</t>
+          <t>2050063207486587148</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46142.32859953704</v>
+        <v>46143.62976851852</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2050976036028919856</t>
+          <t>2050275701312324065</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/Nidhinkn/status/2050976036028919856</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050275701312324065</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA No update from your team. No update from anyone from @EmiratesNBD_KSA 
-Now I will escalate it to @SAMA_GOV</t>
+          <t>@STKgenghis We apologize for the inconvenience, our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1777825766000</v>
+        <v>1777658794000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2048469042315337899</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1936,11 +1953,11 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'Nidhin', 'screenName': 'Nidhinkn', 'followersCount': 2, 'favouritesCount': 202, 'friendsCount': 53, 'description': 'Nation First. Bharat.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1953,50 +1970,50 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2049698552998244828</t>
+          <t>2050170081574056214</t>
         </is>
       </c>
       <c r="P22" s="2" t="n">
-        <v>46145.85377314815</v>
+        <v>46143.92122685185</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/z6894890/status/2050845248088055847</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2050845248088055847</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2050845248088055847</t>
+          <t>2050374137852670288</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/z6894890/status/2050845248088055847</t>
+          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE ابي وظيفه باي فرع من اللي بالرياض</t>
+          <t>@EmiratesNBD_AE Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1777794584000</v>
+        <v>1777682263000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2050845248088055847</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2006,11 +2023,11 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Femal', 'screenName': 'z6894890', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 51, 'description': ''}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -2023,124 +2040,133 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2050275701312324065</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="n">
-        <v>46145.49287037037</v>
+        <v>46144.1928587963</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2050427142379282939</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2050427142379282939</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Emirates NBD to settle Visa payments in UAE dirhams, a major shift for daily transactions https://t.co/hZmnE0KKFU https://t.co/dqextuYMnK</t>
+          <t>@STKgenghis We are extremely sorry and understand your concern. Please note that we are working very closely to resolve your concern and will update you on urgent basis.</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1777797101000</v>
+        <v>1777694900000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHYaeCHXUAAlHfN.jpg', 'type': 'photo', 'id': '2050855783579996160'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'Gulf News', 'screenName': 'gulf_news', 'followersCount': 1541262, 'favouritesCount': 1075, 'friendsCount': 411, 'description': "We don't just cover the news - we uncover the truth. The official Twitter feed from Gulf News."}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>3745</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2050374137852670288</t>
+        </is>
+      </c>
       <c r="P24" s="2" t="n">
-        <v>46145.52200231481</v>
+        <v>46144.33912037037</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/gulf_news/status/2050855805600092255</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2050855805600092255</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2050785564182392905</t>
+          <t>2051475218783158326</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050785564182392905</t>
+          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Whether you're paying your bills, transferring money within the UAE, sending it abroad or exchanging currencies, Emirates NBD makes it simple and secure through the ENBD X app.
-#transfers #payments #DirectRemit #Aani #currencies #travel #GlobalCash
-https://t.co/JhadMTFApo https://t.co/WHukK5bQyz</t>
+          <t>@EmiratesNBD_AE Update. 
+Received email from your social medium team saying "Dear,
+Kindly note that the account is not active."
+No name. My account is active. Not sure what this cryptic email meant.</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1777780354000</v>
+        <v>1777944781000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2050785564182392905</t>
+          <t>2049379193910165928</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamTYXgAAT-o_.jpg', 'type': 'photo', 'id': '2050785556909490176'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHXamj9XMAAx1Ze.jpg', 'type': 'photo', 'id': '2050785561359626240'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174636, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2150,70 +2176,72 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1915</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2050427142379282939</t>
+        </is>
+      </c>
       <c r="P25" s="2" t="n">
-        <v>46145.3281712963</v>
+        <v>46147.23126157407</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2050841752987136094</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2050841752987136094</t>
+          <t>2049066491463553321</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2050841752987136094</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2049066491463553321</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Emirates NBD Egypt Releases Its Third Sustainability Report, Reporting Strong Profit Growth and a Strategic Shift Toward Renewable Energy
- https://t.co/zMJRGwIJEz  | details 
-#fintech_gate
-#Emirates_NBD_Egypt_Releases https://t.co/JnNoI8ViAd</t>
+          <t>Millionaire account limited-time offer
+Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1777793751000</v>
+        <v>1777370496000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2050841752987136094</t>
+          <t>2049066491463553321</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHYNrg9boAAfrzr.jpg', 'type': 'photo', 'id': '2050841721546973184'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 518, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2222,62 +2250,60 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>55195</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" s="2" t="n">
-        <v>46145.48322916667</v>
+        <v>46140.58444444444</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2050807726507516194</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2050807726507516194</t>
+          <t>2051396418695578094</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
+          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>UAE Fintech News this week
-@takeem_ai @CashewPayments @shamssmc @EmiratesNBD_AE @MashreqTweets @OfficialADCB @comfi_ai 
-#digitalpayments #uaefintech #proptech https://t.co/0prr3Cb7B5</t>
+          <t>@EmiratesNBD_AE On which date of the month is the draw held?</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1777785638000</v>
+        <v>1777925993000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2050807726507516194</t>
+          <t>2049066491463553321</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2050806769707098112/img/S26hJZ2jdFx84hGu.jpg', 'type': 'video', 'id': '2050806769707098112'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 24, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+          <t>{'name': 'Muhammad Usman', 'screenName': 'Muhamma38929354', 'followersCount': 751, 'favouritesCount': 43872, 'friendsCount': 2152, 'description': 'The greatest good is positive thinking,     The greatest shame is negative thinking'}</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -2287,69 +2313,73 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2049066491463553321</t>
+        </is>
+      </c>
       <c r="P27" s="2" t="n">
-        <v>46145.38932870371</v>
+        <v>46147.01380787037</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050807726507516194</t>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2050807726507516194</t>
+          <t>2051364056217374823</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2050501839184080980</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/uaefintechvibes/status/2050501839184080980</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051302125989236884</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ziina and @shamssmc have partnered to integrate advanced digital financial solutions directly into Sharjah’s creative business ecosystem.
-Read more: https://t.co/VrIYgQm2sy
-#digitalfinancialsolutions #uaepayments https://t.co/4m9BNOOUxb</t>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1777712709000</v>
+        <v>1777903512000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2050501839184080980</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHTYCiLasAEMOgS.jpg', 'type': 'photo', 'id': '2050501268406448129'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2051302098415812608/pu/img/kiycv3whSbLg1NL6.jpg', 'type': 'video', 'id': '2051302098415812608'}]</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'UAE Fintechvibes', 'screenName': 'uaefintechvibes', 'followersCount': 2, 'favouritesCount': 24, 'friendsCount': 30, 'description': 'Latest Fintech News in the UAE - We provide daily fintech news happening within the UAE. \nSend your news at info@uaefintechvibes.com'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17443, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2358,63 +2388,60 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>410</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" s="2" t="n">
-        <v>46144.54524305555</v>
+        <v>46146.75361111111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2050809333848342901</t>
+          <t>2051364056217374823</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2050802535502365160</t>
+          <t>2051355715994878347</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050802535502365160</t>
+          <t>https://x.com/hisho25/status/2051355715994878347</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Apply smarter, faster, and hassle-free.
-With our Straight Through Processing (STP) journey, complete your application in minutes—no delays.
-Watch how easy it is to get started.
-Apply Now: https://t.co/aeh8nbj5gC https://t.co/y7g1WeVQ6R</t>
+          <t>@EmiratesNBD_KSA متى بتدعمون سامسونج باي؟؟</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1777784401000</v>
+        <v>1777916289000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2050802535502365160</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHVpoO7WQAAHCq4.jpg', 'type': 'video', 'id': '2050661313332854785'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174636, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'H', 'screenName': 'hisho25', 'followersCount': 41, 'favouritesCount': 7770, 'friendsCount': 277, 'description': 'لا إله إلا الله محمد رسول الله\n------\nمهتم بالتقنية و بالالعاب و الاخبار التقنية و مهتم ايضا بالـ PC و الكونسل و الهواتف'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2424,53 +2451,57 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2051302125989236884</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n">
-        <v>46145.37501157408</v>
+        <v>46146.90149305556</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2050809333848342901</t>
+          <t>2051364056217374823</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2050809333848342901</t>
+          <t>2051363915762708887</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051363915762708887</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE اريد تمويل وارغب بالاتصال</t>
+          <t>@hisho25 مرحبا, تم الرد على الخاص.</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1777786022000</v>
+        <v>1777918244000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2050802535502365160</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2480,7 +2511,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'Fahad', 'screenName': 'abotameem430', 'followersCount': 14, 'favouritesCount': 10, 'friendsCount': 38, 'description': 'Fahad'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17443, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2497,51 +2528,50 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2050802535502365160</t>
+          <t>2051355715994878347</t>
         </is>
       </c>
       <c r="P30" s="2" t="n">
-        <v>46145.39377314815</v>
+        <v>46146.92412037037</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/abotameem430/status/2050809333848342901</t>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2050809333848342901</t>
+          <t>2051364056217374823</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2050809681140916631</t>
+          <t>2051364056217374823</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050809681140916631</t>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>@abotameem430 نشكركم على اهتمامكم بمنتجاتنا، يرجى زيارة الرابط أدناه وتعبئة بياناتكم، وسيتواصل معكم فريق المبيعات لدينا خلال يومي عمل. الحد الأدنى للراتب المطلوب هو 5000 درهم إماراتي. شكرًا - زبير
-https://t.co/B8qzTltFYl</t>
+          <t>@EmiratesNBD_KSA ماجاني شي على الخاص</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1777786104000</v>
+        <v>1777918278000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2050802535502365160</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2551,7 +2581,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174636, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'H', 'screenName': 'hisho25', 'followersCount': 41, 'favouritesCount': 7770, 'friendsCount': 277, 'description': 'لا إله إلا الله محمد رسول الله\n------\nمهتم بالتقنية و بالالعاب و الاخبار التقنية و مهتم ايضا بالـ PC و الكونسل و الهواتف'}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2568,16 +2598,2461 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2051363915762708887</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>46146.92451388889</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://x.com/hisho25/status/2051364056217374823</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2051364056217374823</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2051365950771871780</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051365950771871780</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>@hisho25 مرحبا, تم ارسال الرسالة مرة اخرى.</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1777918729000</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2051302125989236884</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17443, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2051364056217374823</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>46146.9297337963</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050914407471849643</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1777811073000</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHZPyC_WYAAg5zq.jpg', 'type': 'photo', 'id': '2050914401528471552'}]</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17443, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="2" t="n">
+        <v>46145.68371527778</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA للاسف تجربه سيئة طلعت الفيزا وكنت استخدمها والامور طيبه وليا 4 شهور ابغي احجز سينما فوكس حسب عرضهم تذكرة وتذكره مجاناً للاسف يطلعلي الحسبه حق التذكرتين واتواصلت مع خدمة العملاء اكثر من مره ماحد حل ليا المشكله الين اضطريت الغي البطاقه عشان عدم المصداقيه</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1777896671000</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'name': 'الفنان سعود عبدالله', 'screenName': 'saudabdullah08', 'followersCount': 0, 'favouritesCount': 11, 'friendsCount': 17, 'description': 'فنان اطمح للعالميه ومحب للفن'}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>46146.67443287037</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://x.com/saudabdullah08/status/2051273429328814571</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2051274681102049577</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051274681102049577</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>@saudabdullah08 نحن آسفون جدًا لسماع أنك مررت بتجربة غير سارة، نرجو منك مشاركتها معنا من خلال عنوان بريدك الإلكتروني المسجل لمزيد من التواصل على البريد الإلكتروني social@emiratesnbd.com وإضافة رقم المرجع الخاص #1007678 في موضوع الرسالة.</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1777896969000</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17443, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2051273429328814571</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>46146.67788194444</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051025258497396907</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ادمین دبی اینترنشنال چرا انقدر حیوونه :)))))))) https://t.co/juEIzEYwCT</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1777837502000</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHa0maLWAAAM-y5.jpg', 'type': 'photo', 'id': '2051025252268769280'}]</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'name': 'Foroogh 🇮🇷', 'screenName': 'bokonndarro', 'followersCount': 1394, 'favouritesCount': 36117, 'friendsCount': 198, 'description': 'نرو، کتلت سفارش دادم.'}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>12</v>
+      </c>
+      <c r="K36" t="n">
+        <v>1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>824</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>58151</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="n">
+        <v>46145.98960648148</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2051282211920588860</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://x.com/BabyIamInJail/status/2051282211920588860</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>@bokonndarro عین سگ، دروغ میگه.
+با پاسپورت کانادا و اقامت امارات، ازت یک کامیون مدارک می خواهند، بعد می فرستند دفتر مرکزی، آیا قبول بشه آیا قبول نشه!!
+امارات حساب باز کردن بعنوان توریسیت واقعا سخته</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1777898764000</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'name': 'حوا🍎', 'screenName': 'BabyIamInJail', 'followersCount': 620, 'favouritesCount': 20504, 'friendsCount': 775, 'description': '🇨🇦 in Dubai'}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>46146.69865740741</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>@BabyIamInJail توریست که چیزی نیست من با صد سال اقامت چند سال پیش با زور آشنا تو Emirates NBD برام حساب باز کردن :))) 
+ولی الان واسه جذب توریست و سرمایه‌گذار چندین طرح جدید ارائه کردن</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1777899117000</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'name': 'Foroogh 🇮🇷', 'screenName': 'bokonndarro', 'followersCount': 1394, 'favouritesCount': 36117, 'friendsCount': 198, 'description': 'نرو، کتلت سفارش دادم.'}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2051282211920588860</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>46146.70274305555</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051283691821834411</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2051287062402540010</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>@bokonndarro عه چی؟
+امروز دقیقا ENBD بودم
+ازم قبض آب از تورنتو می خواست!
+راهی داره اطلاعات مالیاتی ازم نگیرند؟
+تو کانادا ممکنه audit بخورم اگه با هم حرف بزنند. تا ثابت کنی بابا دوهزار بوده، کلی خرج audit شده.</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1777899921000</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'name': 'حوا🍎', 'screenName': 'BabyIamInJail', 'followersCount': 620, 'favouritesCount': 20504, 'friendsCount': 775, 'description': '🇨🇦 in Dubai'}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2051283691821834411</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>46146.71204861111</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://x.com/BabyIamInJail/status/2051287062402540010</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2051287062402540010</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2051290669126242679</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://x.com/bokonndarro/status/2051290669126242679</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>@BabyIamInJail پشمام دنبال قبض آب هم افتادن؟
+متاسفانه اطلاعی ندارم. یه سال و نیمه هی فرم جهت شناسایی شهروندای آمریکا میفرستن، ولی این مدلیشو ندیده بودم</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1777900781000</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2051025258497396907</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'name': 'Foroogh 🇮🇷', 'screenName': 'bokonndarro', 'followersCount': 1394, 'favouritesCount': 36117, 'friendsCount': 198, 'description': 'نرو، کتلت سفارش دادم.'}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2051287062402540010</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>46146.72200231482</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2048745045147123736</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Dear Emirates NBD,
+I received a credit card statement with dues 15 days after requesting cancellation, and was charged an annual fee despite being promised a first-year waiver. Please clarify these discrepancies.</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>1777293857000</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 1, 'favouritesCount': 969, 'friendsCount': 21, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="2" t="n">
+        <v>46139.69741898148</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA Hi, I received a call from your bank representative confirming the cancellation of my card a week back. However, I haven't received any confirmation message till now, via SMS or email. Please confirm that my card has been cancellation.</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>1777893777000</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'name': 'Anwar Quadri', 'screenName': 'anwarquadri7', 'followersCount': 1, 'favouritesCount': 969, 'friendsCount': 21, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>46146.6409375</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://x.com/anwarquadri7/status/2051261292133130490</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2051263125849010218</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051263125849010218</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>@anwarquadri7 Hello, We have replied to your message in private</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1777894214000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2048745045147123736</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17443, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2051261292133130490</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>46146.64599537037</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>@LivBank @EmiratesNBD_AE dear can any one reply on this I am not getting any response</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1777888498000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'name': 'A R mishra', 'screenName': 'abhiseksonusonu', 'followersCount': 0, 'favouritesCount': 0, 'friendsCount': 38, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="2" t="n">
+        <v>46146.57983796296</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://x.com/abhiseksonusonu/status/2051239150909866122</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2051247081315057693</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2051247081315057693</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>@abhiseksonusonu Hi Mishra, thanks for reaching out. We're sorry to hear you're facing an issue. We have replied to your post privately.</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1777890389000</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174655, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2051239150909866122</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>46146.60172453704</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2051210226183905695</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210219850489871</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1777881600000</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdI4bpW0AAzk8W.jpg', 'type': 'photo', 'id': '2051188289621643264'}]</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="n">
+        <v>46146.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2051210226183905695</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2051210223440871854</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210223440871854</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
+⛳جولات الغولف
+🅿️خدمة صف السيارات والمزيد
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام
+https://t.co/pVA5yvt1qT</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>1777881601000</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>46146.50001157408</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2051210226183905695</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2051210226183905695</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️ and amazing rewards:
+🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flights booking and upgrades
+🚀 Fast-track upgrade to Etihad Guest Gold Tier status https://t.co/0SWmjSoGbc</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>1777881602000</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdI4mUWUAAB15O.jpg', 'type': 'photo', 'id': '2051188292486320128'}]</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2051210223440871854</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>46146.50002314815</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2051210226183905695</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2051210228520063073</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051210228520063073</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>🚗 Complimentary airport transfers, meet &amp;amp; greet services
+⛳ Golf rounds at select premium courses
+🅿️ Valet parking, and much more
+Valid till 31 May 2026
+Terms and conditions apply
+https://t.co/oszNDRRljr</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>1777881602000</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2051210219850489871</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2051210226183905695</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>46146.50002314815</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051255518270779594</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2051255518270779594</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2051255518270779594</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051255518270779594</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
+Download the EI + Mobile Banking App today. #EmiratesIslamic
+https://t.co/H1RLoPe6Zu https://t.co/5h5iHPAmUn</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1777892400000</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2051255518270779594</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2051212444874297344/pu/img/sHPu-aR8u5aX_oaG.jpg', 'type': 'video', 'id': '2051212444874297344'}]</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" s="2" t="n">
+        <v>46146.625</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2051285726361227464</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2051285716965986342</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285716965986342</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>1777899600000</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2051285716965986342</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdGISHWAAEPXm-.jpg', 'type': 'photo', 'id': '2051185263406088193'}]</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" s="2" t="n">
+        <v>46146.70833333334</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2051285726361227464</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2051285720577269980</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285720577269980</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
+لمعرفة المزيد:
+https://t.co/mVDWeikQTM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>1777899601000</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2051285716965986342</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2051285716965986342</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>46146.70834490741</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2051285726361227464</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2051285723785871469</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp;amp; FX advisor, preferential pricing on products, https://t.co/ABnbdvENub</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>1777899602000</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2051285716965986342</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdGIg5XoAAWmlu.jpg', 'type': 'photo', 'id': '2051185267374006272'}]</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2051285720577269980</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>46146.70835648148</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2051285726361227464</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2051285726361227464</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
+Learn more:
+https://t.co/J0ZWQGZcId</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>1777899602000</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2051285716965986342</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2051285723785871469</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>46146.70835648148</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2051180030810632404</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180020534546693</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
+📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً) https://t.co/MkXMIn08uG</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>1777874400000</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHadNzTWQAAUjIJ.jpg', 'type': 'photo', 'id': '2050999540749058048'}]</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="2" t="n">
+        <v>46146.41666666666</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2051180030810632404</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2051180024997220725</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180024997220725</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
+📅يسري لغاية 31 مايو 2026.
+تطبق الشروط والأحكام.</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>1777874401000</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>46146.41667824074</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2051180030810632404</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2051180027576750215</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180027576750215</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Drive home your dream car with Emirates Islamic Auto Finance!
+📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.) https://t.co/qqwuS90F3U</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1777874402000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHadODvXQAAw5bH.jpg', 'type': 'photo', 'id': '2050999545161531392'}]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2051180024997220725</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>46146.41668981482</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2051180030810632404</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2051180030810632404</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
+📅Offer valid till 31 May 2026.
+Terms &amp;amp; Conditions apply.</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1777874403000</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2051180020534546693</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2051180027576750215</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>46146.41670138889</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051255517989797926</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2051255517989797926</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2051255517989797926</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051255517989797926</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ابق على اطلاعٍ بمحفظة ثرواتك الرقمية في الوقت الفعلي وابدأ بالتداول على الفور من خلال تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+قم بتحميل تطبيق EI + للخدمات المصرفية عبر الهاتف المتحرك.
+https://t.co/mxT5J6OSOM https://t.co/v6MSR7Y6S1</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1777892400000</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2051255517989797926</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2051197348525576192/pu/img/c6Vk5SxxepU-CAmM.jpg', 'type': 'video', 'id': '2051197348525576192'}]</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="2" t="n">
+        <v>46146.625</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2/status/2049022486218715385</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1777360004000</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG-XFpUagAEQNCt.jpg', 'type': 'photo', 'id': '2049022478723481601'}]</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'name': 'Fatima.M', 'screenName': 'Thefatim2', 'followersCount': 224, 'favouritesCount': 547, 'friendsCount': 48, 'description': '🤍'}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" s="2" t="n">
+        <v>46140.46300925926</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2049060823264350309</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049060823264350309</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>@Thefatim2 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1777369144000</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>46140.5687962963</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2049065369416159269</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2/status/2049065369416159269</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>@emiratesislamic ما شفت منكم اي رضى من تحولت ل بنك الامارات الاسلامي اكبر غلطه</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>1777370228000</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{'name': 'Fatima.M', 'screenName': 'Thefatim2', 'followersCount': 224, 'favouritesCount': 547, 'friendsCount': 48, 'description': '🤍'}</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>2050809333848342901</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="n">
-        <v>46145.39472222222</v>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2049060823264350309</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="n">
+        <v>46140.5813425926</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2049068445883314237</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2049068445883314237</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>@Thefatim2 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>1777370962000</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2049065369416159269</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="n">
+        <v>46140.58983796297</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2050249666336559176</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://x.com/Thefatim2/status/2050249666336559176</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>@emiratesislamic كم يوم طاف الحين ؟</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>1777652586000</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{'name': 'Fatima.M', 'screenName': 'Thefatim2', 'followersCount': 224, 'favouritesCount': 547, 'friendsCount': 48, 'description': '🤍'}</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2049068445883314237</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="n">
+        <v>46143.849375</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2051193239932174341</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>@Thefatim2 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>1777877552000</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2049022486218715385</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2050249666336559176</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="n">
+        <v>46146.45314814815</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051181531461275940</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2051181531461275940</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2051181531461275940</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051181531461275940</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>نشارككم أبرز محطات الخدمات المصرفية للشركات - نظرة على أهم اللحظات من مشاركاتنا وتعاوناتنا الأخيرة.
+Sharing our recent Wholesale Banking highlights, a look back at key moments across our engagements and collaborations. https://t.co/Y6amuYGajF</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>1777874760000</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2051181531461275940</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2050953741415694336/pu/img/_OWQjFIhaq2Dk8W-.jpg', 'type': 'video', 'id': '2050953741415694336'}]</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" s="2" t="n">
+        <v>46146.42083333333</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,38 +517,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/kinsofdubai/status/2052462422221627597</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052462422221627597</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052462422221627597</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049379193910165928</t>
+          <t>https://x.com/kinsofdubai/status/2052462422221627597</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Open an Emirates NBD Millionaire Account to be the next winner, with over 1,400 cash prizes worth AED 50,000,000.
-- Monthly prizes up to AED 1,000,000
-- Grand prizes up to AED 5,000,000
-Dedicated prizes for Emiratis, expats, and businesses 🇦🇪</t>
+          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1777445050000</v>
+        <v>1778180149000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052462422221627597</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -558,78 +555,86 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Kinshuk Kulshreshtha', 'screenName': 'kinsofdubai', 'followersCount': 1582, 'favouritesCount': 766, 'friendsCount': 1531, 'description': 'Real Estate Investments Specialist.  Proud Father &amp; husband. Based in Dubai, mostly live in my head. #Realestate #dubai #Jaipur #Philippines #family'}</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>102190</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" s="2" t="n">
-        <v>46141.44733796296</v>
+        <v>46149.95542824074</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2049468314699825596</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2049468314699825596</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE would not recommend bank that suspends 40 year old accounts wout notification. Only found out when i temp blocked credit card i thought id misplaced. It cant be unblocked because of suspension...
-deprived of services no notification  told KYC take 8-10 buss days 2 get back. So..</t>
+          <t>@EmiratesNBD_KSA 
+خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
+رغم ان  (تقييمي 751 ممتاز) 
+الأغرب؟ 
+حاولت رفع شكوى رسمية عبر الرقم المجاني للبنك فانتظرت 59 دقيقة ثم أغلقوا المكالمة من طرفهم دون رد! (مرفق صورة السجل)
+رفعت الشكوى رسميًا لدى @SAMAcares برقم (C260502xxxxx).
+هذه ليست مسألة تمويل… هذه مسألة **حوكمة** و**مصداقية**.
+سوقنا المصرفي تنافسي وأنا عميل ذو ملاءة مالية مثبتة أبحث عن بنك يقدر السجل الائتماني النظيف ويحترم حقوق العميل.
+من يريد أن يكون الشريك الحقيقي؟ 
+@AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1777466298000</v>
+        <v>1778184531000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvf53hWgAUCXBk.jpg', 'type': 'photo', 'id': '2052480240446767109'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvf53jWUAcT4dG.jpg', 'type': 'photo', 'id': '2052480240455143431'}]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+          <t>{'name': 'سامي الحربي', 'screenName': 'samial7arbi02', 'followersCount': 276, 'favouritesCount': 688, 'friendsCount': 1367, 'description': 'العاقل إن أخطأ تأسف .. والأحمق إن أخطأ تفلسف ..'}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -638,54 +643,50 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2049379193910165928</t>
-        </is>
-      </c>
+          <t>31148</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" s="2" t="n">
-        <v>46141.69326388889</v>
+        <v>46150.00614583334</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2049469132337561727</t>
+          <t>2052597402272407645</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2049469132337561727</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052597402272407645</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE O and also after emails customer support has yet to issue a complaint number. No logging = no complaint. The perfect system.</t>
+          <t>@samial7arbi02 @ENBDdeals @snbalahli مرحبا سامي شكرا لتواصلك معنا تم الرد عبر رسائل الخاص</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1777466493000</v>
+        <v>1778212330000</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -695,11 +696,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -712,50 +713,50 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2049468314699825596</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46141.69552083333</v>
+        <v>46150.32789351852</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2049469842646818920</t>
+          <t>2052597173573886292</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049469842646818920</t>
+          <t>https://x.com/ENBDdeals/status/2052597173573886292</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hi, thank you for sharing your feedback. We’re sorry that you had experienced this, it is not what we expect our customers to feel nor see. We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1004599 for us to assist you better. Thanks.</t>
+          <t>@samial7arbi02 @anb_bank @RiyadBank @BankAlJazira @BankAlbilad @D360bank @alrajhibank @snbalahli مرحبا سامي شكرا لتواصلك معنا تم الرد عبر رسائل الخاص</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1777466662000</v>
+        <v>1778212276000</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -765,11 +766,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -782,50 +783,51 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2049469132337561727</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46141.69747685185</v>
+        <v>46150.32726851852</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2049470212714737829</t>
+          <t>2052481741772755197</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2049470212714737829</t>
+          <t>https://x.com/AskRiyadBank/status/2052481741772755197</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I will give this a try but am not holding my breath.</t>
+          <t>@samial7arbi02 @ENBDdeals @anb_bank @RiyadBank @BankAlJazira @BankAlbilad @D360bank @alrajhibank @snbalahli أهلاً وسهلا 👋
+نسعد بتواصلك معنا عبر الهاتف المجاني 8001242020 وذلك من الساعة 9 صباحاً إلى 8 مساءً بأيام العمل الرسمية للإفادة بالتفاصيل 💙</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1777466750000</v>
+        <v>1778184755000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -835,11 +837,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+          <t>{'name': 'اسأل بنك الرياض', 'screenName': 'AskRiyadBank', 'followersCount': 165888, 'favouritesCount': 0, 'friendsCount': 4, 'description': 'أهلاً بك في الحساب الرسمي لخدمة عملاء بنك الرياض 💙 | تابعوا @RiyadBank لآخر العروض والمنتجات. للعناية بالعملاء اتصل على 8001242225'}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -852,50 +854,52 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>184</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2049469842646818920</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46141.69849537037</v>
+        <v>46150.00873842592</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2049472842727665850</t>
+          <t>2052484628875780240</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049472842727665850</t>
+          <t>https://x.com/BankAlbilad/status/2052484628875780240</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>@STKgenghis Hi khana! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1004599 in the subject line of the email.</t>
+          <t>@samial7arbi02 @ENBDdeals @snbalahli حياك في البلاد أستاذ سامي ، نسعد بتقديم منتجاتنا البنكية ويسعدنا زيارتك الرابط التالي لطلب المنتج وسيتم التواصل معك من قبل فريق المبيعات عبر الهاتف 
+https://t.co/ujj9vXwI2q 
+كما نسعد بتواصلك وخدمتك عبر الرقم المجاني لهاتف المبيعات 8001236666  دمتم بخير</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1777467377000</v>
+        <v>1778185443000</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -905,11 +909,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'بنك البلاد | Bank Albilad', 'screenName': 'BankAlbilad', 'followersCount': 1046505, 'favouritesCount': 442, 'friendsCount': 3, 'description': 'مصرفية يرتاح لها البال | نسعد بخدمتكم على مدار الساعة وطوال أيام الأسبوع'}</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -922,50 +926,51 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>209</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2049470212714737829</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46141.70575231482</v>
+        <v>46150.01670138889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2049474377788604862</t>
+          <t>2052482551898411220</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2049474377788604862</t>
+          <t>https://x.com/anb_care/status/2052482551898411220</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Done. As I said not holding breath.</t>
+          <t>@samial7arbi02 @ENBDdeals @snbalahli حياك الله  أ.سامي 
+أبشر ولايهمك، يمكنك التواصل معنا عبر الرسائل الخاصة ونتشرف في خدمتك  💙 https://t.co/LSIiyoGCbK</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1777467743000</v>
+        <v>1778184948000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -975,11 +980,11 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+          <t>{'name': 'anb | حياكم في البنك العربي الوطني', 'screenName': 'anb_care', 'followersCount': 79703, 'favouritesCount': 454, 'friendsCount': 4, 'description': 'نقدّم لكم تجربة مصرفية سهلة وسريعة | موجودين لمساعدتكم على مدار الساعة | تعرّفوا على جديدنا عبر @anb_bank\n\nتطبيقنـا 👈 https://t.co/hBpkptWU6g'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -992,50 +997,53 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>166</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2049472842727665850</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="P8" s="2" t="n">
-        <v>46141.70998842592</v>
+        <v>46150.01097222222</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2049475517070348292</t>
+          <t>2052492018824138828</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049475517070348292</t>
+          <t>https://x.com/AlJaziraCare/status/2052492018824138828</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@STKgenghis Hello, we will check the email and update you shortly.</t>
+          <t>@samial7arbi02 عزيزي سامي هلابك في الجزيرة
+موجودين لخدمتك تفضل بإرسال تفاصيل طلبك على الخاص لتتم افادتك  
+وشكرا لك🤎
+https://t.co/NUxJdRIqnW</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1777468015000</v>
+        <v>1778187205000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1045,11 +1053,11 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'AlJazirabankCare', 'screenName': 'AlJaziraCare', 'followersCount': 6809, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'نسعد بخدمتكم والإجابة على كافة استفساراتكم على مدار الساعة🤎\nللاطلاع على أحدث العروض زوروا حسابنا @BankAljazira\nوللتواصل من خارج المملكة 00966920006666'}</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1062,52 +1070,50 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>156</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2049474377788604862</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46141.71313657407</v>
+        <v>46150.03709490741</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/heba_hashem/status/2052461879398937044</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052461879398937044</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2049758371734229151</t>
+          <t>2052461879398937044</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2049758371734229151</t>
+          <t>https://x.com/heba_hashem/status/2052461879398937044</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE So once again routed to the 'team'. 
-I will soon travel and will not be able to use my credit card through no fault of my own. 
-Why should a customer with a 40 year track record of no loans and good credit standing trust a bank that doesnt value the relationship?</t>
+          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1777535453000</v>
+        <v>1778180019000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2052461879398937044</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1117,67 +1123,64 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+          <t>{'name': 'Heba Hashem Ⓥ', 'screenName': 'heba_hashem', 'followersCount': 1479, 'favouritesCount': 13352, 'friendsCount': 2389, 'description': 'Freelance journalist in Canada/Dubai'}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>1</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2049475517070348292</t>
-        </is>
-      </c>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" s="2" t="n">
-        <v>46142.49366898148</v>
+        <v>46149.95392361111</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2049759572416495861</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049759572416495861</t>
+          <t>https://x.com/RakshtVaghasiya/status/2032450113100984492</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@STKgenghis We are extremely sorry and we have escalated the matter and will reply to your email as soon as possible with an update.</t>
+          <t>@EmiratesNBD_KSA 
+I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1777535739000</v>
+        <v>1773408842000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1187,7 +1190,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1204,50 +1207,46 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2049758371734229151</t>
-        </is>
-      </c>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" s="2" t="n">
-        <v>46142.49697916667</v>
+        <v>46094.73196759259</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2049927131657081284</t>
+          <t>2032452730443256247</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2049927131657081284</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2032452730443256247</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Right. So its now almost 14 days with credit card not functioning.</t>
+          <t>@RakshtVaghasiya We sincerely regret for the inconvenience To be able to assist further, we kindly request you to kindly share your registered mobile number through direct message, We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1777575688000</v>
+        <v>1773409466000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1257,7 +1256,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1274,50 +1273,50 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>72</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2049759572416495861</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="P12" s="2" t="n">
-        <v>46142.95935185185</v>
+        <v>46094.73918981481</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2050063207486587148</t>
+          <t>2032457337122791694</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050063207486587148</t>
+          <t>https://x.com/RakshtVaghasiya/status/2032457337122791694</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@STKgenghis Please note that our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
+          <t>@EmiratesNBD_KSA 0561891252</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1777608131000</v>
+        <v>1773410565000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1327,7 +1326,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1344,50 +1343,50 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>49</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2049927131657081284</t>
+          <t>2032452730443256247</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46143.33484953704</v>
+        <v>46094.75190972222</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2050170081574056214</t>
+          <t>2032458133151342720</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2050170081574056214</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2032458133151342720</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I dont think you appreciate where this places me through no fault of mine. I have had several subscriptions stopped because card is blocked. A monthly payment didnt go through - i am facing a fine.  OVER TWO WEEKS since i asked for my card to be blocked as a precaution !????</t>
+          <t>@RakshtVaghasiya We have shared your details with the concerned team, and they will contact you shortly.</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1777633612000</v>
+        <v>1773410754000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1397,7 +1396,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1407,57 +1406,57 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>119</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2050063207486587148</t>
+          <t>2032457337122791694</t>
         </is>
       </c>
       <c r="P14" s="2" t="n">
-        <v>46143.62976851852</v>
+        <v>46094.75409722222</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2050275701312324065</t>
+          <t>2035964859116879927</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050275701312324065</t>
+          <t>https://x.com/RakshtVaghasiya/status/2035964859116879927</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@STKgenghis We apologize for the inconvenience, our team is working very closely to resolve the issue, and we will update you with the outcome on urgent basis.</t>
+          <t>@EmiratesNBD_KSA No one contacted yet. This is not acceptable at all from brand like Emirates NBD. Extremely disappointed.</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1777658794000</v>
+        <v>1774246823000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1467,11 +1466,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1484,50 +1483,50 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>74</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2050170081574056214</t>
+          <t>2032458133151342720</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46143.92122685185</v>
+        <v>46104.43082175926</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2050374137852670288</t>
+          <t>2035976151764549748</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2050374137852670288</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Had i the energy I would report this to @centralbankuae but no energy or time. I will now be silent. I blocked the card 17 April. No service since.</t>
+          <t>@RakshtVaghasiya Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1777682263000</v>
+        <v>1774249515000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1537,11 +1536,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1554,50 +1553,51 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2050275701312324065</t>
+          <t>2035964859116879927</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46144.1928587963</v>
+        <v>46104.46197916667</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2050427142379282939</t>
+          <t>2038625938133471268</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050427142379282939</t>
+          <t>https://x.com/RakshtVaghasiya/status/2038625938133471268</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@STKgenghis We are extremely sorry and understand your concern. Please note that we are working very closely to resolve your concern and will update you on urgent basis.</t>
+          <t>@EmiratesNBD_KSA Dispute request #22407819581 was raised on 23rd March'26 and After that I received call from NBD representative &amp;amp; I explained my dispute. But after that no communication or response received from NBD.
+I am really frustrated by response from such reputed bank.</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1777694900000</v>
+        <v>1774881274000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J17" t="n">
@@ -1624,53 +1624,50 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>71</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2050374137852670288</t>
+          <t>2035976151764549748</t>
         </is>
       </c>
       <c r="P17" s="2" t="n">
-        <v>46144.33912037037</v>
+        <v>46111.77400462963</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2051475218783158326</t>
+          <t>2038628104541774071</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/STKgenghis/status/2051475218783158326</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2038628104541774071</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Update. 
-Received email from your social medium team saying "Dear,
-Kindly note that the account is not active."
-No name. My account is active. Not sure what this cryptic email meant.</t>
+          <t>@RakshtVaghasiya Hi Rakshit, we have already escalated the matter and our team will contact you as soon as possible.</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1777944781000</v>
+        <v>1774881790000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2049379193910165928</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1680,11 +1677,11 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'khana-b-dosh', 'screenName': 'STKgenghis', 'followersCount': 238, 'favouritesCount': 18386, 'friendsCount': 492, 'description': 'khana-b-dosh. (gypsy in Urdu). soul-gypsy, #IT #faculty, @WomeninIT, #Speech #Technology, #Dubai #UAE #Robotics #HRI #HCI #Auckland(escaped) #grammarnazi'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
         <v>0</v>
@@ -1697,51 +1694,50 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2050427142379282939</t>
+          <t>2038625938133471268</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46147.23126157407</v>
+        <v>46111.77997685185</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2051396418695578094</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2049066491463553321</t>
+          <t>2041172230642471397</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2049066491463553321</t>
+          <t>https://x.com/RakshtVaghasiya/status/2041172230642471397</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Millionaire account limited-time offer
-Increase your balance and multiply your chances to win from AED 50,000,000 in cash prizes. Boost your balance today.</t>
+          <t>@EmiratesNBD_KSA This is really frustrating from NBD. Nothing has progressed. No meaningful action yet ... Really disappointed from Emirates NBD</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1777370496000</v>
+        <v>1775488357000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2049066491463553321</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1751,7 +1747,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -1764,50 +1760,54 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>55640</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2038628104541774071</t>
+        </is>
+      </c>
       <c r="P19" s="2" t="n">
-        <v>46140.58444444444</v>
+        <v>46118.80042824074</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2051396418695578094</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2051396418695578094</t>
+          <t>2041173077455667467</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2041173077455667467</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE On which date of the month is the draw held?</t>
+          <t>@RakshtVaghasiya Hello, a follow-up on your request has been sent, and you will be contacted as soon as possible.</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1777925993000</v>
+        <v>1775488559000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2049066491463553321</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1817,11 +1817,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Muhammad Usman', 'screenName': 'Muhamma38929354', 'followersCount': 751, 'favouritesCount': 43872, 'friendsCount': 2153, 'description': 'The greatest good is positive thinking,     The greatest shame is negative thinking'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1834,51 +1834,50 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>106</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2049066491463553321</t>
+          <t>2041172230642471397</t>
         </is>
       </c>
       <c r="P20" s="2" t="n">
-        <v>46147.01380787037</v>
+        <v>46118.80276620371</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/Muhamma38929354/status/2051396418695578094</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2051396418695578094</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2051497841378414637</t>
+          <t>2046954276312777137</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051497841378414637</t>
+          <t>https://x.com/RakshtVaghasiya/status/2046954276312777137</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>@Muhamma38929354 Thanks for interest in our products, please visit the below link to check the details 
-https://t.co/ywrne3Fcg2</t>
+          <t>@EmiratesNBD_KSA Still no one contacted me.</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1777950175000</v>
+        <v>1776866904000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2049066491463553321</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1888,11 +1887,11 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -1905,50 +1904,50 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>49</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2051396418695578094</t>
+          <t>2041173077455667467</t>
         </is>
       </c>
       <c r="P21" s="2" t="n">
-        <v>46147.29369212963</v>
+        <v>46134.75583333334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2051370896619974704</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2046956528205259220</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2050086851621593314</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2046956528205259220</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE hello team need your assistance please dm.</t>
+          <t>@RakshtVaghasiya Hello Rakshit, thanks for writing to us please note that a follow-up request has been sent, and you will be contacted as soon as possible.</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1777613768000</v>
+        <v>1776867441000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1958,7 +1957,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J22" t="n">
@@ -1975,46 +1974,50 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2046954276312777137</t>
+        </is>
+      </c>
       <c r="P22" s="2" t="n">
-        <v>46143.40009259259</v>
+        <v>46134.76204861111</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2051370896619974704</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2050093026182131824</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050093026182131824</t>
+          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>@patilabhijeet45 Hello Abhijeet, Thanks for reaching us. We have sent you direct message already. Thanks- Zubair</t>
+          <t>@EmiratesNBD_KSA Same reply every time but no concrete solutions. Just a pathetic approach..</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1777615240000</v>
+        <v>1777050832000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2024,7 +2027,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -2037,54 +2040,54 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>64</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2046956528205259220</t>
         </is>
       </c>
       <c r="P23" s="2" t="n">
-        <v>46143.41712962963</v>
+        <v>46136.88462962963</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2051370896619974704</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2050222500295123129</t>
+          <t>2047728007276544227</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2050222500295123129</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2047728007276544227</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Thank you , I just replied you in dm</t>
+          <t>@RakshtVaghasiya Thanks for writing to us, we have already escalated the matter and our team will contact you as soon as possible.</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1777646110000</v>
+        <v>1777051376000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2094,7 +2097,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2111,50 +2114,50 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>76</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2050093026182131824</t>
+          <t>2047725724354633861</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46143.77442129629</v>
+        <v>46136.89092592592</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2051370896619974704</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2050275958674932182</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2050275958674932182</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@patilabhijeet45 We are so sorry to hear you had an unpleasant experience, please share with us your concern from your registered email address for further communication to social@emiratesnbd.com and tag the case reference number #1005869 in the subject line.</t>
+          <t>@EmiratesNBD_KSA Same reply every time. No action yet.</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1777658855000</v>
+        <v>1778168267000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2164,7 +2167,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2181,50 +2184,50 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2050222500295123129</t>
+          <t>2047728007276544227</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46143.92193287037</v>
+        <v>46149.81790509259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2051370896619974704</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2051149273409143066</t>
+          <t>2052432883583721554</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051149273409143066</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052432883583721554</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I have sent an email.</t>
+          <t>@RakshtVaghasiya Hello Rakshit, we apologize for any delay, we have sent a follow-up to the team and we will update you shortly.</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1777867069000</v>
+        <v>1778173106000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2032450113100984492</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2234,11 +2237,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2251,50 +2254,52 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2050275958674932182</t>
+          <t>2052412587602530439</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46146.33181712963</v>
+        <v>46149.87391203704</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/illliyas/status/2052424796726850019</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2051370896619974704</t>
+          <t>2052424796726850019</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2051153017571840501</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051153017571840501</t>
+          <t>https://x.com/illliyas/status/2052299293927805107</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>@patilabhijeet45 Thanks for sharing, our team will check it and update you accordingly</t>
+          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
+“For security reasons this app cannot be used with VoiceOver enabled.”
+I disabled all accessibility services, but the issue still persists.</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1777867962000</v>
+        <v>1778141256000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2304,11 +2309,11 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Illiyas Mohammed', 'screenName': 'illliyas', 'followersCount': 89, 'favouritesCount': 73, 'friendsCount': 259, 'description': 'Software Engineer'}</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -2317,54 +2322,50 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2051149273409143066</t>
-        </is>
-      </c>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>46146.34215277778</v>
+        <v>46149.50527777777</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/illliyas/status/2052424796726850019</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2051370896619974704</t>
+          <t>2052424796726850019</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2051370896619974704</t>
+          <t>2052300575308402847</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2051370896619974704</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052300575308402847</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Dear @EmiratesNBD_AE  thank you very much for your assistance, really appreciate 🙏.</t>
+          <t>@illliyas Please mention in the email subject social media case #1009168. Thanks- Zubair</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1777919909000</v>
+        <v>1778141561000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2050086851621593314</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2374,11 +2375,11 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 120, 'favouritesCount': 14751, 'friendsCount': 265, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>0</v>
@@ -2391,62 +2392,60 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2051153017571840501</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46146.94339120371</v>
+        <v>46149.50880787037</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051364056217374823</t>
+          <t>https://x.com/illliyas/status/2052424796726850019</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2051364056217374823</t>
+          <t>2052424796726850019</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2051302125989236884</t>
+          <t>2052302615791505912</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2051302125989236884</t>
+          <t>https://x.com/illliyas/status/2052302615791505912</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>لا تشيل هم الفاتورة 🤩
-مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
-للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
+          <t>@EmiratesNBD_AE Sent email.</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1777903512000</v>
+        <v>1778142048000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2051302125989236884</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2051302098415812608/pu/img/kiycv3whSbLg1NL6.jpg', 'type': 'video', 'id': '2051302098415812608'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17444, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Illiyas Mohammed', 'screenName': 'illliyas', 'followersCount': 89, 'favouritesCount': 73, 'friendsCount': 259, 'description': 'Software Engineer'}</t>
         </is>
       </c>
       <c r="J29" t="n">
@@ -2463,46 +2462,50 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2052300575308402847</t>
+        </is>
+      </c>
       <c r="P29" s="2" t="n">
-        <v>46146.75361111111</v>
+        <v>46149.51444444444</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051364056217374823</t>
+          <t>https://x.com/illliyas/status/2052424796726850019</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2051364056217374823</t>
+          <t>2052424796726850019</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2051355715994878347</t>
+          <t>2052303504341893169</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051355715994878347</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052303504341893169</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA متى بتدعمون سامسونج باي؟؟</t>
+          <t>@illliyas Our team will review and will reply you as soon as possible.</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1777916289000</v>
+        <v>1778142260000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2051302125989236884</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2512,7 +2515,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'H', 'screenName': 'hisho25', 'followersCount': 41, 'favouritesCount': 7770, 'friendsCount': 277, 'description': 'لا إله إلا الله محمد رسول الله\n------\nمهتم بالتقنية و بالالعاب و الاخبار التقنية و مهتم ايضا بالـ PC و الكونسل و الهواتف'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2529,50 +2532,50 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>18</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2051302125989236884</t>
+          <t>2052302615791505912</t>
         </is>
       </c>
       <c r="P30" s="2" t="n">
-        <v>46146.90149305556</v>
+        <v>46149.51689814815</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051364056217374823</t>
+          <t>https://x.com/illliyas/status/2052424796726850019</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2051364056217374823</t>
+          <t>2052424796726850019</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2051363915762708887</t>
+          <t>2052424796726850019</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2051363915762708887</t>
+          <t>https://x.com/illliyas/status/2052424796726850019</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>@hisho25 مرحبا, تم الرد على الخاص.</t>
+          <t>@EmiratesNBD_AE Still waiting for the solution. Not happy with the service.</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1777918244000</v>
+        <v>1778171178000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2051302125989236884</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2582,7 +2585,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17444, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Illiyas Mohammed', 'screenName': 'illliyas', 'followersCount': 89, 'favouritesCount': 73, 'friendsCount': 259, 'description': 'Software Engineer'}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2604,45 +2607,45 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2051355715994878347</t>
+          <t>2052303504341893169</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46146.92412037037</v>
+        <v>46149.85159722222</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051364056217374823</t>
+          <t>https://x.com/illliyas/status/2052424796726850019</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2051364056217374823</t>
+          <t>2052424796726850019</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2051364056217374823</t>
+          <t>2052430161430167778</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051364056217374823</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052430161430167778</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA ماجاني شي على الخاص</t>
+          <t>@illliyas Hello, we will reply to your email as soon as possible.</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1777918278000</v>
+        <v>1778172457000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2051302125989236884</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2652,11 +2655,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'H', 'screenName': 'hisho25', 'followersCount': 41, 'favouritesCount': 7770, 'friendsCount': 277, 'description': 'لا إله إلا الله محمد رسول الله\n------\nمهتم بالتقنية و بالالعاب و الاخبار التقنية و مهتم ايضا بالـ PC و الكونسل و الهواتف'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2669,60 +2672,64 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2051363915762708887</t>
+          <t>2052424796726850019</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46146.92451388889</v>
+        <v>46149.86640046296</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051364056217374823</t>
+          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2051364056217374823</t>
+          <t>2052336714459250884</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2051365950771871780</t>
+          <t>2052336714459250884</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2051365950771871780</t>
+          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>@hisho25 مرحبا, تم ارسال الرسالة مرة اخرى.</t>
+          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
+https://t.co/LRj8F5RmtL | التفاصيل 
+@EmiratesNBD_AE
+#fintech_gate
+#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات https://t.co/EdyBD9bZgW</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1777918729000</v>
+        <v>1778150177000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2051302125989236884</t>
+          <t>2052336714459250884</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtdXZCXAAQDiv8.jpg', 'type': 'photo', 'id': '2052336711636549636'}]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17444, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 522, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
         </is>
       </c>
       <c r="J33" t="n">
@@ -2739,126 +2746,130 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2051364056217374823</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>46146.9297337963</v>
+        <v>46149.60853009259</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/RedHat/status/2051310789596754286</t>
+          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2051310789596754286</t>
+          <t>2052336714459250884</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2051309036713205764</t>
+          <t>2052471373839184311</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/RedHat/status/2051309036713205764</t>
+          <t>https://x.com/FintechGate1/status/2052471373839184311</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>The 20th annual #RHSummit Innovation Awards winners show how open technology drives significant impact. Now it's your turn to weigh in: read the blog and vote for your favorite story for Innovator of the Year. https://t.co/fSmY2mFJdm ⬇️ #RHSummit https://t.co/dhsoHd3xYR</t>
+          <t>«محمد بن زايد» و«السيسي» يتفقدان مفرزة المقاتلات المصرية المتمركزة في الإمارات
+https://t.co/j8JzFHiHW9   | التفاصيل 
+#fintech_gate 
+#محمد_بن_زايد #السيسي #الإمارات #المقاتلات_المصرية_المتمركزة https://t.co/ptvqVJOqGm</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1777905160000</v>
+        <v>1778182283000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2051309036713205764</t>
+          <t>2052471373839184311</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2051308691555483648/img/eVa9XguAD4HhQoc1.jpg', 'type': 'video', 'id': '2051308691555483648'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvX1XqXkAEzX5w.jpg', 'type': 'photo', 'id': '2052471367082151937'}]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'Red Hat', 'screenName': 'RedHat', 'followersCount': 300058, 'favouritesCount': 7833, 'friendsCount': 1021, 'description': 'The leading provider of enterprise open source solutions, using a community-powered approach to deliver Linux, hybrid cloud, edge, and Kubernetes technologies.'}</t>
+          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 522, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>87</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" s="2" t="n">
-        <v>46146.77268518518</v>
+        <v>46149.98012731481</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/RedHat/status/2051310789596754286</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2051310789596754286</t>
+          <t>2052316568441229765</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2051310789596754286</t>
+          <t>2052316568441229765</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/RedHat/status/2051310789596754286</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026 Innovation Awards winner @EmiratesNBD_AE manages 9,000 VMs and modern containers on one unified platform -  a modern, stable platform for innovation. See how they did it: https://t.co/Z9terABaJS #RHSummit https://t.co/NaQST8Rad8</t>
+          <t>Unravel new destinations with fabulous offers
+Enjoy 60% off hotel stays and an extra 25% off globally and 30% off across the UAE when you pay with your Emirates NBD card.
+The offer is valid until 30 May 2026.
+T&amp;Cs apply.
+#UnravelwithEmiratesNBD
+#LifestylebyEmiratesNBD #Vacation #HolidaySeason2026 #SummerTrips #Summer2026</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1777905578000</v>
+        <v>1778145374000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2051309036713205764</t>
+          <t>2052316568441229765</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2051310374259990528/img/KR_kPqclpFMvMvkJ.jpg', 'type': 'video', 'id': '2051310374259990528'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtLB8gXoAAvErM.jpg', 'type': 'photo', 'id': '2052316551991238656'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtLCJSXoAI5xML.jpg', 'type': 'photo', 'id': '2052316555422179330'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtLCgQWcAUhnOl.jpg', 'type': 'photo', 'id': '2052316561587728389'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtLCxKXUAYhooF.jpg', 'type': 'photo', 'id': '2052316566126022662'}]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'Red Hat', 'screenName': 'RedHat', 'followersCount': 300058, 'favouritesCount': 7833, 'friendsCount': 1021, 'description': 'The leading provider of enterprise open source solutions, using a community-powered approach to deliver Linux, hybrid cloud, edge, and Kubernetes technologies.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J35" t="n">
@@ -2875,62 +2886,57 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>2051309036713205764</t>
-        </is>
-      </c>
+          <t>349</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" s="2" t="n">
-        <v>46146.77752314815</v>
+        <v>46149.55293981481</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/FreshGulfJob/status/2051298992416272612</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2051298992416272612</t>
+          <t>2052316568441229765</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2051298992416272612</t>
+          <t>2052303842482499725</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/FreshGulfJob/status/2051298992416272612</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052303842482499725</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Emirates NBD Job Vacancies Dubai | Latest Careers UAE (2026)
-Apply Link&amp;gt;&amp;gt; https://t.co/HeXaNRE7wi
-#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #UAEJobs #dubaijobs</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/973dnM780n https://t.co/p1wRUBSROd</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1777902765000</v>
+        <v>1778142340000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2051298992416272612</t>
+          <t>2052303842482499725</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHs_drxXQAATmIq.jpg', 'type': 'photo', 'id': '2052303834395918336'}]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'Fresh Gulf Job', 'screenName': 'FreshGulfJob', 'followersCount': 18315, 'favouritesCount': 1, 'friendsCount': 98, 'description': 'https://t.co/eKEohngXpc provides information about Jobs in All Over World, Oil and Gas Jobs, Construction Jobs, IT Jobs, Government Jobs, Bank Jobs, Jobs in UAE, etc.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2940,202 +2946,204 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>354</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" s="2" t="n">
-        <v>46146.74496527778</v>
+        <v>46149.51782407407</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/FreshGulfJob/status/2051298992416272612</t>
+          <t>https://x.com/lhyx16/status/2052375265490456666</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2051298992416272612</t>
+          <t>2052375265490456666</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2051252771790131268</t>
+          <t>2052248988380758347</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/FreshGulfJob/status/2051252771790131268</t>
+          <t>https://x.com/ProfSteveKeen/status/2052248988380758347</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ENOC Jobs in Dubai - Emirates National Oil Company Hiring Now
-Apply Link&amp;gt;&amp;gt; https://t.co/nrviL7vzo9
-#jobs #careers #jobvacancy #jobs2026 #hiring #freshgulfjob #recruitment #jobvacancy2026 #oilandgas #jobsinuae #dubaijobs</t>
+          <t>3 accounting errors that most China analysts keep making.
+One. Deficits aren't insolvency. China creates yuan. The constraint is resource allocation, not money.
+Two. Capital flight isn't collapse. It devalues the yuan to boost exports. State banks maintain investment regardless of where money goes.
+Three. Wages track GDP. Chinese wages scale with growth while American wages don't. That structural gap is the real story.
+The full conversation is in the comments.
+#SteveKeen #ChinaEconomy #MacroEconomics #PostKeynesian #EconomicDebate</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1777891745000</v>
+        <v>1778129262000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2051252771790131268</t>
+          <t>2052248988380758347</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHsNlEoWUAIKFd0.jpg', 'type': 'photo', 'id': '2052248985746690050'}]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'Fresh Gulf Job', 'screenName': 'FreshGulfJob', 'followersCount': 18315, 'favouritesCount': 1, 'friendsCount': 98, 'description': 'https://t.co/eKEohngXpc provides information about Jobs in All Over World, Oil and Gas Jobs, Construction Jobs, IT Jobs, Government Jobs, Bank Jobs, Jobs in UAE, etc.'}</t>
+          <t>{'name': 'Prof. Steve Keen', 'screenName': 'ProfSteveKeen', 'followersCount': 114373, 'favouritesCount': 72570, 'friendsCount': 1593, 'description': 'Predicted the 2008 financial crisis years early. Honorary Professor at UCL. Learn 50+ years of real economics in only 7 weeks. Apply below on my website.'}</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>468</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>25871</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" s="2" t="n">
-        <v>46146.61741898148</v>
+        <v>46149.36645833333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/InformistMedia/status/2051335593389601255</t>
+          <t>https://x.com/lhyx16/status/2052375265490456666</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2051335593389601255</t>
+          <t>2052375265490456666</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2051335593389601255</t>
+          <t>2052284969158881589</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/InformistMedia/status/2051335593389601255</t>
+          <t>https://x.com/Kathleen_Tyson_/status/2052284969158881589</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>The Securities and Exchange Board of India on Monday approved the change in control of RBL Bank with regard to the ongoing acquisition of "certain" shareholding by Emirates NBD Bank in the Indian lender, RBL Bank said in an exchange filing. The Dubai-based lender has proposed to buy up to 60% stake in the Indian private-sector bank, and the Competition Commission of India has already approved it on Jan. 20.
-#SEBI
-Details Here:
-https://t.co/2oKxA92wg7</t>
+          <t>@ProfSteveKeen Four. Chinese save about 40% of income, many as gold in bank ‘gold accumulation accounts’ that facilitate regular micro-purchases, so as incomes grow, gold buying grows, gold revalues higher. Win. Win. Win.</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1777911492000</v>
+        <v>1778137840000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2051335593389601255</t>
+          <t>2052248988380758347</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHfO2Crb0AA2-R6.jpg', 'type': 'photo', 'id': '2051335583117856768'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'Informist Media', 'screenName': 'InformistMedia', 'followersCount': 5865, 'favouritesCount': 52, 'friendsCount': 337, 'description': 'India’s trusted source for real-time financial news. Fast, accurate updates on markets, economy, policy &amp; companies — now with free-to-view content.'}</t>
+          <t>{'name': 'Kathleen Tyson', 'screenName': 'Kathleen_Tyson_', 'followersCount': 59323, 'favouritesCount': 224879, 'friendsCount': 868, 'description': 'Global liquidity plumber (triparty repo, FX &amp; optimisation), long ago central banker &amp; author Multicurrency Mercantilism: The New International Monetary Order.'}</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>457</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2052248988380758347</t>
+        </is>
+      </c>
       <c r="P38" s="2" t="n">
-        <v>46146.84597222223</v>
+        <v>46149.46574074074</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/InformistMedia/status/2051335593389601255</t>
+          <t>https://x.com/lhyx16/status/2052375265490456666</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2051335593389601255</t>
+          <t>2052375265490456666</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2051339743464706242</t>
+          <t>2052375265490456666</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/InformistMedia/status/2051339743464706242</t>
+          <t>https://x.com/lhyx16/status/2052375265490456666</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>The central government will work with the new governments of Kerala and Tamil Nadu for the development and betterment of citizens, Prime Minister #NarendraModi said on Monday. Addressing Bharatiya Janata Party workers after a landslide victory in West Bengal and ahead of a third consecutive term in Assam, Modi said his party would try to meet expectations.
-Details Here:
-https://t.co/AWT9gSXgug</t>
+          <t>@Kathleen_Tyson_ @ProfSteveKeen Emirates NBD in Dubai also has this option.</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1777912481000</v>
+        <v>1778159369000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2051339743464706242</t>
+          <t>2052248988380758347</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHfSlH_a0AQmOj6.jpg', 'type': 'photo', 'id': '2051339690532589572'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'Informist Media', 'screenName': 'InformistMedia', 'followersCount': 5865, 'favouritesCount': 52, 'friendsCount': 337, 'description': 'India’s trusted source for real-time financial news. Fast, accurate updates on markets, economy, policy &amp; companies — now with free-to-view content.'}</t>
+          <t>{'name': 'Salaam', 'screenName': 'lhyx16', 'followersCount': 60, 'favouritesCount': 9025, 'friendsCount': 193, 'description': ''}</t>
         </is>
       </c>
       <c r="J39" t="n">
@@ -3152,129 +3160,132 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2052284969158881589</t>
+        </is>
+      </c>
       <c r="P39" s="2" t="n">
-        <v>46146.85741898148</v>
+        <v>46149.71491898148</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051288211184332916</t>
+          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2051288211184332916</t>
+          <t>2052303511182811547</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2051280686007337040</t>
+          <t>2052303511182811547</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051280686007337040</t>
+          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FINALLY 🔥🔥💙
-محفظة سامسونج صارت تدعم كل المحافظ الرقمية و البنوك تقريباً و كلها تدعم اضافة البطاقة في داخل التطبيق بضغطة زر 
-Add to Samsung Wallet 👌🏼✅️
-لكن للاسف حتى الآن البنوك الرقمية و المحافظ الرقمية الى الان مايدعمون إضافة الاموال عن طريق الدفع بسامسونج باي ❌️💔 https://t.co/hqlpvr8CYN</t>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/SrP2a36Pw3 https://t.co/k8XmvOtTLs</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1777898401000</v>
+        <v>1778142261000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2051280686007337040</t>
+          <t>2052303511182811547</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHec6dVW0AAagHk.jpg', 'type': 'photo', 'id': '2051280683411099648'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHs_KjTX0AAFve-.jpg', 'type': 'photo', 'id': '2052303505705127936'}]</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'H', 'screenName': 'hisho25', 'followersCount': 41, 'favouritesCount': 7770, 'friendsCount': 277, 'description': 'لا إله إلا الله محمد رسول الله\n------\nمهتم بالتقنية و بالالعاب و الاخبار التقنية و مهتم ايضا بالـ PC و الكونسل و الهواتف'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>10492</t>
+          <t>102</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" s="2" t="n">
-        <v>46146.69445601852</v>
+        <v>46149.51690972222</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051288211184332916</t>
+          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2051288211184332916</t>
+          <t>2052303511182811547</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2051285061933150446</t>
+          <t>2052303458137489515</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/karimmohnaguib1/status/2051285061933150446</t>
+          <t>https://x.com/ENBDdeals/status/2052303458137489515</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>@hisho25 @FinTech_KSA بنك دبي الإمارات الوطني (لسة)</t>
+          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/XpFUmulYZw https://t.co/YIQNu06Kzh</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1777899444000</v>
+        <v>1778142249000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2051280686007337040</t>
+          <t>2052303458137489515</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHs_HcsW8AMUOWf.jpg', 'type': 'photo', 'id': '2052303452391272451'}]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': '𝓚𝓪𝓻𝓲𝓶', 'screenName': 'karimmohnaguib1', 'followersCount': 226, 'favouritesCount': 21392, 'friendsCount': 3310, 'description': 'حبي للتكنولوجيا وعشقي للتطوير 🤓💻 #تكنولوجيا #سامسونج #اندرويد'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3283,69 +3294,61 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>1339</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>2051280686007337040</t>
-        </is>
-      </c>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" s="2" t="n">
-        <v>46146.70652777778</v>
+        <v>46149.51677083333</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051288211184332916</t>
+          <t>https://x.com/ENBDdeals/status/2052303458137489515</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2051288211184332916</t>
+          <t>2052303458137489515</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2051288211184332916</t>
+          <t>2052303325781959087</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/hisho25/status/2051288211184332916</t>
+          <t>https://x.com/ENBDdeals/status/2052303325781959087</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>@karimmohnaguib1 @FinTech_KSA انا قلت تقريبا مب 100% و الاكثر شعبية تفعلوا الان 
-يعني باقي هذولي للاسف
-@MobilyPay 
-@visionbank_sa
-@EmiratesNBD_KSA 
-@FABConnects</t>
+          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
+https://t.co/SrP2a36Pw3 https://t.co/SZAe79aEJu</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1777900195000</v>
+        <v>1778142217000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2051280686007337040</t>
+          <t>2052303325781959087</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHs-_tkWQAQaLSr.jpg', 'type': 'photo', 'id': '2052303319482122244'}]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'H', 'screenName': 'hisho25', 'followersCount': 41, 'favouritesCount': 7770, 'friendsCount': 277, 'description': 'لا إله إلا الله محمد رسول الله\n------\nمهتم بالتقنية و بالالعاب و الاخبار التقنية و مهتم ايضا بالـ PC و الكونسل و الهواتف'}</t>
+          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -3362,50 +3365,46 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>876</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>2051285061933150446</t>
-        </is>
-      </c>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
       <c r="P42" s="2" t="n">
-        <v>46146.7152199074</v>
+        <v>46149.51640046296</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2051294193515917659</t>
+          <t>https://x.com/illliyas/status/2052299293927805107</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2051294193515917659</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2051294193515917659</t>
+          <t>2052300555599372615</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2051294193515917659</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052300555599372615</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ADIB, Emirates NBD close $164mln loan for London property https://t.co/OFhbni8HWp</t>
+          <t>@illliyas Hi Illiyas , we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1777901621000</v>
+        <v>1778141557000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2051294193515917659</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3415,7 +3414,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12531, 'favouritesCount': 443666, 'friendsCount': 8656, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3432,46 +3431,51 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2052299293927805107</t>
+        </is>
+      </c>
       <c r="P43" s="2" t="n">
-        <v>46146.73172453704</v>
+        <v>46149.50876157408</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2051294193515917659</t>
+          <t>https://x.com/illliyas/status/2052299293927805107</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2051294193515917659</t>
+          <t>2052299293927805107</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2051426970584396266</t>
+          <t>2051598903083213064</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/deegrose/status/2051426970584396266</t>
+          <t>https://x.com/illliyas/status/2051598903083213064</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Why the UAE’s OPEC exit matters for oil markets https://t.co/RihV7AWeh9</t>
+          <t>NoBroker is a scam. Paid ₹10,000 for the NRI Super Relax plan, and got a sleepy relationship manager who doesn’t even bother calling interested tenants. But somehow, they have all the energy to keep calling me to upgrade to a higher plan.
+@NoBrokerCom @NoBrokerCare</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1777933278000</v>
+        <v>1777974270000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2051426970584396266</t>
+          <t>2051598903083213064</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3481,206 +3485,202 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'DeeG (Maria)', 'screenName': 'deegrose', 'followersCount': 12531, 'favouritesCount': 443666, 'friendsCount': 8656, 'description': ''}</t>
+          <t>{'name': 'Illiyas Mohammed', 'screenName': 'illliyas', 'followersCount': 89, 'favouritesCount': 73, 'friendsCount': 259, 'description': 'Software Engineer'}</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>87</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" s="2" t="n">
-        <v>46147.098125</v>
+        <v>46147.57256944444</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051171796552937744</t>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2051171796552937744</t>
+          <t>2052293602643148891</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2051171796552937744</t>
+          <t>2052057840244646114</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051171796552937744</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052057840244646114</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Turn your everyday spending into Emirates Skywards Miles with the Emirates NBD Skywards Infinite Credit Card. Enjoy complimentary airport lounge access, valet parking, golf privileges, and more.
-Apply Now and get up to 100,000 bonus Skyward Miles!
-Terms and Conditions Apply!
-Apply Now: https://t.co/TKre1mTLQs</t>
+          <t>Supporting Dubai Culture &amp; Arts Authority in strengthening fraud awareness across their teams.
+By building knowledge and vigilance, we’re helping protect what matters and empowering people to stay alert in a fast-changing digital world.
+#FraudAwareness #FinancialSafety #UnitedAgainstFraud</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1777872439000</v>
+        <v>1778083689000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2051171796552937744</t>
+          <t>2052057840244646114</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2051171759827640320/img/sEz-wHtA8YfMnjRE.jpg', 'type': 'video', 'id': '2051171759827640320'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2052057793599856657/img/uFYYXnfG8i7PvyMn.jpg', 'type': 'video', 'id': '2052057793599856657'}]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>658</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" s="2" t="n">
-        <v>46146.39396990741</v>
+        <v>46148.83899305556</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051171796552937744</t>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2051171796552937744</t>
+          <t>2052293602643148891</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2051265534797181311</t>
+          <t>2052132248523288581</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2051265534797181311</t>
+          <t>https://x.com/hamad5uae/status/2052132248523288581</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Why wait for a payout date?
-Deposit now and get your interest instantly with the new Instant Interest Fixed Deposit
-With Instant Interest Fixed Deposit, you can: 
-•Earn your interest on day 1
-•Choose your preferred Account for
-interest payouts
-•Deposit in AED or USD
-•Enjoy flexible tenure from 3 months to one year
-Know more: https://t.co/wmp1pnFPIc</t>
+          <t>@EmiratesNBD_AE وين الخصوصية اصبحت بلا خصوصية و تكلمت بمشاكل في التطبيق مع امكانية الوصول قبل بضع ايام و اعتقد الحل الوحيد اغلق الحساب و اترك القسم الجاهل في جهله</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1777894788000</v>
+        <v>1778101429000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2051265534797181311</t>
+          <t>2052057840244646114</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHePIetXoAAsHz0.jpg', 'type': 'video', 'id': '2051265487711895553'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174659, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>226304</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2052057840244646114</t>
+        </is>
+      </c>
       <c r="P46" s="2" t="n">
-        <v>46146.65263888889</v>
+        <v>46149.04431712963</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni/status/2051337981815140447</t>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2051337981815140447</t>
+          <t>2052293602643148891</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2050424878524940571</t>
+          <t>2052239541616906712</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni/status/2050424878524940571</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052239541616906712</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>@EmiratesIslamic You claim an AED 22k theft is "secure" just because it’s Apple Wallet? Your system failed to see that a UAE "Darb" enrollment turned into a massive London spending spree. I reported it at the exact minute it happened. This is a failure of your fraud monitoring.</t>
+          <t>@hamad5uae مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل إلى 
+social@EmiratesNBD.com</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1777694360000</v>
+        <v>1778127010000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2050424878524940571</t>
+          <t>2052057840244646114</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3690,11 +3690,11 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'prakash soni', 'screenName': 'praksoni', 'followersCount': 9, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -3707,46 +3707,50 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2052132248523288581</t>
+        </is>
+      </c>
       <c r="P47" s="2" t="n">
-        <v>46144.33287037037</v>
+        <v>46149.34039351852</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni/status/2051337981815140447</t>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2051337981815140447</t>
+          <t>2052293602643148891</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2051173237304734081</t>
+          <t>2052264638478475341</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051173237304734081</t>
+          <t>https://x.com/hamad5uae/status/2052264638478475341</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>@praksoni Dear customer, we have tried to reach you through the direct Message, unfortunately we were not successful due to the direct message (Not Following our page). Please DM us back in order to assist you better.</t>
+          <t>@EmiratesNBD_AE الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1777872783000</v>
+        <v>1778132993000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2050424878524940571</t>
+          <t>2052057840244646114</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3756,11 +3760,11 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -3773,50 +3777,50 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2050424878524940571</t>
+          <t>2052239541616906712</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>46146.39795138889</v>
+        <v>46149.4096412037</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni/status/2051337981815140447</t>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2051337981815140447</t>
+          <t>2052293602643148891</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2051337981815140447</t>
+          <t>2052281866342789437</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/praksoni/status/2051337981815140447</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052281866342789437</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>@emiratesislamic I did not get any message. Following your page.</t>
+          <t>@hamad5uae سنبذل قصارى جهدنا لمعالجة الأمر في أسرع وقت ممكن وتقديم الدعم اللازم.</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1777912061000</v>
+        <v>1778137101000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2050424878524940571</t>
+          <t>2052057840244646114</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3826,11 +3830,11 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'prakash soni', 'screenName': 'praksoni', 'followersCount': 9, 'favouritesCount': 0, 'friendsCount': 23, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3843,60 +3847,60 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2051173237304734081</t>
+          <t>2052264638478475341</t>
         </is>
       </c>
       <c r="P49" s="2" t="n">
-        <v>46146.85255787037</v>
+        <v>46149.4571875</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2051285723785871469</t>
+          <t>2052293602643148891</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2051285716965986342</t>
+          <t>2052293602643148891</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285716965986342</t>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>خدمات مصرفية تقدر قيمة أعمالك. مع الحساب الماسي للأعمال من الإمارات الإسلامي، تستفيد من مدير علاقة ومستشار للتجارة والصرف الأجنبي، وأسعار تفضيلية على المنتجات المصرفية، وبطاقة فيزا سيغنتشر معدنية بحدود سحب ومشتريات أعلى، https://t.co/XkC8ED0e6C</t>
+          <t>@EmiratesNBD_AE غير صحيح لو انتو بتبذلون جهودكم كان اطلقتو اصدار يعالج الاشكال فورا الموضوع عندكم من امس اصبح</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1777899600000</v>
+        <v>1778139899000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2051285716965986342</t>
+          <t>2052057840244646114</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdGISHWAAEPXm-.jpg', 'type': 'photo', 'id': '2051185263406088193'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3909,52 +3913,54 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2052281866342789437</t>
+        </is>
+      </c>
       <c r="P50" s="2" t="n">
-        <v>46146.70833333334</v>
+        <v>46149.48957175926</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
+          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2051285723785871469</t>
+          <t>2052293602643148891</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2051285720577269980</t>
+          <t>2052295354821886462</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285720577269980</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052295354821886462</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>إضافة إلى مزايا نمط حياة مثل دخول صالات المطارات وخصومات عالمية على تأجير السيارات.
-لمعرفة المزيد:
-https://t.co/mVDWeikQTM</t>
+          <t>@hamad5uae يرجى العلم بأن فريقنا سيرد على بريدك الإلكتروني في أقرب وقت ممكن. شكرًا لك.</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1777899601000</v>
+        <v>1778140317000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2051285716965986342</t>
+          <t>2052057840244646114</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3964,11 +3970,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3981,64 +3987,63 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2051285716965986342</t>
+          <t>2052293602643148891</t>
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>46146.70834490741</v>
+        <v>46149.49440972223</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
+          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2051285723785871469</t>
+          <t>2052427177216315673</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2051285723785871469</t>
+          <t>2052427177216315673</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Banking that recognizes the value of your business. With Emirates Islamic Business Banking Diamond Account, enjoy a dedicated relationship manager and Trade &amp;amp; FX advisor, preferential pricing on products, https://t.co/ABnbdvENub</t>
-        </is>
+          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
+        </is>
+      </c>
+      <c r="E52">
+        <f>==&amp;gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand https://t.co/Ys0jEe4GlM</f>
+        <v/>
       </c>
       <c r="F52" t="n">
-        <v>1777899602000</v>
+        <v>1778171745000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2051285716965986342</t>
+          <t>2052427177216315673</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdGIg5XoAAWmlu.jpg', 'type': 'photo', 'id': '2051185267374006272'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1131, 'favouritesCount': 24509, 'friendsCount': 306, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -4051,52 +4056,46 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2051285720577269980</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" s="2" t="n">
-        <v>46146.70835648148</v>
+        <v>46149.85815972222</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285723785871469</t>
+          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2051285723785871469</t>
+          <t>2052427177216315673</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2051285726361227464</t>
+          <t>2052602789923074494</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051285726361227464</t>
+          <t>https://x.com/gold_hadas/status/2052602789923074494</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>a metal Visa Signature Debit Card with higher withdrawal and POS limits, as well as lifestyle benefits such as airport lounge access and global car rental discounts.
-Learn more:
-https://t.co/J0ZWQGZcId</t>
+          <t>Dachau was created for Hitler’s political opponents and enemies. During the Second World War, people whom the Nazis didn’t even think of re-educating were sent there —most of the prisoners were Christians: Protestants, Catholics, and Orthodox. https://t.co/M1Ohe3opmd</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1777899602000</v>
+        <v>1778213615000</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2051285716965986342</t>
+          <t>2052602789923074494</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4106,7 +4105,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1131, 'favouritesCount': 24509, 'friendsCount': 306, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
         </is>
       </c>
       <c r="J53" t="n">
@@ -4123,62 +4122,58 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>2051285723785871469</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
       <c r="P53" s="2" t="n">
-        <v>46146.70835648148</v>
+        <v>46150.34276620371</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051255518270779594</t>
+          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2051255518270779594</t>
+          <t>2052401437611630695</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2051255518270779594</t>
+          <t>2052401437611630695</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051255518270779594</t>
+          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Track your Digital Wealth portfolio on a real-time basis and close a trade instantly through the EI + Mobile Banking App.
-Download the EI + Mobile Banking App today. #EmiratesIslamic
-https://t.co/H1RLoPe6Zu https://t.co/5h5iHPAmUn</t>
+          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
+The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
+#UAE #IslamicBanking #Finance #Investment #Banking</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1777892400000</v>
+        <v>1778165609000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2051255518270779594</t>
+          <t>2052401437611630695</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2051212444874297344/pu/img/sHPu-aR8u5aX_oaG.jpg', 'type': 'video', 'id': '2051212444874297344'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHuYOTMWEAYd8TS.jpg', 'type': 'photo', 'id': '2052401426635034630'}]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Economy Middle East', 'screenName': 'Economy_ME', 'followersCount': 4543, 'favouritesCount': 217, 'friendsCount': 12, 'description': 'Economy Middle East Summit 2026\nThe Economy of Tomorrow: The UAE Emerges Stronger 🇦🇪\n📅 May 21, 2026\n📍 Rosewood, Abu Dhabi\nRegister now ⬇️'}</t>
         </is>
       </c>
       <c r="J54" t="n">
@@ -4188,65 +4183,65 @@
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
         <v>1</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>54</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
       <c r="P54" s="2" t="n">
-        <v>46146.625</v>
+        <v>46149.78714120371</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051255518270779594</t>
+          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2051255518270779594</t>
+          <t>2052401437611630695</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2051210219850489871</t>
+          <t>2052413839942008900</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051210219850489871</t>
+          <t>https://x.com/Economy_ME/status/2052413839942008900</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
-🎟️ما يصل إلى قسيمتي خصم بنسبة %60 من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
-🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/IpubVOi9WK</t>
+          <t>Dubai’s ready villa segment continues strengthening its position as one of the market’s most competitive categories.
+Strong search recovery, sustained demand and active buyer engagement are reinforcing villas as a preferred option for both end users and investors.
+#Dubai #RealEstate #UAE #Property #Investing</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1777881600000</v>
+        <v>1778168566000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2051210219850489871</t>
+          <t>2052413839942008900</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdI4bpW0AAzk8W.jpg', 'type': 'photo', 'id': '2051188289621643264'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2052413614481375243/img/YQhI6H014LqnJy5C.jpg', 'type': 'video', 'id': '2052413614481375243'}]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Economy Middle East', 'screenName': 'Economy_ME', 'followersCount': 4543, 'favouritesCount': 217, 'friendsCount': 12, 'description': 'Economy Middle East Summit 2026\nThe Economy of Tomorrow: The UAE Emerges Stronger 🇦🇪\n📅 May 21, 2026\n📍 Rosewood, Abu Dhabi\nRegister now ⬇️'}</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -4256,64 +4251,65 @@
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>196</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
       <c r="P55" s="2" t="n">
-        <v>46146.5</v>
+        <v>46149.82136574074</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2051180030810632404</t>
+          <t>2052297392632803551</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2051180020534546693</t>
+          <t>2052297385615708568</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051180020534546693</t>
+          <t>https://x.com/emiratesislamic/status/2052297385615708568</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>استمتع بقيادة سيارة أحلامك عند الحصول على تمويل السيارات من الإمارات الإسلامي
-📊 معدلات ربح مميزة ابتداءً من %1.89 ثابتة سنوياً (ما يعادل %3.61 كمعدل ربح متناقص سنوياً) https://t.co/MkXMIn08uG</t>
+          <t>احصل على بطاقة ضيف الاتحاد واستمتع بمكافأة تصل إلى 100,000 ميل من أميال ضيف الاتحاد✈️ بالإضافة إلى مزايا حصرية:
+🎟️ما يصل إلى قسيمتي خصم بنسبة 60% من أميال ضيف الاتحاد، لحجوزات الطيران وترقية فئة الرحلة
+🚀 الترقية السريعة إلى الفئة الذهبية في برنامج ضيف الاتحاد https://t.co/2wdCXgMsmt</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1777874400000</v>
+        <v>1778140801000</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2051180020534546693</t>
+          <t>2052297385615708568</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHadNzTWQAAUjIJ.jpg', 'type': 'photo', 'id': '2050999540749058048'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscfXMXIAQVY3l.jpg', 'type': 'photo', 'id': '2052265380324777988'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscfkyW0AICOO1.jpg', 'type': 'photo', 'id': '2052265383973801986'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscfySXkAI31gD.jpg', 'type': 'photo', 'id': '2052265387597729794'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscgC3W0AMMGUj.jpg', 'type': 'photo', 'id': '2052265392047837187'}]</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -4326,417 +4322,411 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>146</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
       <c r="P56" s="2" t="n">
-        <v>46146.41666666666</v>
+        <v>46149.50001157408</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
+          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2051180030810632404</t>
+          <t>2052297392632803551</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2051180024997220725</t>
+          <t>2052297388321104214</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051180024997220725</t>
+          <t>https://x.com/emiratesislamic/status/2052297388321104214</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
-        <is>
-          <t>💳 برنامج الدفع الميسر %0 على مشتريات بطاقة الإمارات الإسلامي الائتمانية لدى وكلاء السيارات
-📅يسري لغاية 31 مايو 2026.
-تطبق الشروط والأحكام.</t>
-        </is>
-      </c>
-      <c r="F57" t="n">
-        <v>1777874401000</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>2051180020534546693</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>1</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2051180020534546693</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="n">
-        <v>46146.41667824074</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2051180030810632404</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>2051180027576750215</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051180027576750215</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Drive home your dream car with Emirates Islamic Auto Finance!
-📊 Attractive profit rates starting from 1.89% flat p.a. (equivalent to 3.61% reducing profit rate p.a.) https://t.co/qqwuS90F3U</t>
-        </is>
-      </c>
-      <c r="F58" t="n">
-        <v>1777874402000</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>2051180020534546693</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHadODvXQAAw5bH.jpg', 'type': 'photo', 'id': '2050999545161531392'}]</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2051180024997220725</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="n">
-        <v>46146.41668981482</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2051180030810632404</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>2051180030810632404</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051180030810632404</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>💳 0% Easy Payment Plan on Emirates Islamic Credit Card spends at select auto dealerships
-📅Offer valid till 31 May 2026.
-Terms &amp;amp; Conditions apply.</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>1777874403000</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>2051180020534546693</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2051180027576750215</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="n">
-        <v>46146.41670138889</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2051210226183905695</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>2051210223440871854</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051210223440871854</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
         <is>
           <t>🚗 التوصيل من وإلى المطار وخدمات الاستقبال والترحيب
 ⛳جولات الغولف
 🅿️خدمة صف السيارات والمزيد
-يسري العرض لغاية 31 مايو 2026
+يسري العرض لغاية 31 مايو2026
 تطبق الشروط والأحكام
-https://t.co/pVA5yvt1qT</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>1777881601000</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2051210219850489871</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
+https://t.co/pVA5yvt1qT https://t.co/ceXzBmPnkN</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>1778140801000</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2052297385615708568</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscgPdXYAMii81.jpg', 'type': 'photo', 'id': '2052265395428483075'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscgbfXQAAEsEm.jpg', 'type': 'photo', 'id': '2052265398658088960'}]</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
         <v>1</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2051210219850489871</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>46146.50001157408</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2051210226183905695</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>2051210226183905695</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️ and amazing rewards:
-🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flights booking and upgrades
-🚀 Fast-track upgrade to Etihad Guest Gold Tier status https://t.co/0SWmjSoGbc</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>1777881602000</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>2051210219850489871</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHdI4mUWUAAB15O.jpg', 'type': 'photo', 'id': '2051188292486320128'}]</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2052297385615708568</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>46149.50001157408</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2052297392632803551</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2052297392632803551</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️and amazing rewards:
+🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flight bookings and upgrades
+🚀 Fast-track upgrade to Etihad Guest Gold Tier status https://t.co/mDtxfkEthD</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1778140802000</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2052297385615708568</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscgnxXsAEdaoe.jpg', 'type': 'photo', 'id': '2052265401954840577'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscg1KX0AcUU9F.jpg', 'type': 'photo', 'id': '2052265405549367303'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHschDXW0AIssmP.jpg', 'type': 'photo', 'id': '2052265409361924098'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHschRgXEAIXIRT.jpg', 'type': 'photo', 'id': '2052265413157785602'}]</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
         <v>1</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2051210223440871854</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>46146.50002314815</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051210226183905695</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2051210226183905695</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>2051210228520063073</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051210228520063073</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2052297388321104214</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>46149.50002314815</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2052297392632803551</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2052297395296243819</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052297395296243819</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>🚗 Complimentary airport transfers, meet &amp;amp; greet services
 ⛳ Golf rounds at select premium courses
 🅿️ Valet parking, and much more
 Valid till 31 May 2026
 Terms and conditions apply
-https://t.co/oszNDRRljr</t>
+https://t.co/oszNDRRljr https://t.co/ztim5MGGB4</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>1778140803000</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2052297385615708568</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHschi8XkAMonf-.jpg', 'type': 'photo', 'id': '2052265417838661635'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHschv5WMAUB46E.jpg', 'type': 'photo', 'id': '2052265421315649541'}]</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2052297392632803551</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>46149.50003472222</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://x.com/6trr_/status/2052299567262241168</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2052299567262241168</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2051980293121216835</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2051980293121216835</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>يمكنك الآن الاستمتاع بمعدل ربح متوقع %5 سنوياً على مدخراتك مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. ما عليك سوى اتباع الخطوات التالية:
+⭐ افتح حساب التوفير الإلكتروني من الإمارات الإسلامي
+💸 أضف 50,000 درهم وما فوق إلى حساب التوفير الإلكتروني https://t.co/p6de003ec6</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>1778065200000</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2051980293121216835</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoBmKQXIAY2C9I.jpg', 'type': 'photo', 'id': '2051954335320317958'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoBmUjXkAEXtu0.jpg', 'type': 'photo', 'id': '2051954338084392961'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoBmelX0AITvUp.jpg', 'type': 'photo', 'id': '2051954340777152514'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoBmmOXoAEiHbf.jpg', 'type': 'photo', 'id': '2051954342828154881'}]</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" s="2" t="n">
+        <v>46148.625</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://x.com/6trr_/status/2052299567262241168</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2052299567262241168</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2052299567262241168</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://x.com/6trr_/status/2052299567262241168</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>@emiratesislamic بنك تعامله غير مرضي ويتم احتساب رسوم من غير اشعار مباشر للعميل او رساله نصيه ، يتم احتساب رسوم في بطاقات الكريديت كارد. للعلم</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>1778141321000</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2051980293121216835</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'name': 'ع ❥', 'screenName': '6trr_', 'followersCount': 737, 'favouritesCount': 3868, 'friendsCount': 122, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2051980293121216835</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="n">
+        <v>46149.50603009259</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://x.com/6trr_/status/2052299567262241168</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2052299567262241168</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2052313830538059926</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052313830538059926</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>@6trr_ مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1777881602000</v>
+        <v>1778144722000</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2051210219850489871</t>
+          <t>2051980293121216835</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4746,7 +4736,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -4763,64 +4753,65 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2051210226183905695</t>
+          <t>2052299567262241168</t>
         </is>
       </c>
       <c r="P62" s="2" t="n">
-        <v>46146.50002314815</v>
+        <v>46149.54539351852</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+          <t>https://x.com/thekimanikamau/status/2052232251371581529</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2051193239932174341</t>
+          <t>2052232251371581529</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2049022486218715385</t>
+          <t>2052232251371581529</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://x.com/Thefatim2/status/2049022486218715385</t>
+          <t>https://x.com/thekimanikamau/status/2052232251371581529</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>@emiratesislamic اسوء بنك ، اسوء بنك ، اسوء بنك https://t.co/70CQATMqMJ</t>
+          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
+Eg @emiratesislamic</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1777360004000</v>
+        <v>1778125272000</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2049022486218715385</t>
+          <t>2052232251371581529</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HG-XFpUagAEQNCt.jpg', 'type': 'photo', 'id': '2049022478723481601'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>{'name': 'Fatima.M', 'screenName': 'Thefatim2', 'followersCount': 224, 'favouritesCount': 547, 'friendsCount': 48, 'description': '🤍'}</t>
+          <t>{'name': 'Daniel Kimani', 'screenName': 'thekimanikamau', 'followersCount': 18, 'favouritesCount': 38, 'friendsCount': 173, 'description': ''}</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -4833,118 +4824,102 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
       <c r="P63" s="2" t="n">
-        <v>46140.46300925926</v>
+        <v>46149.32027777778</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2051193239932174341</t>
+          <t>2052347842044297241</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2049060823264350309</t>
+          <t>2051965478206128614</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049060823264350309</t>
+          <t>https://x.com/emiratesislamic/status/2051965478206128614</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>@Thefatim2 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/MrOIqMpjyd</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1777369144000</v>
+        <v>1778061668000</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2049022486218715385</t>
+          <t>2051965478206128614</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoLubJWoAITTef.jpg', 'type': 'photo', 'id': '2051965472409559042'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoLul0WgAUvjWI.jpg', 'type': 'photo', 'id': '2051965475274260485'}]</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J64" t="n">
+        <v>3</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
         <v>1</v>
       </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0</v>
-      </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2049022486218715385</t>
-        </is>
-      </c>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
       <c r="P64" s="2" t="n">
-        <v>46140.5687962963</v>
+        <v>46148.58412037037</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2051193239932174341</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>2049065369416159269</t>
-        </is>
-      </c>
+          <t>2052347842044297241</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://x.com/Thefatim2/status/2049065369416159269</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>@emiratesislamic ما شفت منكم اي رضى من تحولت ل بنك الامارات الاسلامي اكبر غلطه</t>
-        </is>
-      </c>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>1777370228000</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>2049022486218715385</t>
-        </is>
-      </c>
+        <v>1778215157452</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4952,68 +4927,51 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>{'name': 'Fatima.M', 'screenName': 'Thefatim2', 'followersCount': 224, 'favouritesCount': 547, 'friendsCount': 48, 'description': '🤍'}</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>1</v>
-      </c>
-      <c r="K65" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2049060823264350309</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
       <c r="P65" s="2" t="n">
-        <v>46140.5813425926</v>
+        <v>46150.36061865741</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2051193239932174341</t>
+          <t>2052347842044297241</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2049068445883314237</t>
+          <t>2052347842044297241</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2049068445883314237</t>
+          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>@Thefatim2 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>@Asayeel171930 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1777370962000</v>
+        <v>1778152830000</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2049022486218715385</t>
+          <t>2051965478206128614</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5023,11 +4981,11 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66" t="n">
         <v>0</v>
@@ -5040,50 +4998,51 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2049065369416159269</t>
+          <t>2052328479933530423</t>
         </is>
       </c>
       <c r="P66" s="2" t="n">
-        <v>46140.58983796297</v>
+        <v>46149.63923611111</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+          <t>https://x.com/emiratesislamic/status/2052347910788890733</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2051193239932174341</t>
+          <t>2052347910788890733</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2050249666336559176</t>
+          <t>2052347910788890733</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://x.com/Thefatim2/status/2050249666336559176</t>
+          <t>https://x.com/emiratesislamic/status/2052347910788890733</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>@emiratesislamic كم يوم طاف الحين ؟</t>
+          <t>@Asayeel171930 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1777652586000</v>
+        <v>1778152847000</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2049022486218715385</t>
+          <t>2051965478206128614</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5093,11 +5052,11 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>{'name': 'Fatima.M', 'screenName': 'Thefatim2', 'followersCount': 224, 'favouritesCount': 547, 'friendsCount': 48, 'description': '🤍'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -5110,64 +5069,67 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2049068445883314237</t>
+          <t>2052329323433193561</t>
         </is>
       </c>
       <c r="P67" s="2" t="n">
-        <v>46143.849375</v>
+        <v>46149.63943287037</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2051193239932174341</t>
+          <t>2052342692424696089</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2051193239932174341</t>
+          <t>2052342683113283967</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051193239932174341</t>
+          <t>https://x.com/emiratesislamic/status/2052342683113283967</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>@Thefatim2 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
+          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
+استمتع بالمزيد من المكافآت:
+💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
+💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني https://t.co/8DI8iDNmnE</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1777877552000</v>
+        <v>1778151600000</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2049022486218715385</t>
+          <t>2052342683113283967</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-RLXwAEHdKD.jpg', 'type': 'photo', 'id': '2052283503472001025'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-bJX0Ak_mq9.jpg', 'type': 'photo', 'id': '2052283506147971081'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-j1W0AIg_GL.jpg', 'type': 'photo', 'id': '2052283508479938562'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-t5WAAAzJb7.jpg', 'type': 'photo', 'id': '2052283511181017088'}]</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -5176,67 +5138,64 @@
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>2050249666336559176</t>
-        </is>
-      </c>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr"/>
       <c r="P68" s="2" t="n">
-        <v>46146.45314814815</v>
+        <v>46149.625</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051168317407207640</t>
+          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2051168317407207640</t>
+          <t>2052342692424696089</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2050198001034092995</t>
+          <t>2052342686976200822</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://x.com/AnkitMittal1403/status/2050198001034092995</t>
+          <t>https://x.com/emiratesislamic/status/2052342686976200822</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>@emiratesislamic  @EI_Customers   I am waiting for 5 days to get the reply from you from last 5 days and attached email and I have visted the branch as well.
-Regards,
-Ankit K Mittal
-+54 702 3869 https://t.co/av2G1Lek3Q</t>
+          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
+وغير ذلك الكثير
+يسري العرض لغاية 31 مايو 2026
+تطبق الشروط والأحكام.
+https://t.co/Hgg0TFDsUE https://t.co/oOsraDJ2sv</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1777640268000</v>
+        <v>1778151601000</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2050198001034092995</t>
+          <t>2052342683113283967</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHPDrhHbwAABqGK.jpg', 'type': 'photo', 'id': '2050197407775047680'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-4kXkAcEP5i.jpg', 'type': 'photo', 'id': '2052283514045829127'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss_DGWoAQH4pW.jpg', 'type': 'photo', 'id': '2052283516872728580'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss_OdXoAA3QyP.jpg', 'type': 'photo', 'id': '2052283519922053120'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss_aXXkAIrsDs.jpg', 'type': 'photo', 'id': '2052283523118108674'}]</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>{'name': 'Ankit Mittal', 'screenName': 'AnkitMittal1403', 'followersCount': 2, 'favouritesCount': 3, 'friendsCount': 11, 'description': ''}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J69" t="n">
@@ -5253,46 +5212,53 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2052342683113283967</t>
+        </is>
+      </c>
       <c r="P69" s="2" t="n">
-        <v>46143.70680555556</v>
+        <v>46149.62501157408</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051168317407207640</t>
+          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2051168317407207640</t>
+          <t>2052342692424696089</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2051168317407207640</t>
+          <t>2052342690600165819</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051168317407207640</t>
+          <t>https://x.com/emiratesislamic/status/2052342690600165819</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>@AnkitMittal1403 To protect your privacy and ensure your security, we kindly ask that you avoid sharing your personal information and phone number on public channels. For any inquiry, please feel free to reach out to us through private chat.Thank you for your trust. We are always here to assist.</t>
+          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
+Enjoy more rewards:
+💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more
+💰 Competitive profit rates on Auto Finance &amp;amp; Home Finance</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1777871610000</v>
+        <v>1778151602000</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2050198001034092995</t>
+          <t>2052342683113283967</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5302,11 +5268,11 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18470, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
@@ -5319,16 +5285,90 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>88</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2050198001034092995</t>
+          <t>2052342686976200822</t>
         </is>
       </c>
       <c r="P70" s="2" t="n">
-        <v>46146.384375</v>
+        <v>46149.62502314815</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2052342692424696089</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2052342692424696089</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
+And much more.
+Offer valid till 31 May 2026
+Terms &amp;amp; conditions apply.
+https://t.co/1MUaqlObLd</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1778151603000</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2052342683113283967</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2052342690600165819</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="n">
+        <v>46149.62503472222</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P71"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,91 +517,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://x.com/kinsofdubai/status/2052462422221627597</t>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2052462422221627597</t>
+          <t>2052836145461887127</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2052462422221627597</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://x.com/kinsofdubai/status/2052462422221627597</t>
+          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE The app and QR code access is an issue. Lost all access to online and app banking. Kindly resolve ASAP.</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1778180149000</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2052462422221627597</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>{'name': 'Kinshuk Kulshreshtha', 'screenName': 'kinsofdubai', 'followersCount': 1582, 'favouritesCount': 766, 'friendsCount': 1531, 'description': 'Real Estate Investments Specialist.  Proud Father &amp; husband. Based in Dubai, mostly live in my head. #Realestate #dubai #Jaipur #Philippines #family'}</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="2" t="n">
-        <v>46149.95542824074</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2052480803209175369</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2052480803209175369</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
@@ -615,8 +549,75 @@
 @AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>1778184531000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2052480803209175369</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvf53hWgAUCXBk.jpg', 'type': 'photo', 'id': '2052480240446767109'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvf53jWUAcT4dG.jpg', 'type': 'photo', 'id': '2052480240455143431'}]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'name': 'سامي الحربي', 'screenName': 'samial7arbi02', 'followersCount': 276, 'favouritesCount': 688, 'friendsCount': 1366, 'description': 'العاقل إن أخطأ تأسف .. والأحمق إن أخطأ تفلسف ..'}</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>9</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>16</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>145981</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="n">
+        <v>46150.00614583334</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2052836145461887127</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2052661557209768191</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/alamair2008/status/2052661557209768191</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>@samial7arbi02 @EmiratesNBD_KSA @SAMA_GOV @ENBDdeals @anb_bank @RiyadBank @BankAlJazira @BankAlbilad @D360bank @alrajhibank @snbalahli أنا مثلك مع هالبنك سبب نزول نقاطي بسمه السبب غلط موظفه بعد شكاوي لم يتحرأ يقول الخطا مها وللاسف البنك المركزي يقف عاجز امام البنوك واضطريت اتسلف وانقل وايضا بنك الرياض مسوي استقطاع لشركة @mrnaksa واسدد بتاريخ ٢٧ كل شهر وللاسف يطلع ب@SAMAcares متاخر سبب نزول الإسكورر
+أنا المتضرر</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>1778184531000</v>
+        <v>1778227626000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -625,16 +626,16 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvf53hWgAUCXBk.jpg', 'type': 'photo', 'id': '2052480240446767109'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvf53jWUAcT4dG.jpg', 'type': 'photo', 'id': '2052480240455143431'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'name': 'سامي الحربي', 'screenName': 'samial7arbi02', 'followersCount': 276, 'favouritesCount': 688, 'friendsCount': 1367, 'description': 'العاقل إن أخطأ تأسف .. والأحمق إن أخطأ تفلسف ..'}</t>
+          <t>{'name': 'AZIZ ALGHAMDI', 'screenName': 'alamair2008', 'followersCount': 4305, 'favouritesCount': 17937, 'friendsCount': 4439, 'description': 'لا تفرض إحساسك وتركض ورى الغير حتى .. لو إنه واحشك ألف وحشه حدّك سلام ، وكيفك أن شاء الله بخير تسترك عن قولة : ترى فلان بلشه'}</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -643,52 +644,56 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>31148</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2052480803209175369</t>
+        </is>
+      </c>
       <c r="P3" s="2" t="n">
-        <v>46150.00614583334</v>
+        <v>46150.50493055556</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>2052836145461887127</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2052667887639237003</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052667887639237003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>@alamair2008 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1778229135000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2052597402272407645</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2052597402272407645</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>@samial7arbi02 @ENBDdeals @snbalahli مرحبا سامي شكرا لتواصلك معنا تم الرد عبر رسائل الخاص</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1778212330000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2052480803209175369</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -696,11 +701,11 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -713,52 +718,55 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2052661557209768191</t>
         </is>
       </c>
       <c r="P4" s="2" t="n">
-        <v>46150.32789351852</v>
+        <v>46150.52239583333</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>2052836145461887127</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2052778577695773164</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/alamair2008/status/2052778577695773164</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
+وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
+ورجعت اخذ آخر تم الرفض بان البدلات غير نظاميه 
+من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1778255526000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2052597173573886292</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>https://x.com/ENBDdeals/status/2052597173573886292</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>@samial7arbi02 @anb_bank @RiyadBank @BankAlJazira @BankAlbilad @D360bank @alrajhibank @snbalahli مرحبا سامي شكرا لتواصلك معنا تم الرد عبر رسائل الخاص</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1778212276000</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2052480803209175369</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>[]</t>
@@ -766,11 +774,11 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'AZIZ ALGHAMDI', 'screenName': 'alamair2008', 'followersCount': 4305, 'favouritesCount': 17937, 'friendsCount': 4439, 'description': 'لا تفرض إحساسك وتركض ورى الغير حتى .. لو إنه واحشك ألف وحشه حدّك سلام ، وكيفك أن شاء الله بخير تسترك عن قولة : ترى فلان بلشه'}</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -783,53 +791,52 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2052667887639237003</t>
         </is>
       </c>
       <c r="P5" s="2" t="n">
-        <v>46150.32726851852</v>
+        <v>46150.82784722222</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>2052836145461887127</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2052780459046617221</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052780459046617221</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>@alamair2008 مرحبا, نأسف لسماع أنك تواجه هذه التجربة, يرجى إرسال رقم هاتفك و رقم الهوية عبر الخاص ليمكننا مساعدتك, شكرا</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1778255974000</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2052481741772755197</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://x.com/AskRiyadBank/status/2052481741772755197</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>@samial7arbi02 @ENBDdeals @anb_bank @RiyadBank @BankAlJazira @BankAlbilad @D360bank @alrajhibank @snbalahli أهلاً وسهلا 👋
-نسعد بتواصلك معنا عبر الهاتف المجاني 8001242020 وذلك من الساعة 9 صباحاً إلى 8 مساءً بأيام العمل الرسمية للإفادة بالتفاصيل 💙</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1778184755000</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2052480803209175369</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>[]</t>
@@ -837,11 +844,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>{'name': 'اسأل بنك الرياض', 'screenName': 'AskRiyadBank', 'followersCount': 165888, 'favouritesCount': 0, 'friendsCount': 4, 'description': 'أهلاً بك في الحساب الرسمي لخدمة عملاء بنك الرياض 💙 | تابعوا @RiyadBank لآخر العروض والمنتجات. للعناية بالعملاء اتصل على 8001242225'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -854,54 +861,52 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2052778577695773164</t>
         </is>
       </c>
       <c r="P6" s="2" t="n">
-        <v>46150.00873842592</v>
+        <v>46150.8330324074</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>2052836145461887127</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2052836145461887127</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA ماعاد يفيد بعد طوي قيد بنككم من اهتمام الاغلبيه</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1778269251000</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2052484628875780240</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/BankAlbilad/status/2052484628875780240</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>@samial7arbi02 @ENBDdeals @snbalahli حياك في البلاد أستاذ سامي ، نسعد بتقديم منتجاتنا البنكية ويسعدنا زيارتك الرابط التالي لطلب المنتج وسيتم التواصل معك من قبل فريق المبيعات عبر الهاتف 
-https://t.co/ujj9vXwI2q 
-كما نسعد بتواصلك وخدمتك عبر الرقم المجاني لهاتف المبيعات 8001236666  دمتم بخير</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1778185443000</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2052480803209175369</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -909,7 +914,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>{'name': 'بنك البلاد | Bank Albilad', 'screenName': 'BankAlbilad', 'followersCount': 1046505, 'favouritesCount': 442, 'friendsCount': 3, 'description': 'مصرفية يرتاح لها البال | نسعد بخدمتكم على مدار الساعة وطوال أيام الأسبوع'}</t>
+          <t>{'name': 'AZIZ ALGHAMDI', 'screenName': 'alamair2008', 'followersCount': 4305, 'favouritesCount': 17937, 'friendsCount': 4439, 'description': 'لا تفرض إحساسك وتركض ورى الغير حتى .. لو إنه واحشك ألف وحشه حدّك سلام ، وكيفك أن شاء الله بخير تسترك عن قولة : ترى فلان بلشه'}</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -926,65 +931,64 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2052780459046617221</t>
         </is>
       </c>
       <c r="P7" s="2" t="n">
-        <v>46150.01670138889</v>
+        <v>46150.98670138889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2052796942841795039</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2052482551898411220</t>
+          <t>2050914407471849643</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://x.com/anb_care/status/2052482551898411220</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050914407471849643</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>@samial7arbi02 @ENBDdeals @snbalahli حياك الله  أ.سامي 
-أبشر ولايهمك، يمكنك التواصل معنا عبر الرسائل الخاصة ونتشرف في خدمتك  💙 https://t.co/LSIiyoGCbK</t>
+          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1778184948000</v>
+        <v>1777811073000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2050914407471849643</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHZPyC_WYAAg5zq.jpg', 'type': 'photo', 'id': '2050914401528471552'}]</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>{'name': 'anb | حياكم في البنك العربي الوطني', 'screenName': 'anb_care', 'followersCount': 79703, 'favouritesCount': 454, 'friendsCount': 4, 'description': 'نقدّم لكم تجربة مصرفية سهلة وسريعة | موجودين لمساعدتكم على مدار الساعة | تعرّفوا على جديدنا عبر @anb_bank\n\nتطبيقنـا 👈 https://t.co/hBpkptWU6g'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -997,53 +1001,46 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2052480803209175369</t>
-        </is>
-      </c>
+          <t>796</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" s="2" t="n">
-        <v>46150.01097222222</v>
+        <v>46145.68371527778</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2052796942841795039</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2052492018824138828</t>
+          <t>2051885677755679118</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://x.com/AlJaziraCare/status/2052492018824138828</t>
+          <t>https://x.com/faisalalamoudi3/status/2051885677755679118</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>@samial7arbi02 عزيزي سامي هلابك في الجزيرة
-موجودين لخدمتك تفضل بإرسال تفاصيل طلبك على الخاص لتتم افادتك  
-وشكرا لك🤎
-https://t.co/NUxJdRIqnW</t>
+          <t>@EmiratesNBD_KSA صباح الخير .. هل التطبيق فيه مشكله لديكم</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1778187205000</v>
+        <v>1778042642000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2050914407471849643</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1053,7 +1050,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>{'name': 'AlJazirabankCare', 'screenName': 'AlJaziraCare', 'followersCount': 6809, 'favouritesCount': 0, 'friendsCount': 1, 'description': 'نسعد بخدمتكم والإجابة على كافة استفساراتكم على مدار الساعة🤎\nللاطلاع على أحدث العروض زوروا حسابنا @BankAljazira\nوللتواصل من خارج المملكة 00966920006666'}</t>
+          <t>{'name': 'فيصل بن عبدالرحمن', 'screenName': 'faisalalamoudi3', 'followersCount': 4871, 'favouritesCount': 1403, 'friendsCount': 1105, 'description': "من يستمر بفعل ما اكره !' لايسالني في اي هامش وضعته ؟!! فانا لا اطيل علاقتي بمن يعكر مزاجي .. (من عشاق الملكي🇳🇬🇸🇦)"}</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1070,50 +1067,50 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>24</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2052480803209175369</t>
+          <t>2050914407471849643</t>
         </is>
       </c>
       <c r="P9" s="2" t="n">
-        <v>46150.03709490741</v>
+        <v>46148.36391203704</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/heba_hashem/status/2052461879398937044</t>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2052461879398937044</t>
+          <t>2052796942841795039</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2052461879398937044</t>
+          <t>2052796942841795039</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/heba_hashem/status/2052461879398937044</t>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I'm an ENBD customer urgently trying to reach @EmiratesNBD_AE  as I'm unable to activate my smart pass and unable to reach customer service from outside Canada. Please contact me.</t>
+          <t>@faisalalamoudi3 @EmiratesNBD_KSA الرجاء النظر في مشكلتي و استرجاع النقاط المكتبة في هذا للشهر والشهر الفائت</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1778180019000</v>
+        <v>1778259904000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2052461879398937044</t>
+          <t>2050914407471849643</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1123,11 +1120,11 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'Heba Hashem Ⓥ', 'screenName': 'heba_hashem', 'followersCount': 1479, 'favouritesCount': 13352, 'friendsCount': 2389, 'description': 'Freelance journalist in Canada/Dubai'}</t>
+          <t>{'name': 'Hadi', 'screenName': 'hadi_msn', 'followersCount': 7, 'favouritesCount': 276, 'friendsCount': 42, 'description': ''}</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -1136,51 +1133,54 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2051885677755679118</t>
+        </is>
+      </c>
       <c r="P10" s="2" t="n">
-        <v>46149.95392361111</v>
+        <v>46150.87851851852</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052796942841795039</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052805357064359950</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2032450113100984492</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052805357064359950</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 
-I raised mail to customer care regarding flight amount deduction descripancy twice but didn't hear from Emirates NBD. This is not acceptable at all. I am very much disappointed with customer care service of Emirates NBD. Zero star.</t>
+          <t>@hadi_msn مرحبا ,تم إرسال رقمك للفريق المختص و سيتم التواصل معك فى أسرع وقت, شكرا.</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1773408842000</v>
+        <v>1778261911000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2050914407471849643</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1190,11 +1190,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -1207,46 +1207,50 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>285</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2052796942841795039</t>
+        </is>
+      </c>
       <c r="P11" s="2" t="n">
-        <v>46094.73196759259</v>
+        <v>46150.90174768519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/jurian777/status/2052925380936491470</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052925380936491470</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2032452730443256247</t>
+          <t>2033502573093920894</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2032452730443256247</t>
+          <t>https://x.com/jurian777/status/2033502573093920894</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya We sincerely regret for the inconvenience To be able to assist further, we kindly request you to kindly share your registered mobile number through direct message, We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>【企業統治】「湾岸アラブ諸国企業における取締役会の役割」https://t.co/NQXuiOV7Fq</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1773409466000</v>
+        <v>1773659768000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2033502573093920894</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1256,11 +1260,11 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': '齋藤純 Jun Saito', 'screenName': 'jurian777', 'followersCount': 1325, 'favouritesCount': 10943, 'friendsCount': 575, 'description': '中東（湾岸アラブ諸国中心）の経済・企業、開発金融、企業金融、企業統治、金融システムが専門の研究者。現地報道や自身の研究についてつぶやいています。猫・酒・舞がやや多め。Researcher：Gulf Economy, Financial Development, and Corporate Governance'}</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1269,54 +1273,50 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2032450113100984492</t>
-        </is>
-      </c>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" s="2" t="n">
-        <v>46094.73918981481</v>
+        <v>46097.6362037037</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/jurian777/status/2052925380936491470</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052925380936491470</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2032457337122791694</t>
+          <t>2052925380936491470</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2032457337122791694</t>
+          <t>https://x.com/jurian777/status/2052925380936491470</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA 0561891252</t>
+          <t>【企業統治】現時点でざっと整理すると、ENBD・NBAD/FAB・UNB→ Abu Dhabi/Dubaiの国家・王族埋め込み型（Royal + State-Elite）。ADIB→ Islamic bankだが、王族色は相対的に弱く、独立取締役比率が高い。Mashreqbank→ 圧倒的なBusiness_Family dominance型。</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1773410565000</v>
+        <v>1778290526000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2033502573093920894</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1326,11 +1326,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': '齋藤純 Jun Saito', 'screenName': 'jurian777', 'followersCount': 1325, 'favouritesCount': 10943, 'friendsCount': 575, 'description': '中東（湾岸アラブ諸国中心）の経済・企業、開発金融、企業金融、企業統治、金融システムが専門の研究者。現地報道や自身の研究についてつぶやいています。猫・酒・舞がやや多め。Researcher：Gulf Economy, Financial Development, and Corporate Governance'}</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1343,60 +1343,60 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2032452730443256247</t>
+          <t>2033502573093920894</t>
         </is>
       </c>
       <c r="P13" s="2" t="n">
-        <v>46094.75190972222</v>
+        <v>46151.23293981481</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/goacm/status/2052788485925617818</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052788485925617818</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2032458133151342720</t>
+          <t>2052788481630589000</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2032458133151342720</t>
+          <t>https://x.com/goacm/status/2052788481630589000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya We have shared your details with the concerned team, and they will contact you shortly.</t>
+          <t>Chief Minister @DrPramodPSawant met Shri R. Subramaniakumar, MD &amp;amp; CEO of @rblbank , and held discussions on various aspects relating to the banking sector, economic growth, and the Bank’s contribution towards India’s financial ecosystem. https://t.co/R2xc5qKMAC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1773410754000</v>
+        <v>1778257887000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052788481630589000</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHz4PZSaQAAUBcY.jpg', 'type': 'photo', 'id': '2052788473543933952'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHz4PZaa0AYoKb_.jpg', 'type': 'photo', 'id': '2052788473577525254'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHz4PZTa0AEt9mc.jpg', 'type': 'photo', 'id': '2052788473548165121'}]</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'CMO Goa', 'screenName': 'goacm', 'followersCount': 102019, 'favouritesCount': 747, 'friendsCount': 118, 'description': "Official Twitter Account of Chief Minister @DrPramodPSawant's Office"}</t>
         </is>
       </c>
       <c r="J14" t="n">
@@ -1406,57 +1406,53 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2032457337122791694</t>
-        </is>
-      </c>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" s="2" t="n">
-        <v>46094.75409722222</v>
+        <v>46150.85517361111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/goacm/status/2052788485925617818</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052788485925617818</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2035964859116879927</t>
+          <t>2052788485925617818</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2035964859116879927</t>
+          <t>https://x.com/goacm/status/2052788485925617818</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA No one contacted yet. This is not acceptable at all from brand like Emirates NBD. Extremely disappointed.</t>
+          <t>During the meeting, the Chief Minister was apprised of the landmark FDI investment of ₹26,850 crore from Emirates NBD into RBL Bank.</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1774246823000</v>
+        <v>1778257888000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052788481630589000</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1466,7 +1462,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'CMO Goa', 'screenName': 'goacm', 'followersCount': 102019, 'favouritesCount': 747, 'friendsCount': 118, 'description': "Official Twitter Account of Chief Minister @DrPramodPSawant's Office"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1479,54 +1475,55 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>169</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2032458133151342720</t>
+          <t>2052788481630589000</t>
         </is>
       </c>
       <c r="P15" s="2" t="n">
-        <v>46104.43082175926</v>
+        <v>46150.85518518519</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/goacm/status/2052788485925617818</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052788485925617818</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2035976151764549748</t>
+          <t>2052788489721401482</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2035976151764549748</t>
+          <t>https://x.com/goacm/status/2052788489721401482</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hi Rakshit, our team tried to contact you, but there was no answer from your side, we have asked our team to contact you again as soon as possible.</t>
+          <t>The discussions also touched upon RBL Bank’s CSR initiatives, including the ‘UMEED’ cycle distribution programme supporting students’ access to education across states.
+The Chief Minister conveyed his best wishes to the team for their continued journey towards a #ViksitBharat.</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1774249515000</v>
+        <v>1778257889000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052788481630589000</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1536,11 +1533,11 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'CMO Goa', 'screenName': 'goacm', 'followersCount': 102019, 'favouritesCount': 747, 'friendsCount': 118, 'description': "Official Twitter Account of Chief Minister @DrPramodPSawant's Office"}</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1549,125 +1546,123 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2035964859116879927</t>
+          <t>2052788485925617818</t>
         </is>
       </c>
       <c r="P16" s="2" t="n">
-        <v>46104.46197916667</v>
+        <v>46150.85519675926</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/hadi_msn/status/2052794731063566348</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052794731063566348</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2038625938133471268</t>
+          <t>2051949760488050729</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2038625938133471268</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051949760488050729</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Dispute request #22407819581 was raised on 23rd March'26 and After that I received call from NBD representative &amp;amp; I explained my dispute. But after that no communication or response received from NBD.
-I am really frustrated by response from such reputed bank.</t>
+          <t>نفحصها ونعتمدها قبل نمولك 🚙
+انطلق بثقة مع تمويل السيارات المستعملة من #بنك_الإمارات_دبي_الوطني 💙
+للتفاصيل:https://t.co/CXCUIwu26x https://t.co/5sMib0U399</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1774881274000</v>
+        <v>1778057920000</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2051949760488050729</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHn9bc2XYAMbu5m.jpg', 'type': 'photo', 'id': '2051949753286483971'}]</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2035976151764549748</t>
-        </is>
-      </c>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" s="2" t="n">
-        <v>46111.77400462963</v>
+        <v>46148.54074074074</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/hadi_msn/status/2052794731063566348</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052794731063566348</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2038628104541774071</t>
+          <t>2052794731063566348</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2038628104541774071</t>
+          <t>https://x.com/hadi_msn/status/2052794731063566348</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hi Rakshit, we have already escalated the matter and our team will contact you as soon as possible.</t>
+          <t>@EmiratesNBD_KSA راح الرايح
+االتطبيق فيه مشكلة .. النقاط صفر</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1774881790000</v>
+        <v>1778259377000</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2051949760488050729</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1677,7 +1672,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Hadi', 'screenName': 'hadi_msn', 'followersCount': 7, 'favouritesCount': 276, 'friendsCount': 42, 'description': ''}</t>
         </is>
       </c>
       <c r="J18" t="n">
@@ -1694,50 +1689,50 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2038625938133471268</t>
+          <t>2051949760488050729</t>
         </is>
       </c>
       <c r="P18" s="2" t="n">
-        <v>46111.77997685185</v>
+        <v>46150.87241898148</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/hadi_msn/status/2052794731063566348</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052794731063566348</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2041172230642471397</t>
+          <t>2052796374337327171</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2041172230642471397</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052796374337327171</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA This is really frustrating from NBD. Nothing has progressed. No meaningful action yet ... Really disappointed from Emirates NBD</t>
+          <t>@hadi_msn مرحبا, تم الرد على الخاص.</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1775488357000</v>
+        <v>1778259769000</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2051949760488050729</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1747,11 +1742,11 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1764,50 +1759,50 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2038628104541774071</t>
+          <t>2052794731063566348</t>
         </is>
       </c>
       <c r="P19" s="2" t="n">
-        <v>46118.80042824074</v>
+        <v>46150.87695601852</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/Farooq_AI/status/2052739053989007588</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052739053989007588</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2041173077455667467</t>
+          <t>2052739053989007588</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2041173077455667467</t>
+          <t>https://x.com/Farooq_AI/status/2052739053989007588</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hello, a follow-up on your request has been sent, and you will be contacted as soon as possible.</t>
+          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1775488559000</v>
+        <v>1778246103000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052739053989007588</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1817,11 +1812,11 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'TT Aspiring', 'screenName': 'Farooq_AI', 'followersCount': 27, 'favouritesCount': 9705, 'friendsCount': 130, 'description': "I don't have any great ambitions. I'd like to rule the world for a while. That's it."}</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1834,50 +1829,47 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2041172230642471397</t>
-        </is>
-      </c>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" s="2" t="n">
-        <v>46118.80276620371</v>
+        <v>46150.71878472222</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/masdarak/status/2052747585438495200</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052747585438495200</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2046954276312777137</t>
+          <t>2052747585438495200</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2046954276312777137</t>
+          <t>https://x.com/masdarak/status/2052747585438495200</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Still no one contacted me.</t>
+          <t>إطلاق حلول تمويل عقاري لشراء الوحدات السكنية على الخريطة في مشاريع شركة إعمار العقارية @emaardubai  بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_AE  وبنك أبوظبي التجاري  @OfficialADCB  بما يشمل غير المقيمين في دولة الإمارات
+https://t.co/ryrSH66Kca</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1776866904000</v>
+        <v>1778248137000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052747585438495200</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1887,67 +1879,64 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'المصدر العقاري', 'screenName': 'masdarak', 'followersCount': 346, 'favouritesCount': 88, 'friendsCount': 11, 'description': 'منصة رقمية متخصصة بتحليل بيانات وتوجهات قطاع العقارات في دبي والإمارات والمنطقة'}</t>
         </is>
       </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2041173077455667467</t>
-        </is>
-      </c>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>46134.75583333334</v>
+        <v>46150.74232638889</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/masdarak/status/2052747585438495200</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052747585438495200</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2046956528205259220</t>
+          <t>2052645870227869950</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2046956528205259220</t>
+          <t>https://x.com/masdarak/status/2052645870227869950</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hello Rakshit, thanks for writing to us please note that a follow-up request has been sent, and you will be contacted as soon as possible.</t>
+          <t>طرحت شركات التطوير العقاري في دبي خلال شهر أبريل الماضي  8 مشاريع  جديدة تضم 1,465 وحدة سكنية بحسب بيانات @REIDINcom 
+ https://t.co/bq6bpOlUdV</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1776867441000</v>
+        <v>1778223886000</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052645870227869950</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1957,67 +1946,65 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'المصدر العقاري', 'screenName': 'masdarak', 'followersCount': 346, 'favouritesCount': 88, 'friendsCount': 11, 'description': 'منصة رقمية متخصصة بتحليل بيانات وتوجهات قطاع العقارات في دبي والإمارات والمنطقة'}</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2046954276312777137</t>
-        </is>
-      </c>
+          <t>98419</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" s="2" t="n">
-        <v>46134.76204861111</v>
+        <v>46150.46164351852</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2052629495237292157</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2047725724354633861</t>
+          <t>https://x.com/ihab/status/2052629495237292157</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Same reply every time but no concrete solutions. Just a pathetic approach..</t>
+          <t>"Your Emirates ID has expired - Please update it now !!!"
+I have been trying for the last 3 days, your systems keep throwing errors and failing uploads/verification. This is somehow my fault? 
+"!!! !!! !!! !!!" haha</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1777050832000</v>
+        <v>1778219982000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052629495237292157</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2027,67 +2014,63 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Ihab', 'screenName': 'ihab', 'followersCount': 4467, 'favouritesCount': 11578, 'friendsCount': 1305, 'description': 'I do Brand Marketing, Technology Transformation and Customer Experiences, basically I make an Impact. Tweets are my own.'}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2046956528205259220</t>
-        </is>
-      </c>
+          <t>12193</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" s="2" t="n">
-        <v>46136.88462962963</v>
+        <v>46150.41645833333</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2047728007276544227</t>
+          <t>2052755611188867362</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2047728007276544227</t>
+          <t>https://x.com/Hayataholica/status/2052755611188867362</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Thanks for writing to us, we have already escalated the matter and our team will contact you as soon as possible.</t>
+          <t>@ihab Just go to the center. Hopefully you didn’t respond to a scam message</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1777051376000</v>
+        <v>1778250050000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052629495237292157</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2097,7 +2080,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Hayat 🇦🇪 ♥️🇧🇭', 'screenName': 'Hayataholica', 'followersCount': 12278, 'favouritesCount': 60960, 'friendsCount': 3191, 'description': 'Emirati (khaleeji) Fan of all things rock &amp; metal. Part-time Globe-trotter, concertgoer, &amp; Adrenaline Junkie ✈️ Occasional reader of philosophy &amp; science. 🌍 49'}</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2110,54 +2093,55 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>575</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2047725724354633861</t>
+          <t>2052629495237292157</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46136.89092592592</v>
+        <v>46150.76446759259</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA Same reply every time. No action yet.</t>
+          <t>@Hayataholica No no it’s not a scam message. I’ve just been bombarded with platforms &amp;amp; apps asking me to update my EmiratesID. 
+Some can pull it from UAEPASS while others require a direct upload / scan, etc. EmiratesNBD has been one and it just keeps failing. Will need an ATM or branch visit.</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1778168267000</v>
+        <v>1778250208000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052629495237292157</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2167,7 +2151,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>{'name': 'Rakshit Vaghasiya', 'screenName': 'RakshtVaghasiya', 'followersCount': 1, 'favouritesCount': 0, 'friendsCount': 4, 'description': ''}</t>
+          <t>{'name': 'Ihab', 'screenName': 'ihab', 'followersCount': 4467, 'favouritesCount': 11578, 'friendsCount': 1305, 'description': 'I do Brand Marketing, Technology Transformation and Customer Experiences, basically I make an Impact. Tweets are my own.'}</t>
         </is>
       </c>
       <c r="J25" t="n">
@@ -2180,54 +2164,55 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>469</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2047728007276544227</t>
+          <t>2052755611188867362</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46149.81790509259</v>
+        <v>46150.76629629629</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/RakshtVaghasiya/status/2052412587602530439</t>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2052432883583721554</t>
+          <t>2052756763477524952</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2052432883583721554</t>
+          <t>https://x.com/ihab/status/2052756763477524952</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>@RakshtVaghasiya Hello Rakshit, we apologize for any delay, we have sent a follow-up to the team and we will update you shortly.</t>
+          <t>@Hayataholica They also have this weird.. scan your face to verify (and somehow can get the new ID.. maybe indirectly through UAEPASS?) and it fails saying the country of origin is invalid or something weird like that. 
+Maybe they can’t tell where I’m from by scanning my face? 😂</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1778173106000</v>
+        <v>1778250325000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2032450113100984492</t>
+          <t>2052629495237292157</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2237,11 +2222,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17460, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Ihab', 'screenName': 'ihab', 'followersCount': 4467, 'favouritesCount': 11578, 'friendsCount': 1305, 'description': 'I do Brand Marketing, Technology Transformation and Customer Experiences, basically I make an Impact. Tweets are my own.'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2250,56 +2235,55 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2052412587602530439</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="P26" s="2" t="n">
-        <v>46149.87391203704</v>
+        <v>46150.76765046296</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052424796726850019</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2052424796726850019</t>
+          <t>2052727923002761539</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052299293927805107</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052691349342941582</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE After the latest app update, I’m unable to access the app on my OnePlus Android phone. Getting this error continuously:
-“For security reasons this app cannot be used with VoiceOver enabled.”
-I disabled all accessibility services, but the issue still persists.</t>
+          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
+AE370260001014895574401</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1778141256000</v>
+        <v>1778234729000</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2309,7 +2293,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>{'name': 'Illiyas Mohammed', 'screenName': 'illliyas', 'followersCount': 89, 'favouritesCount': 73, 'friendsCount': 259, 'description': 'Software Engineer'}</t>
+          <t>{'name': 'Akhtar Motiwala', 'screenName': 'MotiwalaAkhtar', 'followersCount': 31, 'favouritesCount': 383, 'friendsCount': 95, 'description': '@@tik@...💘'}</t>
         </is>
       </c>
       <c r="J27" t="n">
@@ -2326,46 +2310,46 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>46149.50527777777</v>
+        <v>46150.5871412037</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052424796726850019</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2052424796726850019</t>
+          <t>2052727923002761539</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2052300575308402847</t>
+          <t>2052727923002761539</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052300575308402847</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>@illliyas Please mention in the email subject social media case #1009168. Thanks- Zubair</t>
+          <t>@EmiratesNBD_AE I have already sent an email on mentioned email address with case ref, awaiting for the response from your side.</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1778141561000</v>
+        <v>1778243449000</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2375,7 +2359,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Akhtar Motiwala', 'screenName': 'MotiwalaAkhtar', 'followersCount': 31, 'favouritesCount': 383, 'friendsCount': 95, 'description': '@@tik@...💘'}</t>
         </is>
       </c>
       <c r="J28" t="n">
@@ -2392,50 +2376,50 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="P28" s="2" t="n">
-        <v>46149.50880787037</v>
+        <v>46150.68806712963</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052424796726850019</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2052424796726850019</t>
+          <t>2052727923002761539</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2052302615791505912</t>
+          <t>2052734884964090296</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052302615791505912</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052734884964090296</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Sent email.</t>
+          <t>@MotiwalaAkhtar We will review your email and will take necessary action and update you via email as soon as possible. Thanks</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1778142048000</v>
+        <v>1778245109000</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2445,11 +2429,11 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>{'name': 'Illiyas Mohammed', 'screenName': 'illliyas', 'followersCount': 89, 'favouritesCount': 73, 'friendsCount': 259, 'description': 'Software Engineer'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -2462,50 +2446,52 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2052300575308402847</t>
+          <t>2052727923002761539</t>
         </is>
       </c>
       <c r="P29" s="2" t="n">
-        <v>46149.51444444444</v>
+        <v>46150.7072800926</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052424796726850019</t>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2052424796726850019</t>
+          <t>2052730384857600235</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2052303504341893169</t>
+          <t>2052726323349533050</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052303504341893169</t>
+          <t>https://x.com/Moh_Dul95/status/2052726323349533050</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>@illliyas Our team will review and will reply you as soon as possible.</t>
+          <t>@EmiratesNBD_KSA السلام عليكم. 
+لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
+ارجوا الدعم….</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1778142260000</v>
+        <v>1778243067000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052726323349533050</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2515,7 +2501,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Mohammed', 'screenName': 'Moh_Dul95', 'followersCount': 111, 'favouritesCount': 9088, 'friendsCount': 1227, 'description': 'Hufflepuff, Liverpool FC, and video games!'}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2532,50 +2518,46 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>2052302615791505912</t>
-        </is>
-      </c>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" s="2" t="n">
-        <v>46149.51689814815</v>
+        <v>46150.68364583333</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052424796726850019</t>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2052424796726850019</t>
+          <t>2052730384857600235</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2052424796726850019</t>
+          <t>2052728856037949755</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052424796726850019</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052728856037949755</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Still waiting for the solution. Not happy with the service.</t>
+          <t>@Moh_Dul95 مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1778171178000</v>
+        <v>1778243671000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052726323349533050</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2585,7 +2567,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Illiyas Mohammed', 'screenName': 'illliyas', 'followersCount': 89, 'favouritesCount': 73, 'friendsCount': 259, 'description': 'Software Engineer'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2602,50 +2584,51 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2052303504341893169</t>
+          <t>2052726323349533050</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46149.85159722222</v>
+        <v>46150.69063657407</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052424796726850019</t>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2052424796726850019</t>
+          <t>2052730384857600235</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2052430161430167778</t>
+          <t>2052730384857600235</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052430161430167778</t>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>@illliyas Hello, we will reply to your email as soon as possible.</t>
+          <t>@EmiratesNBD_KSA @Moh_Dul95 وانا كذلك المشكلة شائعه
+عموما انا لدي عدة بطائق كاش باك وركزت على بطاقة مزيد ..  لو استمرت المشكلة راح اللغيها واركز على البطاقة الاهلي او الراجحي</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1778172457000</v>
+        <v>1778244036000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052726323349533050</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2655,11 +2638,11 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Hadi Aldubaisi', 'screenName': 'HadiAlduba89157', 'followersCount': 0, 'favouritesCount': 121, 'friendsCount': 17, 'description': ''}</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -2672,68 +2655,64 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>55</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2052424796726850019</t>
+          <t>2052728856037949755</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46149.86640046296</v>
+        <v>46150.69486111111</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2052336714459250884</t>
+          <t>2052730384857600235</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2052336714459250884</t>
+          <t>2052732148784787881</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052732148784787881</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>«الإمارات الإسلامي» يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام الشريعة الإسلامية في الإمارات
-https://t.co/LRj8F5RmtL | التفاصيل 
-@EmiratesNBD_AE
-#fintech_gate
-#الإمارات_الإسلامي #برنامج_لشهادات_الإيداع #الشريعة_الإسلامية #الإمارات https://t.co/EdyBD9bZgW</t>
+          <t>@HadiAlduba89157 مرحباً، شكرا لتواصلك معنا. يُرجى إرسال التفاصيل الخاصه بطلبك و رقم هاتفك المسجل إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1778150177000</v>
+        <v>1778244456000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2052336714459250884</t>
+          <t>2052726323349533050</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtdXZCXAAQDiv8.jpg', 'type': 'photo', 'id': '2052336711636549636'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 522, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2746,134 +2725,130 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2052730384857600235</t>
+        </is>
+      </c>
       <c r="P33" s="2" t="n">
-        <v>46149.60853009259</v>
+        <v>46150.69972222222</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2052336714459250884</t>
+          <t>https://x.com/foode212/status/2052701014034108672</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2052336714459250884</t>
+          <t>2052701014034108672</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2052471373839184311</t>
+          <t>2052642161909244242</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/FintechGate1/status/2052471373839184311</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052642161909244242</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>«محمد بن زايد» و«السيسي» يتفقدان مفرزة المقاتلات المصرية المتمركزة في الإمارات
-https://t.co/j8JzFHiHW9   | التفاصيل 
-#fintech_gate 
-#محمد_بن_زايد #السيسي #الإمارات #المقاتلات_المصرية_المتمركزة https://t.co/ptvqVJOqGm</t>
+          <t>Stay tuned as we introduce Cohort 6 from our National Digital Talent Incubator program on May 11. https://t.co/UatVg9350S</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1778182283000</v>
+        <v>1778223002000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2052471373839184311</t>
+          <t>2052642161909244242</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvX1XqXkAEzX5w.jpg', 'type': 'photo', 'id': '2052471367082151937'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHxzKuMXEAAduiR.jpg', 'type': 'photo', 'id': '2052642158209863680'}]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'FinTech Gate-بوابة التكنولوجيا المالية', 'screenName': 'FintechGate1', 'followersCount': 522, 'favouritesCount': 56, 'friendsCount': 331, 'description': 'منصة إخبارية مهتمة بكل ما يتعلق بالتكنولوجيا المالية والقطاعات التابعة لها التجارة الإلكترونية و المدفوعات والبنوك الرقمية والقطاع المالي غير المصرفي'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>317</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" s="2" t="n">
-        <v>46149.98012731481</v>
+        <v>46150.45141203704</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
+          <t>https://x.com/foode212/status/2052701014034108672</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2052316568441229765</t>
+          <t>2052701014034108672</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2052316568441229765</t>
+          <t>2052701014034108672</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
+          <t>https://x.com/foode212/status/2052701014034108672</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Unravel new destinations with fabulous offers
-Enjoy 60% off hotel stays and an extra 25% off globally and 30% off across the UAE when you pay with your Emirates NBD card.
-The offer is valid until 30 May 2026.
-T&amp;Cs apply.
-#UnravelwithEmiratesNBD
-#LifestylebyEmiratesNBD #Vacation #HolidaySeason2026 #SummerTrips #Summer2026</t>
+          <t>@EmiratesNBD_AE مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي https://t.co/2HIzdWlW7n</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1778145374000</v>
+        <v>1778237033000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2052316568441229765</t>
+          <t>2052642161909244242</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtLB8gXoAAvErM.jpg', 'type': 'photo', 'id': '2052316551991238656'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtLCJSXoAI5xML.jpg', 'type': 'photo', 'id': '2052316555422179330'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtLCgQWcAUhnOl.jpg', 'type': 'photo', 'id': '2052316561587728389'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHtLCxKXUAYhooF.jpg', 'type': 'photo', 'id': '2052316566126022662'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHyoscpWQAocV7D.jpg', 'type': 'photo', 'id': '2052701011731431434'}]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Fahad 212', 'screenName': 'foode212', 'followersCount': 3, 'favouritesCount': 12, 'friendsCount': 66, 'description': ''}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2886,57 +2861,60 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>349</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2052642161909244242</t>
+        </is>
+      </c>
       <c r="P35" s="2" t="n">
-        <v>46149.55293981481</v>
+        <v>46150.61380787037</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052316568441229765</t>
+          <t>https://x.com/foode212/status/2052701014034108672</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2052316568441229765</t>
+          <t>2052701014034108672</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2052303842482499725</t>
+          <t>2052704945833398661</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052303842482499725</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052704945833398661</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/973dnM780n https://t.co/p1wRUBSROd</t>
+          <t>@foode212 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1778142340000</v>
+        <v>1778237971000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2052303842482499725</t>
+          <t>2052642161909244242</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHs_drxXQAATmIq.jpg', 'type': 'photo', 'id': '2052303834395918336'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J36" t="n">
@@ -2946,124 +2924,123 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2052701014034108672</t>
+        </is>
+      </c>
       <c r="P36" s="2" t="n">
-        <v>46149.51782407407</v>
+        <v>46150.62466435185</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/lhyx16/status/2052375265490456666</t>
+          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2052375265490456666</t>
+          <t>2052702947826667947</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2052248988380758347</t>
+          <t>2052464745295577598</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/ProfSteveKeen/status/2052248988380758347</t>
+          <t>https://x.com/ChoteyMamu/status/2052464745295577598</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3 accounting errors that most China analysts keep making.
-One. Deficits aren't insolvency. China creates yuan. The constraint is resource allocation, not money.
-Two. Capital flight isn't collapse. It devalues the yuan to boost exports. State banks maintain investment regardless of where money goes.
-Three. Wages track GDP. Chinese wages scale with growth while American wages don't. That structural gap is the real story.
-The full conversation is in the comments.
-#SteveKeen #ChinaEconomy #MacroEconomics #PostKeynesian #EconomicDebate</t>
+          <t>@EmiratesNBD_AE I keep facing this error even after updating my smart pass pin. Can someone please assist? https://t.co/TA9HAr3KWJ</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1778129262000</v>
+        <v>1778180702000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2052248988380758347</t>
+          <t>2052464745295577598</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHsNlEoWUAIKFd0.jpg', 'type': 'photo', 'id': '2052248985746690050'}]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvRzxKaAAAQLKU.jpg', 'type': 'photo', 'id': '2052464742497910784'}]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'Prof. Steve Keen', 'screenName': 'ProfSteveKeen', 'followersCount': 114373, 'favouritesCount': 72570, 'friendsCount': 1593, 'description': 'Predicted the 2008 financial crisis years early. Honorary Professor at UCL. Learn 50+ years of real economics in only 7 weeks. Apply below on my website.'}</t>
+          <t>{'name': 'SHA', 'screenName': 'ChoteyMamu', 'followersCount': 314, 'favouritesCount': 59614, 'friendsCount': 126, 'description': 'Born in Dubai, reside in Sharjah but I am from Pakistan 🇵🇰🇵🇸'}</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="K37" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>468</v>
+        <v>0</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>25871</t>
+          <t>26</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" s="2" t="n">
-        <v>46149.36645833333</v>
+        <v>46149.9618287037</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/lhyx16/status/2052375265490456666</t>
+          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2052375265490456666</t>
+          <t>2052702947826667947</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2052284969158881589</t>
+          <t>2052609541569667239</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/Kathleen_Tyson_/status/2052284969158881589</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052609541569667239</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>@ProfSteveKeen Four. Chinese save about 40% of income, many as gold in bank ‘gold accumulation accounts’ that facilitate regular micro-purchases, so as incomes grow, gold buying grows, gold revalues higher. Win. Win. Win.</t>
+          <t>@ChoteyMamu Quoting case 1009539 in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1778137840000</v>
+        <v>1778215225000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2052248988380758347</t>
+          <t>2052464745295577598</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3073,67 +3050,67 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'Kathleen Tyson', 'screenName': 'Kathleen_Tyson_', 'followersCount': 59323, 'favouritesCount': 224879, 'friendsCount': 868, 'description': 'Global liquidity plumber (triparty repo, FX &amp; optimisation), long ago central banker &amp; author Multicurrency Mercantilism: The New International Monetary Order.'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2052248988380758347</t>
+          <t>2052464745295577598</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46149.46574074074</v>
+        <v>46150.36140046296</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/lhyx16/status/2052375265490456666</t>
+          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2052375265490456666</t>
+          <t>2052702947826667947</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2052375265490456666</t>
+          <t>2052702947826667947</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/lhyx16/status/2052375265490456666</t>
+          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@Kathleen_Tyson_ @ProfSteveKeen Emirates NBD in Dubai also has this option.</t>
+          <t>@EmiratesNBD_AE Still no update...</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1778159369000</v>
+        <v>1778237494000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2052248988380758347</t>
+          <t>2052464745295577598</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3143,11 +3120,11 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'Salaam', 'screenName': 'lhyx16', 'followersCount': 60, 'favouritesCount': 9025, 'friendsCount': 193, 'description': ''}</t>
+          <t>{'name': 'SHA', 'screenName': 'ChoteyMamu', 'followersCount': 314, 'favouritesCount': 59614, 'friendsCount': 126, 'description': 'Born in Dubai, reside in Sharjah but I am from Pakistan 🇵🇰🇵🇸'}</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -3156,65 +3133,64 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2052284969158881589</t>
+          <t>2052609541569667239</t>
         </is>
       </c>
       <c r="P39" s="2" t="n">
-        <v>46149.71491898148</v>
+        <v>46150.61914351852</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
+          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2052303511182811547</t>
+          <t>2052702947826667947</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2052303511182811547</t>
+          <t>2052704817680728141</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052704817680728141</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/SrP2a36Pw3 https://t.co/k8XmvOtTLs</t>
+          <t>@ChoteyMamu Hello, the team will check your email and update you as soon as possible.</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1778142261000</v>
+        <v>1778237940000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2052303511182811547</t>
+          <t>2052464745295577598</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHs_KjTX0AAFve-.jpg', 'type': 'photo', 'id': '2052303505705127936'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J40" t="n">
@@ -3231,61 +3207,64 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2052702947826667947</t>
+        </is>
+      </c>
       <c r="P40" s="2" t="n">
-        <v>46149.51690972222</v>
+        <v>46150.62430555555</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303511182811547</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2052303511182811547</t>
+          <t>2052694787569201197</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2052303458137489515</t>
+          <t>2052694005251535275</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303458137489515</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052694005251535275</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD SHARE Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/XpFUmulYZw https://t.co/YIQNu06Kzh</t>
+          <t>@MotiwalaAkhtar Hi, We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1009843 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1778142249000</v>
+        <v>1778235362000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2052303458137489515</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHs_HcsW8AMUOWf.jpg', 'type': 'photo', 'id': '2052303452391272451'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -3294,65 +3273,74 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2052691349342941582</t>
+        </is>
+      </c>
       <c r="P41" s="2" t="n">
-        <v>46149.51677083333</v>
+        <v>46150.59446759259</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303458137489515</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2052303458137489515</t>
+          <t>2052694787569201197</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2052303325781959087</t>
+          <t>2052694787569201197</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/ENBDdeals/status/2052303325781959087</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Apply for Emirates NBD noon One Visa Credit Card and get a chance to win Samsung S26+ smartphone.
-https://t.co/SrP2a36Pw3 https://t.co/SZAe79aEJu</t>
+          <t>@EmiratesNBD_AE +971 555 906879 
+BENEFICIARY: 
+AKHTAR NAZIR MOTIWALA
+AC NO: 1014895574401
+IBAN: AE37 0260 0010 1489 5574 401
+Swift: EBILAEADXXX
+BANK: EMIRATES NBD</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1778142217000</v>
+        <v>1778235549000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2052303325781959087</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHs-_tkWQAQaLSr.jpg', 'type': 'photo', 'id': '2052303319482122244'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD Deals', 'screenName': 'ENBDdeals', 'followersCount': 39195, 'favouritesCount': 61, 'friendsCount': 4, 'description': 'Welcome to the official account for Emirates NBD Deals. نرحب بكم في الحساب الرسمي لعروض بنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Akhtar Motiwala', 'screenName': 'MotiwalaAkhtar', 'followersCount': 31, 'favouritesCount': 383, 'friendsCount': 95, 'description': '@@tik@...💘'}</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3361,50 +3349,54 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2052694005251535275</t>
+        </is>
+      </c>
       <c r="P42" s="2" t="n">
-        <v>46149.51640046296</v>
+        <v>46150.59663194444</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052299293927805107</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052694787569201197</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2052300555599372615</t>
+          <t>2052696179746418790</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052300555599372615</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052696179746418790</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>@illliyas Hi Illiyas , we’re sorry to hear that you’re having unpleasant experience. We will be glad to assist you and have it fixed. Kindly send us the details at social@EmiratesNBD.com from your registered email address so we can review and assist.</t>
+          <t>@MotiwalaAkhtar Hi, We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1009843 for us to assist you better. Thanks.</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1778141557000</v>
+        <v>1778235881000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3414,7 +3406,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3431,185 +3423,203 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052694787569201197</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>46149.50876157408</v>
+        <v>46150.60047453704</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2052299293927805107</t>
+          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2052299293927805107</t>
+          <t>2052705073373839474</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2051598903083213064</t>
+          <t>2052705068227432806</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/illliyas/status/2051598903083213064</t>
+          <t>https://x.com/emiratesislamic/status/2052705068227432806</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NoBroker is a scam. Paid ₹10,000 for the NRI Super Relax plan, and got a sleepy relationship manager who doesn’t even bother calling interested tenants. But somehow, they have all the energy to keep calling me to upgrade to a higher plan.
-@NoBrokerCom @NoBrokerCare</t>
+          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
+سعادة بلا حدود!
+تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
+🌟 استرداد يصل إلى 6%، بلا حدود
+🎁 مكافأة ترحيبية https://t.co/vWSnmzcwPL</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1777974270000</v>
+        <v>1778238000000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2051598903083213064</t>
+          <t>2052705068227432806</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2052643891250188290/pu/img/G6rzIGTvL3xY2TTb.jpg', 'type': 'video', 'id': '2052643891250188290'}]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'Illiyas Mohammed', 'screenName': 'illliyas', 'followersCount': 89, 'favouritesCount': 73, 'friendsCount': 259, 'description': 'Software Engineer'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J44" t="n">
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>1</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>104</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" s="2" t="n">
-        <v>46147.57256944444</v>
+        <v>46150.625</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052705073373839474</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2052705073373839474</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052057840244646114</t>
+          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Supporting Dubai Culture &amp; Arts Authority in strengthening fraud awareness across their teams.
-By building knowledge and vigilance, we’re helping protect what matters and empowering people to stay alert in a fast-changing digital world.
-#FraudAwareness #FinancialSafety #UnitedAgainstFraud</t>
+          <t>💳 بدون رسوم سنوية
+🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
+وغير ذلك الكثير!
+تُطبّق الشروط والأحكام.
+تقدم بطلبك الآن https://t.co/9VLrqeVE7Q
+The Amazon Emirates Islamic Mastercard Credit Card
+Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1778083689000</v>
+        <v>1778238001000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2052705068227432806</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2052057793599856657/img/uFYYXnfG8i7PvyMn.jpg', 'type': 'video', 'id': '2052057793599856657'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>658</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr"/>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2052705068227432806</t>
+        </is>
+      </c>
       <c r="P45" s="2" t="n">
-        <v>46148.83899305556</v>
+        <v>46150.62501157408</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052705073373839474</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2052132248523288581</t>
+          <t>2052705076490150108</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052132248523288581</t>
+          <t>https://x.com/emiratesislamic/status/2052705076490150108</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE وين الخصوصية اصبحت بلا خصوصية و تكلمت بمشاكل في التطبيق مع امكانية الوصول قبل بضع ايام و اعتقد الحل الوحيد اغلق الحساب و اترك القسم الجاهل في جهله</t>
+          <t>✨ Up to 6% back, unlimited
+🎁 Welcome bonus
+💳 No annual fee
+🌍 Exclusive travel &amp;amp; lifestyle benefits
+And much more.
+Terms &amp;amp; conditions apply.
+Apply now
+https://t.co/8qeNDgv9OP</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1778101429000</v>
+        <v>1778238002000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2052705068227432806</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3619,11 +3629,11 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -3636,61 +3646,62 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>61</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2052705073373839474</t>
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>46149.04431712963</v>
+        <v>46150.62502314815</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/emiratesislamic/status/2052705196799656250</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052705196799656250</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2052239541616906712</t>
+          <t>2052705193741947100</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052239541616906712</t>
+          <t>https://x.com/emiratesislamic/status/2052705193741947100</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>@hamad5uae مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل إلى 
-social@EmiratesNBD.com</t>
+          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
+اقرأ المزيد:
+ https://t.co/fE1Ixwpizc https://t.co/Bf7mTQqjUc</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1778127010000</v>
+        <v>1778238030000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2052705193741947100</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHysQx8XoAU7NqD.jpg', 'type': 'photo', 'id': '2052704934458531845'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHysfwdWoAUfZVS.jpg', 'type': 'photo', 'id': '2052705191758045189'}]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J47" t="n">
@@ -3703,54 +3714,52 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>2052132248523288581</t>
-        </is>
-      </c>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" s="2" t="n">
-        <v>46149.34039351852</v>
+        <v>46150.62534722222</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/emiratesislamic/status/2052705196799656250</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052705196799656250</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2052264638478475341</t>
+          <t>2052705196799656250</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052264638478475341</t>
+          <t>https://x.com/emiratesislamic/status/2052705196799656250</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE الاشكال عاام انتو بتراجعون موضوعي و بعد سنة بتحلونه. واضح انكم حلولكم سريعة</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. 
+ Read the article: 
+https://t.co/V0HzCCKh4m</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1778132993000</v>
+        <v>1778238030000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2052705193741947100</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3760,11 +3769,11 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -3777,50 +3786,50 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>119</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2052239541616906712</t>
+          <t>2052705193741947100</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>46149.4096412037</v>
+        <v>46150.62534722222</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052704785045086288</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2052281866342789437</t>
+          <t>2052587154140955103</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052281866342789437</t>
+          <t>https://x.com/patilabhijeet45/status/2052587154140955103</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>@hamad5uae سنبذل قصارى جهدنا لمعالجة الأمر في أسرع وقت ممكن وتقديم الدعم اللازم.</t>
+          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1778137101000</v>
+        <v>1778209887000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2052587154140955103</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3830,7 +3839,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 122, 'favouritesCount': 14758, 'friendsCount': 266, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J49" t="n">
@@ -3847,50 +3856,46 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>2052264638478475341</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" s="2" t="n">
-        <v>46149.4571875</v>
+        <v>46150.29961805556</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052704785045086288</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052635691859796067</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/emiratesislamic/status/2052635691859796067</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE غير صحيح لو انتو بتبذلون جهودكم كان اطلقتو اصدار يعالج الاشكال فورا الموضوع عندكم من امس اصبح</t>
+          <t>@patilabhijeet45 Dear customer, we will connect with you on private messaging to serve you better.</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1778139899000</v>
+        <v>1778221459000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2052587154140955103</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3900,7 +3905,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{'name': 'حمد الصعاق 🇦🇪', 'screenName': 'hamad5uae', 'followersCount': 357, 'favouritesCount': 422, 'friendsCount': 173, 'description': 'إذا وضعت أحدا فوق قدره فتوقع منه أن يضعك دون قدرك ..”'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J50" t="n">
@@ -3917,50 +3922,50 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2052281866342789437</t>
+          <t>2052587154140955103</t>
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>46149.48957175926</v>
+        <v>46150.43355324074</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://x.com/hamad5uae/status/2052293602643148891</t>
+          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052704785045086288</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2052295354821886462</t>
+          <t>2052704785045086288</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052295354821886462</t>
+          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>@hamad5uae يرجى العلم بأن فريقنا سيرد على بريدك الإلكتروني في أقرب وقت ممكن. شكرًا لك.</t>
+          <t>@emiratesislamic A waiting to connect via dm please</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1778140317000</v>
+        <v>1778237932000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2052057840244646114</t>
+          <t>2052587154140955103</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3970,11 +3975,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174680, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 122, 'favouritesCount': 14758, 'friendsCount': 266, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3987,49 +3992,50 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2052293602643148891</t>
+          <t>2052635691859796067</t>
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>46149.49440972223</v>
+        <v>46150.62421296296</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
+          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2052427177216315673</t>
+          <t>2052704785045086288</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2052427177216315673</t>
+          <t>2052707828104655235</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
-        </is>
-      </c>
-      <c r="E52">
-        <f>==&amp;gt; Dubai’s Emirates Islamic launches UAE’s first $2 billion Shari’ah-compliant CD program for global liquidity demand https://t.co/Ys0jEe4GlM</f>
-        <v/>
+          <t>https://x.com/emiratesislamic/status/2052707828104655235</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>@patilabhijeet45 Dear customer, we will connect with you on private messaging to serve you better.</t>
+        </is>
       </c>
       <c r="F52" t="n">
-        <v>1778171745000</v>
+        <v>1778238658000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2052427177216315673</t>
+          <t>2052587154140955103</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4039,7 +4045,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1131, 'favouritesCount': 24509, 'friendsCount': 306, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -4056,48 +4062,40 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2052704785045086288</t>
+        </is>
+      </c>
       <c r="P52" s="2" t="n">
-        <v>46149.85815972222</v>
+        <v>46150.63261574074</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2052427177216315673</t>
+          <t>https://x.com/emiratesislamic/status/2052699324711063787</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2052427177216315673</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>2052602789923074494</t>
-        </is>
-      </c>
+          <t>2052699324711063787</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/gold_hadas/status/2052602789923074494</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Dachau was created for Hitler’s political opponents and enemies. During the Second World War, people whom the Nazis didn’t even think of re-educating were sent there —most of the prisoners were Christians: Protestants, Catholics, and Orthodox. https://t.co/M1Ohe3opmd</t>
-        </is>
-      </c>
+          <t>https://x.com/undefined/status/undefined</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
       <c r="F53" t="n">
-        <v>1778213615000</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>2052602789923074494</t>
-        </is>
-      </c>
+        <v>1778295599763</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4105,176 +4103,172 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{'name': 'Nicholas MOLODYKO, writer', 'screenName': 'gold_hadas', 'followersCount': 1131, 'favouritesCount': 24509, 'friendsCount': 306, 'description': "Agency (individual free will) is the collective spiritual value of an individual's words and actions—Existence of free will is central to the U.S. Constitution."}</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" s="2" t="n">
-        <v>46150.34276620371</v>
+        <v>46151.29166392361</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
+          <t>https://x.com/emiratesislamic/status/2052699324711063787</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2052401437611630695</t>
+          <t>2052699324711063787</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2052401437611630695</t>
+          <t>2052699324711063787</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
+          <t>https://x.com/emiratesislamic/status/2052699324711063787</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Emirates Islamic launched the UAE’s first Shari’ah-compliant Certificate of Deposit program, marking a key milestone for the Islamic banking sector and reinforcing the bank’s focus on financial innovation.
-The $2 billion program offers institutional investors a new tool to diversify Islamic money market portfolios, while supporting the bank’s strategy to expand its funding base and strengthen its international market presence.
-#UAE #IslamicBanking #Finance #Investment #Banking</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. Read the article:
+ Read the article: 
+https://t.co/V0HzCCKh4m</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1778165609000</v>
+        <v>1778236630000</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2052401437611630695</t>
+          <t>2052699322202894846</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHuYOTMWEAYd8TS.jpg', 'type': 'photo', 'id': '2052401426635034630'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>{'name': 'Economy Middle East', 'screenName': 'Economy_ME', 'followersCount': 4543, 'favouritesCount': 217, 'friendsCount': 12, 'description': 'Economy Middle East Summit 2026\nThe Economy of Tomorrow: The UAE Emerges Stronger 🇦🇪\n📅 May 21, 2026\n📍 Rosewood, Abu Dhabi\nRegister now ⬇️'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2052699322202894846</t>
+        </is>
+      </c>
       <c r="P54" s="2" t="n">
-        <v>46149.78714120371</v>
+        <v>46150.60914351852</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2052401437611630695</t>
+          <t>https://x.com/emiratesislamic/status/2052674875190317079</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2052401437611630695</t>
+          <t>2052674875190317079</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2052413839942008900</t>
+          <t>2052674875190317079</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://x.com/Economy_ME/status/2052413839942008900</t>
+          <t>https://x.com/emiratesislamic/status/2052674875190317079</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dubai’s ready villa segment continues strengthening its position as one of the market’s most competitive categories.
-Strong search recovery, sustained demand and active buyer engagement are reinforcing villas as a preferred option for both end users and investors.
-#Dubai #RealEstate #UAE #Property #Investing</t>
+          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, a USD 2 billion initiative supporting investment diversification and market growth.
+ Read the article: 
+https://t.co/V0HzCCKh4m</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1778168566000</v>
+        <v>1778230801000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2052413839942008900</t>
+          <t>2052674872631824451</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/amplify_video_thumb/2052413614481375243/img/YQhI6H014LqnJy5C.jpg', 'type': 'video', 'id': '2052413614481375243'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>{'name': 'Economy Middle East', 'screenName': 'Economy_ME', 'followersCount': 4543, 'favouritesCount': 217, 'friendsCount': 12, 'description': 'Economy Middle East Summit 2026\nThe Economy of Tomorrow: The UAE Emerges Stronger 🇦🇪\n📅 May 21, 2026\n📍 Rosewood, Abu Dhabi\nRegister now ⬇️'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2052674872631824451</t>
+        </is>
+      </c>
       <c r="P55" s="2" t="n">
-        <v>46149.82136574074</v>
+        <v>46150.54167824074</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+          <t>https://x.com/emiratesislamic/status/2052717380141199866</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2052297392632803551</t>
+          <t>2052717380141199866</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4309,7 +4303,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J56" t="n">
@@ -4322,11 +4316,11 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>228</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
@@ -4337,12 +4331,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+          <t>https://x.com/emiratesislamic/status/2052717380141199866</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2052297392632803551</t>
+          <t>2052717380141199866</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4380,11 +4374,11 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -4397,7 +4391,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>54</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4412,33 +4406,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+          <t>https://x.com/emiratesislamic/status/2052717380141199866</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2052297392632803551</t>
+          <t>2052717380141199866</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2052297392632803551</t>
+          <t>2052717380141199866</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+          <t>https://x.com/emiratesislamic/status/2052717380141199866</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Apply for an Emirates Islamic Etihad Guest Credit Card and earn up to 100,000 bonus Etihad Guest Miles ✈️and amazing rewards:
-🎟️ Up to two 60% discount vouchers on Etihad Guest Miles for flight bookings and upgrades
-🚀 Fast-track upgrade to Etihad Guest Gold Tier status https://t.co/mDtxfkEthD</t>
+          <t>@Asayeel171930 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
+رسالتك الخاصه.</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1778140802000</v>
+        <v>1778240935000</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4447,16 +4440,16 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscgnxXsAEdaoe.jpg', 'type': 'photo', 'id': '2052265401954840577'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHscg1KX0AcUU9F.jpg', 'type': 'photo', 'id': '2052265405549367303'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHschDXW0AIssmP.jpg', 'type': 'photo', 'id': '2052265409361924098'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHschRgXEAIXIRT.jpg', 'type': 'photo', 'id': '2052265413157785602'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -4469,69 +4462,64 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2052297388321104214</t>
+          <t>2052671279057264714</t>
         </is>
       </c>
       <c r="P58" s="2" t="n">
-        <v>46149.50002314815</v>
+        <v>46150.65896990741</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297392632803551</t>
+          <t>https://x.com/emiratesislamic/status/2052732133949534294</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2052297392632803551</t>
+          <t>2052732133949534294</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2052297395296243819</t>
+          <t>2052704808709292243</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052297395296243819</t>
+          <t>https://x.com/omarzouqi/status/2052704808709292243</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>🚗 Complimentary airport transfers, meet &amp;amp; greet services
-⛳ Golf rounds at select premium courses
-🅿️ Valet parking, and much more
-Valid till 31 May 2026
-Terms and conditions apply
-https://t.co/oszNDRRljr https://t.co/ztim5MGGB4</t>
+          <t>@emiratesislamic شوفو الخاص</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1778140803000</v>
+        <v>1778237938000</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2052297385615708568</t>
+          <t>2052699322202894846</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHschi8XkAMonf-.jpg', 'type': 'photo', 'id': '2052265417838661635'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHschv5WMAUB46E.jpg', 'type': 'photo', 'id': '2052265421315649541'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'OMRAN AL MARZOOQI', 'screenName': 'omarzouqi', 'followersCount': 243, 'favouritesCount': 1974, 'friendsCount': 368, 'description': 'احب الصالحين ولست منهم  (اللهم اغفر لأخي أحمد وارحمه واجعل قبره روضة من رياض الجنة)'}</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -4544,66 +4532,64 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2052297392632803551</t>
+          <t>2052699324711063787</t>
         </is>
       </c>
       <c r="P59" s="2" t="n">
-        <v>46149.50003472222</v>
+        <v>46150.62428240741</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://x.com/6trr_/status/2052299567262241168</t>
+          <t>https://x.com/emiratesislamic/status/2052732133949534294</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2052299567262241168</t>
+          <t>2052732133949534294</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2051980293121216835</t>
+          <t>2052732133949534294</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2051980293121216835</t>
+          <t>https://x.com/emiratesislamic/status/2052732133949534294</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>يمكنك الآن الاستمتاع بمعدل ربح متوقع %5 سنوياً على مدخراتك مع حساب التوفير الإلكتروني الخاص بك من الإمارات الإسلامي. ما عليك سوى اتباع الخطوات التالية:
-⭐ افتح حساب التوفير الإلكتروني من الإمارات الإسلامي
-💸 أضف 50,000 درهم وما فوق إلى حساب التوفير الإلكتروني https://t.co/p6de003ec6</t>
+          <t>@omarzouqi مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل.</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1778065200000</v>
+        <v>1778244453000</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2051980293121216835</t>
+          <t>2052699322202894846</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoBmKQXIAY2C9I.jpg', 'type': 'photo', 'id': '2051954335320317958'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoBmUjXkAEXtu0.jpg', 'type': 'photo', 'id': '2051954338084392961'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoBmelX0AITvUp.jpg', 'type': 'photo', 'id': '2051954340777152514'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoBmmOXoAEiHbf.jpg', 'type': 'photo', 'id': '2051954342828154881'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -4612,50 +4598,55 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2052704808709292243</t>
+        </is>
+      </c>
       <c r="P60" s="2" t="n">
-        <v>46148.625</v>
+        <v>46150.6996875</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://x.com/6trr_/status/2052299567262241168</t>
+          <t>https://x.com/emiratesislamic/status/2052716737154396511</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2052299567262241168</t>
+          <t>2052716737154396511</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2052299567262241168</t>
+          <t>2052232251371581529</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://x.com/6trr_/status/2052299567262241168</t>
+          <t>https://x.com/thekimanikamau/status/2052232251371581529</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>@emiratesislamic بنك تعامله غير مرضي ويتم احتساب رسوم من غير اشعار مباشر للعميل او رساله نصيه ، يتم احتساب رسوم في بطاقات الكريديت كارد. للعلم</t>
+          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
+Eg @emiratesislamic</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1778141321000</v>
+        <v>1778125272000</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2051980293121216835</t>
+          <t>2052232251371581529</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4665,7 +4656,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>{'name': 'ع ❥', 'screenName': '6trr_', 'followersCount': 737, 'favouritesCount': 3868, 'friendsCount': 122, 'description': ''}</t>
+          <t>{'name': 'Daniel Kimani', 'screenName': 'thekimanikamau', 'followersCount': 18, 'favouritesCount': 38, 'friendsCount': 173, 'description': ''}</t>
         </is>
       </c>
       <c r="J61" t="n">
@@ -4682,51 +4673,46 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2051980293121216835</t>
-        </is>
-      </c>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" s="2" t="n">
-        <v>46149.50603009259</v>
+        <v>46149.32027777778</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://x.com/6trr_/status/2052299567262241168</t>
+          <t>https://x.com/emiratesislamic/status/2052716737154396511</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2052299567262241168</t>
+          <t>2052716737154396511</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2052313830538059926</t>
+          <t>2052716737154396511</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052313830538059926</t>
+          <t>https://x.com/emiratesislamic/status/2052716737154396511</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>@6trr_ مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
+          <t>@thekimanikamau Dear Daniel, Thanks for getting in touch. We apologize for any inconvenience caused. Your privacy is important to us, and to ensure your confidentiality, we've sent you a message requesting further details. Please check your direct messages at your earliest convenience.</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1778144722000</v>
+        <v>1778240782000</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2051980293121216835</t>
+          <t>2052232251371581529</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4736,7 +4722,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
         </is>
       </c>
       <c r="J62" t="n">
@@ -4753,622 +4739,16 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2052299567262241168</t>
+          <t>2052232251371581529</t>
         </is>
       </c>
       <c r="P62" s="2" t="n">
-        <v>46149.54539351852</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://x.com/thekimanikamau/status/2052232251371581529</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2052232251371581529</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>2052232251371581529</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>https://x.com/thekimanikamau/status/2052232251371581529</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>The feedback requests after customer care calls should add option to rate the company’s service/the quality of information provided to the reps to assist customers. Mostly I find the company is at fault and are using these reps as shields to their bad service.
-Eg @emiratesislamic</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>1778125272000</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2052232251371581529</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>{'name': 'Daniel Kimani', 'screenName': 'thekimanikamau', 'followersCount': 18, 'favouritesCount': 38, 'friendsCount': 173, 'description': ''}</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" s="2" t="n">
-        <v>46149.32027777778</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2052347842044297241</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>2051965478206128614</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2051965478206128614</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>كل استثمار هو بداية قصة تحتاج إلى اهتمام استثنائي. مع الخدمات المصرفية المميزة من الإمارات الإسلامي، إن استثمارك الأول اليوم هو إرث الغد لأبنائك. اكشتف التميز الذي يصنع الفارق. https://t.co/MrOIqMpjyd</t>
-        </is>
-      </c>
-      <c r="F64" t="n">
-        <v>1778061668000</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>2051965478206128614</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoLubJWoAITTef.jpg', 'type': 'photo', 'id': '2051965472409559042'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHoLul0WgAUvjWI.jpg', 'type': 'photo', 'id': '2051965475274260485'}]</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>3</v>
-      </c>
-      <c r="K64" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="n">
-        <v>1</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" s="2" t="n">
-        <v>46148.58412037037</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2052347842044297241</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="n">
-        <v>1778215157452</v>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" s="2" t="n">
-        <v>46150.36061865741</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2052347842044297241</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>2052347842044297241</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052347842044297241</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>@Asayeel171930 مرحبا ، يأسفنا سماع تجربتك! فريقنا ملتزم بمعالجة هذا الأمر على الفور. لحماية خصوصيتك ، سيتم التواصل معك عبر الرسائل الخاصه لامكانيه مساعدتك بصوره افضل. رضاك أولويتنا.</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>1778152830000</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>2051965478206128614</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2052328479933530423</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="n">
-        <v>46149.63923611111</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052347910788890733</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2052347910788890733</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>2052347910788890733</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052347910788890733</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>@Asayeel171930 مرحبا عزيزي العميل. نشكرك على التواصل معنا. لحماية خصوصيتك ، نود إعلامك بأننا قمنا بالرد عليك في نفس الرسالة ضمن المنشور السابق. ولكي يتسنى لنا خدمتك على نحو أفضل ، يرجى مراجعة 
-رسالتك الخاصه.</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>1778152847000</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>2051965478206128614</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2052329323433193561</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="n">
-        <v>46149.63943287037</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2052342692424696089</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>2052342683113283967</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052342683113283967</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>حوّل راتبك الآن و استمتع بمزايا خاصة واكسب استرداداً نقدياً مضموناً يصل إلى 6,000 درهم!
-استمتع بالمزيد من المكافآت:
-💳 مزايا حصرية على البطاقة الائتمانية والدخول إلى صالات المطارات والمكافآت والمزيد
-💰 معدلات ربح تنافسية على تمويل السيارات والتمويل السكني https://t.co/8DI8iDNmnE</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1778151600000</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>2052342683113283967</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-RLXwAEHdKD.jpg', 'type': 'photo', 'id': '2052283503472001025'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-bJX0Ak_mq9.jpg', 'type': 'photo', 'id': '2052283506147971081'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-j1W0AIg_GL.jpg', 'type': 'photo', 'id': '2052283508479938562'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-t5WAAAzJb7.jpg', 'type': 'photo', 'id': '2052283511181017088'}]</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>2</v>
-      </c>
-      <c r="K68" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="n">
-        <v>3</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" s="2" t="n">
-        <v>46149.625</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2052342692424696089</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>2052342686976200822</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052342686976200822</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>🎁 مكافأة 100 درهم مع حساب ALPHA للأبناء
-وغير ذلك الكثير
-يسري العرض لغاية 31 مايو 2026
-تطبق الشروط والأحكام.
-https://t.co/Hgg0TFDsUE https://t.co/oOsraDJ2sv</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>1778151601000</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>2052342683113283967</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss-4kXkAcEP5i.jpg', 'type': 'photo', 'id': '2052283514045829127'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss_DGWoAQH4pW.jpg', 'type': 'photo', 'id': '2052283516872728580'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss_OdXoAA3QyP.jpg', 'type': 'photo', 'id': '2052283519922053120'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHss_aXXkAIrsDs.jpg', 'type': 'photo', 'id': '2052283523118108674'}]</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>1</v>
-      </c>
-      <c r="K69" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>2052342683113283967</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="n">
-        <v>46149.62501157408</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2052342692424696089</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>2052342690600165819</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052342690600165819</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Transfer your salary now &amp;amp; enjoy rewarding benefits and guaranteed cashback of up to AED 6,000!
-Enjoy more rewards:
-💳 Exclusive Credit Card benefits, airport lounge access, rewards &amp;amp; more
-💰 Competitive profit rates on Auto Finance &amp;amp; Home Finance</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>1778151602000</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>2052342683113283967</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>1</v>
-      </c>
-      <c r="K70" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>2052342686976200822</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="n">
-        <v>46149.62502314815</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2052342692424696089</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>2052342692424696089</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>https://x.com/emiratesislamic/status/2052342692424696089</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>🎁 Reward of AED 100 with an ALPHA Youth Account
-And much more.
-Offer valid till 31 May 2026
-Terms &amp;amp; conditions apply.
-https://t.co/1MUaqlObLd</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>1778151603000</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2052342683113283967</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18483, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>2052342690600165819</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="n">
-        <v>46149.62503472222</v>
+        <v>46150.65719907408</v>
       </c>
     </row>
   </sheetData>

--- a/EI_ENDB_comments.xlsx
+++ b/EI_ENDB_comments.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,25 +517,301 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2052796942841795039</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2050914407471849643</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>1777811073000</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHZPyC_WYAAg5zq.jpg', 'type': 'photo', 'id': '2050914401528471552'}]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="n">
+        <v>46145.68371527778</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2052796942841795039</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2051885677755679118</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://x.com/faisalalamoudi3/status/2051885677755679118</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_KSA صباح الخير .. هل التطبيق فيه مشكله لديكم</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1778042642000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>{'name': 'فيصل بن عبدالرحمن', 'screenName': 'faisalalamoudi3', 'followersCount': 4871, 'favouritesCount': 1403, 'friendsCount': 1105, 'description': "من يستمر بفعل ما اكره !' لايسالني في اي هامش وضعته ؟!! فانا لا اطيل علاقتي بمن يعكر مزاجي .. (من عشاق الملكي🇳🇬🇸🇦)"}</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>46148.36391203704</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2052796942841795039</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2052796942841795039</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>@faisalalamoudi3 @EmiratesNBD_KSA الرجاء النظر في مشكلتي و استرجاع النقاط المكتبة في هذا للشهر والشهر الفائت</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1778259904000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'name': 'Hadi', 'screenName': 'hadi_msn', 'followersCount': 7, 'favouritesCount': 276, 'friendsCount': 42, 'description': ''}</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2051885677755679118</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>46150.87851851852</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2052796942841795039</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2052805357064359950</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052805357064359950</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>@hadi_msn مرحبا ,تم إرسال رقمك للفريق المختص و سيتم التواصل معك فى أسرع وقت, شكرا.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1778261911000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2050914407471849643</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2052796942841795039</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>46150.90174768519</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>2052836145461887127</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://x.com/samial7arbi02/status/2052480803209175369</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA 
 خلال أيام قليلة فقط تحولتُ من عميل حصل على **عرض تمويل رسمي** موقع من @EmiratesNBD_KSA إلى "قائمة سوداء وهمية" لا وجود لها في سجلات سمة ولا في @SAMA_GOV !
@@ -549,209 +825,209 @@
 @AlinmaBank @alrajhibank @SNB_AlAhli @RiyadBank @BankAlbilad @BankAlJazira @anb_bank @D360bank @stcbank_ksa</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F6" t="n">
         <v>1778184531000</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvf53hWgAUCXBk.jpg', 'type': 'photo', 'id': '2052480240446767109'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvf53jWUAcT4dG.jpg', 'type': 'photo', 'id': '2052480240455143431'}]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>{'name': 'سامي الحربي', 'screenName': 'samial7arbi02', 'followersCount': 276, 'favouritesCount': 688, 'friendsCount': 1366, 'description': 'العاقل إن أخطأ تأسف .. والأحمق إن أخطأ تفلسف ..'}</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J6" t="n">
         <v>9</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M6" t="n">
         <v>16</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>145981</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" s="2" t="n">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>146056</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="n">
         <v>46150.00614583334</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>2052836145461887127</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>2052661557209768191</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>https://x.com/alamair2008/status/2052661557209768191</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>@samial7arbi02 @EmiratesNBD_KSA @SAMA_GOV @ENBDdeals @anb_bank @RiyadBank @BankAlJazira @BankAlbilad @D360bank @alrajhibank @snbalahli أنا مثلك مع هالبنك سبب نزول نقاطي بسمه السبب غلط موظفه بعد شكاوي لم يتحرأ يقول الخطا مها وللاسف البنك المركزي يقف عاجز امام البنوك واضطريت اتسلف وانقل وايضا بنك الرياض مسوي استقطاع لشركة @mrnaksa واسدد بتاريخ ٢٧ كل شهر وللاسف يطلع ب@SAMAcares متاخر سبب نزول الإسكورر
 أنا المتضرر</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F7" t="n">
         <v>1778227626000</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>{'name': 'AZIZ ALGHAMDI', 'screenName': 'alamair2008', 'followersCount': 4305, 'favouritesCount': 17937, 'friendsCount': 4439, 'description': 'لا تفرض إحساسك وتركض ورى الغير حتى .. لو إنه واحشك ألف وحشه حدّك سلام ، وكيفك أن شاء الله بخير تسترك عن قولة : ترى فلان بلشه'}</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>{'name': 'AZIZ ALGHAMDI', 'screenName': 'alamair2008', 'followersCount': 4305, 'favouritesCount': 17937, 'friendsCount': 4440, 'description': 'لا تفرض إحساسك وتركض ورى الغير حتى .. لو إنه واحشك ألف وحشه حدّك سلام ، وكيفك أن شاء الله بخير تسترك عن قولة : ترى فلان بلشه'}</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
         <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="P3" s="2" t="n">
+      <c r="P7" s="2" t="n">
         <v>46150.50493055556</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2052836145461887127</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>2052667887639237003</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>https://x.com/EmiratesNBD_KSA/status/2052667887639237003</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>@alamair2008 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F8" t="n">
         <v>1778229135000</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>2052661557209768191</t>
         </is>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P8" s="2" t="n">
         <v>46150.52239583333</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2052836145461887127</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>2052778577695773164</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>https://x.com/alamair2008/status/2052778577695773164</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA للأسف اجبرت اسدد المبلغ واروح بنك آخر يحترم عملاءه 
 وللاسف اخذت قرض سابق وبنفس البدلات والمميزات بحكم أنا موظف حكومي 
@@ -759,358 +1035,82 @@
 من هالبنك حتى يحكم ع منظومة رسميه انها مو رسمي</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F9" t="n">
         <v>1778255526000</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>2052480803209175369</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'name': 'AZIZ ALGHAMDI', 'screenName': 'alamair2008', 'followersCount': 4305, 'favouritesCount': 17937, 'friendsCount': 4439, 'description': 'لا تفرض إحساسك وتركض ورى الغير حتى .. لو إنه واحشك ألف وحشه حدّك سلام ، وكيفك أن شاء الله بخير تسترك عن قولة : ترى فلان بلشه'}</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>{'name': 'AZIZ ALGHAMDI', 'screenName': 'alamair2008', 'followersCount': 4305, 'favouritesCount': 17937, 'friendsCount': 4440, 'description': 'لا تفرض إحساسك وتركض ورى الغير حتى .. لو إنه واحشك ألف وحشه حدّك سلام ، وكيفك أن شاء الله بخير تسترك عن قولة : ترى فلان بلشه'}</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>2052667887639237003</t>
         </is>
       </c>
-      <c r="P5" s="2" t="n">
+      <c r="P9" s="2" t="n">
         <v>46150.82784722222</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://x.com/alamair2008/status/2052836145461887127</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2052836145461887127</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2052780459046617221</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2052780459046617221</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>@alamair2008 مرحبا, نأسف لسماع أنك تواجه هذه التجربة, يرجى إرسال رقم هاتفك و رقم الهوية عبر الخاص ليمكننا مساعدتك, شكرا</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1778255974000</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2052480803209175369</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2052778577695773164</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>46150.8330324074</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://x.com/alamair2008/status/2052836145461887127</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2052836145461887127</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2052836145461887127</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>https://x.com/alamair2008/status/2052836145461887127</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA ماعاد يفيد بعد طوي قيد بنككم من اهتمام الاغلبيه</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>1778269251000</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2052480803209175369</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>{'name': 'AZIZ ALGHAMDI', 'screenName': 'alamair2008', 'followersCount': 4305, 'favouritesCount': 17937, 'friendsCount': 4439, 'description': 'لا تفرض إحساسك وتركض ورى الغير حتى .. لو إنه واحشك ألف وحشه حدّك سلام ، وكيفك أن شاء الله بخير تسترك عن قولة : ترى فلان بلشه'}</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2052780459046617221</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>46150.98670138889</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2052796942841795039</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2050914407471849643</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2050914407471849643</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>نسعد بخدمتكم واستقبال استفساراتكم وشكاويكم عبر قنوات البنك الرسمية📲 https://t.co/afLfJB9QyG</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>1777811073000</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2050914407471849643</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHZPyC_WYAAg5zq.jpg', 'type': 'photo', 'id': '2050914401528471552'}]</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>796</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" s="2" t="n">
-        <v>46145.68371527778</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2052796942841795039</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2051885677755679118</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>https://x.com/faisalalamoudi3/status/2051885677755679118</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_KSA صباح الخير .. هل التطبيق فيه مشكله لديكم</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1778042642000</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2050914407471849643</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>{'name': 'فيصل بن عبدالرحمن', 'screenName': 'faisalalamoudi3', 'followersCount': 4871, 'favouritesCount': 1403, 'friendsCount': 1105, 'description': "من يستمر بفعل ما اكره !' لايسالني في اي هامش وضعته ؟!! فانا لا اطيل علاقتي بمن يعكر مزاجي .. (من عشاق الملكي🇳🇬🇸🇦)"}</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2050914407471849643</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="n">
-        <v>46148.36391203704</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2052796942841795039</t>
+          <t>2052836145461887127</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2052796942841795039</t>
+          <t>2052780459046617221</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052780459046617221</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>@faisalalamoudi3 @EmiratesNBD_KSA الرجاء النظر في مشكلتي و استرجاع النقاط المكتبة في هذا للشهر والشهر الفائت</t>
+          <t>@alamair2008 مرحبا, نأسف لسماع أنك تواجه هذه التجربة, يرجى إرسال رقم هاتفك و رقم الهوية عبر الخاص ليمكننا مساعدتك, شكرا</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1778259904000</v>
+        <v>1778255974000</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2050914407471849643</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>{'name': 'Hadi', 'screenName': 'hadi_msn', 'followersCount': 7, 'favouritesCount': 276, 'friendsCount': 42, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -1137,50 +1137,50 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2051885677755679118</t>
+          <t>2052778577695773164</t>
         </is>
       </c>
       <c r="P10" s="2" t="n">
-        <v>46150.87851851852</v>
+        <v>46150.8330324074</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://x.com/hadi_msn/status/2052796942841795039</t>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2052796942841795039</t>
+          <t>2052836145461887127</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2052805357064359950</t>
+          <t>2052836145461887127</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2052805357064359950</t>
+          <t>https://x.com/alamair2008/status/2052836145461887127</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>@hadi_msn مرحبا ,تم إرسال رقمك للفريق المختص و سيتم التواصل معك فى أسرع وقت, شكرا.</t>
+          <t>@EmiratesNBD_KSA ماعاد يفيد بعد طوي قيد بنككم من اهتمام الاغلبيه</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1778261911000</v>
+        <v>1778269251000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2050914407471849643</t>
+          <t>2052480803209175369</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'AZIZ ALGHAMDI', 'screenName': 'alamair2008', 'followersCount': 4305, 'favouritesCount': 17937, 'friendsCount': 4440, 'description': 'لا تفرض إحساسك وتركض ورى الغير حتى .. لو إنه واحشك ألف وحشه حدّك سلام ، وكيفك أن شاء الله بخير تسترك عن قولة : ترى فلان بلشه'}</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -1207,16 +1207,16 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2052796942841795039</t>
+          <t>2052780459046617221</t>
         </is>
       </c>
       <c r="P11" s="2" t="n">
-        <v>46150.90174768519</v>
+        <v>46150.98670138889</v>
       </c>
     </row>
     <row r="12">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>{'name': '齋藤純 Jun Saito', 'screenName': 'jurian777', 'followersCount': 1325, 'favouritesCount': 10943, 'friendsCount': 575, 'description': '中東（湾岸アラブ諸国中心）の経済・企業、開発金融、企業金融、企業統治、金融システムが専門の研究者。現地報道や自身の研究についてつぶやいています。猫・酒・舞がやや多め。Researcher：Gulf Economy, Financial Development, and Corporate Governance'}</t>
+          <t>{'name': '齋藤純 Jun Saito', 'screenName': 'jurian777', 'followersCount': 1326, 'favouritesCount': 10943, 'friendsCount': 575, 'description': '中東（湾岸アラブ諸国中心）の経済・企業、開発金融、企業金融、企業統治、金融システムが専門の研究者。現地報道や自身の研究についてつぶやいています。猫・酒・舞がやや多め。Researcher：Gulf Economy, Financial Development, and Corporate Governance'}</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>293</t>
         </is>
       </c>
       <c r="O12" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>{'name': '齋藤純 Jun Saito', 'screenName': 'jurian777', 'followersCount': 1325, 'favouritesCount': 10943, 'friendsCount': 575, 'description': '中東（湾岸アラブ諸国中心）の経済・企業、開発金融、企業金融、企業統治、金融システムが専門の研究者。現地報道や自身の研究についてつぶやいています。猫・酒・舞がやや多め。Researcher：Gulf Economy, Financial Development, and Corporate Governance'}</t>
+          <t>{'name': '齋藤純 Jun Saito', 'screenName': 'jurian777', 'followersCount': 1326, 'favouritesCount': 10943, 'friendsCount': 575, 'description': '中東（湾岸アラブ諸国中心）の経済・企業、開発金融、企業金融、企業統治、金融システムが専門の研究者。現地報道や自身の研究についてつぶやいています。猫・酒・舞がやや多め。Researcher：Gulf Economy, Financial Development, and Corporate Governance'}</t>
         </is>
       </c>
       <c r="J13" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>68</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1396,14 +1396,14 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>{'name': 'CMO Goa', 'screenName': 'goacm', 'followersCount': 102019, 'favouritesCount': 747, 'friendsCount': 118, 'description': "Official Twitter Account of Chief Minister @DrPramodPSawant's Office"}</t>
+          <t>{'name': 'CMO Goa', 'screenName': 'goacm', 'followersCount': 102020, 'favouritesCount': 747, 'friendsCount': 118, 'description': "Official Twitter Account of Chief Minister @DrPramodPSawant's Office"}</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>348</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>{'name': 'CMO Goa', 'screenName': 'goacm', 'followersCount': 102019, 'favouritesCount': 747, 'friendsCount': 118, 'description': "Official Twitter Account of Chief Minister @DrPramodPSawant's Office"}</t>
+          <t>{'name': 'CMO Goa', 'screenName': 'goacm', 'followersCount': 102020, 'favouritesCount': 747, 'friendsCount': 118, 'description': "Official Twitter Account of Chief Minister @DrPramodPSawant's Office"}</t>
         </is>
       </c>
       <c r="J15" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>193</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>{'name': 'CMO Goa', 'screenName': 'goacm', 'followersCount': 102019, 'favouritesCount': 747, 'friendsCount': 118, 'description': "Official Twitter Account of Chief Minister @DrPramodPSawant's Office"}</t>
+          <t>{'name': 'CMO Goa', 'screenName': 'goacm', 'followersCount': 102020, 'favouritesCount': 747, 'friendsCount': 118, 'description': "Official Twitter Account of Chief Minister @DrPramodPSawant's Office"}</t>
         </is>
       </c>
       <c r="J16" t="n">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>126</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>710</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1774,35 +1774,36 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://x.com/Farooq_AI/status/2052739053989007588</t>
+          <t>https://x.com/masdarak/status/2052747585438495200</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2052739053989007588</t>
+          <t>2052747585438495200</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2052739053989007588</t>
+          <t>2052747585438495200</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://x.com/Farooq_AI/status/2052739053989007588</t>
+          <t>https://x.com/masdarak/status/2052747585438495200</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>My accountant just sent over the Emirates NBD numbers. 6% deposit growth - and that includes the weeks with missile alerts. Not exactly capital flight. Dubai's losing innocence, not capital. I'm watching who positions for the recovery.</t>
+          <t>إطلاق حلول تمويل عقاري لشراء الوحدات السكنية على الخريطة في مشاريع شركة إعمار العقارية @emaardubai  بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_AE  وبنك أبوظبي التجاري  @OfficialADCB  بما يشمل غير المقيمين في دولة الإمارات
+https://t.co/ryrSH66Kca</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1778246103000</v>
+        <v>1778248137000</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2052739053989007588</t>
+          <t>2052747585438495200</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1812,7 +1813,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>{'name': 'TT Aspiring', 'screenName': 'Farooq_AI', 'followersCount': 27, 'favouritesCount': 9705, 'friendsCount': 130, 'description': "I don't have any great ambitions. I'd like to rule the world for a while. That's it."}</t>
+          <t>{'name': 'المصدر العقاري', 'screenName': 'masdarak', 'followersCount': 346, 'favouritesCount': 88, 'friendsCount': 11, 'description': 'منصة رقمية متخصصة بتحليل بيانات وتوجهات قطاع العقارات في دبي والإمارات والمنطقة'}</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -1825,16 +1826,16 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>110</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" s="2" t="n">
-        <v>46150.71878472222</v>
+        <v>46150.74232638889</v>
       </c>
     </row>
     <row r="21">
@@ -1850,26 +1851,26 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2052747585438495200</t>
+          <t>2052645870227869950</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://x.com/masdarak/status/2052747585438495200</t>
+          <t>https://x.com/masdarak/status/2052645870227869950</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>إطلاق حلول تمويل عقاري لشراء الوحدات السكنية على الخريطة في مشاريع شركة إعمار العقارية @emaardubai  بالتعاون مع بنك الإمارات دبي الوطني @EmiratesNBD_AE  وبنك أبوظبي التجاري  @OfficialADCB  بما يشمل غير المقيمين في دولة الإمارات
-https://t.co/ryrSH66Kca</t>
+          <t>طرحت شركات التطوير العقاري في دبي خلال شهر أبريل الماضي  8 مشاريع  جديدة تضم 1,465 وحدة سكنية بحسب بيانات @REIDINcom 
+ https://t.co/bq6bpOlUdV</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1778248137000</v>
+        <v>1778223886000</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2052747585438495200</t>
+          <t>2052645870227869950</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1889,118 +1890,117 @@
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>98550</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" s="2" t="n">
-        <v>46150.74232638889</v>
+        <v>46150.46164351852</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://x.com/masdarak/status/2052747585438495200</t>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2052747585438495200</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2052645870227869950</t>
+          <t>2052629495237292157</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://x.com/masdarak/status/2052645870227869950</t>
+          <t>https://x.com/ihab/status/2052629495237292157</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>طرحت شركات التطوير العقاري في دبي خلال شهر أبريل الماضي  8 مشاريع  جديدة تضم 1,465 وحدة سكنية بحسب بيانات @REIDINcom 
- https://t.co/bq6bpOlUdV</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>1778223886000</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2052645870227869950</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>{'name': 'المصدر العقاري', 'screenName': 'masdarak', 'followersCount': 346, 'favouritesCount': 88, 'friendsCount': 11, 'description': 'منصة رقمية متخصصة بتحليل بيانات وتوجهات قطاع العقارات في دبي والإمارات والمنطقة'}</t>
-        </is>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>6</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>98419</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" s="2" t="n">
-        <v>46150.46164351852</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://x.com/ihab/status/2052756273901576234</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2052756273901576234</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>2052629495237292157</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>https://x.com/ihab/status/2052629495237292157</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
         <is>
           <t>"Your Emirates ID has expired - Please update it now !!!"
 I have been trying for the last 3 days, your systems keep throwing errors and failing uploads/verification. This is somehow my fault? 
 "!!! !!! !!! !!!" haha</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>1778219982000</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2052629495237292157</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>{'name': 'Ihab', 'screenName': 'ihab', 'followersCount': 4467, 'favouritesCount': 11578, 'friendsCount': 1305, 'description': 'I do Brand Marketing, Technology Transformation and Customer Experiences, basically I make an Impact. Tweets are my own.'}</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" t="n">
+        <v>23</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>12292</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="n">
+        <v>46150.41645833333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2052756273901576234</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2052755611188867362</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://x.com/Hayataholica/status/2052755611188867362</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>@ihab Just go to the center. Hopefully you didn’t respond to a scam message</t>
+        </is>
+      </c>
       <c r="F23" t="n">
-        <v>1778219982000</v>
+        <v>1778250050000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -2014,29 +2014,33 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>{'name': 'Ihab', 'screenName': 'ihab', 'followersCount': 4467, 'favouritesCount': 11578, 'friendsCount': 1305, 'description': 'I do Brand Marketing, Technology Transformation and Customer Experiences, basically I make an Impact. Tweets are my own.'}</t>
+          <t>{'name': 'Hayat 🇦🇪 ♥️🇧🇭', 'screenName': 'Hayataholica', 'followersCount': 12278, 'favouritesCount': 60960, 'friendsCount': 3191, 'description': 'Emirati (khaleeji) Fan of all things rock &amp; metal. Part-time Globe-trotter, concertgoer, &amp; Adrenaline Junkie ✈️ Occasional reader of philosophy &amp; science. 🌍 49'}</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>12193</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
+          <t>583</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2052629495237292157</t>
+        </is>
+      </c>
       <c r="P23" s="2" t="n">
-        <v>46150.41645833333</v>
+        <v>46150.76446759259</v>
       </c>
     </row>
     <row r="24">
@@ -2052,21 +2056,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2052755611188867362</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://x.com/Hayataholica/status/2052755611188867362</t>
+          <t>https://x.com/ihab/status/2052756273901576234</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>@ihab Just go to the center. Hopefully you didn’t respond to a scam message</t>
+          <t>@Hayataholica No no it’s not a scam message. I’ve just been bombarded with platforms &amp;amp; apps asking me to update my EmiratesID. 
+Some can pull it from UAEPASS while others require a direct upload / scan, etc. EmiratesNBD has been one and it just keeps failing. Will need an ATM or branch visit.</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1778250050000</v>
+        <v>1778250208000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -2080,7 +2085,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>{'name': 'Hayat 🇦🇪 ♥️🇧🇭', 'screenName': 'Hayataholica', 'followersCount': 12278, 'favouritesCount': 60960, 'friendsCount': 3191, 'description': 'Emirati (khaleeji) Fan of all things rock &amp; metal. Part-time Globe-trotter, concertgoer, &amp; Adrenaline Junkie ✈️ Occasional reader of philosophy &amp; science. 🌍 49'}</t>
+          <t>{'name': 'Ihab', 'screenName': 'ihab', 'followersCount': 4467, 'favouritesCount': 11578, 'friendsCount': 1305, 'description': 'I do Brand Marketing, Technology Transformation and Customer Experiences, basically I make an Impact. Tweets are my own.'}</t>
         </is>
       </c>
       <c r="J24" t="n">
@@ -2097,16 +2102,16 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>476</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2052629495237292157</t>
+          <t>2052755611188867362</t>
         </is>
       </c>
       <c r="P24" s="2" t="n">
-        <v>46150.76446759259</v>
+        <v>46150.76629629629</v>
       </c>
     </row>
     <row r="25">
@@ -2122,22 +2127,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2052756273901576234</t>
+          <t>2052756763477524952</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://x.com/ihab/status/2052756273901576234</t>
+          <t>https://x.com/ihab/status/2052756763477524952</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>@Hayataholica No no it’s not a scam message. I’ve just been bombarded with platforms &amp;amp; apps asking me to update my EmiratesID. 
-Some can pull it from UAEPASS while others require a direct upload / scan, etc. EmiratesNBD has been one and it just keeps failing. Will need an ATM or branch visit.</t>
+          <t>@Hayataholica They also have this weird.. scan your face to verify (and somehow can get the new ID.. maybe indirectly through UAEPASS?) and it fails saying the country of origin is invalid or something weird like that. 
+Maybe they can’t tell where I’m from by scanning my face? 😂</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1778250208000</v>
+        <v>1778250325000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -2168,51 +2173,51 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>469</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2052755611188867362</t>
+          <t>2052756273901576234</t>
         </is>
       </c>
       <c r="P25" s="2" t="n">
-        <v>46150.76629629629</v>
+        <v>46150.76765046296</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://x.com/ihab/status/2052756273901576234</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2052756273901576234</t>
+          <t>2052727923002761539</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2052756763477524952</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://x.com/ihab/status/2052756763477524952</t>
+          <t>https://x.com/MotiwalaAkhtar/status/2052691349342941582</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>@Hayataholica They also have this weird.. scan your face to verify (and somehow can get the new ID.. maybe indirectly through UAEPASS?) and it fails saying the country of origin is invalid or something weird like that. 
-Maybe they can’t tell where I’m from by scanning my face? 😂</t>
+          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
+AE370260001014895574401</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1778250325000</v>
+        <v>1778234729000</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2052629495237292157</t>
+          <t>2052691349342941582</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2222,11 +2227,11 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>{'name': 'Ihab', 'screenName': 'ihab', 'followersCount': 4467, 'favouritesCount': 11578, 'friendsCount': 1305, 'description': 'I do Brand Marketing, Technology Transformation and Customer Experiences, basically I make an Impact. Tweets are my own.'}</t>
+          <t>{'name': 'Akhtar Motiwala', 'screenName': 'MotiwalaAkhtar', 'followersCount': 31, 'favouritesCount': 383, 'friendsCount': 95, 'description': '@@tik@...💘'}</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -2235,20 +2240,16 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2052756273901576234</t>
-        </is>
-      </c>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" s="2" t="n">
-        <v>46150.76765046296</v>
+        <v>46150.5871412037</v>
       </c>
     </row>
     <row r="27">
@@ -2264,58 +2265,61 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
+          <t>2052727923002761539</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>@EmiratesNBD_AE I have already sent an email on mentioned email address with case ref, awaiting for the response from your side.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1778243449000</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>2052691349342941582</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052691349342941582</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I am trying to login my enbd online banking but it's taking me to fingerprint login setup, once its done it goes back to log out, again ask me to do the same, I am currently in india and unable to transact,
-AE370260001014895574401</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>1778234729000</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>{'name': 'Akhtar Motiwala', 'screenName': 'MotiwalaAkhtar', 'followersCount': 31, 'favouritesCount': 383, 'friendsCount': 95, 'description': '@@tik@...💘'}</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
         <is>
           <t>2052691349342941582</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>{'name': 'Akhtar Motiwala', 'screenName': 'MotiwalaAkhtar', 'followersCount': 31, 'favouritesCount': 383, 'friendsCount': 95, 'description': '@@tik@...💘'}</t>
-        </is>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
       <c r="P27" s="2" t="n">
-        <v>46150.5871412037</v>
+        <v>46150.68806712963</v>
       </c>
     </row>
     <row r="28">
@@ -2331,163 +2335,159 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>2052734884964090296</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_AE/status/2052734884964090296</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>@MotiwalaAkhtar We will review your email and will take necessary action and update you via email as soon as possible. Thanks</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1778245109000</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2052691349342941582</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174684, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
           <t>2052727923002761539</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>@EmiratesNBD_AE I have already sent an email on mentioned email address with case ref, awaiting for the response from your side.</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>1778243449000</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>2052691349342941582</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>{'name': 'Akhtar Motiwala', 'screenName': 'MotiwalaAkhtar', 'followersCount': 31, 'favouritesCount': 383, 'friendsCount': 95, 'description': '@@tik@...💘'}</t>
-        </is>
-      </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>2052691349342941582</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="n">
-        <v>46150.68806712963</v>
+        <v>46150.7072800926</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052727923002761539</t>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2052727923002761539</t>
+          <t>2052730384857600235</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2052734884964090296</t>
+          <t>2052726323349533050</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052734884964090296</t>
+          <t>https://x.com/Moh_Dul95/status/2052726323349533050</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
-        <is>
-          <t>@MotiwalaAkhtar We will review your email and will take necessary action and update you via email as soon as possible. Thanks</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>1778245109000</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>2052691349342941582</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
-        </is>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>2052727923002761539</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="n">
-        <v>46150.7072800926</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2052730384857600235</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>2052726323349533050</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>https://x.com/Moh_Dul95/status/2052726323349533050</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
         <is>
           <t>@EmiratesNBD_KSA السلام عليكم. 
 لماذا تم اختفاء نقاط الكاش باك من البطاقات الاتمانية؟ حيث كان يوجد مبلغ ولكن الان اصبح 0 في البطاقتين….
 ارجوا الدعم….</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>1778243067000</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2052726323349533050</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>{'name': 'Mohammed', 'screenName': 'Moh_Dul95', 'followersCount': 111, 'favouritesCount': 9088, 'friendsCount': 1227, 'description': 'Hufflepuff, Liverpool FC, and video games!'}</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="2" t="n">
+        <v>46150.68364583333</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2052730384857600235</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2052728856037949755</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052728856037949755</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>@Moh_Dul95 مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
+        </is>
+      </c>
       <c r="F30" t="n">
-        <v>1778243067000</v>
+        <v>1778243671000</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>{'name': 'Mohammed', 'screenName': 'Moh_Dul95', 'followersCount': 111, 'favouritesCount': 9088, 'friendsCount': 1227, 'description': 'Hufflepuff, Liverpool FC, and video games!'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J30" t="n">
@@ -2518,12 +2518,16 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2052726323349533050</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="n">
-        <v>46150.68364583333</v>
+        <v>46150.69063657407</v>
       </c>
     </row>
     <row r="31">
@@ -2539,21 +2543,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2052728856037949755</t>
+          <t>2052730384857600235</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2052728856037949755</t>
+          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>@Moh_Dul95 مرحباً, يرجى الاتصال بخدمة العملاء لدينا على الرقم  المجاني 8007547777 و من خارج المملكة على 009660112122333 وسيتمكن أحد موظفينا من مساعدتك بهذا الأمر.</t>
+          <t>@EmiratesNBD_KSA @Moh_Dul95 وانا كذلك المشكلة شائعه
+عموما انا لدي عدة بطائق كاش باك وركزت على بطاقة مزيد ..  لو استمرت المشكلة راح اللغيها واركز على البطاقة الاهلي او الراجحي</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1778243671000</v>
+        <v>1778244036000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2567,7 +2572,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'Hadi Aldubaisi', 'screenName': 'HadiAlduba89157', 'followersCount': 0, 'favouritesCount': 121, 'friendsCount': 17, 'description': ''}</t>
         </is>
       </c>
       <c r="J31" t="n">
@@ -2584,16 +2589,16 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>61</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2052726323349533050</t>
+          <t>2052728856037949755</t>
         </is>
       </c>
       <c r="P31" s="2" t="n">
-        <v>46150.69063657407</v>
+        <v>46150.69486111111</v>
       </c>
     </row>
     <row r="32">
@@ -2609,22 +2614,21 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2052730384857600235</t>
+          <t>2052732148784787881</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052732148784787881</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_KSA @Moh_Dul95 وانا كذلك المشكلة شائعه
-عموما انا لدي عدة بطائق كاش باك وركزت على بطاقة مزيد ..  لو استمرت المشكلة راح اللغيها واركز على البطاقة الاهلي او الراجحي</t>
+          <t>@HadiAlduba89157 مرحباً، شكرا لتواصلك معنا. يُرجى إرسال التفاصيل الخاصه بطلبك و رقم هاتفك المسجل إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1778244036000</v>
+        <v>1778244456000</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2638,7 +2642,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>{'name': 'Hadi Aldubaisi', 'screenName': 'HadiAlduba89157', 'followersCount': 0, 'favouritesCount': 121, 'friendsCount': 17, 'description': ''}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J32" t="n">
@@ -2655,50 +2659,54 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>35</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2052728856037949755</t>
+          <t>2052730384857600235</t>
         </is>
       </c>
       <c r="P32" s="2" t="n">
-        <v>46150.69486111111</v>
+        <v>46150.69972222222</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://x.com/HadiAlduba89157/status/2052730384857600235</t>
+          <t>https://x.com/Suhrob64184475/status/2052681405897880031</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2052730384857600235</t>
+          <t>2052681405897880031</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2052732148784787881</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_KSA/status/2052732148784787881</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>@HadiAlduba89157 مرحباً، شكرا لتواصلك معنا. يُرجى إرسال التفاصيل الخاصه بطلبك و رقم هاتفك المسجل إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
+          <t>The UAE just built a real-time AED to USD stablecoin rail. 👀
+Both fully licensed. Reserves held 1:1 at Emirates NBD and Mashreq.  1 AED = 1 AEC
+The region is building the future! 🔑  
+Would you want $AEC and $USDU on ⬡ mb io? 
+Let us know! cc @AECoin_UAE  and @Universal_USDU</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1778244456000</v>
+        <v>1778232089000</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2052726323349533050</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2708,147 +2716,147 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
+          <t>{'name': 'mb.io', 'screenName': 'multibank_io', 'followersCount': 136464, 'favouritesCount': 7225, 'friendsCount': 212, 'description': 'Crypto. Buy. Sell. Trade. | One of the most regulated exchanges on Earth. And the simplest. | $MBG | RWA | Part of @MultiBankGroup'}</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>2052730384857600235</t>
-        </is>
-      </c>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" s="2" t="n">
-        <v>46150.69972222222</v>
+        <v>46150.55658564815</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://x.com/foode212/status/2052701014034108672</t>
+          <t>https://x.com/Suhrob64184475/status/2052681405897880031</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2052701014034108672</t>
+          <t>2052681405897880031</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2052642161909244242</t>
+          <t>2052681405897880031</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052642161909244242</t>
+          <t>https://x.com/Suhrob64184475/status/2052681405897880031</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Stay tuned as we introduce Cohort 6 from our National Digital Talent Incubator program on May 11. https://t.co/UatVg9350S</t>
+          <t>@multibank_io @AECoin_UAE Emirates NBD and Mashreq both holding reserves that's actually solid backing ngl</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1778223002000</v>
+        <v>1778232358000</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2052642161909244242</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHxzKuMXEAAduiR.jpg', 'type': 'photo', 'id': '2052642158209863680'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Morgan', 'screenName': 'Suhrob64184475', 'followersCount': 194, 'favouritesCount': 71, 'friendsCount': 7, 'description': 'self-directed portfolio builder. collecting digital art that moves me. believer in ownership without permission. 🔑'}</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>317</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2052680277336703430</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="n">
-        <v>46150.45141203704</v>
+        <v>46150.55969907407</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://x.com/foode212/status/2052701014034108672</t>
+          <t>https://x.com/RohitSa70875783/status/2052683161734148463</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2052701014034108672</t>
+          <t>2052683161734148463</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2052701014034108672</t>
+          <t>2052683161734148463</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://x.com/foode212/status/2052701014034108672</t>
+          <t>https://x.com/RohitSa70875783/status/2052683161734148463</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE مو معقول كل يوم انتظر بالساعات ولا احد يرد ولا يتجاوب ادا احتجت شي ضروري من خدمة العملاء ايش اسوي https://t.co/2HIzdWlW7n</t>
+          <t>@multibank_io @AECoin_UAE Would love to see AEC on mb io especially with Emirates NBD backing it thats huge trust signal</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1778237033000</v>
+        <v>1778232777000</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2052642161909244242</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHyoscpWQAocV7D.jpg', 'type': 'photo', 'id': '2052701011731431434'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>{'name': 'Fahad 212', 'screenName': 'foode212', 'followersCount': 3, 'favouritesCount': 12, 'friendsCount': 66, 'description': ''}</t>
+          <t>{'name': 'Luna Web3', 'screenName': 'RohitSa70875783', 'followersCount': 194, 'favouritesCount': 72, 'friendsCount': 21, 'description': 'ex-Goldman guy who realized the plumbing was broken. now building better rails. crypto native. 🏗️'}</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2861,50 +2869,50 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2052642161909244242</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="P35" s="2" t="n">
-        <v>46150.61380787037</v>
+        <v>46150.56454861111</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://x.com/foode212/status/2052701014034108672</t>
+          <t>https://x.com/IrfanAmeable/status/2052687458446578021</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2052701014034108672</t>
+          <t>2052687458446578021</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2052704945833398661</t>
+          <t>2052687458446578021</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052704945833398661</t>
+          <t>https://x.com/IrfanAmeable/status/2052687458446578021</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>@foode212 مرحباً، نأسف لسماع أنك تواجه تجربة غير سارة. يسعدنا مساعدتك وحلها. يُرجى إرسال التفاصيل الخاصه بشكواك إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
+          <t>@EmiratesNBD_AE  why does your application iOS require face pass or smart touch to login after IOS 18.7.8</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1778237971000</v>
+        <v>1778233801000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2052642161909244242</t>
+          <t>2052687458446578021</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2914,11 +2922,11 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'mohammed irfan', 'screenName': 'IrfanAmeable', 'followersCount': 5, 'favouritesCount': 29, 'friendsCount': 37, 'description': ''}</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -2931,64 +2939,60 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>2052701014034108672</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" s="2" t="n">
-        <v>46150.62466435185</v>
+        <v>46150.57640046296</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
+          <t>https://x.com/IrfanAmeable/status/2052687458446578021</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2052702947826667947</t>
+          <t>2052687458446578021</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2052464745295577598</t>
+          <t>2052697695811227957</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://x.com/ChoteyMamu/status/2052464745295577598</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052697695811227957</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE I keep facing this error even after updating my smart pass pin. Can someone please assist? https://t.co/TA9HAr3KWJ</t>
+          <t>@IrfanAmeable Hi Mohammed! Thanks for reaching us. Apologies for any inconvenience caused. We kindly request you to reach out to us from your registered email address at social@emiratesnbd.com quoting case #1009832 in the subject line of the email.</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1778180702000</v>
+        <v>1778236242000</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2052464745295577598</t>
+          <t>2052687458446578021</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHvRzxKaAAAQLKU.jpg', 'type': 'photo', 'id': '2052464742497910784'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>{'name': 'SHA', 'screenName': 'ChoteyMamu', 'followersCount': 314, 'favouritesCount': 59614, 'friendsCount': 126, 'description': 'Born in Dubai, reside in Sharjah but I am from Pakistan 🇵🇰🇵🇸'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174684, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
@@ -3001,46 +3005,50 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2052687458446578021</t>
+        </is>
+      </c>
       <c r="P37" s="2" t="n">
-        <v>46149.9618287037</v>
+        <v>46150.60465277778</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
+          <t>https://x.com/IrfanAmeable/status/2052687458446578021</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2052702947826667947</t>
+          <t>2052687458446578021</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2052609541569667239</t>
+          <t>2052697713691549886</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052609541569667239</t>
+          <t>https://x.com/EmiratesNBD_AE/status/2052697713691549886</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>@ChoteyMamu Quoting case 1009539 in the subject line of the email from your registered email address We will make every effort to address the matter promptly and provide the necessary support. Thanks</t>
+          <t>@IrfanAmeable We will make every effort to address the matter promptly and provide the necessary support.</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1778215225000</v>
+        <v>1778236246000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2052464745295577598</t>
+          <t>2052687458446578021</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3050,11 +3058,11 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174684, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -3067,120 +3075,118 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2052464745295577598</t>
+          <t>2052687458446578021</t>
         </is>
       </c>
       <c r="P38" s="2" t="n">
-        <v>46150.36140046296</v>
+        <v>46150.60469907407</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
+          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2052702947826667947</t>
+          <t>2052680648222032220</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2052702947826667947</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2051302125989236884</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE Still no update...</t>
+          <t>لا تشيل هم الفاتورة 🤩
+مع 5% كاش باك على مقاضي السوبر ماركت مع بطاقة مزيد الائتمانية من #بنك_الإمارات_دبي_الوطني 👌🏼💙
+للتفاصيل:https://t.co/oJpg7cbDbn https://t.co/cWHpRlVIyY</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1778237494000</v>
+        <v>1777903512000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2052464745295577598</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2051302098415812608/pu/img/kiycv3whSbLg1NL6.jpg', 'type': 'video', 'id': '2051302098415812608'}]</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>{'name': 'SHA', 'screenName': 'ChoteyMamu', 'followersCount': 314, 'favouritesCount': 59614, 'friendsCount': 126, 'description': 'Born in Dubai, reside in Sharjah but I am from Pakistan 🇵🇰🇵🇸'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J39" t="n">
+        <v>2</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>2052609541569667239</t>
-        </is>
-      </c>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" s="2" t="n">
-        <v>46150.61914351852</v>
+        <v>46146.75361111111</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://x.com/ChoteyMamu/status/2052702947826667947</t>
+          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2052702947826667947</t>
+          <t>2052680648222032220</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2052704817680728141</t>
+          <t>2052680648222032220</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052704817680728141</t>
+          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>@ChoteyMamu Hello, the team will check your email and update you as soon as possible.</t>
+          <t>@EmiratesNBD_KSA السلام عليكم .. لدي بطاقة مزيد ومتشكر منكم  كما عودتونا كشف الحساب يصدر بيوم 8 من كل شهر .. لسى ماجاني كشف الحساب وايضا صفر لي للنقاط هل هذا بسبب اليوم صادف عطلة نهاية الاسبوع ولا ايش</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1778237940000</v>
+        <v>1778232178000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2052464745295577598</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3190,11 +3196,11 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Hadi Aldubaisi', 'screenName': 'HadiAlduba89157', 'followersCount': 0, 'favouritesCount': 121, 'friendsCount': 17, 'description': ''}</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -3207,50 +3213,50 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2052702947826667947</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="P40" s="2" t="n">
-        <v>46150.62430555555</v>
+        <v>46150.55761574074</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
+          <t>https://x.com/HadiAlduba89157/status/2052680648222032220</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2052694787569201197</t>
+          <t>2052680648222032220</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2052694005251535275</t>
+          <t>2052682500061659633</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052694005251535275</t>
+          <t>https://x.com/EmiratesNBD_KSA/status/2052682500061659633</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>@MotiwalaAkhtar Hi, We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1009843 for us to assist you better. Thanks.</t>
+          <t>@HadiAlduba89157 مرحباً، شكرا لتواصلك معنا. يُرجى إرسال التفاصيل الخاصه بطلبك و رقم هاتفك المسجل إلى رسائل الخاص حتي نتمكن من مساعدتك بشكل أفضل</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1778235362000</v>
+        <v>1778232619000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2052691349342941582</t>
+          <t>2051302125989236884</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3260,7 +3266,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Emirates NBD KSA', 'screenName': 'EmiratesNBD_KSA', 'followersCount': 17463, 'favouritesCount': 3, 'friendsCount': 2, 'description': 'نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني في المملكة العربية السعودية. The official Emirates NBD feed in KSA.'}</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -3277,56 +3283,50 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>54</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2052691349342941582</t>
+          <t>2052680648222032220</t>
         </is>
       </c>
       <c r="P41" s="2" t="n">
-        <v>46150.59446759259</v>
+        <v>46150.56271990741</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2052694787569201197</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2052694787569201197</t>
+          <t>2052691212344209418</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
+          <t>https://x.com/is_that_sniff/status/2052691212344209418</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>@EmiratesNBD_AE +971 555 906879 
-BENEFICIARY: 
-AKHTAR NAZIR MOTIWALA
-AC NO: 1014895574401
-IBAN: AE37 0260 0010 1489 5574 401
-Swift: EBILAEADXXX
-BANK: EMIRATES NBD</t>
+          <t>@multibank_io @AECoin_UAE Hmm like how soon could this actually go live on the platform if they say yes</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1778235549000</v>
+        <v>1778234696000</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2052691349342941582</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3336,11 +3336,11 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>{'name': 'Akhtar Motiwala', 'screenName': 'MotiwalaAkhtar', 'followersCount': 31, 'favouritesCount': 383, 'friendsCount': 95, 'description': '@@tik@...💘'}</t>
+          <t>{'name': 'Zack Smith', 'screenName': 'is_that_sniff', 'followersCount': 953, 'favouritesCount': 6406, 'friendsCount': 532, 'description': 'just put your money on man utd'}</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -3358,45 +3358,45 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2052694005251535275</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="P42" s="2" t="n">
-        <v>46150.59663194444</v>
+        <v>46150.58675925926</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://x.com/MotiwalaAkhtar/status/2052694787569201197</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2052694787569201197</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2052696179746418790</t>
+          <t>2052703324697141646</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://x.com/EmiratesNBD_AE/status/2052696179746418790</t>
+          <t>https://x.com/PloySup02575660/status/2052703324697141646</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>@MotiwalaAkhtar Hi, We kindly request you to send us more details and your registered mobile number via social@emiratesnbd.com and quote Case #1009843 for us to assist you better. Thanks.</t>
+          <t>@multibank_io @AECoin_UAE People underestimate how huge regulated stablecoins will become</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1778235881000</v>
+        <v>1778237584000</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2052691349342941582</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>{'name': 'Emirates NBD', 'screenName': 'EmiratesNBD_AE', 'followersCount': 174683, 'favouritesCount': 961, 'friendsCount': 7, 'description': 'The official Emirates NBD feed. We are here to serve you on Twitter daily from 9am – 9pm نرحب بكم في الحساب الرسمي لبنك الإمارات دبي الوطني'}</t>
+          <t>{'name': 'Lucas.eth', 'screenName': 'PloySup02575660', 'followersCount': 201, 'favouritesCount': 434, 'friendsCount': 19, 'description': 'Building the next layer of the internet, one decentralized solution at a time. Passionate about innovation, collaboration, and real-world impact. 🌐'}</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -3423,68 +3423,64 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2052694787569201197</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="P43" s="2" t="n">
-        <v>46150.60047453704</v>
+        <v>46150.62018518519</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2052705073373839474</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2052705068227432806</t>
+          <t>2052681191409504526</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705068227432806</t>
+          <t>https://x.com/bala22016208/status/2052681191409504526</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>بطاقة أمازون الائتمانية من الإمارات الإسلامي وماستركارد
-سعادة بلا حدود!
-تعرف على البطاقة التي تحوّل كل عملية شراء إلى سعادة بلا حدود 💳✨
-🌟 استرداد يصل إلى 6%، بلا حدود
-🎁 مكافأة ترحيبية https://t.co/vWSnmzcwPL</t>
+          <t>@multibank_io @AECoin_UAE UAE moving fast while others still debating stablecoin frameworks</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1778238000000</v>
+        <v>1778232307000</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2052705068227432806</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/ext_tw_video_thumb/2052643891250188290/pu/img/G6rzIGTvL3xY2TTb.jpg', 'type': 'video', 'id': '2052643891250188290'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Liam Token', 'screenName': 'bala22016208', 'followersCount': 205, 'favouritesCount': 416, 'friendsCount': 1, 'description': 'Bitcoin OG turned NFT enthusiast since 2021. Exploring blockchain scalability and digital asset innovation. Always seeking new possibilities in DeFi. 🔗'}</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -3493,56 +3489,54 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr"/>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2052680277336703430</t>
+        </is>
+      </c>
       <c r="P44" s="2" t="n">
-        <v>46150.625</v>
+        <v>46150.5591087963</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2052705073373839474</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2052705073373839474</t>
+          <t>2052707828784099767</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
+          <t>https://x.com/Amirul52235103/status/2052707828784099767</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>💳 بدون رسوم سنوية
-🌍 ميزات وخصومات خاصة للسفر ونمط حياة حصرية
-وغير ذلك الكثير!
-تُطبّق الشروط والأحكام.
-تقدم بطلبك الآن https://t.co/9VLrqeVE7Q
-The Amazon Emirates Islamic Mastercard Credit Card
-Meet the card that turns every purchase into Unlimited Joy 💳✨</t>
+          <t>@multibank_io @AECoin_UAE the region been cooking for a while now and this just proves it</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1778238001000</v>
+        <v>1778238658000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2052705068227432806</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3552,11 +3546,11 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Ava.eth', 'screenName': 'Amirul52235103', 'followersCount': 200, 'favouritesCount': 634, 'friendsCount': 26, 'description': 'Virtual land mogul exploring the infinite possibilities of the metaverse. Investing in digital dreams and shaping tomorrow, one pixel at a time. 🌌'}</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -3569,57 +3563,50 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2052705068227432806</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="P45" s="2" t="n">
-        <v>46150.62501157408</v>
+        <v>46150.63261574074</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705073373839474</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2052705073373839474</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2052705076490150108</t>
+          <t>2052693848602604018</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705076490150108</t>
+          <t>https://x.com/Andhyevan/status/2052693848602604018</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>✨ Up to 6% back, unlimited
-🎁 Welcome bonus
-💳 No annual fee
-🌍 Exclusive travel &amp;amp; lifestyle benefits
-And much more.
-Terms &amp;amp; conditions apply.
-Apply now
-https://t.co/8qeNDgv9OP</t>
+          <t>@multibank_io @AECoin_UAE This is what real-world crypto adoption looks like</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1778238002000</v>
+        <v>1778235325000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2052705068227432806</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3629,7 +3616,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Evelyn Kade', 'screenName': 'Andhyevan', 'followersCount': 590, 'favouritesCount': 295, 'friendsCount': 1, 'description': 'Ex-Wall Street banker turned Web3 enthusiast. I choose decentralized freedom over corporate chains. Building my own path in this digital frontier. 🌐✨'}</t>
         </is>
       </c>
       <c r="J46" t="n">
@@ -3646,66 +3633,64 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>20</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2052705073373839474</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="P46" s="2" t="n">
-        <v>46150.62502314815</v>
+        <v>46150.59403935185</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705196799656250</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2052705196799656250</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2052705193741947100</t>
+          <t>2052706854438899891</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705193741947100</t>
+          <t>https://x.com/BiolTisha/status/2052706854438899891</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>الإمارات الإسلامي يطلق أول برنامج لشهادات الإيداع المتوافقة مع أحكام ومبادئ الشريعة الإسلامية في الدولة، بما يدعم تنويع الاستثمارات ونمو السوق. 
-اقرأ المزيد:
- https://t.co/fE1Ixwpizc https://t.co/Bf7mTQqjUc</t>
+          <t>@multibank_io @AECoin_UAE This is bigger than payments. It’s infrastructure</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1778238030000</v>
+        <v>1778238426000</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2052705193741947100</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>[{'mediaUrlHttps': 'https://pbs.twimg.com/media/HHysQx8XoAU7NqD.jpg', 'type': 'photo', 'id': '2052704934458531845'}, {'mediaUrlHttps': 'https://pbs.twimg.com/media/HHysfwdWoAUfZVS.jpg', 'type': 'photo', 'id': '2052705191758045189'}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Niloy Khan', 'screenName': 'BiolTisha', 'followersCount': 599, 'favouritesCount': 1246, 'friendsCount': 349, 'description': 'NFT | COLLAB MG and HEAD MOD @Hopiumdao_ | HOPIUM DAO | $ETH | $SOL |'}</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -3714,52 +3699,54 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2052680277336703430</t>
+        </is>
+      </c>
       <c r="P47" s="2" t="n">
-        <v>46150.62534722222</v>
+        <v>46150.62993055556</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705196799656250</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2052705196799656250</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2052705196799656250</t>
+          <t>2052701873715446130</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052705196799656250</t>
+          <t>https://x.com/Victor32721087/status/2052701873715446130</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Emirates Islamic launches the UAE’s first Shariah-compliant Certificate of Deposit Programme, supporting investment diversification and market growth. 
- Read the article: 
-https://t.co/V0HzCCKh4m</t>
+          <t>@multibank_io @AECoin_UAE MENA becoming a serious crypto hub wasn’t just talk after all.</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1778238030000</v>
+        <v>1778237238000</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2052705193741947100</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3769,7 +3756,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Luna.eth', 'screenName': 'Victor32721087', 'followersCount': 295, 'favouritesCount': 424, 'friendsCount': 14, 'description': 'Champion of privacy and self-custody. Navigating the crypto world with caution, relying on no one but myself. Trust is earned, never given. 🔑'}</t>
         </is>
       </c>
       <c r="J48" t="n">
@@ -3786,50 +3773,50 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>21</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>2052705193741947100</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="P48" s="2" t="n">
-        <v>46150.62534722222</v>
+        <v>46150.61618055555</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2052704785045086288</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2052587154140955103</t>
+          <t>2052708578469855254</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2052587154140955103</t>
+          <t>https://x.com/YieldJam/status/2052708578469855254</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>@emiratesislamic Hello Team need your assistance please dm.</t>
+          <t>@multibank_io @AECoin_UAE So like both coins are fully licensed meaning this is actually legit and not just vibes right</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1778209887000</v>
+        <v>1778238837000</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2052587154140955103</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3839,11 +3826,11 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 122, 'favouritesCount': 14758, 'friendsCount': 266, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': 'Jennifer Rebb', 'screenName': 'YieldJam', 'followersCount': 225, 'favouritesCount': 3537, 'friendsCount': 60, 'description': 'I like cryptocurrency'}</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -3856,46 +3843,50 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2052680277336703430</t>
+        </is>
+      </c>
       <c r="P49" s="2" t="n">
-        <v>46150.29961805556</v>
+        <v>46150.6346875</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2052704785045086288</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2052635691859796067</t>
+          <t>2052689096183836992</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052635691859796067</t>
+          <t>https://x.com/Universal_USDU/status/2052689096183836992</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>@patilabhijeet45 Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>@multibank_io @AECoin_UAE Thank you for the support, exciting to see the broader ecosystem continuing to evolve around practical digital asset infrastructure and regulated settlement use cases in the UAE.</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1778221459000</v>
+        <v>1778234192000</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2052587154140955103</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3905,11 +3896,11 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'USDU / Universal', 'screenName': 'Universal_USDU', 'followersCount': 166, 'favouritesCount': 98, 'friendsCount': 26, 'description': 'FSRA-regulated ADGM issuer of USDU, a USD-backed stablecoin registered with the Central Bank of the UAE for regulated digital asset settlement.'}</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -3922,50 +3913,50 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>36</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2052587154140955103</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="P50" s="2" t="n">
-        <v>46150.43355324074</v>
+        <v>46150.58092592593</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2052704785045086288</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2052704785045086288</t>
+          <t>2052696504154894809</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
+          <t>https://x.com/ma11_omar/status/2052696504154894809</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>@emiratesislamic A waiting to connect via dm please</t>
+          <t>@multibank_io @AECoin_UAE A real time AED to USD rail is lowkey huge for anyone doing cross border payments in the region</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1778237932000</v>
+        <v>1778235958000</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2052587154140955103</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3975,11 +3966,11 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>{'name': 'abhijeet patil', 'screenName': 'patilabhijeet45', 'followersCount': 122, 'favouritesCount': 14758, 'friendsCount': 266, 'description': 'Instagram- abhi4590patil live in Dubai From Mumbai India . .नमस्ते 🇮🇳🙏🇲🇴🇭🇰🇨🇳🇶🇦🇸🇬🇲🇾🇨🇷🇪🇺🇫🇷🇳🇱🇨🇿🇰🇼'}</t>
+          <t>{'name': '0xLuna', 'screenName': 'ma11_omar', 'followersCount': 333, 'favouritesCount': 481, 'friendsCount': 145, 'description': 'hodling since 2011 • ethereum collector • still studying blockchains • digital art saved my portfolio twice 🖼️'}</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
@@ -3992,50 +3983,50 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2052635691859796067</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="P51" s="2" t="n">
-        <v>46150.62421296296</v>
+        <v>46150.60136574074</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://x.com/patilabhijeet45/status/2052704785045086288</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2052704785045086288</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2052707828104655235</t>
+          <t>2052703293273415974</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052707828104655235</t>
+          <t>https://x.com/phiwokuhle_02/status/2052703293273415974</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>@patilabhijeet45 Dear customer, we will connect with you on private messaging to serve you better.</t>
+          <t>@multibank_io @AECoin_UAE Would 100% use an AED stablecoin rail for transfers honestly been waiting for something like this</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1778238658000</v>
+        <v>1778237577000</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2052587154140955103</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4045,7 +4036,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>{'name': 'emiratesislamic', 'screenName': 'emiratesislamic', 'followersCount': 18488, 'favouritesCount': 90, 'friendsCount': 27, 'description': 'الصفحة الرئيسية لمصرف الإمارات الإسلامي (ش.م.ع)\nOfficial page of Emirates Islamic Bank (P.J.S.C.)'}</t>
+          <t>{'name': 'Alex', 'screenName': 'phiwokuhle_02', 'followersCount': 210, 'favouritesCount': 157, 'friendsCount': 45, 'description': 'buying mints, flipping gains, repeat. building community one trade at a time 📈'}</t>
         </is>
       </c>
       <c r="J52" t="n">
@@ -4062,40 +4053,52 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2052704785045086288</t>
+          <t>2052680277336703430</t>
         </is>
       </c>
       <c r="P52" s="2" t="n">
-        <v>46150.63261574074</v>
+        <v>46150.62010416666</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://x.com/emiratesislamic/status/2052699324711063787</t>
+          <t>https://x.com/multibank_io/status/2052680277336703430</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2052699324711063787</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>2052680277336703430</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2052698760883384325</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://x.com/undefined/status/undefined</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>https://x.com/Chevy34092622/status/2052698760883384325</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>@multibank_io @AECoin_UAE Would definitely like seeing $AEC and $USDU trading on mb io</t>
+        </is>
+      </c>
       <c r="F53" t="n">
-        <v>1778295599763</v>
-      </c>
-      <c r="G53" t="inlineStr"/>
+        <v>1778236496000</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2052680277336703430</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4103,253 +4106,1823 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
+          <t>{'name': 'Rozilyn Diondre', 'screenName': 'Chevy34092622', 'followersCount': 204, 'favouritesCount': 613, 'friendsCount': 3, 'description': 'Hi world! This is an enthusiastic coder who loves NFTs. Follow me 💡'}</t>
+     